--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
         <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="G4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="H4" t="n">
         <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J4" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="K4" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1169,13 +1169,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q4" t="n">
         <v>1.61</v>
@@ -1211,10 +1211,10 @@
         <v>370</v>
       </c>
       <c r="AB4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD4" t="n">
         <v>36</v>
@@ -1226,7 +1226,7 @@
         <v>11</v>
       </c>
       <c r="AG4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH4" t="n">
         <v>32</v>
@@ -1235,10 +1235,10 @@
         <v>130</v>
       </c>
       <c r="AJ4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL4" t="n">
         <v>36</v>
@@ -1256,25 +1256,25 @@
         <v>20</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.8</v>
+        <v>28</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU4" t="n">
         <v>10.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AX4" t="n">
         <v>7.8</v>
@@ -1286,7 +1286,7 @@
         <v>21</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BB4" t="n">
         <v>10</v>
@@ -1295,20 +1295,20 @@
         <v>12</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BF4" t="n">
         <v>4.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
         <v>2.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R5" t="n">
         <v>1.42</v>
@@ -1402,7 +1402,7 @@
         <v>14.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB5" t="n">
         <v>15</v>
@@ -1414,10 +1414,10 @@
         <v>11.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG5" t="n">
         <v>15.5</v>
@@ -1429,7 +1429,7 @@
         <v>34</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK5" t="n">
         <v>42</v>
@@ -1444,7 +1444,7 @@
         <v>38</v>
       </c>
       <c r="AO5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AP5" t="n">
         <v>15</v>
@@ -1456,7 +1456,7 @@
         <v>12.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT5" t="n">
         <v>13</v>
@@ -1474,19 +1474,19 @@
         <v>19.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB5" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="BC5" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="BD5" t="n">
         <v>26</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
         <v>120</v>
       </c>
       <c r="AP7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>19.5</v>
@@ -1865,7 +1865,7 @@
         <v>9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>18.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA7" t="n">
         <v>12.5</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="G9" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="H9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I9" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="J9" t="n">
         <v>3.25</v>
       </c>
       <c r="K9" t="n">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
         <v>10.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH10" t="n">
         <v>21</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -2617,7 +2617,7 @@
         <v>13.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AS11" t="n">
         <v>42</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="G12" t="n">
         <v>1.45</v>
@@ -2706,7 +2706,7 @@
         <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J12" t="n">
         <v>4.9</v>
@@ -2766,7 +2766,7 @@
         <v>8</v>
       </c>
       <c r="AC12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD12" t="n">
         <v>34</v>
@@ -2823,10 +2823,10 @@
         <v>10</v>
       </c>
       <c r="AV12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AW12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX12" t="n">
         <v>7.2</v>
@@ -2835,7 +2835,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA12" t="n">
         <v>42</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="G13" t="n">
         <v>2.62</v>
@@ -2924,16 +2924,16 @@
         <v>2.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S13" t="n">
         <v>3.05</v>
       </c>
       <c r="T13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U13" t="n">
         <v>2.36</v>
@@ -2954,10 +2954,10 @@
         <v>21</v>
       </c>
       <c r="AA13" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB13" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC13" t="n">
         <v>8.199999999999999</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -3088,25 +3088,25 @@
         <v>1.82</v>
       </c>
       <c r="G14" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="H14" t="n">
-        <v>3.45</v>
+        <v>4.9</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K14" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3148,10 +3148,10 @@
         <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC14" t="n">
         <v>9.800000000000001</v>
@@ -3160,7 +3160,7 @@
         <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF14" t="n">
         <v>12</v>
@@ -3169,7 +3169,7 @@
         <v>13</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI14" t="n">
         <v>140</v>
@@ -3199,56 +3199,56 @@
         <v>11</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU14" t="n">
         <v>7</v>
       </c>
       <c r="AV14" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX14" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB14" t="n">
         <v>3.95</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BC14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD14" t="n">
         <v>4.3</v>
       </c>
-      <c r="BB14" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BE14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF14" t="n">
         <v>16</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G16" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="H16" t="n">
-        <v>3.05</v>
+        <v>4.6</v>
       </c>
       <c r="I16" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K16" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
         <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -1148,34 +1148,34 @@
         <v>1.34</v>
       </c>
       <c r="G4" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="I4" t="n">
         <v>11</v>
       </c>
       <c r="J4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
         <v>5.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P4" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q4" t="n">
         <v>1.61</v>
@@ -1187,10 +1187,10 @@
         <v>2.52</v>
       </c>
       <c r="T4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U4" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
         <v>14</v>
       </c>
       <c r="AD4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AE4" t="n">
         <v>170</v>
@@ -1247,7 +1247,7 @@
         <v>160</v>
       </c>
       <c r="AN4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO4" t="n">
         <v>200</v>
@@ -1259,7 +1259,7 @@
         <v>28</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AS4" t="n">
         <v>6</v>
@@ -1271,10 +1271,10 @@
         <v>10.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX4" t="n">
         <v>7.8</v>
@@ -1286,7 +1286,7 @@
         <v>21</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BB4" t="n">
         <v>10</v>
@@ -1295,20 +1295,20 @@
         <v>12</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF4" t="n">
         <v>4.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         <v>2.22</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K5" t="n">
         <v>3.8</v>
@@ -1372,7 +1372,7 @@
         <v>2.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R5" t="n">
         <v>1.42</v>
@@ -1414,7 +1414,7 @@
         <v>11.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF5" t="n">
         <v>27</v>
@@ -1444,7 +1444,7 @@
         <v>38</v>
       </c>
       <c r="AO5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP5" t="n">
         <v>15</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v>3.95</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
         <v>3.45</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G9" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I9" t="n">
         <v>6.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
         <v>3.9</v>
       </c>
       <c r="O10" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
@@ -2348,7 +2348,7 @@
         <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T10" t="n">
         <v>1.93</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
         <v>5.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K11" t="n">
         <v>3.8</v>
@@ -2548,7 +2548,7 @@
         <v>2.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="G12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H12" t="n">
         <v>9</v>
@@ -2709,10 +2709,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2742,7 +2742,7 @@
         <v>2.14</v>
       </c>
       <c r="U12" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AG12" t="n">
         <v>10.5</v>
@@ -2796,7 +2796,7 @@
         <v>42</v>
       </c>
       <c r="AM12" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
         <v>7</v>
@@ -2805,7 +2805,7 @@
         <v>280</v>
       </c>
       <c r="AP12" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ12" t="n">
         <v>19.5</v>
@@ -2814,7 +2814,7 @@
         <v>48</v>
       </c>
       <c r="AS12" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AT12" t="n">
         <v>7.4</v>
@@ -2823,7 +2823,7 @@
         <v>10</v>
       </c>
       <c r="AV12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AW12" t="n">
         <v>44</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -2894,19 +2894,19 @@
         <v>2.56</v>
       </c>
       <c r="G13" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H13" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="I13" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2954,7 +2954,7 @@
         <v>21</v>
       </c>
       <c r="AA13" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB13" t="n">
         <v>12.5</v>
@@ -2969,7 +2969,7 @@
         <v>50</v>
       </c>
       <c r="AF13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG13" t="n">
         <v>12.5</v>
@@ -3035,10 +3035,10 @@
         <v>32</v>
       </c>
       <c r="BB13" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="BC13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BD13" t="n">
         <v>30</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -3091,13 +3091,13 @@
         <v>2.06</v>
       </c>
       <c r="H14" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I14" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J14" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K14" t="n">
         <v>3.8</v>
@@ -3145,7 +3145,7 @@
         <v>16</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA14" t="n">
         <v>190</v>
@@ -3202,7 +3202,7 @@
         <v>4.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AT14" t="n">
         <v>5.5</v>
@@ -3211,7 +3211,7 @@
         <v>7</v>
       </c>
       <c r="AV14" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AW14" t="n">
         <v>4.4</v>
@@ -3226,7 +3226,7 @@
         <v>4</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BB14" t="n">
         <v>3.95</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>1.8</v>
       </c>
       <c r="G16" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="H16" t="n">
         <v>4.6</v>
@@ -3485,10 +3485,10 @@
         <v>6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
         <v>1.96</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I2" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
         <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="G3" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="H3" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="I3" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="G4" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="H4" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="I4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J4" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="K4" t="n">
         <v>6.2</v>
@@ -1172,10 +1172,10 @@
         <v>5.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q4" t="n">
         <v>1.61</v>
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Y4" t="n">
         <v>36</v>
@@ -1211,7 +1211,7 @@
         <v>370</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC4" t="n">
         <v>14</v>
@@ -1223,7 +1223,7 @@
         <v>170</v>
       </c>
       <c r="AF4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG4" t="n">
         <v>11</v>
@@ -1286,7 +1286,7 @@
         <v>21</v>
       </c>
       <c r="BA4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BB4" t="n">
         <v>10</v>
@@ -1301,14 +1301,14 @@
         <v>6</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BG4" t="n">
         <v>6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -1342,19 +1342,19 @@
         <v>3.55</v>
       </c>
       <c r="G5" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H5" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="I5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1483,7 +1483,7 @@
         <v>29</v>
       </c>
       <c r="BB5" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="BC5" t="n">
         <v>23</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G6" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H6" t="n">
         <v>3.95</v>
@@ -1572,7 +1572,7 @@
         <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T6" t="n">
         <v>1.9</v>
@@ -1674,7 +1674,7 @@
         <v>17</v>
       </c>
       <c r="BA6" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB6" t="n">
         <v>20</v>
@@ -1683,7 +1683,7 @@
         <v>21</v>
       </c>
       <c r="BD6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE6" t="n">
         <v>40</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -1763,7 +1763,7 @@
         <v>1.78</v>
       </c>
       <c r="R7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1802,7 +1802,7 @@
         <v>24</v>
       </c>
       <c r="AE7" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
         <v>120</v>
       </c>
       <c r="AP7" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ7" t="n">
         <v>19.5</v>
@@ -1844,7 +1844,7 @@
         <v>11.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AT7" t="n">
         <v>8.4</v>
@@ -1865,7 +1865,7 @@
         <v>9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>8.800000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="BA7" t="n">
         <v>12.5</v>
@@ -1880,17 +1880,17 @@
         <v>27</v>
       </c>
       <c r="BE7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BF7" t="n">
         <v>7.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
         <v>1.58</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -2312,13 +2312,13 @@
         <v>1.74</v>
       </c>
       <c r="G10" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H10" t="n">
         <v>5.2</v>
       </c>
       <c r="I10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J10" t="n">
         <v>4.1</v>
@@ -2351,7 +2351,7 @@
         <v>3.45</v>
       </c>
       <c r="T10" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U10" t="n">
         <v>2.02</v>
@@ -2369,7 +2369,7 @@
         <v>18</v>
       </c>
       <c r="Z10" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
@@ -2378,7 +2378,7 @@
         <v>8.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD10" t="n">
         <v>21</v>
@@ -2459,7 +2459,7 @@
         <v>16.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BE10" t="n">
         <v>42</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -2515,10 +2515,10 @@
         <v>5.5</v>
       </c>
       <c r="J11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K11" t="n">
         <v>3.75</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.8</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
         <v>1.41</v>
       </c>
       <c r="P11" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q11" t="n">
         <v>2.24</v>
@@ -2548,7 +2548,7 @@
         <v>2.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
         <v>15.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
@@ -2599,7 +2599,7 @@
         <v>22</v>
       </c>
       <c r="AL11" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
@@ -2644,7 +2644,7 @@
         <v>20</v>
       </c>
       <c r="BA11" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="BB11" t="n">
         <v>17.5</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -2703,13 +2703,13 @@
         <v>1.44</v>
       </c>
       <c r="H12" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="I12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K12" t="n">
         <v>5.3</v>
@@ -2757,7 +2757,7 @@
         <v>27</v>
       </c>
       <c r="Z12" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
         <v>410</v>
@@ -2769,7 +2769,7 @@
         <v>11.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
@@ -2793,7 +2793,7 @@
         <v>16</v>
       </c>
       <c r="AL12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
@@ -2808,7 +2808,7 @@
         <v>16</v>
       </c>
       <c r="AQ12" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR12" t="n">
         <v>48</v>
@@ -2835,7 +2835,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA12" t="n">
         <v>42</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -2894,13 +2894,13 @@
         <v>2.56</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H13" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I13" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J13" t="n">
         <v>3.65</v>
@@ -2987,7 +2987,7 @@
         <v>27</v>
       </c>
       <c r="AL13" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
         <v>1.55</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3145,7 +3145,7 @@
         <v>16</v>
       </c>
       <c r="Z14" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
         <v>190</v>
@@ -3169,7 +3169,7 @@
         <v>13</v>
       </c>
       <c r="AH14" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
         <v>140</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="K15" t="n">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="G16" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="H16" t="n">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="G18" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="H18" t="n">
-        <v>2.06</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
-        <v>950</v>
+        <v>3.95</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="G2" t="n">
         <v>2.04</v>
@@ -772,7 +772,7 @@
         <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G4" t="n">
         <v>1.37</v>
       </c>
       <c r="H4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="K4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1172,7 +1172,7 @@
         <v>5.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P4" t="n">
         <v>2.38</v>
@@ -1190,7 +1190,7 @@
         <v>1.9</v>
       </c>
       <c r="U4" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G5" t="n">
         <v>3.6</v>
       </c>
       <c r="H5" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K5" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1378,10 +1378,10 @@
         <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U5" t="n">
         <v>2.26</v>
@@ -1393,16 +1393,16 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z5" t="n">
         <v>14.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AB5" t="n">
         <v>15</v>
@@ -1414,13 +1414,13 @@
         <v>11.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH5" t="n">
         <v>17</v>
@@ -1429,10 +1429,10 @@
         <v>34</v>
       </c>
       <c r="AJ5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL5" t="n">
         <v>48</v>
@@ -1441,10 +1441,10 @@
         <v>85</v>
       </c>
       <c r="AN5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO5" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP5" t="n">
         <v>15</v>
@@ -1456,7 +1456,7 @@
         <v>12.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT5" t="n">
         <v>13</v>
@@ -1471,10 +1471,10 @@
         <v>19.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AY5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ5" t="n">
         <v>15</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G6" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H6" t="n">
         <v>3.95</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J6" t="n">
         <v>3.45</v>
@@ -1647,7 +1647,7 @@
         <v>12</v>
       </c>
       <c r="AR6" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="AS6" t="n">
         <v>34</v>
@@ -1674,7 +1674,7 @@
         <v>17</v>
       </c>
       <c r="BA6" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="BB6" t="n">
         <v>20</v>
@@ -1683,7 +1683,7 @@
         <v>21</v>
       </c>
       <c r="BD6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE6" t="n">
         <v>40</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O7" t="n">
         <v>1.26</v>
@@ -1763,7 +1763,7 @@
         <v>1.78</v>
       </c>
       <c r="R7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1787,7 +1787,7 @@
         <v>23</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA7" t="n">
         <v>200</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -2309,49 +2309,49 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="G10" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="H10" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="I10" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J10" t="n">
         <v>4.1</v>
       </c>
       <c r="K10" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R10" t="n">
         <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U10" t="n">
         <v>2.02</v>
@@ -2363,13 +2363,13 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z10" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
@@ -2378,7 +2378,7 @@
         <v>8.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AD10" t="n">
         <v>21</v>
@@ -2387,7 +2387,7 @@
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG10" t="n">
         <v>9.800000000000001</v>
@@ -2399,31 +2399,31 @@
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK10" t="n">
         <v>18</v>
       </c>
-      <c r="AK10" t="n">
-        <v>19</v>
-      </c>
       <c r="AL10" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ10" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AS10" t="n">
         <v>42</v>
@@ -2435,28 +2435,28 @@
         <v>8.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AW10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX10" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB10" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD10" t="n">
         <v>23</v>
@@ -2465,14 +2465,14 @@
         <v>42</v>
       </c>
       <c r="BF10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG10" t="n">
         <v>36</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -2515,10 +2515,10 @@
         <v>5.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K11" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
         <v>1.41</v>
       </c>
       <c r="P11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q11" t="n">
         <v>2.24</v>
@@ -2548,7 +2548,7 @@
         <v>2.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
         <v>15.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
@@ -2584,13 +2584,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
         <v>24</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ11" t="n">
         <v>19.5</v>
@@ -2617,7 +2617,7 @@
         <v>13.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AS11" t="n">
         <v>42</v>
@@ -2647,7 +2647,7 @@
         <v>60</v>
       </c>
       <c r="BB11" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BC11" t="n">
         <v>19</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>1.44</v>
       </c>
       <c r="H12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I12" t="n">
         <v>10</v>
@@ -2712,7 +2712,7 @@
         <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         <v>17.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z12" t="n">
         <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="AB12" t="n">
         <v>8</v>
@@ -2787,13 +2787,13 @@
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK12" t="n">
         <v>16</v>
       </c>
       <c r="AL12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
@@ -2802,10 +2802,10 @@
         <v>7</v>
       </c>
       <c r="AO12" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AP12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ12" t="n">
         <v>20</v>
@@ -2814,10 +2814,10 @@
         <v>48</v>
       </c>
       <c r="AS12" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU12" t="n">
         <v>10</v>
@@ -2832,7 +2832,7 @@
         <v>7.2</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
         <v>25</v>
@@ -2856,11 +2856,11 @@
         <v>6.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>2.56</v>
       </c>
       <c r="G13" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H13" t="n">
         <v>2.94</v>
@@ -2945,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y13" t="n">
         <v>13.5</v>
@@ -2960,13 +2960,13 @@
         <v>12.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD13" t="n">
         <v>13</v>
       </c>
       <c r="AE13" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AF13" t="n">
         <v>18</v>
@@ -2978,7 +2978,7 @@
         <v>16</v>
       </c>
       <c r="AI13" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="AJ13" t="n">
         <v>38</v>
@@ -3023,7 +3023,7 @@
         <v>26</v>
       </c>
       <c r="AX13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY13" t="n">
         <v>11</v>
@@ -3035,7 +3035,7 @@
         <v>32</v>
       </c>
       <c r="BB13" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BC13" t="n">
         <v>21</v>
@@ -3047,14 +3047,14 @@
         <v>34</v>
       </c>
       <c r="BF13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BG13" t="n">
         <v>20</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
         <v>1.55</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3145,7 +3145,7 @@
         <v>16</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA14" t="n">
         <v>190</v>
@@ -3169,7 +3169,7 @@
         <v>13</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI14" t="n">
         <v>140</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="G16" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H16" t="n">
         <v>3.95</v>
@@ -3485,7 +3485,7 @@
         <v>5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K16" t="n">
         <v>3.95</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="G2" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="H2" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H3" t="n">
         <v>5.5</v>
       </c>
       <c r="I3" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
         <v>3.9</v>
@@ -984,7 +984,7 @@
         <v>1.78</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -1148,19 +1148,19 @@
         <v>1.36</v>
       </c>
       <c r="G4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J4" t="n">
         <v>5.7</v>
       </c>
       <c r="K4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1172,19 +1172,19 @@
         <v>5.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P4" t="n">
         <v>2.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R4" t="n">
         <v>1.54</v>
       </c>
       <c r="S4" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T4" t="n">
         <v>1.9</v>
@@ -1202,25 +1202,25 @@
         <v>32</v>
       </c>
       <c r="Y4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="Z4" t="n">
         <v>110</v>
       </c>
       <c r="AA4" t="n">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="AB4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC4" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AE4" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AF4" t="n">
         <v>10.5</v>
@@ -1229,10 +1229,10 @@
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI4" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AJ4" t="n">
         <v>12</v>
@@ -1244,22 +1244,22 @@
         <v>36</v>
       </c>
       <c r="AM4" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN4" t="n">
         <v>6.2</v>
       </c>
       <c r="AO4" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AP4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>28</v>
+        <v>5.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AS4" t="n">
         <v>6</v>
@@ -1268,13 +1268,13 @@
         <v>8.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AW4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AX4" t="n">
         <v>7.8</v>
@@ -1283,10 +1283,10 @@
         <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BB4" t="n">
         <v>10</v>
@@ -1295,20 +1295,20 @@
         <v>12</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BG4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H5" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I5" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="J5" t="n">
         <v>3.7</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1378,13 +1378,13 @@
         <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U5" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1396,28 +1396,28 @@
         <v>16.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
         <v>14.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
         <v>23</v>
       </c>
       <c r="AF5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG5" t="n">
         <v>15</v>
@@ -1447,7 +1447,7 @@
         <v>15.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>9.800000000000001</v>
@@ -1456,7 +1456,7 @@
         <v>12.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AT5" t="n">
         <v>13</v>
@@ -1468,10 +1468,10 @@
         <v>10</v>
       </c>
       <c r="AW5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX5" t="n">
         <v>19.5</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>21</v>
       </c>
       <c r="AY5" t="n">
         <v>13</v>
@@ -1480,10 +1480,10 @@
         <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB5" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BC5" t="n">
         <v>23</v>
@@ -1498,11 +1498,11 @@
         <v>22</v>
       </c>
       <c r="BG5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -1536,19 +1536,19 @@
         <v>2.16</v>
       </c>
       <c r="G6" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H6" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,13 +1563,13 @@
         <v>1.37</v>
       </c>
       <c r="P6" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q6" t="n">
         <v>2.12</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
         <v>3.9</v>
@@ -1593,16 +1593,16 @@
         <v>13.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA6" t="n">
         <v>90</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD6" t="n">
         <v>17</v>
@@ -1614,7 +1614,7 @@
         <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH6" t="n">
         <v>19.5</v>
@@ -1626,16 +1626,16 @@
         <v>28</v>
       </c>
       <c r="AK6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL6" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM6" t="n">
         <v>120</v>
       </c>
       <c r="AN6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AO6" t="n">
         <v>65</v>
@@ -1644,10 +1644,10 @@
         <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS6" t="n">
         <v>34</v>
@@ -1656,7 +1656,7 @@
         <v>8</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
         <v>14.5</v>
@@ -1671,16 +1671,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BB6" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC6" t="n">
         <v>20</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>21</v>
       </c>
       <c r="BD6" t="n">
         <v>26</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
         <v>1.26</v>
@@ -1766,7 +1766,7 @@
         <v>1.46</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T7" t="n">
         <v>1.86</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y7" t="n">
         <v>23</v>
@@ -1796,19 +1796,19 @@
         <v>9.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD7" t="n">
         <v>24</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF7" t="n">
         <v>10</v>
       </c>
       <c r="AG7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH7" t="n">
         <v>21</v>
@@ -1820,7 +1820,7 @@
         <v>15.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AL7" t="n">
         <v>34</v>
@@ -1835,16 +1835,16 @@
         <v>120</v>
       </c>
       <c r="AP7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>19.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>11.5</v>
+        <v>44</v>
       </c>
       <c r="AS7" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT7" t="n">
         <v>8.4</v>
@@ -1856,7 +1856,7 @@
         <v>20</v>
       </c>
       <c r="AW7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AX7" t="n">
         <v>9</v>
@@ -1865,10 +1865,10 @@
         <v>9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA7" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB7" t="n">
         <v>14</v>
@@ -1877,20 +1877,20 @@
         <v>14.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>27</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BF7" t="n">
         <v>7.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -1930,10 +1930,10 @@
         <v>1.68</v>
       </c>
       <c r="I8" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="J8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
         <v>3.9</v>
@@ -1954,7 +1954,7 @@
         <v>1.58</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="G9" t="n">
         <v>1.99</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -2315,13 +2315,13 @@
         <v>1.72</v>
       </c>
       <c r="H10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I10" t="n">
         <v>5.8</v>
       </c>
       <c r="J10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K10" t="n">
         <v>4.4</v>
@@ -2333,13 +2333,13 @@
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
         <v>1.31</v>
       </c>
       <c r="P10" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
         <v>1.93</v>
@@ -2354,7 +2354,7 @@
         <v>1.94</v>
       </c>
       <c r="U10" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2381,19 +2381,19 @@
         <v>9.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG10" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
@@ -2438,19 +2438,19 @@
         <v>19</v>
       </c>
       <c r="AW10" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AX10" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA10" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BB10" t="n">
         <v>14.5</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="G11" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I11" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J11" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K11" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
         <v>1.41</v>
       </c>
       <c r="P11" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q11" t="n">
         <v>2.24</v>
@@ -2590,7 +2590,7 @@
         <v>24</v>
       </c>
       <c r="AI11" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
         <v>19.5</v>
@@ -2599,7 +2599,7 @@
         <v>22</v>
       </c>
       <c r="AL11" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
@@ -2614,10 +2614,10 @@
         <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AS11" t="n">
         <v>42</v>
@@ -2632,19 +2632,19 @@
         <v>18.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AX11" t="n">
         <v>9</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
         <v>20</v>
       </c>
       <c r="BA11" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="BB11" t="n">
         <v>17</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -2700,10 +2700,10 @@
         <v>1.42</v>
       </c>
       <c r="G12" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="H12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I12" t="n">
         <v>10</v>
@@ -2727,13 +2727,13 @@
         <v>1.29</v>
       </c>
       <c r="P12" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q12" t="n">
         <v>1.87</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
         <v>3.2</v>
@@ -2811,7 +2811,7 @@
         <v>20</v>
       </c>
       <c r="AR12" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AS12" t="n">
         <v>110</v>
@@ -2823,7 +2823,7 @@
         <v>10</v>
       </c>
       <c r="AV12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW12" t="n">
         <v>44</v>
@@ -2838,7 +2838,7 @@
         <v>25</v>
       </c>
       <c r="BA12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB12" t="n">
         <v>10.5</v>
@@ -2856,11 +2856,11 @@
         <v>6.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -2894,16 +2894,16 @@
         <v>2.56</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H13" t="n">
         <v>2.94</v>
       </c>
       <c r="I13" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J13" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K13" t="n">
         <v>3.75</v>
@@ -2918,10 +2918,10 @@
         <v>4.4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P13" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q13" t="n">
         <v>1.83</v>
@@ -2933,7 +2933,7 @@
         <v>3.05</v>
       </c>
       <c r="T13" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U13" t="n">
         <v>2.36</v>
@@ -2954,7 +2954,7 @@
         <v>21</v>
       </c>
       <c r="AA13" t="n">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="AB13" t="n">
         <v>12.5</v>
@@ -2984,7 +2984,7 @@
         <v>38</v>
       </c>
       <c r="AK13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL13" t="n">
         <v>36</v>
@@ -3005,10 +3005,10 @@
         <v>12</v>
       </c>
       <c r="AR13" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AT13" t="n">
         <v>11</v>
@@ -3020,7 +3020,7 @@
         <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AX13" t="n">
         <v>15.5</v>
@@ -3032,16 +3032,16 @@
         <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB13" t="n">
         <v>30</v>
       </c>
       <c r="BC13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD13" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BE13" t="n">
         <v>34</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>1.82</v>
       </c>
       <c r="G14" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="H14" t="n">
         <v>4.8</v>
@@ -3097,7 +3097,7 @@
         <v>5.7</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="K14" t="n">
         <v>3.8</v>
@@ -3106,7 +3106,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -3145,37 +3145,37 @@
         <v>16</v>
       </c>
       <c r="Z14" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
         <v>190</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC14" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE14" t="n">
         <v>120</v>
       </c>
       <c r="AF14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG14" t="n">
         <v>13</v>
       </c>
       <c r="AH14" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
         <v>140</v>
       </c>
       <c r="AJ14" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
         <v>1000</v>
@@ -3196,13 +3196,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AT14" t="n">
         <v>5.5</v>
@@ -3211,44 +3211,44 @@
         <v>7</v>
       </c>
       <c r="AV14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>3.9</v>
       </c>
-      <c r="AW14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>4</v>
-      </c>
       <c r="BA14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BD14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE14" t="n">
         <v>4.3</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>4.5</v>
       </c>
       <c r="BF14" t="n">
         <v>16</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="G15" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="I15" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="K15" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.76</v>
+        <v>1.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -3476,10 +3476,10 @@
         <v>1.91</v>
       </c>
       <c r="G16" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H16" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="I16" t="n">
         <v>5</v>
@@ -3488,7 +3488,7 @@
         <v>3.35</v>
       </c>
       <c r="K16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q16" t="n">
         <v>2</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="H18" t="n">
-        <v>6</v>
+        <v>2.06</v>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J18" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.95</v>
+        <v>950</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH18"/>
+  <dimension ref="A1:BH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,16 +769,16 @@
         <v>4.2</v>
       </c>
       <c r="J2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K2" t="n">
         <v>3.6</v>
       </c>
-      <c r="K2" t="n">
-        <v>3.7</v>
-      </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
         <v>3.8</v>
@@ -787,19 +787,19 @@
         <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="U2" t="n">
         <v>2.16</v>
@@ -808,7 +808,7 @@
         <v>1.31</v>
       </c>
       <c r="W2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X2" t="n">
         <v>14.5</v>
@@ -817,7 +817,7 @@
         <v>16.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA2" t="n">
         <v>90</v>
@@ -841,7 +841,7 @@
         <v>10.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
         <v>75</v>
@@ -856,7 +856,7 @@
         <v>36</v>
       </c>
       <c r="AM2" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN2" t="n">
         <v>15</v>
@@ -874,7 +874,7 @@
         <v>22</v>
       </c>
       <c r="AS2" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AT2" t="n">
         <v>8.800000000000001</v>
@@ -910,24 +910,24 @@
         <v>30</v>
       </c>
       <c r="BE2" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-17 12:01:47</t>
+          <t>2026-03-17 14:12:51</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,36 +937,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Genclerbirligi</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.78</v>
+        <v>5.7</v>
       </c>
       <c r="G3" t="n">
-        <v>1.86</v>
+        <v>22</v>
       </c>
       <c r="H3" t="n">
-        <v>5.5</v>
+        <v>1.23</v>
       </c>
       <c r="I3" t="n">
-        <v>6.4</v>
+        <v>1.38</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-17 12:01:47</t>
+          <t>2026-03-17 14:12:51</t>
         </is>
       </c>
     </row>
@@ -1136,61 +1136,61 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kasimpasa</t>
+          <t>Genclerbirligi</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.36</v>
+        <v>1.81</v>
       </c>
       <c r="G4" t="n">
-        <v>1.38</v>
+        <v>1.86</v>
       </c>
       <c r="H4" t="n">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="I4" t="n">
-        <v>11.5</v>
+        <v>5.8</v>
       </c>
       <c r="J4" t="n">
-        <v>5.7</v>
+        <v>3.55</v>
       </c>
       <c r="K4" t="n">
-        <v>6.2</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.38</v>
+        <v>1.79</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.6</v>
+        <v>2.04</v>
       </c>
       <c r="R4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -1199,123 +1199,123 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-17 12:01:47</t>
+          <t>2026-03-17 14:12:51</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,184 +1325,184 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Kasimpasa</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.45</v>
+        <v>1.35</v>
       </c>
       <c r="G5" t="n">
-        <v>3.55</v>
+        <v>1.38</v>
       </c>
       <c r="H5" t="n">
-        <v>2.24</v>
+        <v>10.5</v>
       </c>
       <c r="I5" t="n">
-        <v>2.28</v>
+        <v>11.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>5.7</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>6.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="S5" t="n">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="U5" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="X5" t="n">
-        <v>16.5</v>
+        <v>32</v>
       </c>
       <c r="Y5" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>400</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>180</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG5" t="n">
         <v>11</v>
       </c>
-      <c r="Z5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AH5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>220</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW5" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AD5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV5" t="n">
+      <c r="AX5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB5" t="n">
         <v>10</v>
       </c>
-      <c r="AW5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>50</v>
-      </c>
       <c r="BC5" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="BD5" t="n">
-        <v>26</v>
+        <v>6.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="BF5" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="BG5" t="n">
-        <v>13.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-17 12:01:47</t>
+          <t>2026-03-17 14:12:51</t>
         </is>
       </c>
     </row>
@@ -1524,61 +1524,61 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.16</v>
+        <v>3.45</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2</v>
+        <v>3.55</v>
       </c>
       <c r="H6" t="n">
-        <v>3.9</v>
+        <v>2.24</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>2.28</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="U6" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1587,116 +1587,116 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR6" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF6" t="n">
+      <c r="AS6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT6" t="n">
         <v>13</v>
       </c>
-      <c r="AG6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH6" t="n">
+      <c r="AU6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX6" t="n">
         <v>19.5</v>
       </c>
-      <c r="AI6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ6" t="n">
+      <c r="AY6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA6" t="n">
         <v>28</v>
       </c>
-      <c r="AK6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>50</v>
-      </c>
       <c r="BB6" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="BC6" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BD6" t="n">
         <v>26</v>
       </c>
       <c r="BE6" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BF6" t="n">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="BG6" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-17 12:01:47</t>
+          <t>2026-03-17 14:12:51</t>
         </is>
       </c>
     </row>
@@ -1718,61 +1718,61 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Genk</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.61</v>
+        <v>2.16</v>
       </c>
       <c r="G7" t="n">
-        <v>1.63</v>
+        <v>2.18</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="I7" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="O7" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="P7" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="R7" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="S7" t="n">
-        <v>2.98</v>
+        <v>3.85</v>
       </c>
       <c r="T7" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="U7" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1781,123 +1781,123 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="Z7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE7" t="n">
         <v>55</v>
       </c>
-      <c r="AA7" t="n">
-        <v>200</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>110</v>
-      </c>
       <c r="AF7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY7" t="n">
         <v>10</v>
       </c>
-      <c r="AG7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH7" t="n">
+      <c r="AZ7" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB7" t="n">
         <v>21</v>
       </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
+      <c r="BC7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF7" t="n">
         <v>15.5</v>
       </c>
-      <c r="AK7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BG7" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-17 12:01:47</t>
+          <t>2026-03-17 14:12:51</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Genk</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5.2</v>
+        <v>1.61</v>
       </c>
       <c r="G8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN8" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H8" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0</v>
-      </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-17 12:01:47</t>
+          <t>2026-03-17 14:12:51</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,33 +2101,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tecnico Universitario</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="G9" t="n">
-        <v>1.99</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>4.8</v>
+        <v>1.68</v>
       </c>
       <c r="I9" t="n">
-        <v>6.4</v>
+        <v>1.98</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K9" t="n">
         <v>3.9</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-17 12:01:47</t>
+          <t>2026-03-17 14:12:51</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,66 +2295,66 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Tecnico Universitario</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="G10" t="n">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="H10" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="I10" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="J10" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2363,116 +2363,116 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-17 12:01:47</t>
+          <t>2026-03-17 14:12:51</t>
         </is>
       </c>
     </row>
@@ -2494,62 +2494,62 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U11" t="n">
         <v>1.82</v>
       </c>
-      <c r="G11" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="H11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.85</v>
-      </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
@@ -2557,116 +2557,116 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.5</v>
+        <v>28</v>
       </c>
       <c r="Z11" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AB11" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="AE11" t="n">
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AL11" t="n">
-        <v>230</v>
+        <v>42</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AP11" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AR11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD11" t="n">
         <v>34</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>38</v>
       </c>
       <c r="BE11" t="n">
         <v>46</v>
       </c>
       <c r="BF11" t="n">
-        <v>13</v>
+        <v>6.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-17 12:01:47</t>
+          <t>2026-03-17 14:12:51</t>
         </is>
       </c>
     </row>
@@ -2688,31 +2688,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.42</v>
+        <v>2.56</v>
       </c>
       <c r="G12" t="n">
-        <v>1.43</v>
+        <v>2.6</v>
       </c>
       <c r="H12" t="n">
-        <v>9.4</v>
+        <v>2.94</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>2.98</v>
       </c>
       <c r="J12" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="K12" t="n">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2721,28 +2721,28 @@
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P12" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="R12" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="T12" t="n">
-        <v>2.14</v>
+        <v>1.69</v>
       </c>
       <c r="U12" t="n">
-        <v>1.81</v>
+        <v>2.38</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -2754,113 +2754,113 @@
         <v>17.5</v>
       </c>
       <c r="Y12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK12" t="n">
         <v>28</v>
       </c>
-      <c r="Z12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>420</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC12" t="n">
+      <c r="AL12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV12" t="n">
         <v>11.5</v>
       </c>
-      <c r="AD12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>290</v>
-      </c>
-      <c r="AP12" t="n">
+      <c r="AW12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX12" t="n">
         <v>15.5</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AY12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG12" t="n">
         <v>20</v>
       </c>
-      <c r="AR12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>110</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>46</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>95</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-17 12:01:47</t>
+          <t>2026-03-17 14:12:51</t>
         </is>
       </c>
     </row>
@@ -2882,25 +2882,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.56</v>
+        <v>1.87</v>
       </c>
       <c r="G13" t="n">
-        <v>2.58</v>
+        <v>1.89</v>
       </c>
       <c r="H13" t="n">
-        <v>2.94</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>2.96</v>
+        <v>5.2</v>
       </c>
       <c r="J13" t="n">
         <v>3.7</v>
@@ -2912,31 +2912,31 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R13" t="n">
         <v>1.27</v>
       </c>
-      <c r="P13" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.45</v>
-      </c>
       <c r="S13" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="U13" t="n">
-        <v>2.36</v>
+        <v>1.84</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -2945,123 +2945,123 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="Y13" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD13" t="n">
         <v>21</v>
       </c>
-      <c r="AA13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>13</v>
-      </c>
       <c r="AE13" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AG13" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AI13" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="AK13" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AL13" t="n">
-        <v>36</v>
+        <v>240</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV13" t="n">
         <v>18.5</v>
       </c>
-      <c r="AS13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AW13" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AX13" t="n">
-        <v>15.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BA13" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="BB13" t="n">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BD13" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="BE13" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BF13" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-17 12:01:47</t>
+          <t>2026-03-17 14:12:51</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,66 +3071,66 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="G14" t="n">
-        <v>2.14</v>
+        <v>1.71</v>
       </c>
       <c r="H14" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="I14" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J14" t="n">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P14" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.44</v>
+        <v>1.93</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3139,123 +3139,123 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="Z14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA14" t="n">
         <v>1000</v>
       </c>
-      <c r="AA14" t="n">
-        <v>190</v>
-      </c>
       <c r="AB14" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AD14" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AG14" t="n">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM14" t="n">
         <v>1000</v>
       </c>
-      <c r="AI14" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>270</v>
-      </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>8.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="AR14" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.3</v>
+        <v>42</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>3.8</v>
+        <v>18.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.3</v>
+        <v>34</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF14" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>16</v>
-      </c>
       <c r="BG14" t="n">
-        <v>4.3</v>
+        <v>38</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-17 12:01:47</t>
+          <t>2026-03-17 14:12:51</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,42 +3265,42 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Alianza FC Valledupar</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G15" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="I15" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J15" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K15" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3333,123 +3333,123 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-17 12:01:47</t>
+          <t>2026-03-17 14:12:51</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,36 +3459,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Gremio</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>EC Vitoria Salvador</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="G16" t="n">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="H16" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.84</v>
+        <v>1.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-17 12:01:47</t>
+          <t>2026-03-17 14:12:51</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,36 +3653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Gremio</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>EC Vitoria Salvador</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>1.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,201 +3830,395 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-17 12:01:47</t>
+          <t>2026-03-17 14:12:51</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Sportivo Trinidense</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Club Sportivo Ameliano</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-03-17 14:12:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>20:20:00</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Tolima</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Fortaleza FC</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G18" t="n">
+      <c r="F19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G19" t="n">
         <v>1.94</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2.06</v>
       </c>
-      <c r="I18" t="n">
-        <v>14</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K18" t="n">
-        <v>950</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>2026-03-17 12:01:47</t>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-03-17 14:12:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH19"/>
+  <dimension ref="A1:BH30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fatih Karagumruk Istanbul</t>
+          <t>Dynamo Kiev</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.06</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>2.12</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>4.2</v>
+        <v>1.47</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>3.8</v>
+        <v>1.97</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.31</v>
+        <v>3.1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Fatih Karagumruk Istanbul</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5.7</v>
+        <v>2.08</v>
       </c>
       <c r="G3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK3" t="n">
         <v>22</v>
       </c>
-      <c r="H3" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,36 +1131,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Genclerbirligi</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.81</v>
+        <v>13.5</v>
       </c>
       <c r="G4" t="n">
-        <v>1.86</v>
+        <v>17.5</v>
       </c>
       <c r="H4" t="n">
-        <v>5.5</v>
+        <v>1.24</v>
       </c>
       <c r="I4" t="n">
-        <v>5.8</v>
+        <v>1.3</v>
       </c>
       <c r="J4" t="n">
-        <v>3.55</v>
+        <v>6.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>7.8</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Metalist 1925</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kasimpasa</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="G5" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="H5" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="I5" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="K5" t="n">
-        <v>6.2</v>
+        <v>24</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>5.1</v>
+        <v>2.24</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="R5" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="X5" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Genclerbirligi</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J6" t="n">
         <v>3.45</v>
       </c>
-      <c r="G6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.7</v>
-      </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="O6" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="P6" t="n">
-        <v>2.08</v>
+        <v>1.78</v>
       </c>
       <c r="Q6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T6" t="n">
         <v>1.87</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.74</v>
-      </c>
       <c r="U6" t="n">
-        <v>2.28</v>
+        <v>1.9</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X6" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG6" t="n">
         <v>11</v>
       </c>
-      <c r="Z6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>29</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD6" t="n">
+      <c r="AH6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP6" t="n">
         <v>11</v>
       </c>
-      <c r="AE6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH6" t="n">
+      <c r="AQ6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB6" t="n">
         <v>17</v>
       </c>
-      <c r="AI6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU6" t="n">
+      <c r="BC6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG6" t="n">
         <v>7.6</v>
       </c>
-      <c r="AV6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>46</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>26</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>34</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>14</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Kasimpasa</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.16</v>
+        <v>1.35</v>
       </c>
       <c r="G7" t="n">
-        <v>2.18</v>
+        <v>1.36</v>
       </c>
       <c r="H7" t="n">
-        <v>3.9</v>
+        <v>11</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="P7" t="n">
-        <v>1.85</v>
+        <v>2.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="S7" t="n">
-        <v>3.85</v>
+        <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U7" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X7" t="n">
-        <v>12.5</v>
+        <v>32</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.5</v>
+        <v>36</v>
       </c>
       <c r="Z7" t="n">
-        <v>29</v>
+        <v>110</v>
       </c>
       <c r="AA7" t="n">
-        <v>90</v>
+        <v>400</v>
       </c>
       <c r="AB7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="AD7" t="n">
-        <v>16.5</v>
+        <v>38</v>
       </c>
       <c r="AE7" t="n">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="AF7" t="n">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG7" t="n">
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>19.5</v>
+        <v>29</v>
       </c>
       <c r="AI7" t="n">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="AJ7" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="AK7" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AL7" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AM7" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="AN7" t="n">
-        <v>19</v>
+        <v>5.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>65</v>
+        <v>210</v>
       </c>
       <c r="AP7" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AQ7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU7" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AV7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>20</v>
       </c>
-      <c r="AS7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU7" t="n">
+      <c r="BA7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD7" t="n">
         <v>7</v>
       </c>
-      <c r="AV7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>26</v>
-      </c>
       <c r="BE7" t="n">
-        <v>40</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF7" t="n">
-        <v>15.5</v>
+        <v>4</v>
       </c>
       <c r="BG7" t="n">
-        <v>30</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Genk</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="G8" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="I8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X8" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>130</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>270</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>210</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT8" t="n">
         <v>6.6</v>
       </c>
-      <c r="J8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>200</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="AU8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY8" t="n">
         <v>9.4</v>
       </c>
-      <c r="AC8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="BA8" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>14.5</v>
+        <v>3.7</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>10.5</v>
+        <v>4.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="BG8" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="H9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I9" t="n">
         <v>1.68</v>
       </c>
-      <c r="I9" t="n">
-        <v>1.98</v>
-      </c>
       <c r="J9" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P9" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.34</v>
+        <v>2.02</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Rakow Czestochowa</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tecnico Universitario</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.79</v>
+        <v>2.6</v>
       </c>
       <c r="G10" t="n">
-        <v>1.99</v>
+        <v>2.82</v>
       </c>
       <c r="H10" t="n">
-        <v>4.8</v>
+        <v>2.76</v>
       </c>
       <c r="I10" t="n">
-        <v>6.4</v>
+        <v>2.96</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P10" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.16</v>
+        <v>1.82</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,184 +2489,184 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>NK Celje</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="G11" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="H11" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="I11" t="n">
+        <v>16</v>
+      </c>
+      <c r="J11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>160</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
         <v>10.5</v>
       </c>
-      <c r="J11" t="n">
-        <v>5</v>
-      </c>
-      <c r="K11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
+      <c r="AC11" t="n">
         <v>17.5</v>
       </c>
-      <c r="Y11" t="n">
-        <v>28</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>90</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>430</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AD11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>280</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH11" t="n">
         <v>36</v>
       </c>
-      <c r="AE11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AG11" t="n">
+      <c r="AI11" t="n">
+        <v>200</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH11" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AK11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL11" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX11" t="n">
         <v>7</v>
       </c>
-      <c r="AO11" t="n">
-        <v>290</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>24</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU11" t="n">
+      <c r="AY11" t="n">
         <v>10</v>
       </c>
-      <c r="AV11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>25</v>
+        <v>6.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>42</v>
+        <v>7.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC11" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BD11" t="n">
-        <v>34</v>
+        <v>6.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>46</v>
+        <v>7.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>95</v>
+        <v>7.4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -2683,184 +2683,184 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.56</v>
+        <v>3.5</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6</v>
+        <v>3.55</v>
       </c>
       <c r="H12" t="n">
-        <v>2.94</v>
+        <v>2.24</v>
       </c>
       <c r="I12" t="n">
-        <v>2.98</v>
+        <v>2.26</v>
       </c>
       <c r="J12" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K12" t="n">
         <v>3.75</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P12" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="R12" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="U12" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X12" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Y12" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="AB12" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC12" t="n">
         <v>8.4</v>
       </c>
       <c r="AD12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR12" t="n">
         <v>13</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>18.5</v>
       </c>
       <c r="AS12" t="n">
         <v>25</v>
       </c>
       <c r="AT12" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AU12" t="n">
         <v>7.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AX12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>15.5</v>
       </c>
-      <c r="AY12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>14</v>
-      </c>
       <c r="BA12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB12" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="BC12" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="BD12" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="BE12" t="n">
         <v>34</v>
       </c>
       <c r="BF12" t="n">
-        <v>16.5</v>
+        <v>30</v>
       </c>
       <c r="BG12" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -2877,184 +2877,184 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="G13" t="n">
-        <v>1.89</v>
+        <v>2.18</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="I13" t="n">
-        <v>5.2</v>
+        <v>3.95</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M13" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="O13" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="P13" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="R13" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="U13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W13" t="n">
         <v>1.84</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>12</v>
       </c>
       <c r="Y13" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AC13" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF13" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK13" t="n">
         <v>24</v>
       </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>23</v>
-      </c>
       <c r="AL13" t="n">
-        <v>240</v>
+        <v>42</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN13" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR13" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AS13" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AT13" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AU13" t="n">
         <v>7.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AX13" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AY13" t="n">
         <v>10</v>
       </c>
       <c r="AZ13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC13" t="n">
         <v>21</v>
       </c>
-      <c r="BA13" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>20</v>
-      </c>
       <c r="BD13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE13" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BF13" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Genk</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="G14" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="H14" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N14" t="n">
         <v>4.4</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.95</v>
-      </c>
       <c r="O14" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="T14" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="U14" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="X14" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="Z14" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG14" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK14" t="n">
         <v>17</v>
       </c>
-      <c r="AK14" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AL14" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN14" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB14" t="n">
         <v>14</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB14" t="n">
+      <c r="BC14" t="n">
         <v>14.5</v>
       </c>
-      <c r="BC14" t="n">
-        <v>16</v>
-      </c>
       <c r="BD14" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="BE14" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="BF14" t="n">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>38</v>
+        <v>12.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,108 +3265,108 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.83</v>
+        <v>5.2</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>4.8</v>
+        <v>1.68</v>
       </c>
       <c r="I15" t="n">
-        <v>5.7</v>
+        <v>1.98</v>
       </c>
       <c r="J15" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M15" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P15" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
         <v>1000</v>
@@ -3378,7 +3378,7 @@
         <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
         <v>1000</v>
@@ -3387,69 +3387,69 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Dinamo Bucharest</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Universitatea Craiova</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.84</v>
+        <v>2.74</v>
       </c>
       <c r="G16" t="n">
-        <v>2.36</v>
+        <v>3.15</v>
       </c>
       <c r="H16" t="n">
-        <v>3.55</v>
+        <v>2.74</v>
       </c>
       <c r="I16" t="n">
-        <v>5.6</v>
+        <v>3.15</v>
       </c>
       <c r="J16" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K16" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="P16" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Gremio</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EC Vitoria Salvador</t>
+          <t>Tecnico Universitario</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="G17" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="H17" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="I17" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="J17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S17" t="n">
         <v>3.5</v>
       </c>
-      <c r="K17" t="n">
-        <v>4</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,42 +3847,42 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>1.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -3903,10 +3903,10 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3915,310 +3915,2444 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Shakhtar</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Lech Poznan</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:24:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I20" t="n">
+        <v>12</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>570</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>250</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>200</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:24:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Sparta Prague</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Az Alkmaar</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:24:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>430</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>290</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>110</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>95</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:24:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:24:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H24" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>240</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>40</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:24:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>38</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:24:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Alianza FC Valledupar</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Jaguares de Cordoba</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:24:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:24:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Gremio</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>EC Vitoria Salvador</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:24:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Sportivo Trinidense</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Club Sportivo Ameliano</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:24:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>20:20:00</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Tolima</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Fortaleza FC</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="F30" t="n">
         <v>1.62</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G30" t="n">
         <v>1.94</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H30" t="n">
         <v>5.1</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I30" t="n">
         <v>9.6</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J30" t="n">
         <v>3.4</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K30" t="n">
         <v>5.1</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
         <v>1.59</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="Q30" t="n">
         <v>2.06</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>2026-03-17 14:12:51</t>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
@@ -763,7 +763,7 @@
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="I2" t="n">
         <v>1.47</v>
@@ -772,10 +772,10 @@
         <v>4.5</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>12.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
         <v>1.01</v>
@@ -865,52 +865,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -954,19 +954,19 @@
         <v>2.08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
         <v>1.38</v>
@@ -981,10 +981,10 @@
         <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R3" t="n">
         <v>1.38</v>
@@ -999,7 +999,7 @@
         <v>2.16</v>
       </c>
       <c r="V3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
         <v>1.9</v>
@@ -1008,13 +1008,13 @@
         <v>14.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z3" t="n">
         <v>30</v>
       </c>
       <c r="AA3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB3" t="n">
         <v>10</v>
@@ -1038,7 +1038,7 @@
         <v>18</v>
       </c>
       <c r="AI3" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ3" t="n">
         <v>25</v>
@@ -1062,13 +1062,13 @@
         <v>12.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AS3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT3" t="n">
         <v>8.800000000000001</v>
@@ -1080,7 +1080,7 @@
         <v>15</v>
       </c>
       <c r="AW3" t="n">
-        <v>44</v>
+        <v>11.5</v>
       </c>
       <c r="AX3" t="n">
         <v>11.5</v>
@@ -1092,7 +1092,7 @@
         <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB3" t="n">
         <v>21</v>
@@ -1101,20 +1101,20 @@
         <v>19</v>
       </c>
       <c r="BD3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF3" t="n">
         <v>13</v>
       </c>
       <c r="BG3" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
         <v>17.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="I4" t="n">
         <v>1.3</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -1339,46 +1339,46 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="G5" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="H5" t="n">
-        <v>13.5</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="J5" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="K5" t="n">
-        <v>24</v>
+        <v>9.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="O5" t="n">
         <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="R5" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1387,10 +1387,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -1536,10 +1536,10 @@
         <v>1.79</v>
       </c>
       <c r="G6" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H6" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I6" t="n">
         <v>5.8</v>
@@ -1575,10 +1575,10 @@
         <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U6" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="V6" t="n">
         <v>1.21</v>
@@ -1602,7 +1602,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD6" t="n">
         <v>22</v>
@@ -1647,10 +1647,10 @@
         <v>14</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT6" t="n">
         <v>7</v>
@@ -1662,7 +1662,7 @@
         <v>17.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="AX6" t="n">
         <v>9.199999999999999</v>
@@ -1674,7 +1674,7 @@
         <v>18</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB6" t="n">
         <v>17</v>
@@ -1683,20 +1683,20 @@
         <v>17.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF6" t="n">
         <v>11</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -1730,16 +1730,16 @@
         <v>1.35</v>
       </c>
       <c r="G7" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="H7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
         <v>11.5</v>
       </c>
       <c r="J7" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="K7" t="n">
         <v>6.2</v>
@@ -1754,7 +1754,7 @@
         <v>5.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P7" t="n">
         <v>2.36</v>
@@ -1769,7 +1769,7 @@
         <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="U7" t="n">
         <v>2.02</v>
@@ -1778,10 +1778,10 @@
         <v>1.09</v>
       </c>
       <c r="W7" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="X7" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="Y7" t="n">
         <v>36</v>
@@ -1796,76 +1796,76 @@
         <v>10</v>
       </c>
       <c r="AC7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD7" t="n">
         <v>38</v>
       </c>
       <c r="AE7" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF7" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI7" t="n">
         <v>140</v>
       </c>
       <c r="AJ7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM7" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN7" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AO7" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP7" t="n">
         <v>21</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="AR7" t="n">
         <v>8</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU7" t="n">
         <v>11.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="AW7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX7" t="n">
         <v>7.8</v>
       </c>
       <c r="AY7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BA7" t="n">
         <v>8.199999999999999</v>
@@ -1874,23 +1874,23 @@
         <v>10</v>
       </c>
       <c r="BC7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="BE7" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BF7" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -1933,13 +1933,13 @@
         <v>12.5</v>
       </c>
       <c r="J8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K8" t="n">
         <v>5.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
@@ -1987,7 +1987,7 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC8" t="n">
         <v>14</v>
@@ -1999,7 +1999,7 @@
         <v>270</v>
       </c>
       <c r="AF8" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
         <v>13</v>
@@ -2011,7 +2011,7 @@
         <v>210</v>
       </c>
       <c r="AJ8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK8" t="n">
         <v>19.5</v>
@@ -2023,7 +2023,7 @@
         <v>250</v>
       </c>
       <c r="AN8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
@@ -2032,25 +2032,25 @@
         <v>14.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU8" t="n">
         <v>10</v>
       </c>
       <c r="AV8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AX8" t="n">
         <v>6.8</v>
@@ -2059,32 +2059,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB8" t="n">
         <v>9.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BF8" t="n">
         <v>5</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>4.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
@@ -2169,7 +2169,7 @@
         <v>1.18</v>
       </c>
       <c r="X9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y9" t="n">
         <v>8</v>
@@ -2199,7 +2199,7 @@
         <v>26</v>
       </c>
       <c r="AH9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI9" t="n">
         <v>40</v>
@@ -2226,7 +2226,7 @@
         <v>13.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR9" t="n">
         <v>8</v>
@@ -2259,26 +2259,26 @@
         <v>32</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BD9" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BE9" t="n">
         <v>9.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG9" t="n">
         <v>9</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>2.6</v>
       </c>
       <c r="G10" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="H10" t="n">
         <v>2.76</v>
@@ -2321,13 +2321,13 @@
         <v>2.96</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
         <v>3.75</v>
       </c>
       <c r="L10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
@@ -2336,13 +2336,13 @@
         <v>3.75</v>
       </c>
       <c r="O10" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P10" t="n">
         <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="R10" t="n">
         <v>1.37</v>
@@ -2438,7 +2438,7 @@
         <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX10" t="n">
         <v>15.5</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
         <v>1.6</v>
       </c>
       <c r="S11" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="T11" t="n">
         <v>2.1</v>
@@ -2593,7 +2593,7 @@
         <v>200</v>
       </c>
       <c r="AJ11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AK11" t="n">
         <v>17</v>
@@ -2617,10 +2617,10 @@
         <v>36</v>
       </c>
       <c r="AR11" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT11" t="n">
         <v>8.6</v>
@@ -2629,22 +2629,22 @@
         <v>13</v>
       </c>
       <c r="AV11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB11" t="n">
         <v>8.199999999999999</v>
@@ -2653,20 +2653,20 @@
         <v>12</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF11" t="n">
         <v>3.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G12" t="n">
         <v>3.55</v>
@@ -2706,7 +2706,7 @@
         <v>2.24</v>
       </c>
       <c r="I12" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="J12" t="n">
         <v>3.7</v>
@@ -2715,13 +2715,13 @@
         <v>3.75</v>
       </c>
       <c r="L12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O12" t="n">
         <v>1.29</v>
@@ -2766,13 +2766,13 @@
         <v>14.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD12" t="n">
         <v>11</v>
       </c>
       <c r="AE12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF12" t="n">
         <v>25</v>
@@ -2781,7 +2781,7 @@
         <v>14.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI12" t="n">
         <v>34</v>
@@ -2841,7 +2841,7 @@
         <v>30</v>
       </c>
       <c r="BB12" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BC12" t="n">
         <v>34</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G13" t="n">
         <v>2.18</v>
@@ -2900,7 +2900,7 @@
         <v>3.9</v>
       </c>
       <c r="I13" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="J13" t="n">
         <v>3.5</v>
@@ -2909,7 +2909,7 @@
         <v>3.55</v>
       </c>
       <c r="L13" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="M13" t="n">
         <v>1.08</v>
@@ -2924,13 +2924,13 @@
         <v>1.84</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T13" t="n">
         <v>1.9</v>
@@ -2939,10 +2939,10 @@
         <v>2.04</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W13" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="X13" t="n">
         <v>12</v>
@@ -2957,16 +2957,16 @@
         <v>85</v>
       </c>
       <c r="AB13" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD13" t="n">
         <v>16</v>
       </c>
       <c r="AE13" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF13" t="n">
         <v>12.5</v>
@@ -2981,7 +2981,7 @@
         <v>65</v>
       </c>
       <c r="AJ13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK13" t="n">
         <v>24</v>
@@ -3008,16 +3008,16 @@
         <v>24</v>
       </c>
       <c r="AS13" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AU13" t="n">
         <v>7.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW13" t="n">
         <v>44</v>
@@ -3038,10 +3038,10 @@
         <v>23</v>
       </c>
       <c r="BC13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD13" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE13" t="n">
         <v>40</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G14" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="H14" t="n">
         <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J14" t="n">
         <v>4.3</v>
@@ -3103,28 +3103,28 @@
         <v>4.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O14" t="n">
         <v>1.26</v>
       </c>
       <c r="P14" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R14" t="n">
         <v>1.47</v>
       </c>
       <c r="S14" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
         <v>1.86</v>
@@ -3136,16 +3136,16 @@
         <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="X14" t="n">
         <v>18.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
         <v>200</v>
@@ -3157,10 +3157,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE14" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
         <v>10</v>
@@ -3178,7 +3178,7 @@
         <v>15.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL14" t="n">
         <v>34</v>
@@ -3190,7 +3190,7 @@
         <v>8</v>
       </c>
       <c r="AO14" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP14" t="n">
         <v>17</v>
@@ -3199,10 +3199,10 @@
         <v>19.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>44</v>
+        <v>12.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AT14" t="n">
         <v>8.6</v>
@@ -3214,7 +3214,7 @@
         <v>20</v>
       </c>
       <c r="AW14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX14" t="n">
         <v>9</v>
@@ -3223,10 +3223,10 @@
         <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BB14" t="n">
         <v>14</v>
@@ -3235,20 +3235,20 @@
         <v>14.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BF14" t="n">
         <v>7.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>2.74</v>
       </c>
       <c r="G16" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H16" t="n">
         <v>2.74</v>
@@ -3494,7 +3494,7 @@
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N16" t="n">
         <v>2.68</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="G17" t="n">
         <v>1.98</v>
@@ -3676,161 +3676,161 @@
         <v>4.8</v>
       </c>
       <c r="I17" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="J17" t="n">
         <v>3.3</v>
       </c>
       <c r="K17" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L17" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="O17" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="P17" t="n">
         <v>1.67</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W17" t="n">
         <v>2.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -3879,16 +3879,16 @@
         <v>4.3</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P18" t="n">
         <v>1.9</v>
@@ -3897,10 +3897,10 @@
         <v>1.97</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T18" t="n">
         <v>1.94</v>
@@ -3909,10 +3909,10 @@
         <v>1.92</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="X18" t="n">
         <v>18</v>
@@ -3933,7 +3933,7 @@
         <v>10.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE18" t="n">
         <v>110</v>
@@ -3945,25 +3945,25 @@
         <v>12</v>
       </c>
       <c r="AH18" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI18" t="n">
         <v>110</v>
       </c>
       <c r="AJ18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL18" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM18" t="n">
         <v>160</v>
       </c>
       <c r="AN18" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO18" t="n">
         <v>140</v>
@@ -3975,10 +3975,10 @@
         <v>16</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT18" t="n">
         <v>7.2</v>
@@ -3990,19 +3990,19 @@
         <v>18</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AX18" t="n">
         <v>8.6</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ18" t="n">
         <v>19.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BB18" t="n">
         <v>15</v>
@@ -4011,20 +4011,20 @@
         <v>16</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BF18" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -4058,13 +4058,13 @@
         <v>2.12</v>
       </c>
       <c r="G19" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H19" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I19" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J19" t="n">
         <v>3.7</v>
@@ -4073,16 +4073,16 @@
         <v>3.9</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P19" t="n">
         <v>2.1</v>
@@ -4091,10 +4091,10 @@
         <v>1.79</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
         <v>1.68</v>
@@ -4103,16 +4103,16 @@
         <v>2.28</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="X19" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z19" t="n">
         <v>32</v>
@@ -4139,22 +4139,22 @@
         <v>12.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI19" t="n">
         <v>55</v>
       </c>
       <c r="AJ19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK19" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM19" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN19" t="n">
         <v>16</v>
@@ -4169,10 +4169,10 @@
         <v>13.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT19" t="n">
         <v>10</v>
@@ -4184,7 +4184,7 @@
         <v>13.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX19" t="n">
         <v>12.5</v>
@@ -4196,29 +4196,29 @@
         <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC19" t="n">
         <v>18.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BF19" t="n">
         <v>10.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Sparta Prague</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Az Alkmaar</t>
         </is>
       </c>
       <c r="F20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L20" t="n">
         <v>1.4</v>
       </c>
-      <c r="G20" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="H20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="I20" t="n">
+      <c r="M20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X20" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AX20" t="n">
         <v>12</v>
       </c>
-      <c r="J20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K20" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>36</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>570</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="AY20" t="n">
         <v>9.4</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AZ20" t="n">
         <v>14.5</v>
       </c>
-      <c r="AD20" t="n">
-        <v>48</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>250</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV20" t="n">
+      <c r="BA20" t="n">
         <v>4</v>
       </c>
-      <c r="AW20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BB20" t="n">
-        <v>9.6</v>
+        <v>3.85</v>
       </c>
       <c r="BC20" t="n">
-        <v>13.5</v>
+        <v>3.75</v>
       </c>
       <c r="BD20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE20" t="n">
         <v>4.1</v>
       </c>
-      <c r="BE20" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BF20" t="n">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -4434,179 +4434,179 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sparta Prague</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Az Alkmaar</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="G21" t="n">
-        <v>2.42</v>
+        <v>1.43</v>
       </c>
       <c r="H21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I21" t="n">
+        <v>12</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W21" t="n">
         <v>3.3</v>
       </c>
-      <c r="I21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
       <c r="X21" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="Y21" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="Z21" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>570</v>
       </c>
       <c r="AB21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>250</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>200</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>13</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AK21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU21" t="n">
         <v>10</v>
       </c>
-      <c r="AD21" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG21" t="n">
+      <c r="AV21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC21" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BD21" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BF21" t="n">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="BG21" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
         <v>1.43</v>
       </c>
       <c r="H22" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="I22" t="n">
         <v>10.5</v>
@@ -4655,7 +4655,7 @@
         <v>5.2</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M22" t="n">
         <v>1.06</v>
@@ -4670,7 +4670,7 @@
         <v>2.08</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R22" t="n">
         <v>1.42</v>
@@ -4685,55 +4685,55 @@
         <v>1.82</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X22" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y22" t="n">
         <v>28</v>
       </c>
       <c r="Z22" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AA22" t="n">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AB22" t="n">
         <v>8</v>
       </c>
       <c r="AC22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD22" t="n">
         <v>36</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF22" t="n">
         <v>7.8</v>
       </c>
       <c r="AG22" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ22" t="n">
         <v>11.5</v>
       </c>
       <c r="AK22" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
@@ -4742,22 +4742,22 @@
         <v>7</v>
       </c>
       <c r="AO22" t="n">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="AP22" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR22" t="n">
         <v>50</v>
       </c>
       <c r="AS22" t="n">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU22" t="n">
         <v>10</v>
@@ -4772,22 +4772,22 @@
         <v>7.2</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA22" t="n">
         <v>42</v>
       </c>
       <c r="BB22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD22" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE22" t="n">
         <v>46</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -4831,13 +4831,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G23" t="n">
         <v>2.58</v>
       </c>
       <c r="H23" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I23" t="n">
         <v>2.98</v>
@@ -4846,10 +4846,10 @@
         <v>3.65</v>
       </c>
       <c r="K23" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M23" t="n">
         <v>1.06</v>
@@ -4861,13 +4861,13 @@
         <v>1.29</v>
       </c>
       <c r="P23" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S23" t="n">
         <v>3.15</v>
@@ -4876,16 +4876,16 @@
         <v>1.71</v>
       </c>
       <c r="U23" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X23" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y23" t="n">
         <v>13</v>
@@ -4894,25 +4894,25 @@
         <v>20</v>
       </c>
       <c r="AA23" t="n">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="AB23" t="n">
         <v>12</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD23" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF23" t="n">
         <v>17</v>
       </c>
       <c r="AG23" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH23" t="n">
         <v>16.5</v>
@@ -4921,10 +4921,10 @@
         <v>42</v>
       </c>
       <c r="AJ23" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK23" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL23" t="n">
         <v>38</v>
@@ -4942,16 +4942,16 @@
         <v>14.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR23" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS23" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU23" t="n">
         <v>7.4</v>
@@ -4960,10 +4960,10 @@
         <v>12</v>
       </c>
       <c r="AW23" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AX23" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY23" t="n">
         <v>11</v>
@@ -4972,29 +4972,29 @@
         <v>15</v>
       </c>
       <c r="BA23" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BB23" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BC23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD23" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE23" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BF23" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BG23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -5025,25 +5025,25 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G24" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I24" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="J24" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K24" t="n">
         <v>3.75</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M24" t="n">
         <v>1.09</v>
@@ -5073,25 +5073,25 @@
         <v>1.85</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z24" t="n">
         <v>38</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB24" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC24" t="n">
         <v>8</v>
@@ -5100,13 +5100,13 @@
         <v>21</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF24" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG24" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH24" t="n">
         <v>24</v>
@@ -5115,13 +5115,13 @@
         <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL24" t="n">
-        <v>240</v>
+        <v>48</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
@@ -5130,16 +5130,16 @@
         <v>16</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP24" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AR24" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS24" t="n">
         <v>42</v>
@@ -5148,22 +5148,22 @@
         <v>6.8</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW24" t="n">
         <v>34</v>
       </c>
       <c r="AX24" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY24" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA24" t="n">
         <v>38</v>
@@ -5175,20 +5175,20 @@
         <v>20</v>
       </c>
       <c r="BD24" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BE24" t="n">
         <v>46</v>
       </c>
       <c r="BF24" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG24" t="n">
         <v>40</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G25" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H25" t="n">
         <v>5.4</v>
@@ -5231,19 +5231,19 @@
         <v>5.8</v>
       </c>
       <c r="J25" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K25" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M25" t="n">
         <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
         <v>1.31</v>
@@ -5255,7 +5255,7 @@
         <v>1.93</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S25" t="n">
         <v>3.4</v>
@@ -5267,34 +5267,34 @@
         <v>1.99</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X25" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y25" t="n">
         <v>18.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB25" t="n">
         <v>8.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD25" t="n">
         <v>22</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF25" t="n">
         <v>9.800000000000001</v>
@@ -5303,70 +5303,70 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK25" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL25" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN25" t="n">
         <v>10.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP25" t="n">
         <v>14</v>
       </c>
       <c r="AQ25" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AS25" t="n">
         <v>42</v>
       </c>
       <c r="AT25" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU25" t="n">
         <v>8.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW25" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AX25" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY25" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA25" t="n">
         <v>36</v>
       </c>
       <c r="BB25" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC25" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD25" t="n">
         <v>32</v>
@@ -5375,14 +5375,14 @@
         <v>42</v>
       </c>
       <c r="BF25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG25" t="n">
         <v>38</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="G26" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="H26" t="n">
         <v>4.8</v>
@@ -5425,22 +5425,22 @@
         <v>5.7</v>
       </c>
       <c r="J26" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K26" t="n">
         <v>3.8</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
         <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P26" t="n">
         <v>1.55</v>
@@ -5449,22 +5449,22 @@
         <v>2.46</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="X26" t="n">
         <v>11.5</v>
@@ -5527,10 +5527,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT26" t="n">
         <v>5.5</v>
@@ -5539,7 +5539,7 @@
         <v>7</v>
       </c>
       <c r="AV26" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AW26" t="n">
         <v>4.3</v>
@@ -5551,7 +5551,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ26" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BA26" t="n">
         <v>4.3</v>
@@ -5563,20 +5563,20 @@
         <v>3.9</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF26" t="n">
         <v>16</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -5607,13 +5607,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="G27" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="H27" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I27" t="n">
         <v>5.6</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -5831,10 +5831,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -6189,10 +6189,10 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="G30" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="H30" t="n">
         <v>5.1</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
@@ -802,7 +802,7 @@
         <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="V2" t="n">
         <v>3.1</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -954,19 +954,19 @@
         <v>2.08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I3" t="n">
         <v>4.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L3" t="n">
         <v>1.38</v>
@@ -1002,19 +1002,19 @@
         <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="X3" t="n">
         <v>14.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z3" t="n">
         <v>30</v>
       </c>
       <c r="AA3" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB3" t="n">
         <v>10</v>
@@ -1023,10 +1023,10 @@
         <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AE3" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF3" t="n">
         <v>13</v>
@@ -1038,7 +1038,7 @@
         <v>18</v>
       </c>
       <c r="AI3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="n">
         <v>25</v>
@@ -1059,16 +1059,16 @@
         <v>55</v>
       </c>
       <c r="AP3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="n">
         <v>25</v>
       </c>
       <c r="AS3" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AT3" t="n">
         <v>8.800000000000001</v>
@@ -1077,10 +1077,10 @@
         <v>7.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>11.5</v>
+        <v>32</v>
       </c>
       <c r="AX3" t="n">
         <v>11.5</v>
@@ -1092,7 +1092,7 @@
         <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB3" t="n">
         <v>21</v>
@@ -1104,7 +1104,7 @@
         <v>32</v>
       </c>
       <c r="BE3" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BF3" t="n">
         <v>13</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -1342,16 +1342,16 @@
         <v>1.16</v>
       </c>
       <c r="G5" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="I5" t="n">
         <v>34</v>
       </c>
       <c r="J5" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
         <v>9.6</v>
@@ -1378,7 +1378,7 @@
         <v>1.59</v>
       </c>
       <c r="S5" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1390,7 +1390,7 @@
         <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -1533,25 +1533,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="G6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J6" t="n">
         <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
@@ -1575,10 +1575,10 @@
         <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U6" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="V6" t="n">
         <v>1.21</v>
@@ -1662,7 +1662,7 @@
         <v>17.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="AX6" t="n">
         <v>9.199999999999999</v>
@@ -1671,7 +1671,7 @@
         <v>9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA6" t="n">
         <v>8.199999999999999</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -1730,19 +1730,19 @@
         <v>1.35</v>
       </c>
       <c r="G7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H7" t="n">
         <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="J7" t="n">
         <v>5.7</v>
       </c>
       <c r="K7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
         <v>1.29</v>
@@ -1784,7 +1784,7 @@
         <v>26</v>
       </c>
       <c r="Y7" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="Z7" t="n">
         <v>110</v>
@@ -1793,13 +1793,13 @@
         <v>400</v>
       </c>
       <c r="AB7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC7" t="n">
         <v>13.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AE7" t="n">
         <v>170</v>
@@ -1829,7 +1829,7 @@
         <v>160</v>
       </c>
       <c r="AN7" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AO7" t="n">
         <v>200</v>
@@ -1838,13 +1838,13 @@
         <v>21</v>
       </c>
       <c r="AQ7" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AR7" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT7" t="n">
         <v>8.800000000000001</v>
@@ -1853,10 +1853,10 @@
         <v>11.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AW7" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX7" t="n">
         <v>7.8</v>
@@ -1868,7 +1868,7 @@
         <v>23</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB7" t="n">
         <v>10</v>
@@ -1880,17 +1880,17 @@
         <v>28</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF7" t="n">
         <v>4.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="G8" t="n">
         <v>1.43</v>
@@ -1963,7 +1963,7 @@
         <v>3.1</v>
       </c>
       <c r="T8" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U8" t="n">
         <v>1.7</v>
@@ -2077,14 +2077,14 @@
         <v>4.9</v>
       </c>
       <c r="BF8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG8" t="n">
         <v>4.9</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -2121,16 +2121,16 @@
         <v>6.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="I9" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="K9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L9" t="n">
         <v>1.38</v>
@@ -2145,25 +2145,25 @@
         <v>1.32</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
         <v>2.02</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
         <v>3.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U9" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="V9" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="W9" t="n">
         <v>1.18</v>
@@ -2175,22 +2175,22 @@
         <v>8</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AB9" t="n">
         <v>20</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD9" t="n">
         <v>11</v>
       </c>
       <c r="AE9" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AF9" t="n">
         <v>55</v>
@@ -2202,7 +2202,7 @@
         <v>27</v>
       </c>
       <c r="AI9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ9" t="n">
         <v>220</v>
@@ -2220,16 +2220,16 @@
         <v>150</v>
       </c>
       <c r="AO9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AP9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS9" t="n">
         <v>13.5</v>
@@ -2238,7 +2238,7 @@
         <v>16.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV9" t="n">
         <v>9.199999999999999</v>
@@ -2247,38 +2247,38 @@
         <v>15.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AY9" t="n">
         <v>21</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BA9" t="n">
         <v>32</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BC9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF9" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG9" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G10" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H10" t="n">
         <v>2.76</v>
@@ -2333,16 +2333,16 @@
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O10" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P10" t="n">
         <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R10" t="n">
         <v>1.37</v>
@@ -2351,7 +2351,7 @@
         <v>3.35</v>
       </c>
       <c r="T10" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U10" t="n">
         <v>2.18</v>
@@ -2363,7 +2363,7 @@
         <v>1.55</v>
       </c>
       <c r="X10" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="Y10" t="n">
         <v>12.5</v>
@@ -2426,7 +2426,7 @@
         <v>16.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT10" t="n">
         <v>9.800000000000001</v>
@@ -2450,19 +2450,19 @@
         <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BC10" t="n">
         <v>24</v>
       </c>
       <c r="BD10" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF10" t="n">
         <v>17.5</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
         <v>1.18</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q11" t="n">
         <v>1.59</v>
@@ -2542,13 +2542,13 @@
         <v>1.6</v>
       </c>
       <c r="S11" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
         <v>2.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V11" t="n">
         <v>1.06</v>
@@ -2629,7 +2629,7 @@
         <v>13</v>
       </c>
       <c r="AV11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AW11" t="n">
         <v>7.6</v>
@@ -2653,7 +2653,7 @@
         <v>12</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE11" t="n">
         <v>7.6</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G12" t="n">
         <v>3.55</v>
       </c>
       <c r="H12" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I12" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J12" t="n">
         <v>3.7</v>
       </c>
       <c r="K12" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L12" t="n">
         <v>1.38</v>
@@ -2727,10 +2727,10 @@
         <v>1.29</v>
       </c>
       <c r="P12" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R12" t="n">
         <v>1.42</v>
@@ -2766,7 +2766,7 @@
         <v>14.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD12" t="n">
         <v>11</v>
@@ -2820,7 +2820,7 @@
         <v>13.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV12" t="n">
         <v>10</v>
@@ -2838,10 +2838,10 @@
         <v>15.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BB12" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BC12" t="n">
         <v>34</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G13" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H13" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I13" t="n">
         <v>4.1</v>
@@ -2915,7 +2915,7 @@
         <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O13" t="n">
         <v>1.38</v>
@@ -2942,7 +2942,7 @@
         <v>1.32</v>
       </c>
       <c r="W13" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="X13" t="n">
         <v>12</v>
@@ -2960,7 +2960,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD13" t="n">
         <v>16</v>
@@ -3008,7 +3008,7 @@
         <v>24</v>
       </c>
       <c r="AS13" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AT13" t="n">
         <v>8</v>
@@ -3038,7 +3038,7 @@
         <v>23</v>
       </c>
       <c r="BC13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD13" t="n">
         <v>36</v>
@@ -3050,11 +3050,11 @@
         <v>16.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>1.62</v>
       </c>
       <c r="G14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H14" t="n">
         <v>6</v>
@@ -3136,10 +3136,10 @@
         <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="X14" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y14" t="n">
         <v>22</v>
@@ -3157,13 +3157,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG14" t="n">
         <v>10.5</v>
@@ -3187,22 +3187,22 @@
         <v>130</v>
       </c>
       <c r="AN14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO14" t="n">
         <v>110</v>
       </c>
       <c r="AP14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ14" t="n">
         <v>19.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AS14" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AT14" t="n">
         <v>8.6</v>
@@ -3214,7 +3214,7 @@
         <v>20</v>
       </c>
       <c r="AW14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AX14" t="n">
         <v>9</v>
@@ -3223,10 +3223,10 @@
         <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BB14" t="n">
         <v>14</v>
@@ -3235,20 +3235,20 @@
         <v>14.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF14" t="n">
         <v>7.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
         <v>1.02</v>
       </c>
       <c r="O15" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="P15" t="n">
         <v>1.58</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G16" t="n">
         <v>3.1</v>
       </c>
       <c r="H16" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="I16" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J16" t="n">
         <v>3.15</v>
@@ -3515,31 +3515,31 @@
         <v>4.8</v>
       </c>
       <c r="T16" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U16" t="n">
         <v>1.81</v>
       </c>
       <c r="V16" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X16" t="n">
         <v>10</v>
       </c>
       <c r="Y16" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z16" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC16" t="n">
         <v>7.6</v>
@@ -3551,10 +3551,10 @@
         <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
         <v>1000</v>
@@ -3587,10 +3587,10 @@
         <v>7.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AT16" t="n">
         <v>7.6</v>
@@ -3602,41 +3602,41 @@
         <v>11</v>
       </c>
       <c r="AW16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>6</v>
       </c>
-      <c r="AX16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BA16" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BF16" t="n">
         <v>34</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -3861,25 +3861,25 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="G18" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="H18" t="n">
         <v>5.7</v>
       </c>
       <c r="I18" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
@@ -3891,7 +3891,7 @@
         <v>1.33</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q18" t="n">
         <v>1.97</v>
@@ -3903,22 +3903,22 @@
         <v>3.5</v>
       </c>
       <c r="T18" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U18" t="n">
         <v>1.92</v>
       </c>
       <c r="V18" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W18" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="X18" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z18" t="n">
         <v>60</v>
@@ -3951,10 +3951,10 @@
         <v>110</v>
       </c>
       <c r="AJ18" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL18" t="n">
         <v>44</v>
@@ -3975,28 +3975,28 @@
         <v>16</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.7</v>
+        <v>40</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AT18" t="n">
         <v>7.2</v>
       </c>
       <c r="AU18" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="AX18" t="n">
         <v>8.6</v>
       </c>
       <c r="AY18" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
         <v>19.5</v>
@@ -4011,7 +4011,7 @@
         <v>16</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BE18" t="n">
         <v>5</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         <v>1.79</v>
       </c>
       <c r="R19" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -4106,7 +4106,7 @@
         <v>1.35</v>
       </c>
       <c r="W19" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X19" t="n">
         <v>19.5</v>
@@ -4142,7 +4142,7 @@
         <v>18.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ19" t="n">
         <v>30</v>
@@ -4151,7 +4151,7 @@
         <v>22</v>
       </c>
       <c r="AL19" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
         <v>85</v>
@@ -4169,10 +4169,10 @@
         <v>13.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.5</v>
+        <v>55</v>
       </c>
       <c r="AT19" t="n">
         <v>10</v>
@@ -4184,7 +4184,7 @@
         <v>13.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.3</v>
+        <v>36</v>
       </c>
       <c r="AX19" t="n">
         <v>12.5</v>
@@ -4196,10 +4196,10 @@
         <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.3</v>
+        <v>40</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC19" t="n">
         <v>18.5</v>
@@ -4208,7 +4208,7 @@
         <v>5</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF19" t="n">
         <v>10.5</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="G20" t="n">
         <v>2.42</v>
@@ -4288,7 +4288,7 @@
         <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T20" t="n">
         <v>1.71</v>
@@ -4297,7 +4297,7 @@
         <v>2.18</v>
       </c>
       <c r="V20" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W20" t="n">
         <v>1.71</v>
@@ -4315,7 +4315,7 @@
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC20" t="n">
         <v>10</v>
@@ -4336,7 +4336,7 @@
         <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ20" t="n">
         <v>38</v>
@@ -4354,7 +4354,7 @@
         <v>21</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP20" t="n">
         <v>13</v>
@@ -4363,10 +4363,10 @@
         <v>10.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AS20" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AT20" t="n">
         <v>9.199999999999999</v>
@@ -4378,7 +4378,7 @@
         <v>11.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>3.95</v>
+        <v>28</v>
       </c>
       <c r="AX20" t="n">
         <v>12</v>
@@ -4390,29 +4390,29 @@
         <v>14.5</v>
       </c>
       <c r="BA20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC20" t="n">
         <v>4</v>
       </c>
-      <c r="BB20" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>3.75</v>
-      </c>
       <c r="BD20" t="n">
-        <v>3.9</v>
+        <v>29</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BF20" t="n">
         <v>12.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="G21" t="n">
         <v>1.43</v>
@@ -4452,16 +4452,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J21" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K21" t="n">
         <v>5.4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="M21" t="n">
         <v>1.05</v>
@@ -4476,10 +4476,10 @@
         <v>2.04</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
         <v>3.05</v>
@@ -4491,7 +4491,7 @@
         <v>1.71</v>
       </c>
       <c r="V21" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W21" t="n">
         <v>3.3</v>
@@ -4536,7 +4536,7 @@
         <v>13</v>
       </c>
       <c r="AK21" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AL21" t="n">
         <v>48</v>
@@ -4554,13 +4554,13 @@
         <v>15</v>
       </c>
       <c r="AQ21" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AS21" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT21" t="n">
         <v>6.8</v>
@@ -4569,25 +4569,25 @@
         <v>10</v>
       </c>
       <c r="AV21" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AW21" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AX21" t="n">
         <v>6.8</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BA21" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BB21" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC21" t="n">
         <v>13.5</v>
@@ -4596,17 +4596,17 @@
         <v>36</v>
       </c>
       <c r="BE21" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF21" t="n">
         <v>5</v>
       </c>
       <c r="BG21" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G22" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="H22" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J22" t="n">
         <v>5</v>
@@ -4655,7 +4655,7 @@
         <v>5.2</v>
       </c>
       <c r="L22" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M22" t="n">
         <v>1.06</v>
@@ -4670,13 +4670,13 @@
         <v>2.08</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R22" t="n">
         <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T22" t="n">
         <v>2.14</v>
@@ -4688,7 +4688,7 @@
         <v>1.11</v>
       </c>
       <c r="W22" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="X22" t="n">
         <v>16.5</v>
@@ -4742,16 +4742,16 @@
         <v>7</v>
       </c>
       <c r="AO22" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AP22" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ22" t="n">
         <v>25</v>
       </c>
       <c r="AR22" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AS22" t="n">
         <v>23</v>
@@ -4775,7 +4775,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA22" t="n">
         <v>42</v>
@@ -4787,7 +4787,7 @@
         <v>14</v>
       </c>
       <c r="BD22" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BE22" t="n">
         <v>46</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G23" t="n">
         <v>2.58</v>
@@ -4840,16 +4840,16 @@
         <v>2.96</v>
       </c>
       <c r="I23" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
         <v>3.65</v>
       </c>
       <c r="K23" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L23" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M23" t="n">
         <v>1.06</v>
@@ -4861,22 +4861,22 @@
         <v>1.29</v>
       </c>
       <c r="P23" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R23" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T23" t="n">
         <v>1.71</v>
       </c>
       <c r="U23" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V23" t="n">
         <v>1.5</v>
@@ -4918,7 +4918,7 @@
         <v>16.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ23" t="n">
         <v>36</v>
@@ -4975,7 +4975,7 @@
         <v>36</v>
       </c>
       <c r="BB23" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC23" t="n">
         <v>24</v>
@@ -4984,7 +4984,7 @@
         <v>32</v>
       </c>
       <c r="BE23" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BF23" t="n">
         <v>18</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
         <v>5.1</v>
       </c>
       <c r="I24" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J24" t="n">
         <v>3.65</v>
@@ -5043,19 +5043,19 @@
         <v>3.75</v>
       </c>
       <c r="L24" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="M24" t="n">
         <v>1.09</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O24" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P24" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q24" t="n">
         <v>2.32</v>
@@ -5064,7 +5064,7 @@
         <v>1.27</v>
       </c>
       <c r="S24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T24" t="n">
         <v>2.1</v>
@@ -5085,7 +5085,7 @@
         <v>15</v>
       </c>
       <c r="Z24" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA24" t="n">
         <v>140</v>
@@ -5112,7 +5112,7 @@
         <v>24</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ24" t="n">
         <v>20</v>
@@ -5145,7 +5145,7 @@
         <v>42</v>
       </c>
       <c r="AT24" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU24" t="n">
         <v>7.4</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G25" t="n">
         <v>1.73</v>
@@ -5252,22 +5252,22 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R25" t="n">
         <v>1.39</v>
       </c>
       <c r="S25" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T25" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U25" t="n">
         <v>1.99</v>
       </c>
       <c r="V25" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W25" t="n">
         <v>2.36</v>
@@ -5282,10 +5282,10 @@
         <v>44</v>
       </c>
       <c r="AA25" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC25" t="n">
         <v>9</v>
@@ -5300,13 +5300,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG25" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH25" t="n">
         <v>21</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ25" t="n">
         <v>16.5</v>
@@ -5339,7 +5339,7 @@
         <v>42</v>
       </c>
       <c r="AT25" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU25" t="n">
         <v>8.6</v>
@@ -5348,7 +5348,7 @@
         <v>19</v>
       </c>
       <c r="AW25" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AX25" t="n">
         <v>9.199999999999999</v>
@@ -5357,10 +5357,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="BB25" t="n">
         <v>15</v>
@@ -5378,11 +5378,11 @@
         <v>9.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>1.82</v>
       </c>
       <c r="G26" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
         <v>4.8</v>
@@ -5449,22 +5449,22 @@
         <v>2.46</v>
       </c>
       <c r="R26" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="S26" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="T26" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="V26" t="n">
         <v>1.21</v>
       </c>
       <c r="W26" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="X26" t="n">
         <v>11.5</v>
@@ -5473,13 +5473,13 @@
         <v>16</v>
       </c>
       <c r="Z26" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
         <v>190</v>
       </c>
       <c r="AB26" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC26" t="n">
         <v>9.800000000000001</v>
@@ -5494,7 +5494,7 @@
         <v>12.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH26" t="n">
         <v>34</v>
@@ -5503,10 +5503,10 @@
         <v>140</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL26" t="n">
         <v>1000</v>
@@ -5515,7 +5515,7 @@
         <v>270</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
@@ -5527,10 +5527,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AT26" t="n">
         <v>5.5</v>
@@ -5539,44 +5539,44 @@
         <v>7</v>
       </c>
       <c r="AV26" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AX26" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY26" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ26" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BA26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB26" t="n">
         <v>4.3</v>
       </c>
-      <c r="BB26" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BC26" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BF26" t="n">
         <v>16</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -5607,170 +5607,170 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="G27" t="n">
-        <v>2.48</v>
+        <v>110</v>
       </c>
       <c r="H27" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="I27" t="n">
+        <v>110</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K27" t="n">
         <v>5.6</v>
       </c>
-      <c r="J27" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K27" t="n">
-        <v>4.7</v>
-      </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P27" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -5801,170 +5801,170 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G28" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="H28" t="n">
         <v>4.2</v>
       </c>
       <c r="I28" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J28" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K28" t="n">
         <v>4</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P28" t="n">
         <v>1.85</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -6013,16 +6013,16 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P29" t="n">
         <v>1.24</v>
@@ -6031,134 +6031,134 @@
         <v>1.01</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>
@@ -6189,34 +6189,34 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="G30" t="n">
         <v>1.95</v>
       </c>
       <c r="H30" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="I30" t="n">
         <v>9.6</v>
       </c>
       <c r="J30" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="K30" t="n">
         <v>5.1</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P30" t="n">
         <v>1.59</v>
@@ -6225,134 +6225,134 @@
         <v>2.06</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-17 18:34:35</t>
+          <t>2026-03-17 20:44:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH24"/>
+  <dimension ref="A1:BH33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
@@ -1114,14 +1114,14 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ukrainian Premier League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1136,186 +1136,186 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Metalist 1925</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>1.22</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="I4" t="n">
-        <v>34</v>
+        <v>1.39</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="K4" t="n">
-        <v>9.4</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,184 +1325,184 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Metalist 1925</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Genclerbirligi</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.82</v>
+        <v>1.16</v>
       </c>
       <c r="G5" t="n">
-        <v>1.88</v>
+        <v>1.24</v>
       </c>
       <c r="H5" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="I5" t="n">
-        <v>5.7</v>
+        <v>34</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>9.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.06</v>
+        <v>1.53</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="S5" t="n">
-        <v>3.7</v>
+        <v>2.18</v>
       </c>
       <c r="T5" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.92</v>
+        <v>1.53</v>
       </c>
       <c r="V5" t="n">
-        <v>1.21</v>
+        <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>2.12</v>
+        <v>5</v>
       </c>
       <c r="X5" t="n">
-        <v>14.5</v>
+        <v>34</v>
       </c>
       <c r="Y5" t="n">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="Z5" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.4</v>
+        <v>24</v>
       </c>
       <c r="AD5" t="n">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="AE5" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="AI5" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>22</v>
+        <v>9.6</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AL5" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="AM5" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>15.5</v>
+        <v>4.4</v>
       </c>
       <c r="AO5" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>11</v>
+        <v>4.1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.5</v>
+        <v>4.3</v>
       </c>
       <c r="AR5" t="n">
-        <v>32</v>
+        <v>4.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.8</v>
+        <v>3.25</v>
       </c>
       <c r="AU5" t="n">
-        <v>7</v>
+        <v>3.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>18</v>
+        <v>4.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="AX5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AY5" t="n">
-        <v>9</v>
+        <v>3.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>18</v>
+        <v>4.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>17.5</v>
+        <v>3.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>18</v>
+        <v>3.75</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
@@ -1524,186 +1524,186 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kasimpasa</t>
+          <t>Genclerbirligi</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.35</v>
+        <v>1.82</v>
       </c>
       <c r="G6" t="n">
-        <v>1.39</v>
+        <v>1.89</v>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>5.4</v>
       </c>
       <c r="I6" t="n">
-        <v>12.5</v>
+        <v>5.7</v>
       </c>
       <c r="J6" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R6" t="n">
         <v>1.29</v>
       </c>
-      <c r="M6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.54</v>
-      </c>
       <c r="S6" t="n">
-        <v>2.48</v>
+        <v>3.7</v>
       </c>
       <c r="T6" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="U6" t="n">
         <v>1.92</v>
       </c>
       <c r="V6" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>3.6</v>
+        <v>2.12</v>
       </c>
       <c r="X6" t="n">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="Y6" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z6" t="n">
         <v>42</v>
       </c>
-      <c r="Z6" t="n">
-        <v>110</v>
-      </c>
       <c r="AA6" t="n">
-        <v>400</v>
+        <v>160</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>13.5</v>
       </c>
-      <c r="AD6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>170</v>
-      </c>
-      <c r="AF6" t="n">
+      <c r="AR6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX6" t="n">
         <v>9</v>
       </c>
-      <c r="AG6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AR6" t="n">
+      <c r="AY6" t="n">
         <v>9</v>
       </c>
-      <c r="AS6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BB6" t="n">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="BD6" t="n">
-        <v>28</v>
+        <v>6.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="BG6" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Kasimpasa</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.12</v>
+        <v>1.35</v>
       </c>
       <c r="G7" t="n">
-        <v>2.16</v>
+        <v>1.39</v>
       </c>
       <c r="H7" t="n">
-        <v>3.95</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
       </c>
       <c r="K7" t="n">
-        <v>3.55</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="P7" t="n">
-        <v>1.84</v>
+        <v>2.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.16</v>
+        <v>1.6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.31</v>
+        <v>1.54</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>2.48</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="U7" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="V7" t="n">
-        <v>1.32</v>
+        <v>1.09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.86</v>
+        <v>3.6</v>
       </c>
       <c r="X7" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="Y7" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>400</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC7" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AD7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH7" t="n">
         <v>28</v>
       </c>
-      <c r="AA7" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="AI7" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT7" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AU7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX7" t="n">
         <v>7.8</v>
       </c>
-      <c r="AD7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF7" t="n">
+      <c r="AY7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC7" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>21</v>
-      </c>
       <c r="BD7" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="BE7" t="n">
-        <v>40</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF7" t="n">
-        <v>16.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>50</v>
+        <v>9.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,179 +1912,179 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.5</v>
+        <v>1.38</v>
       </c>
       <c r="G8" t="n">
-        <v>3.55</v>
+        <v>1.43</v>
       </c>
       <c r="H8" t="n">
-        <v>2.22</v>
+        <v>10.5</v>
       </c>
       <c r="I8" t="n">
-        <v>2.26</v>
+        <v>13</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="K8" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="O8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="S8" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="U8" t="n">
-        <v>2.26</v>
+        <v>1.7</v>
       </c>
       <c r="V8" t="n">
-        <v>1.79</v>
+        <v>1.08</v>
       </c>
       <c r="W8" t="n">
-        <v>1.39</v>
+        <v>3.3</v>
       </c>
       <c r="X8" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Y8" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>14.5</v>
+        <v>130</v>
       </c>
       <c r="AA8" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>14.5</v>
+        <v>7.8</v>
       </c>
       <c r="AC8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>270</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>210</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD8" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AD8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>46</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>34</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>42</v>
-      </c>
       <c r="BE8" t="n">
-        <v>34</v>
+        <v>9.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>30</v>
+        <v>5.1</v>
       </c>
       <c r="BG8" t="n">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
@@ -2106,186 +2106,186 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NK Celje</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.24</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>1.31</v>
+        <v>6.4</v>
       </c>
       <c r="H9" t="n">
-        <v>13</v>
+        <v>1.62</v>
       </c>
       <c r="I9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA9" t="n">
         <v>16</v>
       </c>
-      <c r="J9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X9" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>48</v>
-      </c>
-      <c r="Z9" t="n">
+      <c r="AB9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>230</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN9" t="n">
         <v>160</v>
       </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>280</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ9" t="n">
+      <c r="AO9" t="n">
         <v>10</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AP9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW9" t="n">
         <v>15</v>
       </c>
-      <c r="AL9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT9" t="n">
+      <c r="AX9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA9" t="n">
         <v>8.6</v>
       </c>
-      <c r="AU9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BB9" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC9" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="BD9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG9" t="n">
         <v>7.4</v>
       </c>
-      <c r="BE9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,179 +2300,179 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Rakow Czestochowa</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Genk</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.64</v>
+        <v>2.66</v>
       </c>
       <c r="G10" t="n">
-        <v>1.65</v>
+        <v>2.88</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>2.72</v>
       </c>
       <c r="I10" t="n">
-        <v>6.4</v>
+        <v>2.9</v>
       </c>
       <c r="J10" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="L10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.35</v>
       </c>
-      <c r="M10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.47</v>
-      </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="T10" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="U10" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V10" t="n">
-        <v>1.19</v>
+        <v>1.52</v>
       </c>
       <c r="W10" t="n">
-        <v>2.54</v>
+        <v>1.53</v>
       </c>
       <c r="X10" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="Y10" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>50</v>
+        <v>19.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>170</v>
+        <v>46</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AF10" t="n">
-        <v>10</v>
+        <v>19.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AH10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="AJ10" t="n">
-        <v>15.5</v>
+        <v>42</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="AL10" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="AO10" t="n">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="AP10" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="AQ10" t="n">
-        <v>20</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR10" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="AS10" t="n">
-        <v>44</v>
+        <v>7.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU10" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="AV10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG10" t="n">
         <v>21</v>
       </c>
-      <c r="AW10" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>38</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>36</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>NK Celje</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>1.25</v>
       </c>
       <c r="G11" t="n">
-        <v>6.4</v>
+        <v>1.31</v>
       </c>
       <c r="H11" t="n">
-        <v>1.62</v>
+        <v>13</v>
       </c>
       <c r="I11" t="n">
-        <v>1.64</v>
+        <v>16</v>
       </c>
       <c r="J11" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="K11" t="n">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="M11" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="O11" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="P11" t="n">
-        <v>1.93</v>
+        <v>2.52</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.02</v>
+        <v>1.59</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="S11" t="n">
-        <v>3.45</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="V11" t="n">
-        <v>2.56</v>
+        <v>1.06</v>
       </c>
       <c r="W11" t="n">
-        <v>1.19</v>
+        <v>4.2</v>
       </c>
       <c r="X11" t="n">
-        <v>16.5</v>
+        <v>32</v>
       </c>
       <c r="Y11" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
+        <v>160</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>280</v>
+      </c>
+      <c r="AF11" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AA11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>55</v>
-      </c>
       <c r="AG11" t="n">
-        <v>27</v>
+        <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AI11" t="n">
-        <v>42</v>
+        <v>200</v>
       </c>
       <c r="AJ11" t="n">
-        <v>230</v>
+        <v>10</v>
       </c>
       <c r="AK11" t="n">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="AL11" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="AN11" t="n">
-        <v>160</v>
+        <v>4.4</v>
       </c>
       <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY11" t="n">
         <v>10</v>
       </c>
-      <c r="AP11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ11" t="n">
+      <c r="AZ11" t="n">
         <v>7</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>21</v>
       </c>
       <c r="BA11" t="n">
         <v>8.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BD11" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>9.199999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L12" t="n">
         <v>1.38</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="H12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I12" t="n">
-        <v>13</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.36</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P12" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="R12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W12" t="n">
         <v>1.39</v>
       </c>
-      <c r="S12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W12" t="n">
-        <v>3.3</v>
-      </c>
       <c r="X12" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>130</v>
+        <v>14.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AB12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU12" t="n">
         <v>7.8</v>
       </c>
-      <c r="AC12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>270</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>210</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU12" t="n">
+      <c r="AV12" t="n">
         <v>10</v>
       </c>
-      <c r="AV12" t="n">
-        <v>8</v>
-      </c>
       <c r="AW12" t="n">
-        <v>9.6</v>
+        <v>20</v>
       </c>
       <c r="AX12" t="n">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>7.6</v>
+        <v>15.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.6</v>
+        <v>29</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.4</v>
+        <v>48</v>
       </c>
       <c r="BC12" t="n">
-        <v>12.5</v>
+        <v>34</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="BE12" t="n">
-        <v>9.6</v>
+        <v>70</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.1</v>
+        <v>30</v>
       </c>
       <c r="BG12" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Rakow Czestochowa</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.66</v>
+        <v>2.12</v>
       </c>
       <c r="G13" t="n">
-        <v>2.88</v>
+        <v>2.16</v>
       </c>
       <c r="H13" t="n">
-        <v>2.72</v>
+        <v>3.95</v>
       </c>
       <c r="I13" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="J13" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L13" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="O13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.32</v>
       </c>
-      <c r="P13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.52</v>
-      </c>
       <c r="W13" t="n">
-        <v>1.53</v>
+        <v>1.86</v>
       </c>
       <c r="X13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y13" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>19.5</v>
+        <v>28</v>
       </c>
       <c r="AA13" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="AB13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF13" t="n">
         <v>12.5</v>
       </c>
-      <c r="AC13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AG13" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="AJ13" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AK13" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AL13" t="n">
         <v>42</v>
       </c>
       <c r="AM13" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN13" t="n">
-        <v>26</v>
+        <v>18.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="AP13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AR13" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AU13" t="n">
         <v>7.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.2</v>
+        <v>40</v>
       </c>
       <c r="AX13" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.4</v>
+        <v>46</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="BC13" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.4</v>
+        <v>36</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="BF13" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Dinamo Bucharest</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Universitatea Craiova</t>
+          <t>Genk</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.78</v>
+        <v>1.63</v>
       </c>
       <c r="G14" t="n">
-        <v>3.2</v>
+        <v>1.65</v>
       </c>
       <c r="H14" t="n">
-        <v>2.58</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="J14" t="n">
-        <v>2.74</v>
+        <v>4.3</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M14" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.49</v>
+        <v>1.26</v>
       </c>
       <c r="P14" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="R14" t="n">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="S14" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="U14" t="n">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.49</v>
+        <v>1.19</v>
       </c>
       <c r="W14" t="n">
-        <v>1.46</v>
+        <v>2.54</v>
       </c>
       <c r="X14" t="n">
-        <v>11</v>
+        <v>18.5</v>
       </c>
       <c r="Y14" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX14" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Z14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ14" t="n">
+      <c r="AY14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF14" t="n">
         <v>7.4</v>
       </c>
-      <c r="AR14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BG14" t="n">
-        <v>7.2</v>
+        <v>36</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.62</v>
+        <v>5.2</v>
       </c>
       <c r="G15" t="n">
-        <v>1.74</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="I15" t="n">
-        <v>6.6</v>
+        <v>1.99</v>
       </c>
       <c r="J15" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="L15" t="n">
         <v>1.42</v>
       </c>
       <c r="M15" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>3.65</v>
+        <v>1.02</v>
       </c>
       <c r="O15" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="P15" t="n">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="R15" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S15" t="n">
-        <v>1.98</v>
+        <v>3.9</v>
       </c>
       <c r="T15" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.18</v>
+        <v>2</v>
       </c>
       <c r="W15" t="n">
-        <v>2.38</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,78 +3459,78 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Shakhtar</t>
+          <t>Dinamo Bucharest</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>Universitatea Craiova</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.12</v>
+        <v>2.78</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="H16" t="n">
-        <v>3.65</v>
+        <v>2.64</v>
       </c>
       <c r="I16" t="n">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="K16" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="N16" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="T16" t="n">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="U16" t="n">
-        <v>2.28</v>
+        <v>1.83</v>
       </c>
       <c r="V16" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.84</v>
+        <v>1.46</v>
       </c>
       <c r="X16" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="Y16" t="n">
-        <v>16.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z16" t="n">
         <v>1000</v>
@@ -3539,111 +3539,111 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
         <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY16" t="n">
         <v>11</v>
       </c>
-      <c r="AH16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AZ16" t="n">
-        <v>14.5</v>
+        <v>6</v>
       </c>
       <c r="BA16" t="n">
-        <v>40</v>
+        <v>7.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>20</v>
+        <v>7.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>18.5</v>
+        <v>7</v>
       </c>
       <c r="BD16" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="BF16" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,184 +3653,184 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sparta Prague</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Az Alkmaar</t>
+          <t>Tecnico Universitario</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="G17" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J17" t="n">
         <v>3.3</v>
       </c>
-      <c r="I17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.55</v>
-      </c>
       <c r="K17" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O17" t="n">
         <v>1.4</v>
       </c>
-      <c r="M17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.29</v>
-      </c>
       <c r="P17" t="n">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="R17" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="T17" t="n">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="U17" t="n">
-        <v>2.18</v>
+        <v>1.82</v>
       </c>
       <c r="V17" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="W17" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="X17" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Y17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z17" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG17" t="n">
         <v>12.5</v>
       </c>
-      <c r="AC17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AH17" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AI17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL17" t="n">
         <v>60</v>
       </c>
-      <c r="AJ17" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>44</v>
-      </c>
       <c r="AM17" t="n">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="AN17" t="n">
         <v>21</v>
       </c>
       <c r="AO17" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS17" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS17" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AT17" t="n">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AX17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF17" t="n">
         <v>12</v>
       </c>
-      <c r="AY17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC17" t="n">
+      <c r="BG17" t="n">
         <v>4.2</v>
       </c>
-      <c r="BD17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
@@ -3852,186 +3852,186 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
       <c r="G18" t="n">
-        <v>1.43</v>
+        <v>1.72</v>
       </c>
       <c r="H18" t="n">
-        <v>9.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="I18" t="n">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="J18" t="n">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="K18" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="O18" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="P18" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="T18" t="n">
-        <v>2.18</v>
+        <v>1.96</v>
       </c>
       <c r="U18" t="n">
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="W18" t="n">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="X18" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA18" t="n">
-        <v>570</v>
+        <v>210</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AE18" t="n">
-        <v>250</v>
+        <v>110</v>
       </c>
       <c r="AF18" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AG18" t="n">
         <v>11.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AI18" t="n">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="AJ18" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AK18" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM18" t="n">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="AN18" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AQ18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV18" t="n">
         <v>20</v>
       </c>
-      <c r="AR18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AW18" t="n">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="AX18" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="BB18" t="n">
-        <v>9.4</v>
+        <v>14.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,31 +4046,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Lech Poznan</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.43</v>
+        <v>2.12</v>
       </c>
       <c r="G19" t="n">
-        <v>1.44</v>
+        <v>2.18</v>
       </c>
       <c r="H19" t="n">
-        <v>9.199999999999999</v>
+        <v>3.65</v>
       </c>
       <c r="I19" t="n">
-        <v>9.800000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="J19" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="K19" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="L19" t="n">
         <v>1.38</v>
@@ -4082,150 +4082,150 @@
         <v>4.2</v>
       </c>
       <c r="O19" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P19" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.14</v>
+        <v>1.68</v>
       </c>
       <c r="U19" t="n">
-        <v>1.82</v>
+        <v>2.28</v>
       </c>
       <c r="V19" t="n">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="W19" t="n">
-        <v>3.25</v>
+        <v>1.85</v>
       </c>
       <c r="X19" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y19" t="n">
         <v>16.5</v>
       </c>
-      <c r="Y19" t="n">
-        <v>28</v>
-      </c>
       <c r="Z19" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC19" t="n">
         <v>8.6</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AD19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG19" t="n">
         <v>11</v>
       </c>
-      <c r="AD19" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>170</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>10</v>
-      </c>
       <c r="AH19" t="n">
-        <v>28</v>
+        <v>16.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN19" t="n">
-        <v>7.2</v>
+        <v>14</v>
       </c>
       <c r="AO19" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
         <v>15</v>
       </c>
       <c r="AQ19" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="AR19" t="n">
-        <v>34</v>
+        <v>8.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AT19" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AU19" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="AW19" t="n">
-        <v>44</v>
+        <v>9.4</v>
       </c>
       <c r="AX19" t="n">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="AY19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG19" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ19" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>46</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>48</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,186 +4240,186 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Sparta Prague</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Az Alkmaar</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="G20" t="n">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="H20" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="J20" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K20" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L20" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="O20" t="n">
         <v>1.29</v>
       </c>
       <c r="P20" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="S20" t="n">
         <v>3.2</v>
       </c>
       <c r="T20" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U20" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="W20" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="X20" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Y20" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Z20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE20" t="n">
         <v>48</v>
       </c>
-      <c r="AB20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>32</v>
-      </c>
       <c r="AF20" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AJ20" t="n">
         <v>36</v>
       </c>
       <c r="AK20" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AL20" t="n">
         <v>44</v>
       </c>
       <c r="AM20" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AN20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO20" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AP20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>14.5</v>
       </c>
-      <c r="AQ20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>15</v>
-      </c>
       <c r="BA20" t="n">
-        <v>36</v>
+        <v>4.2</v>
       </c>
       <c r="BB20" t="n">
-        <v>32</v>
+        <v>4.1</v>
       </c>
       <c r="BC20" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="BD20" t="n">
-        <v>32</v>
+        <v>4.1</v>
       </c>
       <c r="BE20" t="n">
-        <v>34</v>
+        <v>4.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>22</v>
+        <v>4.1</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,179 +4434,179 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.86</v>
+        <v>1.39</v>
       </c>
       <c r="G21" t="n">
-        <v>1.89</v>
+        <v>1.42</v>
       </c>
       <c r="H21" t="n">
-        <v>5.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>5.3</v>
+        <v>11</v>
       </c>
       <c r="J21" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="K21" t="n">
-        <v>3.75</v>
+        <v>5.4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="M21" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="P21" t="n">
-        <v>1.74</v>
+        <v>2.02</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.32</v>
+        <v>1.81</v>
       </c>
       <c r="R21" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="T21" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="U21" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="V21" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="W21" t="n">
-        <v>2.12</v>
+        <v>3.3</v>
       </c>
       <c r="X21" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>570</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>250</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG21" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AH21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>200</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
         <v>15</v>
       </c>
-      <c r="Z21" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC21" t="n">
+      <c r="AQ21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS21" t="n">
         <v>8</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>42</v>
       </c>
       <c r="AT21" t="n">
         <v>6.8</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AV21" t="n">
-        <v>19</v>
+        <v>6.8</v>
       </c>
       <c r="AW21" t="n">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="AX21" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA21" t="n">
-        <v>38</v>
+        <v>7.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>18</v>
+        <v>9.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="BE21" t="n">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="BF21" t="n">
-        <v>15</v>
+        <v>5.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="G22" t="n">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="H22" t="n">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>5.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="K22" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M22" t="n">
         <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O22" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="R22" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="T22" t="n">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="U22" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="V22" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="W22" t="n">
-        <v>2.36</v>
+        <v>3.25</v>
       </c>
       <c r="X22" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>18.5</v>
+        <v>28</v>
       </c>
       <c r="Z22" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AB22" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AC22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AD22" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AE22" t="n">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="AF22" t="n">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AG22" t="n">
         <v>10</v>
       </c>
       <c r="AH22" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AI22" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="AJ22" t="n">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="AK22" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AL22" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>240</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD22" t="n">
         <v>36</v>
       </c>
-      <c r="AM22" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>65</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>32</v>
-      </c>
       <c r="BE22" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BF22" t="n">
-        <v>9.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BG22" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,378 +4817,2124 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Gremio</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>EC Vitoria Salvador</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F23" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q23" t="n">
         <v>1.91</v>
       </c>
-      <c r="G23" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="H23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K23" t="n">
-        <v>4</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="R23" t="n">
         <v>1.42</v>
       </c>
-      <c r="M23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.32</v>
-      </c>
       <c r="S23" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T23" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="V23" t="n">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="X23" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP23" t="n">
         <v>14.5</v>
       </c>
-      <c r="Y23" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z23" t="n">
+      <c r="AQ23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA23" t="n">
         <v>36</v>
       </c>
-      <c r="AA23" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ23" t="n">
+      <c r="BB23" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC23" t="n">
         <v>24</v>
       </c>
-      <c r="AK23" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB23" t="n">
+      <c r="BD23" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF23" t="n">
         <v>18</v>
       </c>
-      <c r="BC23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BG23" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="X24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>40</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-03-18 01:04:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="X25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>65</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-03-18 01:04:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Alianza FC Valledupar</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Jaguares de Cordoba</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-03-18 01:04:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-03-18 01:04:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Gremio</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>EC Vitoria Salvador</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-03-18 01:04:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Sportivo Trinidense</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Club Sportivo Ameliano</t>
         </is>
       </c>
-      <c r="F24" t="n">
+      <c r="F29" t="n">
         <v>0</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H29" t="n">
         <v>0</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I29" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J29" t="n">
         <v>0</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K29" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N24" t="n">
+      <c r="L29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N29" t="n">
         <v>1.02</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O29" t="n">
         <v>1.45</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P29" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R24" t="n">
+      <c r="Q29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R29" t="n">
         <v>1.18</v>
       </c>
-      <c r="S24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH24" t="inlineStr">
-        <is>
-          <t>2026-03-17 22:55:16</t>
+      <c r="S29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-03-18 01:04:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>20:20:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Fortaleza FC</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="H30" t="n">
+        <v>6</v>
+      </c>
+      <c r="I30" t="n">
+        <v>7</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="X30" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>250</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-03-18 01:04:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Emelec</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Independiente (Ecu)</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-03-18 01:04:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X32" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-03-18 01:04:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Ind Medellin</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Junior FC Barranquilla</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X33" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH33"/>
+  <dimension ref="A1:BH34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H2" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="I2" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K2" t="n">
-        <v>12.5</v>
+        <v>500</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>2.74</v>
       </c>
       <c r="U2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="V2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>3.1</v>
       </c>
-      <c r="W2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -957,19 +957,19 @@
         <v>2.14</v>
       </c>
       <c r="H3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I3" t="n">
         <v>4.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
@@ -981,7 +981,7 @@
         <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
         <v>1.89</v>
@@ -1023,7 +1023,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AE3" t="n">
         <v>48</v>
@@ -1068,7 +1068,7 @@
         <v>25</v>
       </c>
       <c r="AS3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT3" t="n">
         <v>9.199999999999999</v>
@@ -1080,7 +1080,7 @@
         <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX3" t="n">
         <v>12</v>
@@ -1092,7 +1092,7 @@
         <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BB3" t="n">
         <v>22</v>
@@ -1101,20 +1101,20 @@
         <v>19.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF3" t="n">
         <v>13</v>
       </c>
       <c r="BG3" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>23</v>
+      </c>
+      <c r="H4" t="n">
         <v>1.04</v>
       </c>
-      <c r="G4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.23</v>
-      </c>
       <c r="I4" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="J4" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ukrainian Premier League</t>
+          <t>Estonian Esiliiga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1330,73 +1330,73 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Metalist 1925</t>
+          <t>Viimsi JK</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P5" t="n">
         <v>1.24</v>
       </c>
-      <c r="H5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>34</v>
-      </c>
-      <c r="J5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="Q5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V5" t="n">
         <v>1.01</v>
       </c>
-      <c r="N5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.03</v>
-      </c>
       <c r="W5" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
         <v>1000</v>
@@ -1405,111 +1405,111 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,184 +1519,184 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Metalist 1925</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Genclerbirligi</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.82</v>
+        <v>1.16</v>
       </c>
       <c r="G6" t="n">
-        <v>1.89</v>
+        <v>1.24</v>
       </c>
       <c r="H6" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="I6" t="n">
-        <v>5.7</v>
+        <v>34</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="K6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>80</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BC6" t="n">
         <v>3.75</v>
       </c>
-      <c r="L6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="X6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>18</v>
-      </c>
       <c r="BD6" t="n">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kasimpasa</t>
+          <t>Genclerbirligi</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.35</v>
+        <v>1.81</v>
       </c>
       <c r="G7" t="n">
-        <v>1.39</v>
+        <v>1.9</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>5.4</v>
       </c>
       <c r="I7" t="n">
-        <v>12.5</v>
+        <v>5.7</v>
       </c>
       <c r="J7" t="n">
-        <v>5.7</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="L7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.29</v>
       </c>
-      <c r="M7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.54</v>
-      </c>
       <c r="S7" t="n">
-        <v>2.48</v>
+        <v>3.7</v>
       </c>
       <c r="T7" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="U7" t="n">
         <v>1.92</v>
       </c>
       <c r="V7" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="W7" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="X7" t="n">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="Y7" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z7" t="n">
         <v>42</v>
       </c>
-      <c r="Z7" t="n">
-        <v>110</v>
-      </c>
       <c r="AA7" t="n">
-        <v>400</v>
+        <v>160</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>13.5</v>
       </c>
-      <c r="AD7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>170</v>
-      </c>
-      <c r="AF7" t="n">
+      <c r="AR7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX7" t="n">
         <v>9</v>
       </c>
-      <c r="AG7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AR7" t="n">
+      <c r="AY7" t="n">
         <v>9</v>
       </c>
-      <c r="AS7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ7" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BB7" t="n">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="BD7" t="n">
-        <v>28</v>
+        <v>6.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="BG7" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,184 +1907,184 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Kasimpasa</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="G8" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="H8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" t="n">
+        <v>12</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X8" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>400</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>180</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG8" t="n">
         <v>10.5</v>
       </c>
-      <c r="I8" t="n">
-        <v>13</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X8" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>130</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>270</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>11</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI8" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="AJ8" t="n">
         <v>11.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM8" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="AN8" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP8" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="AR8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY8" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AS8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>7.6</v>
+        <v>22</v>
       </c>
       <c r="BA8" t="n">
         <v>9.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BC8" t="n">
         <v>12.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BE8" t="n">
         <v>9.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BG8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -2106,179 +2106,179 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>1.38</v>
       </c>
       <c r="G9" t="n">
-        <v>6.4</v>
+        <v>1.42</v>
       </c>
       <c r="H9" t="n">
-        <v>1.62</v>
+        <v>10.5</v>
       </c>
       <c r="I9" t="n">
-        <v>1.64</v>
+        <v>12.5</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="K9" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="P9" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="T9" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="U9" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="V9" t="n">
-        <v>2.56</v>
+        <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>1.19</v>
+        <v>3.35</v>
       </c>
       <c r="X9" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="Y9" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.800000000000001</v>
+        <v>130</v>
       </c>
       <c r="AA9" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>20</v>
+        <v>7.8</v>
       </c>
       <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>270</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>210</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR9" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>230</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>160</v>
-      </c>
-      <c r="AO9" t="n">
+      <c r="AS9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU9" t="n">
         <v>10</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AV9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC9" t="n">
         <v>14</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BD9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>9.6</v>
+        <v>5.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -2300,179 +2300,179 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Rakow Czestochowa</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.66</v>
+        <v>6.2</v>
       </c>
       <c r="G10" t="n">
-        <v>2.88</v>
+        <v>6.4</v>
       </c>
       <c r="H10" t="n">
-        <v>2.72</v>
+        <v>1.62</v>
       </c>
       <c r="I10" t="n">
-        <v>2.9</v>
+        <v>1.63</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
         <v>1.32</v>
       </c>
       <c r="P10" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="R10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="T10" t="n">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="U10" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="V10" t="n">
-        <v>1.52</v>
+        <v>2.6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.53</v>
+        <v>1.19</v>
       </c>
       <c r="X10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>230</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW10" t="n">
         <v>15</v>
       </c>
-      <c r="Y10" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV10" t="n">
+      <c r="AX10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC10" t="n">
         <v>11</v>
       </c>
-      <c r="AW10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY10" t="n">
+      <c r="BD10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF10" t="n">
         <v>10.5</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA10" t="n">
+      <c r="BG10" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>21</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Rakow Czestochowa</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>NK Celje</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.25</v>
+        <v>2.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1.31</v>
+        <v>2.86</v>
       </c>
       <c r="H11" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X11" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG11" t="n">
         <v>13</v>
       </c>
-      <c r="I11" t="n">
+      <c r="AH11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR11" t="n">
         <v>16</v>
       </c>
-      <c r="J11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="AS11" t="n">
         <v>7.6</v>
       </c>
-      <c r="L11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X11" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>160</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="AT11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY11" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>280</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA11" t="n">
         <v>7.6</v>
       </c>
-      <c r="AW11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BB11" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE11" t="n">
         <v>8.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.7</v>
+        <v>17.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.6</v>
+        <v>21</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>NK Celje</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.5</v>
+        <v>1.26</v>
       </c>
       <c r="G12" t="n">
-        <v>3.55</v>
+        <v>1.31</v>
       </c>
       <c r="H12" t="n">
-        <v>2.22</v>
+        <v>13</v>
       </c>
       <c r="I12" t="n">
-        <v>2.26</v>
+        <v>16</v>
       </c>
       <c r="J12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>160</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>260</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>190</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF12" t="n">
         <v>3.7</v>
       </c>
-      <c r="K12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X12" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>48</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>34</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>70</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>30</v>
-      </c>
       <c r="BG12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -2882,179 +2882,179 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.12</v>
+        <v>3.5</v>
       </c>
       <c r="G13" t="n">
-        <v>2.16</v>
+        <v>3.55</v>
       </c>
       <c r="H13" t="n">
-        <v>3.95</v>
+        <v>2.22</v>
       </c>
       <c r="I13" t="n">
-        <v>4.1</v>
+        <v>2.26</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K13" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="L13" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="M13" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="P13" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="U13" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.32</v>
+        <v>1.79</v>
       </c>
       <c r="W13" t="n">
-        <v>1.86</v>
+        <v>1.39</v>
       </c>
       <c r="X13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR13" t="n">
         <v>13</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AS13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT13" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC13" t="n">
+      <c r="AU13" t="n">
         <v>7.8</v>
       </c>
-      <c r="AD13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS13" t="n">
+      <c r="AV13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC13" t="n">
         <v>34</v>
       </c>
-      <c r="AT13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW13" t="n">
+      <c r="BD13" t="n">
         <v>40</v>
       </c>
-      <c r="AX13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>36</v>
-      </c>
       <c r="BE13" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="BF13" t="n">
-        <v>16.5</v>
+        <v>30</v>
       </c>
       <c r="BG13" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Genk</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.63</v>
+        <v>2.12</v>
       </c>
       <c r="G14" t="n">
-        <v>1.65</v>
+        <v>2.16</v>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>3.95</v>
       </c>
       <c r="I14" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="J14" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="L14" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="M14" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="O14" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.78</v>
+        <v>2.16</v>
       </c>
       <c r="R14" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="V14" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="W14" t="n">
-        <v>2.54</v>
+        <v>1.86</v>
       </c>
       <c r="X14" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN14" t="n">
         <v>18.5</v>
       </c>
-      <c r="Y14" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD14" t="n">
+      <c r="AO14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB14" t="n">
         <v>23</v>
       </c>
-      <c r="AE14" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AH14" t="n">
+      <c r="BC14" t="n">
         <v>21</v>
       </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP14" t="n">
+      <c r="BD14" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF14" t="n">
         <v>16.5</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>44</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>44</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>38</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BG14" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Genk</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5.2</v>
+        <v>1.63</v>
       </c>
       <c r="G15" t="n">
-        <v>8.199999999999999</v>
+        <v>1.65</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>1.99</v>
+        <v>6.4</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>1.02</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="P15" t="n">
-        <v>1.58</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="R15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V15" t="n">
         <v>1.19</v>
       </c>
-      <c r="S15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V15" t="n">
-        <v>2</v>
-      </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>2.54</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI15" t="n">
         <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,54 +3459,54 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Dinamo Bucharest</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Universitatea Craiova</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.78</v>
+        <v>5.2</v>
       </c>
       <c r="G16" t="n">
-        <v>3.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>2.64</v>
+        <v>1.6</v>
       </c>
       <c r="I16" t="n">
-        <v>3.05</v>
+        <v>1.97</v>
       </c>
       <c r="J16" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M16" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="O16" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="P16" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="R16" t="n">
         <v>1.21</v>
@@ -3515,37 +3515,37 @@
         <v>4.7</v>
       </c>
       <c r="T16" t="n">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="U16" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="W16" t="n">
-        <v>1.46</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Z16" t="n">
         <v>11</v>
       </c>
-      <c r="Y16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1000</v>
-      </c>
       <c r="AA16" t="n">
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
         <v>1000</v>
@@ -3581,69 +3581,69 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>8.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.2</v>
+        <v>13.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="AU16" t="n">
         <v>6.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>7</v>
+        <v>3.8</v>
       </c>
       <c r="AX16" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="AY16" t="n">
-        <v>11</v>
+        <v>3.9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>6</v>
+        <v>19.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC16" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Dinamo Bucharest</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tecnico Universitario</t>
+          <t>Universitatea Craiova</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.82</v>
+        <v>2.78</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="H17" t="n">
-        <v>4.8</v>
+        <v>2.64</v>
       </c>
       <c r="I17" t="n">
-        <v>6.6</v>
+        <v>3.05</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="K17" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="L17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W17" t="n">
         <v>1.46</v>
       </c>
-      <c r="M17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2</v>
-      </c>
       <c r="X17" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Y17" t="n">
-        <v>18</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z17" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.5</v>
+        <v>7.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>3.95</v>
+        <v>5.7</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU17" t="n">
         <v>6.2</v>
       </c>
-      <c r="AU17" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AV17" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="AX17" t="n">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ17" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>18</v>
+        <v>7.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="BD17" t="n">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="BF17" t="n">
-        <v>12</v>
+        <v>7.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,184 +3847,184 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Tecnico Universitario</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="G18" t="n">
-        <v>1.72</v>
+        <v>1.98</v>
       </c>
       <c r="H18" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="I18" t="n">
         <v>6.6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="L18" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="M18" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>3.65</v>
+        <v>2.98</v>
       </c>
       <c r="O18" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="P18" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="T18" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U18" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="V18" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="W18" t="n">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="X18" t="n">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="Y18" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="Z18" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AA18" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AE18" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG18" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI18" t="n">
         <v>110</v>
       </c>
       <c r="AJ18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN18" t="n">
         <v>21</v>
       </c>
-      <c r="AK18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>13</v>
-      </c>
       <c r="AO18" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AT18" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AU18" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AX18" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AY18" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="BC18" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BD18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE18" t="n">
         <v>4.2</v>
       </c>
-      <c r="BE18" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BF18" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -4046,179 +4046,179 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Shakhtar</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.12</v>
+        <v>1.63</v>
       </c>
       <c r="G19" t="n">
-        <v>2.18</v>
+        <v>1.71</v>
       </c>
       <c r="H19" t="n">
-        <v>3.65</v>
+        <v>5.7</v>
       </c>
       <c r="I19" t="n">
-        <v>3.9</v>
+        <v>6.6</v>
       </c>
       <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N19" t="n">
         <v>3.7</v>
       </c>
-      <c r="K19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.2</v>
-      </c>
       <c r="O19" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="T19" t="n">
-        <v>1.68</v>
+        <v>1.97</v>
       </c>
       <c r="U19" t="n">
-        <v>2.28</v>
+        <v>1.9</v>
       </c>
       <c r="V19" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="W19" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="X19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>210</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV19" t="n">
         <v>20</v>
       </c>
-      <c r="Y19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC19" t="n">
+      <c r="AW19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX19" t="n">
         <v>8.6</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AY19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC19" t="n">
         <v>16</v>
       </c>
-      <c r="AE19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA19" t="n">
+      <c r="BD19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF19" t="n">
         <v>9.6</v>
       </c>
-      <c r="BB19" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BG19" t="n">
-        <v>9.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sparta Prague</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Az Alkmaar</t>
+          <t>Lech Poznan</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="G20" t="n">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="H20" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="I20" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="J20" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K20" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L20" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P20" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="Q20" t="n">
         <v>1.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="T20" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="U20" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="V20" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W20" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="X20" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX20" t="n">
         <v>12.5</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AY20" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9.4</v>
       </c>
       <c r="AZ20" t="n">
         <v>14.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.1</v>
+        <v>21</v>
       </c>
       <c r="BC20" t="n">
-        <v>4</v>
+        <v>18.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.1</v>
+        <v>9.4</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -4434,186 +4434,186 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Sparta Prague</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Az Alkmaar</t>
         </is>
       </c>
       <c r="F21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R21" t="n">
         <v>1.39</v>
       </c>
-      <c r="G21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="H21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="I21" t="n">
-        <v>11</v>
-      </c>
-      <c r="J21" t="n">
-        <v>5</v>
-      </c>
-      <c r="K21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N21" t="n">
-        <v>4</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.4</v>
-      </c>
       <c r="S21" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="T21" t="n">
-        <v>2.18</v>
+        <v>1.72</v>
       </c>
       <c r="U21" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.1</v>
+        <v>1.38</v>
       </c>
       <c r="W21" t="n">
-        <v>3.3</v>
+        <v>1.72</v>
       </c>
       <c r="X21" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Y21" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA21" t="n">
-        <v>570</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>42</v>
+        <v>17.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>250</v>
+        <v>48</v>
       </c>
       <c r="AF21" t="n">
-        <v>8.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="AG21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV21" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH21" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AW21" t="n">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="AX21" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="AY21" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.8</v>
+        <v>4.5</v>
       </c>
       <c r="BB21" t="n">
-        <v>9.4</v>
+        <v>4.3</v>
       </c>
       <c r="BC21" t="n">
-        <v>13.5</v>
+        <v>4.2</v>
       </c>
       <c r="BD21" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>8</v>
+        <v>4.7</v>
       </c>
       <c r="BF21" t="n">
-        <v>5.6</v>
+        <v>12.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,179 +4628,179 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="G22" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="H22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="J22" t="n">
         <v>5</v>
       </c>
       <c r="K22" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M22" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="T22" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U22" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="V22" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="W22" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="X22" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="Y22" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Z22" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>360</v>
+        <v>570</v>
       </c>
       <c r="AB22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>250</v>
+      </c>
+      <c r="AF22" t="n">
         <v>8</v>
       </c>
-      <c r="AC22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>170</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AG22" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AI22" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="AJ22" t="n">
         <v>11.5</v>
       </c>
       <c r="AK22" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN22" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AO22" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
         <v>15</v>
       </c>
       <c r="AQ22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AR22" t="n">
-        <v>34</v>
+        <v>8.4</v>
       </c>
       <c r="AS22" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU22" t="n">
         <v>10</v>
       </c>
       <c r="AV22" t="n">
-        <v>30</v>
+        <v>7.4</v>
       </c>
       <c r="AW22" t="n">
-        <v>44</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX22" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BA22" t="n">
-        <v>42</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB22" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>36</v>
+        <v>7.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>46</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF22" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -4822,31 +4822,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.54</v>
+        <v>1.43</v>
       </c>
       <c r="G23" t="n">
-        <v>2.58</v>
+        <v>1.44</v>
       </c>
       <c r="H23" t="n">
-        <v>2.96</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>9.6</v>
       </c>
       <c r="J23" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="K23" t="n">
-        <v>3.75</v>
+        <v>5.1</v>
       </c>
       <c r="L23" t="n">
         <v>1.38</v>
@@ -4861,140 +4861,140 @@
         <v>1.29</v>
       </c>
       <c r="P23" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="R23" t="n">
         <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T23" t="n">
-        <v>1.72</v>
+        <v>2.14</v>
       </c>
       <c r="U23" t="n">
-        <v>2.32</v>
+        <v>1.83</v>
       </c>
       <c r="V23" t="n">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="W23" t="n">
-        <v>1.63</v>
+        <v>3.25</v>
       </c>
       <c r="X23" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="Z23" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="AA23" t="n">
+        <v>360</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>240</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG23" t="n">
         <v>48</v>
       </c>
-      <c r="AB23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>34</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>22</v>
-      </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -5016,25 +5016,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.87</v>
+        <v>2.54</v>
       </c>
       <c r="G24" t="n">
-        <v>1.88</v>
+        <v>2.58</v>
       </c>
       <c r="H24" t="n">
-        <v>5.1</v>
+        <v>2.94</v>
       </c>
       <c r="I24" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
         <v>3.65</v>
@@ -5043,152 +5043,152 @@
         <v>3.75</v>
       </c>
       <c r="L24" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="M24" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="O24" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="P24" t="n">
-        <v>1.74</v>
+        <v>2.08</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="R24" t="n">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="S24" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="T24" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="U24" t="n">
-        <v>1.85</v>
+        <v>2.32</v>
       </c>
       <c r="V24" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="W24" t="n">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="X24" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="Y24" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z24" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="AA24" t="n">
-        <v>140</v>
+        <v>48</v>
       </c>
       <c r="AB24" t="n">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="AC24" t="n">
         <v>8</v>
       </c>
       <c r="AD24" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="AF24" t="n">
-        <v>9.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="AG24" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AH24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC24" t="n">
         <v>24</v>
       </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK24" t="n">
+      <c r="BD24" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG24" t="n">
         <v>22</v>
       </c>
-      <c r="AL24" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>46</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>40</v>
-      </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -5210,139 +5210,139 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="G25" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="H25" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I25" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="J25" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="K25" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="L25" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="M25" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="S25" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="T25" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="U25" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="V25" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W25" t="n">
-        <v>2.36</v>
+        <v>2.12</v>
       </c>
       <c r="X25" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="Z25" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB25" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE25" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF25" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AG25" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AK25" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AL25" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO25" t="n">
         <v>120</v>
       </c>
-      <c r="AN25" t="n">
+      <c r="AP25" t="n">
         <v>10.5</v>
       </c>
-      <c r="AO25" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP25" t="n">
+      <c r="AQ25" t="n">
         <v>14</v>
       </c>
-      <c r="AQ25" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AR25" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AS25" t="n">
         <v>42</v>
       </c>
       <c r="AT25" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AU25" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV25" t="n">
         <v>19</v>
@@ -5351,45 +5351,45 @@
         <v>34</v>
       </c>
       <c r="AX25" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BA25" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BB25" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BD25" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BE25" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BF25" t="n">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="BG25" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="G26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P26" t="n">
         <v>2</v>
       </c>
-      <c r="H26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I26" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.55</v>
-      </c>
       <c r="Q26" t="n">
-        <v>2.46</v>
+        <v>1.95</v>
       </c>
       <c r="R26" t="n">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="T26" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="U26" t="n">
-        <v>1.69</v>
+        <v>1.99</v>
       </c>
       <c r="V26" t="n">
         <v>1.21</v>
       </c>
       <c r="W26" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="X26" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA26" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF26" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AD26" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE26" t="n">
+      <c r="AG26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM26" t="n">
         <v>120</v>
       </c>
-      <c r="AF26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>270</v>
-      </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT26" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AQ26" t="n">
+      <c r="AU26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF26" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AR26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>16</v>
-      </c>
       <c r="BG26" t="n">
-        <v>4.8</v>
+        <v>65</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Alianza FC Valledupar</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="G27" t="n">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="I27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS27" t="n">
         <v>4.9</v>
       </c>
-      <c r="J27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S27" t="n">
+      <c r="AT27" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY27" t="n">
         <v>3.5</v>
       </c>
-      <c r="T27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AZ27" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Gremio</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>EC Vitoria Salvador</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="H28" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I28" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J28" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="K28" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="L28" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="M28" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="O28" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="P28" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T28" t="n">
         <v>1.87</v>
       </c>
-      <c r="Q28" t="n">
-        <v>2</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.82</v>
-      </c>
       <c r="U28" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="V28" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W28" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="X28" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y28" t="n">
         <v>16</v>
       </c>
       <c r="Z28" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA28" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC28" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AC28" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AD28" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AE28" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG28" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG28" t="n">
-        <v>11</v>
-      </c>
       <c r="AH28" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI28" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AK28" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AL28" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AM28" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN28" t="n">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="AO28" t="n">
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT28" t="n">
         <v>7.2</v>
       </c>
-      <c r="AS28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AU28" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV28" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW28" t="n">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
       <c r="AX28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY28" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ28" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA28" t="n">
-        <v>50</v>
+        <v>4.9</v>
       </c>
       <c r="BB28" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BC28" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="BD28" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="BE28" t="n">
-        <v>8.4</v>
+        <v>5</v>
       </c>
       <c r="BF28" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Gremio</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>EC Vitoria Salvador</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M29" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>1.02</v>
+        <v>3.5</v>
       </c>
       <c r="O29" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="P29" t="n">
-        <v>1.24</v>
+        <v>1.89</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="R29" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="T29" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="U29" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,120 +6175,120 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fortaleza FC</t>
+          <t>Club Sportivo Ameliano</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N30" t="n">
-        <v>2.98</v>
+        <v>1.02</v>
       </c>
       <c r="O30" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="P30" t="n">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="R30" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="T30" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="U30" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="V30" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD30" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE30" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH30" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
         <v>1000</v>
@@ -6297,69 +6297,69 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR30" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU30" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV30" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW30" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AX30" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AY30" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA30" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BB30" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC30" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD30" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BE30" t="n">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="BF30" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG30" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,39 +6369,39 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>Fortaleza FC</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.7</v>
+        <v>1.69</v>
       </c>
       <c r="G31" t="n">
-        <v>4.7</v>
+        <v>1.78</v>
       </c>
       <c r="H31" t="n">
-        <v>2.12</v>
+        <v>6</v>
       </c>
       <c r="I31" t="n">
-        <v>2.32</v>
+        <v>7</v>
       </c>
       <c r="J31" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="K31" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M31" t="n">
         <v>1.09</v>
@@ -6410,150 +6410,150 @@
         <v>3.05</v>
       </c>
       <c r="O31" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P31" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="R31" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S31" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="T31" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="U31" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="V31" t="n">
-        <v>1.77</v>
+        <v>1.17</v>
       </c>
       <c r="W31" t="n">
-        <v>1.31</v>
+        <v>2.28</v>
       </c>
       <c r="X31" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y31" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW31" t="n">
         <v>10</v>
       </c>
-      <c r="Z31" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>110</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>85</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AQ31" t="n">
+      <c r="AX31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB31" t="n">
         <v>6.8</v>
       </c>
-      <c r="AR31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BC31" t="n">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.1</v>
+        <v>9</v>
       </c>
       <c r="BE31" t="n">
-        <v>4.1</v>
+        <v>2.76</v>
       </c>
       <c r="BF31" t="n">
-        <v>4.1</v>
+        <v>11.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>16.5</v>
+        <v>2.04</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,78 +6563,78 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Independiente (Ecu)</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="G32" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="H32" t="n">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="I32" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="J32" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K32" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="L32" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="M32" t="n">
         <v>1.09</v>
       </c>
       <c r="N32" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="O32" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="P32" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="R32" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S32" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="T32" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="U32" t="n">
         <v>1.92</v>
       </c>
       <c r="V32" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="W32" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="X32" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="Z32" t="n">
         <v>16</v>
@@ -6643,111 +6643,111 @@
         <v>36</v>
       </c>
       <c r="AB32" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AC32" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD32" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AF32" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AG32" t="n">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="AH32" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI32" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AJ32" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK32" t="n">
         <v>70</v>
       </c>
-      <c r="AK32" t="n">
-        <v>50</v>
-      </c>
       <c r="AL32" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AM32" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AN32" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AO32" t="n">
         <v>28</v>
       </c>
       <c r="AP32" t="n">
-        <v>9.6</v>
+        <v>3.25</v>
       </c>
       <c r="AQ32" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR32" t="n">
-        <v>12.5</v>
+        <v>3.4</v>
       </c>
       <c r="AS32" t="n">
-        <v>25</v>
+        <v>3.85</v>
       </c>
       <c r="AT32" t="n">
-        <v>9.800000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="AU32" t="n">
         <v>6.6</v>
       </c>
       <c r="AV32" t="n">
-        <v>10.5</v>
+        <v>3.25</v>
       </c>
       <c r="AW32" t="n">
-        <v>25</v>
+        <v>3.8</v>
       </c>
       <c r="AX32" t="n">
-        <v>19</v>
+        <v>3.8</v>
       </c>
       <c r="AY32" t="n">
-        <v>13</v>
+        <v>3.55</v>
       </c>
       <c r="AZ32" t="n">
-        <v>18</v>
+        <v>3.65</v>
       </c>
       <c r="BA32" t="n">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="BB32" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="BC32" t="n">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="BD32" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="BE32" t="n">
-        <v>7.8</v>
+        <v>4.1</v>
       </c>
       <c r="BF32" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="BG32" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,184 +6757,378 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.04</v>
+        <v>3.45</v>
       </c>
       <c r="G33" t="n">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="H33" t="n">
-        <v>3.8</v>
+        <v>2.34</v>
       </c>
       <c r="I33" t="n">
-        <v>4.7</v>
+        <v>2.44</v>
       </c>
       <c r="J33" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K33" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="L33" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="M33" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N33" t="n">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="O33" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="P33" t="n">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.83</v>
+        <v>2.28</v>
       </c>
       <c r="R33" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S33" t="n">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="T33" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="U33" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="V33" t="n">
-        <v>1.31</v>
+        <v>1.69</v>
       </c>
       <c r="W33" t="n">
-        <v>1.86</v>
+        <v>1.37</v>
       </c>
       <c r="X33" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Y33" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="Z33" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="AA33" t="n">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="AB33" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD33" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="AF33" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AG33" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AH33" t="n">
         <v>23</v>
       </c>
       <c r="AI33" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-03-18 03:13:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Ind Medellin</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Junior FC Barranquilla</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="X34" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI34" t="n">
         <v>75</v>
       </c>
-      <c r="AJ33" t="n">
+      <c r="AJ34" t="n">
         <v>32</v>
       </c>
-      <c r="AK33" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM33" t="n">
+      <c r="AK34" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM34" t="n">
         <v>130</v>
       </c>
-      <c r="AN33" t="n">
+      <c r="AN34" t="n">
         <v>20</v>
       </c>
-      <c r="AO33" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP33" t="n">
+      <c r="AO34" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AQ34" t="n">
         <v>3.45</v>
       </c>
-      <c r="AQ33" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AR33" t="n">
+      <c r="AR34" t="n">
         <v>3.9</v>
       </c>
-      <c r="AS33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT33" t="n">
+      <c r="AS34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT34" t="n">
         <v>3.1</v>
       </c>
-      <c r="AU33" t="n">
+      <c r="AU34" t="n">
         <v>3</v>
       </c>
-      <c r="AV33" t="n">
+      <c r="AV34" t="n">
         <v>3.6</v>
       </c>
-      <c r="AW33" t="n">
+      <c r="AW34" t="n">
         <v>4</v>
       </c>
-      <c r="AX33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY33" t="n">
+      <c r="AX34" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AY34" t="n">
         <v>3.25</v>
       </c>
-      <c r="AZ33" t="n">
+      <c r="AZ34" t="n">
         <v>3.65</v>
       </c>
-      <c r="BA33" t="n">
+      <c r="BA34" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE34" t="n">
         <v>4.1</v>
       </c>
-      <c r="BB33" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF33" t="n">
+      <c r="BF34" t="n">
         <v>11.5</v>
       </c>
-      <c r="BG33" t="n">
+      <c r="BG34" t="n">
         <v>4.1</v>
       </c>
-      <c r="BH33" t="inlineStr">
-        <is>
-          <t>2026-03-18 01:04:20</t>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH34"/>
+  <dimension ref="A1:BH36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,46 +766,46 @@
         <v>1.24</v>
       </c>
       <c r="I2" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="J2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K2" t="n">
         <v>500</v>
       </c>
       <c r="L2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O2" t="n">
         <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="Q2" t="n">
         <v>1.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S2" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="U2" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="V2" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="W2" t="n">
         <v>1.04</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AU2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV2" t="n">
         <v>4.1</v>
       </c>
-      <c r="AV2" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AW2" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.97</v>
+        <v>1.42</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
@@ -954,10 +954,10 @@
         <v>2.08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
         <v>4.1</v>
@@ -1002,7 +1002,7 @@
         <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X3" t="n">
         <v>15</v>
@@ -1029,7 +1029,7 @@
         <v>48</v>
       </c>
       <c r="AF3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG3" t="n">
         <v>10.5</v>
@@ -1065,7 +1065,7 @@
         <v>13</v>
       </c>
       <c r="AR3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS3" t="n">
         <v>11</v>
@@ -1077,7 +1077,7 @@
         <v>7.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW3" t="n">
         <v>34</v>
@@ -1110,18 +1110,18 @@
         <v>13</v>
       </c>
       <c r="BG3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Azerbaijan Premier League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:15:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>FC Sabah</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>FK Sumqayit</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>1.27</v>
       </c>
       <c r="G4" t="n">
-        <v>23</v>
+        <v>1.66</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="I4" t="n">
-        <v>1.32</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>6.2</v>
+        <v>3.85</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>13</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Estonian Esiliiga</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1330,186 +1330,186 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Viimsi JK</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>1.29</v>
       </c>
       <c r="J5" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ukrainian Premier League</t>
+          <t>Estonian Esiliiga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,73 +1524,73 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Metalist 1925</t>
+          <t>Viimsi JK</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>1.24</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="O6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="R6" t="n">
         <v>1.18</v>
       </c>
-      <c r="P6" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.57</v>
-      </c>
       <c r="S6" t="n">
-        <v>2.18</v>
+        <v>1.09</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.53</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1599,111 +1599,111 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,184 +1713,184 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Metalist 1925</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Genclerbirligi</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.81</v>
+        <v>1.16</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9</v>
+        <v>1.24</v>
       </c>
       <c r="H7" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="I7" t="n">
-        <v>5.7</v>
+        <v>34</v>
       </c>
       <c r="J7" t="n">
-        <v>3.45</v>
+        <v>6.8</v>
       </c>
       <c r="K7" t="n">
-        <v>3.85</v>
+        <v>9.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="P7" t="n">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.06</v>
+        <v>1.53</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="S7" t="n">
-        <v>3.7</v>
+        <v>2.18</v>
       </c>
       <c r="T7" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.92</v>
+        <v>1.53</v>
       </c>
       <c r="V7" t="n">
-        <v>1.21</v>
+        <v>1.03</v>
       </c>
       <c r="W7" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>14.5</v>
+        <v>34</v>
       </c>
       <c r="Y7" t="n">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="Z7" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.4</v>
+        <v>24</v>
       </c>
       <c r="AD7" t="n">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="AE7" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="AI7" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22</v>
+        <v>9.6</v>
       </c>
       <c r="AK7" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AL7" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="AM7" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>15.5</v>
+        <v>4.4</v>
       </c>
       <c r="AO7" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>11</v>
+        <v>4.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13.5</v>
+        <v>4.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>32</v>
+        <v>4.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.8</v>
+        <v>3.25</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>3.9</v>
       </c>
       <c r="AV7" t="n">
-        <v>18</v>
+        <v>4.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AY7" t="n">
-        <v>9</v>
+        <v>3.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>18</v>
+        <v>4.3</v>
       </c>
       <c r="BA7" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>17.5</v>
+        <v>3.1</v>
       </c>
       <c r="BC7" t="n">
-        <v>18</v>
+        <v>3.75</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kasimpasa</t>
+          <t>Genclerbirligi</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.35</v>
+        <v>1.81</v>
       </c>
       <c r="G8" t="n">
-        <v>1.39</v>
+        <v>1.88</v>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>5.4</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>5.7</v>
       </c>
       <c r="J8" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="L8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R8" t="n">
         <v>1.29</v>
       </c>
-      <c r="M8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.54</v>
-      </c>
       <c r="S8" t="n">
-        <v>2.48</v>
+        <v>3.7</v>
       </c>
       <c r="T8" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="U8" t="n">
         <v>1.92</v>
       </c>
       <c r="V8" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="W8" t="n">
-        <v>3.6</v>
+        <v>2.12</v>
       </c>
       <c r="X8" t="n">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="Z8" t="n">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="AA8" t="n">
-        <v>400</v>
+        <v>160</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC8" t="n">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="AE8" t="n">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="AF8" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="AJ8" t="n">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="AK8" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="AL8" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AM8" t="n">
         <v>150</v>
       </c>
       <c r="AN8" t="n">
-        <v>5.8</v>
+        <v>15.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="AP8" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AQ8" t="n">
-        <v>34</v>
+        <v>13.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>9.4</v>
+        <v>32</v>
       </c>
       <c r="AS8" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="AT8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX8" t="n">
         <v>9</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="AY8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF8" t="n">
         <v>11</v>
       </c>
-      <c r="AV8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BG8" t="n">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Kasimpasa</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="G9" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="H9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n">
+        <v>12</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X9" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>400</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>180</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG9" t="n">
         <v>10.5</v>
       </c>
-      <c r="I9" t="n">
+      <c r="AH9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>190</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC9" t="n">
         <v>12.5</v>
       </c>
-      <c r="J9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N9" t="n">
-        <v>4</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="X9" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>130</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>270</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>210</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU9" t="n">
+      <c r="BD9" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE9" t="n">
         <v>10</v>
       </c>
-      <c r="AV9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BF9" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.7</v>
+        <v>10</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Genk</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6.2</v>
+        <v>1.63</v>
       </c>
       <c r="G10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" t="n">
         <v>6.4</v>
       </c>
-      <c r="H10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.63</v>
-      </c>
       <c r="J10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K10" t="n">
         <v>4.5</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N10" t="n">
         <v>4.6</v>
       </c>
-      <c r="L10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.8</v>
-      </c>
       <c r="O10" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="P10" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.02</v>
+        <v>1.79</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="S10" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="T10" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="U10" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
-        <v>2.6</v>
+        <v>1.18</v>
       </c>
       <c r="W10" t="n">
-        <v>1.19</v>
+        <v>2.54</v>
       </c>
       <c r="X10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP10" t="n">
         <v>16.5</v>
       </c>
-      <c r="Y10" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z10" t="n">
+      <c r="AQ10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT10" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AA10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>230</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>160</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AU10" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.6</v>
+        <v>21</v>
       </c>
       <c r="AW10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC10" t="n">
         <v>15</v>
       </c>
-      <c r="AX10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>11</v>
-      </c>
       <c r="BD10" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="BE10" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="BF10" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.4</v>
+        <v>36</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Rakow Czestochowa</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.7</v>
+        <v>2.12</v>
       </c>
       <c r="G11" t="n">
-        <v>2.86</v>
+        <v>2.16</v>
       </c>
       <c r="H11" t="n">
-        <v>2.72</v>
+        <v>3.95</v>
       </c>
       <c r="I11" t="n">
-        <v>2.92</v>
+        <v>4.1</v>
       </c>
       <c r="J11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N11" t="n">
         <v>3.45</v>
       </c>
-      <c r="K11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.75</v>
-      </c>
       <c r="O11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.32</v>
       </c>
-      <c r="P11" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.36</v>
-      </c>
       <c r="S11" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="U11" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="V11" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="W11" t="n">
-        <v>1.54</v>
+        <v>1.86</v>
       </c>
       <c r="X11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="AA11" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="AB11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF11" t="n">
         <v>12.5</v>
       </c>
-      <c r="AC11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AG11" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AK11" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AL11" t="n">
         <v>42</v>
       </c>
       <c r="AM11" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN11" t="n">
-        <v>26</v>
+        <v>18.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="AP11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="AT11" t="n">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AU11" t="n">
         <v>7.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.2</v>
+        <v>40</v>
       </c>
       <c r="AX11" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.6</v>
+        <v>46</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="BC11" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.4</v>
+        <v>40</v>
       </c>
       <c r="BF11" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>NK Celje</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.26</v>
+        <v>3.45</v>
       </c>
       <c r="G12" t="n">
-        <v>1.31</v>
+        <v>3.55</v>
       </c>
       <c r="H12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR12" t="n">
         <v>13</v>
       </c>
-      <c r="I12" t="n">
-        <v>16</v>
-      </c>
-      <c r="J12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X12" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>160</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>260</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>190</v>
-      </c>
-      <c r="AJ12" t="n">
+      <c r="AS12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV12" t="n">
         <v>10</v>
       </c>
-      <c r="AK12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP12" t="n">
+      <c r="AW12" t="n">
         <v>20</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AX12" t="n">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="AY12" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>7.2</v>
+        <v>15.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.199999999999999</v>
+        <v>44</v>
       </c>
       <c r="BC12" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.6</v>
+        <v>40</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.800000000000001</v>
+        <v>70</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.7</v>
+        <v>30</v>
       </c>
       <c r="BG12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.5</v>
+        <v>1.39</v>
       </c>
       <c r="G13" t="n">
-        <v>3.55</v>
+        <v>1.42</v>
       </c>
       <c r="H13" t="n">
-        <v>2.22</v>
+        <v>10.5</v>
       </c>
       <c r="I13" t="n">
-        <v>2.26</v>
+        <v>12.5</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
         <v>1.29</v>
       </c>
       <c r="P13" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T13" t="n">
-        <v>1.73</v>
+        <v>2.22</v>
       </c>
       <c r="U13" t="n">
-        <v>2.3</v>
+        <v>1.71</v>
       </c>
       <c r="V13" t="n">
-        <v>1.79</v>
+        <v>1.09</v>
       </c>
       <c r="W13" t="n">
-        <v>1.39</v>
+        <v>3.35</v>
       </c>
       <c r="X13" t="n">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="Y13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>130</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>270</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG13" t="n">
         <v>11</v>
       </c>
-      <c r="Z13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AH13" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="AJ13" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="AN13" t="n">
-        <v>34</v>
+        <v>6.8</v>
       </c>
       <c r="AO13" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU13" t="n">
         <v>10</v>
       </c>
-      <c r="AR13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AV13" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AW13" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AX13" t="n">
-        <v>23</v>
+        <v>6.8</v>
       </c>
       <c r="AY13" t="n">
-        <v>13.5</v>
+        <v>9.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15.5</v>
+        <v>8.4</v>
       </c>
       <c r="BA13" t="n">
-        <v>30</v>
+        <v>10.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>50</v>
+        <v>9.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="BD13" t="n">
-        <v>40</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE13" t="n">
-        <v>70</v>
+        <v>10.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="BG13" t="n">
-        <v>14</v>
+        <v>5.7</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Rakow Czestochowa</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.12</v>
+        <v>2.7</v>
       </c>
       <c r="G14" t="n">
-        <v>2.16</v>
+        <v>2.84</v>
       </c>
       <c r="H14" t="n">
-        <v>3.95</v>
+        <v>2.74</v>
       </c>
       <c r="I14" t="n">
-        <v>4.1</v>
+        <v>2.86</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K14" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="M14" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="O14" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="P14" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="R14" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="U14" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="V14" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="W14" t="n">
-        <v>1.86</v>
+        <v>1.54</v>
       </c>
       <c r="X14" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG14" t="n">
         <v>13</v>
       </c>
-      <c r="Y14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AH14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI14" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AJ14" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AK14" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AL14" t="n">
         <v>42</v>
       </c>
       <c r="AM14" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN14" t="n">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="AO14" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="AP14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR14" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AS14" t="n">
-        <v>34</v>
+        <v>7.8</v>
       </c>
       <c r="AT14" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU14" t="n">
         <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>40</v>
+        <v>7.2</v>
       </c>
       <c r="AX14" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF14" t="n">
         <v>17.5</v>
       </c>
-      <c r="BA14" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC14" t="n">
+      <c r="BG14" t="n">
         <v>21</v>
       </c>
-      <c r="BD14" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>40</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>30</v>
-      </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Genk</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I15" t="n">
         <v>1.63</v>
       </c>
-      <c r="G15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="H15" t="n">
-        <v>6</v>
-      </c>
-      <c r="I15" t="n">
-        <v>6.4</v>
-      </c>
       <c r="J15" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L15" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.79</v>
+        <v>2.02</v>
       </c>
       <c r="R15" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="T15" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="U15" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="V15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W15" t="n">
         <v>1.19</v>
       </c>
-      <c r="W15" t="n">
-        <v>2.54</v>
-      </c>
       <c r="X15" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="Z15" t="n">
-        <v>50</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>230</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM15" t="n">
         <v>170</v>
       </c>
-      <c r="AB15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC15" t="n">
+      <c r="AN15" t="n">
+        <v>160</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV15" t="n">
         <v>9.6</v>
       </c>
-      <c r="AD15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AH15" t="n">
+      <c r="AW15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY15" t="n">
         <v>21</v>
       </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>44</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>44</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV15" t="n">
+      <c r="AZ15" t="n">
         <v>21</v>
       </c>
-      <c r="AW15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BA15" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BB15" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BC15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BD15" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="BE15" t="n">
-        <v>38</v>
+        <v>12.5</v>
       </c>
       <c r="BF15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG15" t="n">
         <v>7.4</v>
       </c>
-      <c r="BG15" t="n">
-        <v>36</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>NK Celje</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>5.2</v>
+        <v>1.28</v>
       </c>
       <c r="G16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>13</v>
+      </c>
+      <c r="I16" t="n">
+        <v>15</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>250</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V16" t="n">
-        <v>2</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X16" t="n">
+      <c r="BA16" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC16" t="n">
         <v>12</v>
       </c>
-      <c r="Y16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC16" t="n">
+      <c r="BD16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE16" t="n">
         <v>10</v>
       </c>
-      <c r="AD16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW16" t="n">
+      <c r="BF16" t="n">
         <v>3.8</v>
       </c>
-      <c r="AX16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BG16" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,54 +3653,54 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Dinamo Bucharest</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Universitatea Craiova</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.78</v>
+        <v>5.3</v>
       </c>
       <c r="G17" t="n">
-        <v>3.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>2.64</v>
+        <v>1.6</v>
       </c>
       <c r="I17" t="n">
-        <v>3.05</v>
+        <v>1.96</v>
       </c>
       <c r="J17" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K17" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="L17" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="M17" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="O17" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="P17" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="R17" t="n">
         <v>1.21</v>
@@ -3709,37 +3709,37 @@
         <v>4.7</v>
       </c>
       <c r="T17" t="n">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="U17" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5</v>
+        <v>2.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.46</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Z17" t="n">
         <v>11</v>
       </c>
-      <c r="Y17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1000</v>
-      </c>
       <c r="AA17" t="n">
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
@@ -3775,69 +3775,69 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>8.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.2</v>
+        <v>13.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="AU17" t="n">
         <v>6.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="AW17" t="n">
-        <v>7</v>
+        <v>3.8</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="AY17" t="n">
-        <v>11</v>
+        <v>3.9</v>
       </c>
       <c r="AZ17" t="n">
-        <v>6</v>
+        <v>19.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC17" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Dinamo Bucharest</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tecnico Universitario</t>
+          <t>Universitatea Craiova</t>
         </is>
       </c>
       <c r="F18" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U18" t="n">
         <v>1.83</v>
       </c>
-      <c r="G18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="H18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L18" t="n">
+      <c r="V18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.46</v>
       </c>
-      <c r="M18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.02</v>
-      </c>
       <c r="X18" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Y18" t="n">
-        <v>18</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z18" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12.5</v>
+        <v>7.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU18" t="n">
         <v>6.2</v>
       </c>
-      <c r="AU18" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AV18" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AX18" t="n">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="AY18" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ18" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB18" t="n">
-        <v>18</v>
+        <v>7.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="BD18" t="n">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="BF18" t="n">
-        <v>12.5</v>
+        <v>7.2</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,184 +4041,184 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Tecnico Universitario</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="G19" t="n">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="H19" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="I19" t="n">
         <v>6.6</v>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="L19" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="M19" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="P19" t="n">
-        <v>1.94</v>
+        <v>1.68</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="R19" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="U19" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="V19" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="W19" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="X19" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y19" t="n">
         <v>18.5</v>
       </c>
-      <c r="Y19" t="n">
-        <v>23</v>
-      </c>
       <c r="Z19" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AA19" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="AB19" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH19" t="n">
         <v>28</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>27</v>
       </c>
       <c r="AI19" t="n">
         <v>110</v>
       </c>
       <c r="AJ19" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AK19" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AL19" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AM19" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AN19" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AO19" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="AT19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU19" t="n">
         <v>7</v>
       </c>
-      <c r="AU19" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AV19" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="AX19" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AY19" t="n">
         <v>9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BB19" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="BC19" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BF19" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Shakhtar</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.16</v>
+        <v>1.68</v>
       </c>
       <c r="G20" t="n">
-        <v>2.18</v>
+        <v>1.73</v>
       </c>
       <c r="H20" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N20" t="n">
         <v>3.7</v>
       </c>
-      <c r="I20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4.2</v>
-      </c>
       <c r="O20" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="P20" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="T20" t="n">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="U20" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="V20" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="W20" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="X20" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>210</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>19.5</v>
       </c>
-      <c r="Y20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD20" t="n">
+      <c r="BA20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC20" t="n">
         <v>16</v>
       </c>
-      <c r="AE20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BD20" t="n">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="BE20" t="n">
-        <v>10.5</v>
+        <v>5.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG20" t="n">
-        <v>9.4</v>
+        <v>5.4</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
@@ -4434,70 +4434,70 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sparta Prague</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Az Alkmaar</t>
+          <t>Lech Poznan</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="G21" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="H21" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="I21" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="J21" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="K21" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M21" t="n">
         <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O21" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R21" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="S21" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="U21" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V21" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W21" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="X21" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y21" t="n">
         <v>17</v>
@@ -4506,107 +4506,107 @@
         <v>30</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB21" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD21" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE21" t="n">
         <v>48</v>
       </c>
       <c r="AF21" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ21" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AK21" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="AL21" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AM21" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AN21" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.9</v>
+        <v>15</v>
       </c>
       <c r="AQ21" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="AT21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.4</v>
+        <v>11</v>
       </c>
       <c r="AX21" t="n">
         <v>12</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.3</v>
+        <v>21</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.2</v>
+        <v>18</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.4</v>
+        <v>28</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.7</v>
+        <v>12</v>
       </c>
       <c r="BF21" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.3</v>
+        <v>32</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Sparta Prague</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Az Alkmaar</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.38</v>
+        <v>2.24</v>
       </c>
       <c r="G22" t="n">
-        <v>1.42</v>
+        <v>2.38</v>
       </c>
       <c r="H22" t="n">
-        <v>9.800000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="I22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X22" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
         <v>12.5</v>
       </c>
-      <c r="J22" t="n">
-        <v>5</v>
-      </c>
-      <c r="K22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W22" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="X22" t="n">
+      <c r="AC22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH22" t="n">
         <v>21</v>
       </c>
-      <c r="Y22" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>570</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>42</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>250</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG22" t="n">
+      <c r="AI22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV22" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH22" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AW22" t="n">
-        <v>8.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="AX22" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="AY22" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>8.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>9.4</v>
+        <v>4.3</v>
       </c>
       <c r="BC22" t="n">
-        <v>13.5</v>
+        <v>4.2</v>
       </c>
       <c r="BD22" t="n">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="BF22" t="n">
-        <v>5.6</v>
+        <v>12.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>9</v>
+        <v>4.3</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,179 +4822,179 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="G23" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="H23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="J23" t="n">
         <v>5</v>
       </c>
       <c r="K23" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="L23" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M23" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P23" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="T23" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="U23" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="V23" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="W23" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="X23" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="Y23" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Z23" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>360</v>
+        <v>570</v>
       </c>
       <c r="AB23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>250</v>
+      </c>
+      <c r="AF23" t="n">
         <v>8</v>
       </c>
-      <c r="AC23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>170</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AG23" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AI23" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="AJ23" t="n">
         <v>11.5</v>
       </c>
       <c r="AK23" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL23" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN23" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AO23" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ23" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>34</v>
+        <v>8.4</v>
       </c>
       <c r="AS23" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="AT23" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU23" t="n">
         <v>10</v>
       </c>
       <c r="AV23" t="n">
-        <v>30</v>
+        <v>7.4</v>
       </c>
       <c r="AW23" t="n">
-        <v>44</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX23" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ23" t="n">
         <v>25</v>
       </c>
       <c r="BA23" t="n">
-        <v>42</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB23" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BC23" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>36</v>
+        <v>7.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>46</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF23" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BG23" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
@@ -5016,31 +5016,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.54</v>
+        <v>1.43</v>
       </c>
       <c r="G24" t="n">
-        <v>2.58</v>
+        <v>1.45</v>
       </c>
       <c r="H24" t="n">
-        <v>2.94</v>
+        <v>9.4</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>9.6</v>
       </c>
       <c r="J24" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>3.75</v>
+        <v>5.1</v>
       </c>
       <c r="L24" t="n">
         <v>1.38</v>
@@ -5049,7 +5049,7 @@
         <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O24" t="n">
         <v>1.29</v>
@@ -5058,137 +5058,137 @@
         <v>2.08</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="R24" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T24" t="n">
-        <v>1.72</v>
+        <v>2.14</v>
       </c>
       <c r="U24" t="n">
-        <v>2.32</v>
+        <v>1.81</v>
       </c>
       <c r="V24" t="n">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="W24" t="n">
-        <v>1.62</v>
+        <v>3.25</v>
       </c>
       <c r="X24" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="Z24" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="AA24" t="n">
+        <v>360</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>240</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG24" t="n">
         <v>48</v>
       </c>
-      <c r="AB24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>34</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>22</v>
-      </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
@@ -5210,25 +5210,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.86</v>
+        <v>2.56</v>
       </c>
       <c r="G25" t="n">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
       <c r="H25" t="n">
-        <v>5.1</v>
+        <v>2.94</v>
       </c>
       <c r="I25" t="n">
-        <v>5.3</v>
+        <v>2.98</v>
       </c>
       <c r="J25" t="n">
         <v>3.65</v>
@@ -5237,152 +5237,152 @@
         <v>3.75</v>
       </c>
       <c r="L25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V25" t="n">
         <v>1.5</v>
       </c>
-      <c r="M25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.23</v>
-      </c>
       <c r="W25" t="n">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="X25" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="Y25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z25" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="AA25" t="n">
-        <v>140</v>
+        <v>46</v>
       </c>
       <c r="AB25" t="n">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="AC25" t="n">
         <v>8</v>
       </c>
       <c r="AD25" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="AF25" t="n">
-        <v>9.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="AG25" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AH25" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ25" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="AK25" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AL25" t="n">
         <v>46</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN25" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="AP25" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AQ25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB25" t="n">
         <v>32</v>
       </c>
-      <c r="AS25" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW25" t="n">
+      <c r="BC25" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE25" t="n">
         <v>34</v>
       </c>
-      <c r="AX25" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ25" t="n">
+      <c r="BF25" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG25" t="n">
         <v>22</v>
       </c>
-      <c r="BA25" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>46</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>40</v>
-      </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
@@ -5404,139 +5404,139 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="G26" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="H26" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I26" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="J26" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="K26" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="L26" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="M26" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="O26" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="R26" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="S26" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="U26" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="V26" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W26" t="n">
-        <v>2.36</v>
+        <v>2.12</v>
       </c>
       <c r="X26" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="Z26" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB26" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE26" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF26" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AG26" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI26" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AK26" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AL26" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO26" t="n">
         <v>120</v>
       </c>
-      <c r="AN26" t="n">
+      <c r="AP26" t="n">
         <v>10.5</v>
       </c>
-      <c r="AO26" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP26" t="n">
+      <c r="AQ26" t="n">
         <v>14</v>
       </c>
-      <c r="AQ26" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AR26" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AS26" t="n">
         <v>42</v>
       </c>
       <c r="AT26" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AU26" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV26" t="n">
         <v>19</v>
@@ -5545,45 +5545,45 @@
         <v>34</v>
       </c>
       <c r="AX26" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ26" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BA26" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BB26" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BD26" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BE26" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BF26" t="n">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="BG26" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="G27" t="n">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="H27" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="I27" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="J27" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="K27" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="L27" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="M27" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="N27" t="n">
-        <v>2.68</v>
+        <v>3.95</v>
       </c>
       <c r="O27" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="P27" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.48</v>
+        <v>1.96</v>
       </c>
       <c r="R27" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="T27" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="U27" t="n">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="V27" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W27" t="n">
-        <v>2.02</v>
+        <v>2.36</v>
       </c>
       <c r="X27" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA27" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="AB27" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF27" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AD27" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE27" t="n">
+      <c r="AG27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM27" t="n">
         <v>120</v>
       </c>
-      <c r="AF27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>270</v>
-      </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP27" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="AQ27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF27" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AR27" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>16</v>
-      </c>
       <c r="BG27" t="n">
-        <v>4.9</v>
+        <v>75</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Platense FC</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>CD Motagua</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="G28" t="n">
-        <v>2.16</v>
+        <v>1000</v>
       </c>
       <c r="H28" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="K28" t="n">
-        <v>3.75</v>
+        <v>950</v>
       </c>
       <c r="L28" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>3.2</v>
+        <v>1.25</v>
       </c>
       <c r="O28" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="P28" t="n">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.1</v>
+        <v>1.32</v>
       </c>
       <c r="R28" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>3.55</v>
+        <v>1.32</v>
       </c>
       <c r="T28" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="U28" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="X28" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z28" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD28" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE28" t="n">
         <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG28" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH28" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI28" t="n">
         <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK28" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR28" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS28" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AT28" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV28" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX28" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB28" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BC28" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE28" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BF28" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Gremio</t>
+          <t>Alianza FC Valledupar</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>EC Vitoria Salvador</t>
+          <t>Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="G29" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W29" t="n">
         <v>2.02</v>
       </c>
-      <c r="H29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I29" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K29" t="n">
-        <v>4</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.98</v>
-      </c>
       <c r="X29" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y29" t="n">
         <v>16</v>
       </c>
       <c r="Z29" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="AB29" t="n">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD29" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="AE29" t="n">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="AF29" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ29" t="n">
         <v>11</v>
       </c>
-      <c r="AH29" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>13</v>
-      </c>
       <c r="AR29" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="AS29" t="n">
-        <v>8.6</v>
+        <v>5.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU29" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV29" t="n">
-        <v>15.5</v>
+        <v>4.6</v>
       </c>
       <c r="AW29" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="AX29" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY29" t="n">
-        <v>9.199999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="AZ29" t="n">
-        <v>16.5</v>
+        <v>4.8</v>
       </c>
       <c r="BA29" t="n">
-        <v>50</v>
+        <v>5.4</v>
       </c>
       <c r="BB29" t="n">
-        <v>18</v>
+        <v>4.6</v>
       </c>
       <c r="BC29" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="BD29" t="n">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>8.6</v>
+        <v>5.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="BG29" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,191 +6175,191 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M30" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="N30" t="n">
-        <v>1.02</v>
+        <v>3.2</v>
       </c>
       <c r="O30" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="P30" t="n">
-        <v>1.24</v>
+        <v>1.76</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="R30" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S30" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="T30" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U30" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE30" t="n">
         <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI30" t="n">
         <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO30" t="n">
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,191 +6369,191 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Gremio</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fortaleza FC</t>
+          <t>EC Vitoria Salvador</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.69</v>
+        <v>1.91</v>
       </c>
       <c r="G31" t="n">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="H31" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="I31" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="J31" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K31" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L31" t="n">
         <v>1.42</v>
       </c>
       <c r="M31" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="O31" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="P31" t="n">
-        <v>1.69</v>
+        <v>1.89</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.26</v>
+        <v>1.91</v>
       </c>
       <c r="R31" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="T31" t="n">
-        <v>2.12</v>
+        <v>1.82</v>
       </c>
       <c r="U31" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="V31" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="W31" t="n">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="X31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF31" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y31" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>240</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE31" t="n">
+      <c r="AG31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM31" t="n">
         <v>130</v>
       </c>
-      <c r="AF31" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>220</v>
-      </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>5.9</v>
+        <v>12</v>
       </c>
       <c r="AQ31" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="AR31" t="n">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.76</v>
+        <v>8.6</v>
       </c>
       <c r="AT31" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="AU31" t="n">
         <v>7.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>7.8</v>
+        <v>15.5</v>
       </c>
       <c r="AW31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX31" t="n">
         <v>10</v>
       </c>
-      <c r="AX31" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AY31" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ31" t="n">
-        <v>7.8</v>
+        <v>16.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="BB31" t="n">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="BC31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD31" t="n">
         <v>7.4</v>
       </c>
-      <c r="BD31" t="n">
-        <v>9</v>
-      </c>
       <c r="BE31" t="n">
-        <v>2.76</v>
+        <v>8.6</v>
       </c>
       <c r="BF31" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>2.04</v>
+        <v>8</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,191 +6563,191 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>Club Sportivo Ameliano</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N32" t="n">
-        <v>3.05</v>
+        <v>1.02</v>
       </c>
       <c r="O32" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="P32" t="n">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="R32" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="T32" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U32" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Z32" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA32" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE32" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AG32" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AH32" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI32" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM32" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR32" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS32" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AT32" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV32" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AW32" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX32" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY32" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BA32" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BB32" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BC32" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF32" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG32" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,54 +6757,54 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Fortaleza FC</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.45</v>
+        <v>1.69</v>
       </c>
       <c r="G33" t="n">
-        <v>3.75</v>
+        <v>1.78</v>
       </c>
       <c r="H33" t="n">
-        <v>2.34</v>
+        <v>6</v>
       </c>
       <c r="I33" t="n">
-        <v>2.44</v>
+        <v>7</v>
       </c>
       <c r="J33" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="K33" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="L33" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="M33" t="n">
         <v>1.09</v>
       </c>
       <c r="N33" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="O33" t="n">
         <v>1.43</v>
       </c>
       <c r="P33" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R33" t="n">
         <v>1.25</v>
@@ -6813,135 +6813,135 @@
         <v>4.4</v>
       </c>
       <c r="T33" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="U33" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="V33" t="n">
-        <v>1.69</v>
+        <v>1.17</v>
       </c>
       <c r="W33" t="n">
-        <v>1.37</v>
+        <v>2.28</v>
       </c>
       <c r="X33" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="Z33" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="AA33" t="n">
-        <v>36</v>
+        <v>240</v>
       </c>
       <c r="AB33" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BF33" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC33" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BG33" t="n">
-        <v>21</v>
+        <v>2.04</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-18 03:13:28</t>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6951,156 +6951,156 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ind Medellin</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>Independiente (Ecu)</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="G34" t="n">
-        <v>2.22</v>
+        <v>4.2</v>
       </c>
       <c r="H34" t="n">
-        <v>3.85</v>
+        <v>2.14</v>
       </c>
       <c r="I34" t="n">
-        <v>4.6</v>
+        <v>2.32</v>
       </c>
       <c r="J34" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K34" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="L34" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M34" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N34" t="n">
         <v>3.05</v>
       </c>
       <c r="O34" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="P34" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="R34" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="S34" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="T34" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="U34" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="V34" t="n">
-        <v>1.31</v>
+        <v>1.76</v>
       </c>
       <c r="W34" t="n">
-        <v>1.85</v>
+        <v>1.28</v>
       </c>
       <c r="X34" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="Z34" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="AA34" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ34" t="n">
         <v>110</v>
       </c>
-      <c r="AB34" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>32</v>
-      </c>
       <c r="AK34" t="n">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="AL34" t="n">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="AM34" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AN34" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="AO34" t="n">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="AP34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR34" t="n">
         <v>3.4</v>
       </c>
-      <c r="AQ34" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AS34" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AU34" t="n">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="AV34" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AW34" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AX34" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="AY34" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="AZ34" t="n">
         <v>3.65</v>
@@ -7109,26 +7109,414 @@
         <v>4</v>
       </c>
       <c r="BB34" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BC34" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BE34" t="n">
         <v>4.1</v>
       </c>
       <c r="BF34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-03-18 05:22:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X35" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB35" t="n">
         <v>11.5</v>
       </c>
-      <c r="BG34" t="n">
+      <c r="AC35" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>55</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>44</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-03-18 05:22:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Ind Medellin</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Junior FC Barranquilla</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X36" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AS36" t="n">
         <v>4.1</v>
       </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>2026-03-18 03:13:28</t>
+      <c r="AT36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-03-18 05:22:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
@@ -760,22 +760,22 @@
         <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="I2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K2" t="n">
         <v>500</v>
       </c>
       <c r="L2" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
@@ -784,7 +784,7 @@
         <v>3.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
         <v>1.92</v>
@@ -799,7 +799,7 @@
         <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="U2" t="n">
         <v>1.47</v>
@@ -808,7 +808,7 @@
         <v>4.1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AT2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB2" t="n">
         <v>5.3</v>
       </c>
-      <c r="AU2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BC2" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.42</v>
+        <v>1.91</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>2.08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -963,7 +963,7 @@
         <v>4.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K3" t="n">
         <v>3.7</v>
@@ -972,37 +972,37 @@
         <v>1.4</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O3" t="n">
         <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="R3" t="n">
         <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T3" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="U3" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V3" t="n">
         <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="X3" t="n">
         <v>15</v>
@@ -1017,7 +1017,7 @@
         <v>80</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC3" t="n">
         <v>8.199999999999999</v>
@@ -1041,7 +1041,7 @@
         <v>55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK3" t="n">
         <v>22</v>
@@ -1050,16 +1050,16 @@
         <v>36</v>
       </c>
       <c r="AM3" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AN3" t="n">
         <v>15.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AP3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>13</v>
@@ -1068,10 +1068,10 @@
         <v>26</v>
       </c>
       <c r="AS3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU3" t="n">
         <v>7.4</v>
@@ -1080,7 +1080,7 @@
         <v>14.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="AX3" t="n">
         <v>12</v>
@@ -1092,7 +1092,7 @@
         <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB3" t="n">
         <v>22</v>
@@ -1104,17 +1104,17 @@
         <v>32</v>
       </c>
       <c r="BE3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF3" t="n">
         <v>13</v>
       </c>
       <c r="BG3" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -1145,64 +1145,64 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="G4" t="n">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
       <c r="H4" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K4" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="P4" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>1.58</v>
+        <v>2.6</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W4" t="n">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z4" t="n">
         <v>1000</v>
@@ -1211,104 +1211,104 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE4" t="n">
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>2.98</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>13.5</v>
       </c>
       <c r="G5" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="H5" t="n">
         <v>1.25</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>1.24</v>
       </c>
       <c r="H7" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
         <v>34</v>
@@ -1745,7 +1745,7 @@
         <v>9.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
         <v>1.02</v>
@@ -1760,7 +1760,7 @@
         <v>2.26</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="R7" t="n">
         <v>1.57</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G8" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="H8" t="n">
         <v>5.4</v>
@@ -1933,7 +1933,7 @@
         <v>5.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
         <v>3.8</v>
@@ -1945,7 +1945,7 @@
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O8" t="n">
         <v>1.36</v>
@@ -1972,97 +1972,97 @@
         <v>1.21</v>
       </c>
       <c r="W8" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X8" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y8" t="n">
         <v>17</v>
       </c>
       <c r="Z8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA8" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC8" t="n">
         <v>8.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE8" t="n">
         <v>85</v>
       </c>
       <c r="AF8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH8" t="n">
         <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AJ8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK8" t="n">
         <v>22</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>23</v>
       </c>
       <c r="AL8" t="n">
         <v>44</v>
       </c>
       <c r="AM8" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AN8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO8" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP8" t="n">
         <v>11</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR8" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT8" t="n">
         <v>6.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AX8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY8" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BB8" t="n">
         <v>17.5</v>
@@ -2071,20 +2071,20 @@
         <v>18</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.6</v>
+        <v>34</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -2121,13 +2121,13 @@
         <v>1.39</v>
       </c>
       <c r="H9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I9" t="n">
         <v>12</v>
       </c>
       <c r="J9" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="K9" t="n">
         <v>5.9</v>
@@ -2145,7 +2145,7 @@
         <v>1.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="Q9" t="n">
         <v>1.6</v>
@@ -2157,40 +2157,40 @@
         <v>2.48</v>
       </c>
       <c r="T9" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U9" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="V9" t="n">
         <v>1.09</v>
       </c>
       <c r="W9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="X9" t="n">
         <v>24</v>
       </c>
       <c r="Y9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Z9" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AA9" t="n">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="AB9" t="n">
         <v>10</v>
       </c>
       <c r="AC9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AE9" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="AF9" t="n">
         <v>9</v>
@@ -2214,25 +2214,25 @@
         <v>34</v>
       </c>
       <c r="AM9" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AO9" t="n">
         <v>190</v>
       </c>
       <c r="AP9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AR9" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AS9" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT9" t="n">
         <v>9</v>
@@ -2244,7 +2244,7 @@
         <v>32</v>
       </c>
       <c r="AW9" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AX9" t="n">
         <v>7.8</v>
@@ -2256,7 +2256,7 @@
         <v>22</v>
       </c>
       <c r="BA9" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BB9" t="n">
         <v>10</v>
@@ -2268,17 +2268,17 @@
         <v>28</v>
       </c>
       <c r="BE9" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -2339,10 +2339,10 @@
         <v>1.26</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R10" t="n">
         <v>1.47</v>
@@ -2360,10 +2360,10 @@
         <v>1.18</v>
       </c>
       <c r="W10" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="X10" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y10" t="n">
         <v>22</v>
@@ -2375,7 +2375,7 @@
         <v>170</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC10" t="n">
         <v>9.6</v>
@@ -2411,7 +2411,7 @@
         <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO10" t="n">
         <v>85</v>
@@ -2441,7 +2441,7 @@
         <v>50</v>
       </c>
       <c r="AX10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY10" t="n">
         <v>9.199999999999999</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>2.12</v>
       </c>
       <c r="G11" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H11" t="n">
         <v>3.95</v>
@@ -2527,7 +2527,7 @@
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
         <v>1.38</v>
@@ -2539,7 +2539,7 @@
         <v>2.16</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -2548,13 +2548,13 @@
         <v>1.9</v>
       </c>
       <c r="U11" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
         <v>1.32</v>
       </c>
       <c r="W11" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X11" t="n">
         <v>13</v>
@@ -2575,7 +2575,7 @@
         <v>7.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE11" t="n">
         <v>55</v>
@@ -2623,7 +2623,7 @@
         <v>34</v>
       </c>
       <c r="AT11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU11" t="n">
         <v>7.2</v>
@@ -2632,7 +2632,7 @@
         <v>15</v>
       </c>
       <c r="AW11" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX11" t="n">
         <v>11.5</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -2700,10 +2700,10 @@
         <v>3.45</v>
       </c>
       <c r="G12" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H12" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I12" t="n">
         <v>2.26</v>
@@ -2715,7 +2715,7 @@
         <v>3.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
@@ -2727,7 +2727,7 @@
         <v>1.29</v>
       </c>
       <c r="P12" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
         <v>1.87</v>
@@ -2736,19 +2736,19 @@
         <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
         <v>1.73</v>
       </c>
       <c r="U12" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V12" t="n">
         <v>1.79</v>
       </c>
       <c r="W12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X12" t="n">
         <v>15.5</v>
@@ -2766,28 +2766,28 @@
         <v>14.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD12" t="n">
         <v>10.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF12" t="n">
         <v>25</v>
       </c>
       <c r="AG12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI12" t="n">
         <v>34</v>
       </c>
       <c r="AJ12" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK12" t="n">
         <v>38</v>
@@ -2811,16 +2811,16 @@
         <v>10</v>
       </c>
       <c r="AR12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS12" t="n">
         <v>26</v>
       </c>
       <c r="AT12" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV12" t="n">
         <v>10</v>
@@ -2829,7 +2829,7 @@
         <v>20</v>
       </c>
       <c r="AX12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY12" t="n">
         <v>13.5</v>
@@ -2841,7 +2841,7 @@
         <v>30</v>
       </c>
       <c r="BB12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BC12" t="n">
         <v>34</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>10.5</v>
       </c>
       <c r="I13" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J13" t="n">
         <v>4.9</v>
@@ -2924,13 +2924,13 @@
         <v>2.02</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="R13" t="n">
         <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T13" t="n">
         <v>2.22</v>
@@ -2939,13 +2939,13 @@
         <v>1.71</v>
       </c>
       <c r="V13" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W13" t="n">
         <v>3.35</v>
       </c>
       <c r="X13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="n">
         <v>1000</v>
@@ -2954,13 +2954,13 @@
         <v>130</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>620</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD13" t="n">
         <v>1000</v>
@@ -2969,19 +2969,19 @@
         <v>270</v>
       </c>
       <c r="AF13" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH13" t="n">
         <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AK13" t="n">
         <v>1000</v>
@@ -2990,10 +2990,10 @@
         <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AN13" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
@@ -3002,25 +3002,25 @@
         <v>14.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>8.4</v>
+        <v>4.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>10.5</v>
+        <v>4.9</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="AT13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU13" t="n">
         <v>10</v>
       </c>
       <c r="AV13" t="n">
-        <v>30</v>
+        <v>4.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AX13" t="n">
         <v>6.8</v>
@@ -3029,32 +3029,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>8.4</v>
+        <v>4.4</v>
       </c>
       <c r="BA13" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC13" t="n">
         <v>14</v>
       </c>
       <c r="BD13" t="n">
-        <v>9.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="BF13" t="n">
         <v>6</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
         <v>2.74</v>
       </c>
       <c r="I14" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="J14" t="n">
         <v>3.45</v>
@@ -3118,10 +3118,10 @@
         <v>1.96</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="R14" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
         <v>3.35</v>
@@ -3130,7 +3130,7 @@
         <v>1.74</v>
       </c>
       <c r="U14" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V14" t="n">
         <v>1.53</v>
@@ -3142,7 +3142,7 @@
         <v>15</v>
       </c>
       <c r="Y14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z14" t="n">
         <v>19.5</v>
@@ -3151,31 +3151,31 @@
         <v>46</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD14" t="n">
         <v>13.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF14" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG14" t="n">
         <v>13</v>
       </c>
       <c r="AH14" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AI14" t="n">
         <v>44</v>
       </c>
       <c r="AJ14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK14" t="n">
         <v>32</v>
@@ -3196,16 +3196,16 @@
         <v>13</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU14" t="n">
         <v>7.2</v>
@@ -3214,10 +3214,10 @@
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="AX14" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY14" t="n">
         <v>10.5</v>
@@ -3226,29 +3226,29 @@
         <v>14.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BC14" t="n">
         <v>24</v>
       </c>
       <c r="BD14" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG14" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="G15" t="n">
         <v>6.4</v>
@@ -3288,7 +3288,7 @@
         <v>1.62</v>
       </c>
       <c r="I15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="J15" t="n">
         <v>4.5</v>
@@ -3303,31 +3303,31 @@
         <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="O15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P15" t="n">
         <v>1.93</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U15" t="n">
         <v>1.88</v>
       </c>
       <c r="V15" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="W15" t="n">
         <v>1.19</v>
@@ -3339,7 +3339,7 @@
         <v>8</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AA15" t="n">
         <v>15.5</v>
@@ -3360,13 +3360,13 @@
         <v>55</v>
       </c>
       <c r="AG15" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AH15" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AI15" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AJ15" t="n">
         <v>230</v>
@@ -3378,16 +3378,16 @@
         <v>110</v>
       </c>
       <c r="AM15" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN15" t="n">
         <v>160</v>
       </c>
       <c r="AO15" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AP15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ15" t="n">
         <v>7.2</v>
@@ -3396,7 +3396,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AS15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AT15" t="n">
         <v>17</v>
@@ -3408,10 +3408,10 @@
         <v>9.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AY15" t="n">
         <v>21</v>
@@ -3423,26 +3423,26 @@
         <v>29</v>
       </c>
       <c r="BB15" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD15" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE15" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -3473,37 +3473,37 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="H16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I16" t="n">
         <v>15</v>
       </c>
       <c r="J16" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="K16" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="L16" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M16" t="n">
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O16" t="n">
         <v>1.19</v>
       </c>
       <c r="P16" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
         <v>1.59</v>
@@ -3515,22 +3515,22 @@
         <v>2.4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V16" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W16" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="X16" t="n">
         <v>32</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="Z16" t="n">
         <v>150</v>
@@ -3539,34 +3539,34 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE16" t="n">
         <v>250</v>
       </c>
       <c r="AF16" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG16" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AI16" t="n">
         <v>180</v>
       </c>
       <c r="AJ16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AL16" t="n">
         <v>1000</v>
@@ -3575,22 +3575,22 @@
         <v>200</v>
       </c>
       <c r="AN16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="AR16" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="AT16" t="n">
         <v>9</v>
@@ -3599,22 +3599,22 @@
         <v>13</v>
       </c>
       <c r="AV16" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="AW16" t="n">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="AX16" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY16" t="n">
         <v>10</v>
       </c>
       <c r="AZ16" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BA16" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="BB16" t="n">
         <v>8.6</v>
@@ -3623,20 +3623,20 @@
         <v>12</v>
       </c>
       <c r="BD16" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BG16" t="n">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="G17" t="n">
         <v>8.199999999999999</v>
@@ -3676,7 +3676,7 @@
         <v>1.6</v>
       </c>
       <c r="I17" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="J17" t="n">
         <v>3.35</v>
@@ -3706,7 +3706,7 @@
         <v>1.21</v>
       </c>
       <c r="S17" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
         <v>2.16</v>
@@ -3715,10 +3715,10 @@
         <v>1.67</v>
       </c>
       <c r="V17" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
         <v>12</v>
@@ -3730,10 +3730,10 @@
         <v>11</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AB17" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AC17" t="n">
         <v>10</v>
@@ -3742,7 +3742,7 @@
         <v>13</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF17" t="n">
         <v>1000</v>
@@ -3772,28 +3772,28 @@
         <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP17" t="n">
-        <v>3.2</v>
+        <v>8.6</v>
       </c>
       <c r="AQ17" t="n">
         <v>5.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>6.8</v>
+        <v>3.15</v>
       </c>
       <c r="AS17" t="n">
-        <v>13.5</v>
+        <v>3.7</v>
       </c>
       <c r="AT17" t="n">
         <v>11.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AV17" t="n">
-        <v>7.8</v>
+        <v>3.3</v>
       </c>
       <c r="AW17" t="n">
         <v>3.8</v>
@@ -3802,10 +3802,10 @@
         <v>4.1</v>
       </c>
       <c r="AY17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>3.9</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>19.5</v>
       </c>
       <c r="BA17" t="n">
         <v>4.1</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -3867,13 +3867,13 @@
         <v>3.2</v>
       </c>
       <c r="H18" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J18" t="n">
         <v>3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.05</v>
       </c>
       <c r="K18" t="n">
         <v>3.45</v>
@@ -3891,7 +3891,7 @@
         <v>1.49</v>
       </c>
       <c r="P18" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q18" t="n">
         <v>2.4</v>
@@ -3903,16 +3903,16 @@
         <v>4.7</v>
       </c>
       <c r="T18" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U18" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="V18" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W18" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X18" t="n">
         <v>11</v>
@@ -3933,7 +3933,7 @@
         <v>7.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE18" t="n">
         <v>1000</v>
@@ -3942,7 +3942,7 @@
         <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH18" t="n">
         <v>1000</v>
@@ -3972,13 +3972,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS18" t="n">
         <v>7.4</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>7.2</v>
       </c>
       <c r="AT18" t="n">
         <v>7.8</v>
@@ -3987,34 +3987,34 @@
         <v>6.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW18" t="n">
         <v>7</v>
       </c>
       <c r="AX18" t="n">
-        <v>5.8</v>
+        <v>15.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB18" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BC18" t="n">
         <v>7.2</v>
       </c>
-      <c r="BC18" t="n">
-        <v>7</v>
-      </c>
       <c r="BD18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF18" t="n">
         <v>7.2</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -4058,13 +4058,13 @@
         <v>1.83</v>
       </c>
       <c r="G19" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="H19" t="n">
         <v>4.8</v>
       </c>
       <c r="I19" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="J19" t="n">
         <v>3.3</v>
@@ -4115,7 +4115,7 @@
         <v>18.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AA19" t="n">
         <v>180</v>
@@ -4136,7 +4136,7 @@
         <v>13</v>
       </c>
       <c r="AG19" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH19" t="n">
         <v>28</v>
@@ -4169,10 +4169,10 @@
         <v>12.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT19" t="n">
         <v>6.2</v>
@@ -4184,7 +4184,7 @@
         <v>17.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AX19" t="n">
         <v>9</v>
@@ -4196,7 +4196,7 @@
         <v>19</v>
       </c>
       <c r="BA19" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BB19" t="n">
         <v>18</v>
@@ -4205,20 +4205,20 @@
         <v>19</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF19" t="n">
         <v>12</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="G20" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H20" t="n">
         <v>5.9</v>
@@ -4273,85 +4273,85 @@
         <v>1.07</v>
       </c>
       <c r="N20" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O20" t="n">
         <v>1.33</v>
       </c>
       <c r="P20" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q20" t="n">
         <v>1.97</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T20" t="n">
         <v>1.96</v>
       </c>
       <c r="U20" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V20" t="n">
         <v>1.18</v>
       </c>
       <c r="W20" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X20" t="n">
         <v>18</v>
       </c>
       <c r="Y20" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AA20" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AB20" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AE20" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF20" t="n">
         <v>11</v>
       </c>
       <c r="AG20" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI20" t="n">
         <v>110</v>
       </c>
       <c r="AJ20" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AK20" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM20" t="n">
         <v>160</v>
       </c>
       <c r="AN20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO20" t="n">
         <v>150</v>
@@ -4360,37 +4360,37 @@
         <v>13</v>
       </c>
       <c r="AQ20" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR20" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT20" t="n">
         <v>7.2</v>
       </c>
       <c r="AU20" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV20" t="n">
         <v>20</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX20" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ20" t="n">
         <v>19.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB20" t="n">
         <v>14.5</v>
@@ -4399,20 +4399,20 @@
         <v>16</v>
       </c>
       <c r="BD20" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="BF20" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG20" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G21" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H21" t="n">
         <v>3.85</v>
       </c>
       <c r="I21" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="J21" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K21" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L21" t="n">
         <v>1.38</v>
@@ -4476,40 +4476,40 @@
         <v>2.12</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="R21" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T21" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U21" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V21" t="n">
         <v>1.33</v>
       </c>
       <c r="W21" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="X21" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Y21" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z21" t="n">
         <v>30</v>
       </c>
       <c r="AA21" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AC21" t="n">
         <v>8.800000000000001</v>
@@ -4518,7 +4518,7 @@
         <v>16.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AF21" t="n">
         <v>13.5</v>
@@ -4527,7 +4527,7 @@
         <v>10.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI21" t="n">
         <v>50</v>
@@ -4536,7 +4536,7 @@
         <v>25</v>
       </c>
       <c r="AK21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL21" t="n">
         <v>32</v>
@@ -4551,16 +4551,16 @@
         <v>40</v>
       </c>
       <c r="AP21" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>9.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="AS21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AT21" t="n">
         <v>9.800000000000001</v>
@@ -4572,19 +4572,19 @@
         <v>14.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX21" t="n">
         <v>12</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ21" t="n">
         <v>15</v>
       </c>
       <c r="BA21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB21" t="n">
         <v>21</v>
@@ -4596,17 +4596,17 @@
         <v>28</v>
       </c>
       <c r="BE21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF21" t="n">
         <v>11.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -4640,10 +4640,10 @@
         <v>2.24</v>
       </c>
       <c r="G22" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H22" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I22" t="n">
         <v>3.5</v>
@@ -4652,7 +4652,7 @@
         <v>3.55</v>
       </c>
       <c r="K22" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L22" t="n">
         <v>1.4</v>
@@ -4670,16 +4670,16 @@
         <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R22" t="n">
         <v>1.39</v>
       </c>
       <c r="S22" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U22" t="n">
         <v>2.2</v>
@@ -4688,7 +4688,7 @@
         <v>1.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X22" t="n">
         <v>19</v>
@@ -4703,10 +4703,10 @@
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD22" t="n">
         <v>17.5</v>
@@ -4727,7 +4727,7 @@
         <v>60</v>
       </c>
       <c r="AJ22" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK22" t="n">
         <v>29</v>
@@ -4742,65 +4742,65 @@
         <v>21</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP22" t="n">
-        <v>3.9</v>
+        <v>13.5</v>
       </c>
       <c r="AQ22" t="n">
         <v>12</v>
       </c>
       <c r="AR22" t="n">
-        <v>4.2</v>
+        <v>18</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AT22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU22" t="n">
         <v>7.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AX22" t="n">
         <v>12</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ22" t="n">
         <v>14.5</v>
       </c>
       <c r="BA22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE22" t="n">
         <v>4.5</v>
       </c>
-      <c r="BB22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BF22" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.3</v>
+        <v>25</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -4831,13 +4831,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="G23" t="n">
         <v>1.42</v>
       </c>
       <c r="H23" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I23" t="n">
         <v>12</v>
@@ -4852,7 +4852,7 @@
         <v>1.39</v>
       </c>
       <c r="M23" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N23" t="n">
         <v>4</v>
@@ -4861,22 +4861,22 @@
         <v>1.27</v>
       </c>
       <c r="P23" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="R23" t="n">
         <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="T23" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="V23" t="n">
         <v>1.09</v>
@@ -4894,10 +4894,10 @@
         <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>570</v>
+        <v>590</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC23" t="n">
         <v>12.5</v>
@@ -4906,10 +4906,10 @@
         <v>42</v>
       </c>
       <c r="AE23" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AF23" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AG23" t="n">
         <v>11.5</v>
@@ -4921,10 +4921,10 @@
         <v>200</v>
       </c>
       <c r="AJ23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AK23" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AL23" t="n">
         <v>1000</v>
@@ -4939,40 +4939,40 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ23" t="n">
         <v>19.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS23" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AT23" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU23" t="n">
         <v>10</v>
       </c>
       <c r="AV23" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AW23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AX23" t="n">
         <v>6.8</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ23" t="n">
         <v>25</v>
       </c>
       <c r="BA23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BB23" t="n">
         <v>9.6</v>
@@ -4981,20 +4981,20 @@
         <v>13.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF23" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG23" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="G24" t="n">
         <v>1.45</v>
       </c>
       <c r="H24" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I24" t="n">
         <v>9.6</v>
@@ -5055,7 +5055,7 @@
         <v>1.29</v>
       </c>
       <c r="P24" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
         <v>1.87</v>
@@ -5070,13 +5070,13 @@
         <v>2.14</v>
       </c>
       <c r="U24" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V24" t="n">
         <v>1.11</v>
       </c>
       <c r="W24" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="X24" t="n">
         <v>16.5</v>
@@ -5088,7 +5088,7 @@
         <v>85</v>
       </c>
       <c r="AA24" t="n">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="AB24" t="n">
         <v>8</v>
@@ -5097,10 +5097,10 @@
         <v>11</v>
       </c>
       <c r="AD24" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE24" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AF24" t="n">
         <v>7.8</v>
@@ -5109,10 +5109,10 @@
         <v>10</v>
       </c>
       <c r="AH24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI24" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ24" t="n">
         <v>11.5</v>
@@ -5124,13 +5124,13 @@
         <v>40</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN24" t="n">
         <v>7</v>
       </c>
       <c r="AO24" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AP24" t="n">
         <v>15.5</v>
@@ -5142,7 +5142,7 @@
         <v>34</v>
       </c>
       <c r="AS24" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AT24" t="n">
         <v>7.4</v>
@@ -5157,7 +5157,7 @@
         <v>44</v>
       </c>
       <c r="AX24" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY24" t="n">
         <v>9.6</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G25" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H25" t="n">
         <v>2.94</v>
@@ -5237,7 +5237,7 @@
         <v>3.75</v>
       </c>
       <c r="L25" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M25" t="n">
         <v>1.06</v>
@@ -5255,22 +5255,22 @@
         <v>1.9</v>
       </c>
       <c r="R25" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T25" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U25" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V25" t="n">
         <v>1.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X25" t="n">
         <v>16</v>
@@ -5309,13 +5309,13 @@
         <v>40</v>
       </c>
       <c r="AJ25" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK25" t="n">
         <v>26</v>
       </c>
       <c r="AL25" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AM25" t="n">
         <v>80</v>
@@ -5336,7 +5336,7 @@
         <v>18</v>
       </c>
       <c r="AS25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT25" t="n">
         <v>11</v>
@@ -5360,7 +5360,7 @@
         <v>15</v>
       </c>
       <c r="BA25" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB25" t="n">
         <v>32</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -5422,25 +5422,25 @@
         <v>5.1</v>
       </c>
       <c r="I26" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J26" t="n">
         <v>3.65</v>
       </c>
       <c r="K26" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L26" t="n">
         <v>1.49</v>
       </c>
       <c r="M26" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N26" t="n">
         <v>3.25</v>
       </c>
       <c r="O26" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P26" t="n">
         <v>1.74</v>
@@ -5467,7 +5467,7 @@
         <v>2.12</v>
       </c>
       <c r="X26" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y26" t="n">
         <v>15</v>
@@ -5500,7 +5500,7 @@
         <v>23</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ26" t="n">
         <v>20</v>
@@ -5509,10 +5509,10 @@
         <v>22</v>
       </c>
       <c r="AL26" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN26" t="n">
         <v>16</v>
@@ -5563,7 +5563,7 @@
         <v>20</v>
       </c>
       <c r="BD26" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE26" t="n">
         <v>46</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -5616,10 +5616,10 @@
         <v>5.4</v>
       </c>
       <c r="I27" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K27" t="n">
         <v>4.3</v>
@@ -5628,16 +5628,16 @@
         <v>1.4</v>
       </c>
       <c r="M27" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O27" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q27" t="n">
         <v>1.96</v>
@@ -5652,7 +5652,7 @@
         <v>1.95</v>
       </c>
       <c r="U27" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V27" t="n">
         <v>1.21</v>
@@ -5664,16 +5664,16 @@
         <v>14.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z27" t="n">
         <v>44</v>
       </c>
       <c r="AA27" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC27" t="n">
         <v>9</v>
@@ -5697,7 +5697,7 @@
         <v>80</v>
       </c>
       <c r="AJ27" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AK27" t="n">
         <v>18</v>
@@ -5718,13 +5718,13 @@
         <v>14</v>
       </c>
       <c r="AQ27" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR27" t="n">
         <v>38</v>
       </c>
       <c r="AS27" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AT27" t="n">
         <v>8.199999999999999</v>
@@ -5736,41 +5736,41 @@
         <v>19</v>
       </c>
       <c r="AW27" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AX27" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY27" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA27" t="n">
         <v>50</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC27" t="n">
         <v>16.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE27" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BF27" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG27" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -5834,19 +5834,19 @@
         <v>1.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="R28" t="n">
         <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T28" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U28" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V28" t="n">
         <v>1.01</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -5998,55 +5998,55 @@
         <v>1.84</v>
       </c>
       <c r="G29" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H29" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="I29" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J29" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K29" t="n">
         <v>3.7</v>
       </c>
       <c r="L29" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M29" t="n">
         <v>1.12</v>
       </c>
       <c r="N29" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O29" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P29" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R29" t="n">
         <v>1.2</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="T29" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U29" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V29" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W29" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X29" t="n">
         <v>11.5</v>
@@ -6061,7 +6061,7 @@
         <v>190</v>
       </c>
       <c r="AB29" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC29" t="n">
         <v>9.800000000000001</v>
@@ -6070,19 +6070,19 @@
         <v>27</v>
       </c>
       <c r="AE29" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI29" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AJ29" t="n">
         <v>28</v>
@@ -6094,7 +6094,7 @@
         <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AN29" t="n">
         <v>27</v>
@@ -6106,59 +6106,59 @@
         <v>8.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS29" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AU29" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV29" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="AW29" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="AX29" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB29" t="n">
         <v>3.8</v>
       </c>
-      <c r="AZ29" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BC29" t="n">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="BF29" t="n">
         <v>16</v>
       </c>
       <c r="BG29" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -6189,16 +6189,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="G30" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I30" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="J30" t="n">
         <v>3.3</v>
@@ -6213,10 +6213,10 @@
         <v>1.08</v>
       </c>
       <c r="N30" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P30" t="n">
         <v>1.76</v>
@@ -6228,19 +6228,19 @@
         <v>1.29</v>
       </c>
       <c r="S30" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="T30" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U30" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V30" t="n">
         <v>1.29</v>
       </c>
       <c r="W30" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="X30" t="n">
         <v>14</v>
@@ -6264,7 +6264,7 @@
         <v>21</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF30" t="n">
         <v>14</v>
@@ -6273,7 +6273,7 @@
         <v>12.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI30" t="n">
         <v>1000</v>
@@ -6312,7 +6312,7 @@
         <v>7.2</v>
       </c>
       <c r="AU30" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV30" t="n">
         <v>15</v>
@@ -6324,7 +6324,7 @@
         <v>10.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ30" t="n">
         <v>17</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -6383,19 +6383,19 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="G31" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H31" t="n">
         <v>4.2</v>
       </c>
       <c r="I31" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J31" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K31" t="n">
         <v>4</v>
@@ -6407,22 +6407,22 @@
         <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O31" t="n">
         <v>1.33</v>
       </c>
       <c r="P31" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="R31" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S31" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T31" t="n">
         <v>1.82</v>
@@ -6431,61 +6431,61 @@
         <v>2</v>
       </c>
       <c r="V31" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W31" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="X31" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="Y31" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AA31" t="n">
         <v>130</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD31" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AE31" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG31" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG31" t="n">
-        <v>11</v>
-      </c>
       <c r="AH31" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AI31" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ31" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AK31" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AL31" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AM31" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN31" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
@@ -6497,10 +6497,10 @@
         <v>13</v>
       </c>
       <c r="AR31" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="AS31" t="n">
-        <v>8.6</v>
+        <v>4.4</v>
       </c>
       <c r="AT31" t="n">
         <v>7.6</v>
@@ -6509,10 +6509,10 @@
         <v>7.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>15.5</v>
+        <v>3.75</v>
       </c>
       <c r="AW31" t="n">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="AX31" t="n">
         <v>10</v>
@@ -6521,32 +6521,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ31" t="n">
-        <v>16.5</v>
+        <v>3.8</v>
       </c>
       <c r="BA31" t="n">
-        <v>50</v>
+        <v>4.3</v>
       </c>
       <c r="BB31" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>6.6</v>
+        <v>3.85</v>
       </c>
       <c r="BD31" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="BE31" t="n">
-        <v>8.6</v>
+        <v>4.4</v>
       </c>
       <c r="BF31" t="n">
         <v>10.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
         <v>1.25</v>
       </c>
       <c r="S33" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="T33" t="n">
         <v>2.12</v>
@@ -6825,116 +6825,116 @@
         <v>2.28</v>
       </c>
       <c r="X33" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y33" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="Z33" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA33" t="n">
         <v>240</v>
       </c>
       <c r="AB33" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AC33" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD33" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AE33" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AF33" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AG33" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH33" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AI33" t="n">
         <v>140</v>
       </c>
       <c r="AJ33" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AK33" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AL33" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM33" t="n">
         <v>220</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO33" t="n">
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>5.9</v>
+        <v>3.65</v>
       </c>
       <c r="AQ33" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="AR33" t="n">
-        <v>9.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.76</v>
+        <v>5</v>
       </c>
       <c r="AT33" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU33" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV33" t="n">
-        <v>7.8</v>
+        <v>4.3</v>
       </c>
       <c r="AW33" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="AX33" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="AY33" t="n">
-        <v>9</v>
+        <v>3.55</v>
       </c>
       <c r="AZ33" t="n">
-        <v>7.8</v>
+        <v>4.3</v>
       </c>
       <c r="BA33" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="BB33" t="n">
-        <v>6.8</v>
+        <v>4.1</v>
       </c>
       <c r="BC33" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="BD33" t="n">
-        <v>9</v>
+        <v>4.7</v>
       </c>
       <c r="BE33" t="n">
-        <v>2.76</v>
+        <v>5</v>
       </c>
       <c r="BF33" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG33" t="n">
-        <v>2.04</v>
+        <v>5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -6968,13 +6968,13 @@
         <v>3.7</v>
       </c>
       <c r="G34" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H34" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="I34" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="J34" t="n">
         <v>3.2</v>
@@ -6998,7 +6998,7 @@
         <v>1.7</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="R34" t="n">
         <v>1.26</v>
@@ -7013,10 +7013,10 @@
         <v>1.92</v>
       </c>
       <c r="V34" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="W34" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="X34" t="n">
         <v>13.5</v>
@@ -7076,7 +7076,7 @@
         <v>3.25</v>
       </c>
       <c r="AQ34" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR34" t="n">
         <v>3.4</v>
@@ -7118,7 +7118,7 @@
         <v>4.1</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF34" t="n">
         <v>4.1</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -7180,7 +7180,7 @@
         <v>1.5</v>
       </c>
       <c r="M35" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N35" t="n">
         <v>2.98</v>
@@ -7192,13 +7192,13 @@
         <v>1.68</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R35" t="n">
         <v>1.25</v>
       </c>
       <c r="S35" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T35" t="n">
         <v>1.94</v>
@@ -7216,37 +7216,37 @@
         <v>11</v>
       </c>
       <c r="Y35" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="Z35" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA35" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB35" t="n">
         <v>11.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE35" t="n">
         <v>30</v>
       </c>
       <c r="AF35" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG35" t="n">
         <v>15.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI35" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ35" t="n">
         <v>90</v>
@@ -7264,7 +7264,7 @@
         <v>65</v>
       </c>
       <c r="AO35" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AP35" t="n">
         <v>9.6</v>
@@ -7273,10 +7273,10 @@
         <v>7.6</v>
       </c>
       <c r="AR35" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS35" t="n">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="AT35" t="n">
         <v>9.800000000000001</v>
@@ -7291,38 +7291,38 @@
         <v>25</v>
       </c>
       <c r="AX35" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY35" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ35" t="n">
         <v>18</v>
       </c>
       <c r="BA35" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="BB35" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="BC35" t="n">
-        <v>40</v>
+        <v>11.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="BE35" t="n">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="BF35" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="BG35" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>
@@ -7353,19 +7353,19 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G36" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H36" t="n">
         <v>3.8</v>
       </c>
       <c r="I36" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="J36" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="K36" t="n">
         <v>3.85</v>
@@ -7377,7 +7377,7 @@
         <v>1.07</v>
       </c>
       <c r="N36" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="O36" t="n">
         <v>1.32</v>
@@ -7386,13 +7386,13 @@
         <v>1.85</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="R36" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S36" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="T36" t="n">
         <v>1.78</v>
@@ -7401,7 +7401,7 @@
         <v>2.02</v>
       </c>
       <c r="V36" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W36" t="n">
         <v>1.86</v>
@@ -7425,7 +7425,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD36" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AE36" t="n">
         <v>65</v>
@@ -7461,7 +7461,7 @@
         <v>70</v>
       </c>
       <c r="AP36" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AQ36" t="n">
         <v>3.45</v>
@@ -7473,10 +7473,10 @@
         <v>4.1</v>
       </c>
       <c r="AT36" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AU36" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="AV36" t="n">
         <v>3.55</v>
@@ -7488,10 +7488,10 @@
         <v>3.35</v>
       </c>
       <c r="AY36" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AZ36" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BA36" t="n">
         <v>4</v>
@@ -7503,10 +7503,10 @@
         <v>3.7</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BE36" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF36" t="n">
         <v>11.5</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-18 05:22:48</t>
+          <t>2026-03-18 07:32:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
@@ -757,34 +757,34 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="I2" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K2" t="n">
-        <v>10.5</v>
+        <v>5.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>1.67</v>
+        <v>2.98</v>
       </c>
       <c r="O2" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="P2" t="n">
         <v>1.67</v>
@@ -793,58 +793,58 @@
         <v>1.87</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>1.87</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="V2" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF2" t="n">
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
@@ -862,65 +862,65 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>2.82</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>2.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
         <v>7.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -1080,7 +1080,7 @@
         <v>4.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX3" t="n">
         <v>5.6</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
         <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.4</v>
@@ -1172,7 +1172,7 @@
         <v>3.85</v>
       </c>
       <c r="O4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P4" t="n">
         <v>1.98</v>
@@ -1187,22 +1187,22 @@
         <v>3.15</v>
       </c>
       <c r="T4" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="U4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X4" t="n">
         <v>14.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z4" t="n">
         <v>27</v>
@@ -1220,7 +1220,7 @@
         <v>15.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF4" t="n">
         <v>13.5</v>
@@ -1229,13 +1229,13 @@
         <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI4" t="n">
         <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK4" t="n">
         <v>23</v>
@@ -1247,13 +1247,13 @@
         <v>95</v>
       </c>
       <c r="AN4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO4" t="n">
         <v>46</v>
       </c>
       <c r="AP4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>13.5</v>
@@ -1262,7 +1262,7 @@
         <v>24</v>
       </c>
       <c r="AS4" t="n">
-        <v>46</v>
+        <v>14.5</v>
       </c>
       <c r="AT4" t="n">
         <v>9</v>
@@ -1274,7 +1274,7 @@
         <v>13.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX4" t="n">
         <v>12</v>
@@ -1286,7 +1286,7 @@
         <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>42</v>
+        <v>13.5</v>
       </c>
       <c r="BB4" t="n">
         <v>23</v>
@@ -1298,17 +1298,17 @@
         <v>32</v>
       </c>
       <c r="BE4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BF4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BG4" t="n">
         <v>34</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -1345,16 +1345,16 @@
         <v>1.46</v>
       </c>
       <c r="H5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I5" t="n">
         <v>16.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="L5" t="n">
         <v>1.3</v>
@@ -1363,28 +1363,28 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="R5" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="T5" t="n">
         <v>2.12</v>
       </c>
       <c r="U5" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V5" t="n">
         <v>1.06</v>
@@ -1447,52 +1447,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT5" t="n">
         <v>3</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AV5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX5" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF5" t="n">
         <v>2.72</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
         <v>17</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="G8" t="n">
         <v>1.15</v>
@@ -1936,46 +1936,46 @@
         <v>1.1</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M8" t="n">
         <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>4.9</v>
+        <v>3.85</v>
       </c>
       <c r="O8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P8" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="S8" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="T8" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="U8" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="V8" t="n">
         <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="X8" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Y8" t="n">
         <v>110</v>
@@ -1987,10 +1987,10 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
@@ -2002,10 +2002,10 @@
         <v>7.2</v>
       </c>
       <c r="AG8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH8" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
@@ -2014,7 +2014,7 @@
         <v>7.6</v>
       </c>
       <c r="AK8" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AL8" t="n">
         <v>110</v>
@@ -2029,62 +2029,62 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AQ8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU8" t="n">
         <v>5.6</v>
       </c>
-      <c r="AR8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU8" t="n">
+      <c r="AV8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AY8" t="n">
         <v>5</v>
       </c>
-      <c r="AV8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.9</v>
+        <v>2.32</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="G9" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="J9" t="n">
         <v>5.6</v>
@@ -2139,13 +2139,13 @@
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O9" t="n">
         <v>1.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q9" t="n">
         <v>1.6</v>
@@ -2160,25 +2160,25 @@
         <v>1.92</v>
       </c>
       <c r="U9" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="V9" t="n">
         <v>1.1</v>
       </c>
       <c r="W9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="X9" t="n">
         <v>24</v>
       </c>
       <c r="Y9" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Z9" t="n">
         <v>100</v>
       </c>
       <c r="AA9" t="n">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="AB9" t="n">
         <v>10</v>
@@ -2190,7 +2190,7 @@
         <v>950</v>
       </c>
       <c r="AE9" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF9" t="n">
         <v>9</v>
@@ -2202,7 +2202,7 @@
         <v>27</v>
       </c>
       <c r="AI9" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ9" t="n">
         <v>11.5</v>
@@ -2214,7 +2214,7 @@
         <v>34</v>
       </c>
       <c r="AM9" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AN9" t="n">
         <v>5.4</v>
@@ -2226,16 +2226,16 @@
         <v>20</v>
       </c>
       <c r="AQ9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AR9" t="n">
         <v>11.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU9" t="n">
         <v>11</v>
@@ -2244,7 +2244,7 @@
         <v>32</v>
       </c>
       <c r="AW9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX9" t="n">
         <v>7.8</v>
@@ -2268,17 +2268,17 @@
         <v>28</v>
       </c>
       <c r="BE9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF9" t="n">
         <v>4.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
         <v>18.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="AX10" t="n">
         <v>9.199999999999999</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
         <v>4.9</v>
       </c>
       <c r="K11" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L11" t="n">
         <v>1.36</v>
@@ -2536,7 +2536,7 @@
         <v>2.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R11" t="n">
         <v>1.4</v>
@@ -2560,13 +2560,13 @@
         <v>20</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z11" t="n">
         <v>130</v>
       </c>
       <c r="AA11" t="n">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="AB11" t="n">
         <v>8.800000000000001</v>
@@ -2593,7 +2593,7 @@
         <v>210</v>
       </c>
       <c r="AJ11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK11" t="n">
         <v>1000</v>
@@ -2614,13 +2614,13 @@
         <v>14.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AT11" t="n">
         <v>6.8</v>
@@ -2629,10 +2629,10 @@
         <v>10</v>
       </c>
       <c r="AV11" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AX11" t="n">
         <v>6.8</v>
@@ -2641,10 +2641,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BB11" t="n">
         <v>9.6</v>
@@ -2653,20 +2653,20 @@
         <v>14</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BF11" t="n">
         <v>6</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -2706,10 +2706,10 @@
         <v>1.62</v>
       </c>
       <c r="I12" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="J12" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="K12" t="n">
         <v>4.6</v>
@@ -2739,19 +2739,19 @@
         <v>3.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U12" t="n">
         <v>1.88</v>
       </c>
       <c r="V12" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y12" t="n">
         <v>8</v>
@@ -2760,10 +2760,10 @@
         <v>9</v>
       </c>
       <c r="AA12" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AB12" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC12" t="n">
         <v>10</v>
@@ -2772,13 +2772,13 @@
         <v>10.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AF12" t="n">
         <v>55</v>
       </c>
       <c r="AG12" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AH12" t="n">
         <v>27</v>
@@ -2796,10 +2796,10 @@
         <v>110</v>
       </c>
       <c r="AM12" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN12" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AO12" t="n">
         <v>9.800000000000001</v>
@@ -2817,7 +2817,7 @@
         <v>14</v>
       </c>
       <c r="AT12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU12" t="n">
         <v>8.6</v>
@@ -2841,26 +2841,26 @@
         <v>29</v>
       </c>
       <c r="BB12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC12" t="n">
         <v>11.5</v>
       </c>
-      <c r="BC12" t="n">
-        <v>11</v>
-      </c>
       <c r="BD12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF12" t="n">
         <v>11</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G13" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H13" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I13" t="n">
         <v>2.86</v>
@@ -2924,7 +2924,7 @@
         <v>1.97</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R13" t="n">
         <v>1.36</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
         <v>1.32</v>
       </c>
       <c r="H14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="I14" t="n">
         <v>13.5</v>
@@ -3100,7 +3100,7 @@
         <v>6.4</v>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.28</v>
@@ -3115,10 +3115,10 @@
         <v>1.18</v>
       </c>
       <c r="P14" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="R14" t="n">
         <v>1.62</v>
@@ -3130,7 +3130,7 @@
         <v>2.12</v>
       </c>
       <c r="U14" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="V14" t="n">
         <v>1.08</v>
@@ -3142,7 +3142,7 @@
         <v>32</v>
       </c>
       <c r="Y14" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Z14" t="n">
         <v>140</v>
@@ -3154,13 +3154,13 @@
         <v>11</v>
       </c>
       <c r="AC14" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AD14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AE14" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AF14" t="n">
         <v>8.800000000000001</v>
@@ -3196,13 +3196,13 @@
         <v>22</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT14" t="n">
         <v>9</v>
@@ -3211,10 +3211,10 @@
         <v>13</v>
       </c>
       <c r="AV14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AX14" t="n">
         <v>7.4</v>
@@ -3223,10 +3223,10 @@
         <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB14" t="n">
         <v>8.6</v>
@@ -3235,20 +3235,20 @@
         <v>12</v>
       </c>
       <c r="BD14" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF14" t="n">
         <v>3.85</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
         <v>3.45</v>
       </c>
       <c r="H15" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I15" t="n">
         <v>2.28</v>
@@ -3330,7 +3330,7 @@
         <v>1.78</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X15" t="n">
         <v>15.5</v>
@@ -3363,7 +3363,7 @@
         <v>14</v>
       </c>
       <c r="AH15" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI15" t="n">
         <v>34</v>
@@ -3402,7 +3402,7 @@
         <v>13</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV15" t="n">
         <v>10</v>
@@ -3423,7 +3423,7 @@
         <v>30</v>
       </c>
       <c r="BB15" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BC15" t="n">
         <v>34</v>
@@ -3432,17 +3432,17 @@
         <v>40</v>
       </c>
       <c r="BE15" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BF15" t="n">
         <v>30</v>
       </c>
       <c r="BG15" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G16" t="n">
         <v>2.16</v>
@@ -3488,7 +3488,7 @@
         <v>3.5</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L16" t="n">
         <v>1.46</v>
@@ -3515,7 +3515,7 @@
         <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U16" t="n">
         <v>2.02</v>
@@ -3533,10 +3533,10 @@
         <v>13.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA16" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB16" t="n">
         <v>8.800000000000001</v>
@@ -3545,16 +3545,16 @@
         <v>7.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE16" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF16" t="n">
         <v>12.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
         <v>19</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -3667,28 +3667,28 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="G17" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I17" t="n">
         <v>6.2</v>
       </c>
-      <c r="I17" t="n">
-        <v>6.4</v>
-      </c>
       <c r="J17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K17" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.36</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
         <v>4.5</v>
@@ -3709,7 +3709,7 @@
         <v>3.05</v>
       </c>
       <c r="T17" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U17" t="n">
         <v>2.08</v>
@@ -3718,10 +3718,10 @@
         <v>1.18</v>
       </c>
       <c r="W17" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X17" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y17" t="n">
         <v>22</v>
@@ -3742,13 +3742,13 @@
         <v>23</v>
       </c>
       <c r="AE17" t="n">
-        <v>990</v>
+        <v>80</v>
       </c>
       <c r="AF17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG17" t="n">
         <v>10</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AH17" t="n">
         <v>21</v>
@@ -3763,7 +3763,7 @@
         <v>16</v>
       </c>
       <c r="AL17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM17" t="n">
         <v>110</v>
@@ -3802,16 +3802,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA17" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="BB17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC17" t="n">
         <v>15</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -3984,7 +3984,7 @@
         <v>11.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV18" t="n">
         <v>7.8</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -4055,13 +4055,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G19" t="n">
         <v>3.15</v>
       </c>
       <c r="H19" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="I19" t="n">
         <v>3.05</v>
@@ -4070,16 +4070,16 @@
         <v>3.05</v>
       </c>
       <c r="K19" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M19" t="n">
         <v>1.12</v>
       </c>
       <c r="N19" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="O19" t="n">
         <v>1.48</v>
@@ -4088,13 +4088,13 @@
         <v>1.57</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R19" t="n">
         <v>1.21</v>
       </c>
       <c r="S19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T19" t="n">
         <v>1.98</v>
@@ -4103,7 +4103,7 @@
         <v>1.81</v>
       </c>
       <c r="V19" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W19" t="n">
         <v>1.46</v>
@@ -4112,7 +4112,7 @@
         <v>11</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z19" t="n">
         <v>1000</v>
@@ -4169,10 +4169,10 @@
         <v>7.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>5.9</v>
+        <v>13</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT19" t="n">
         <v>7.8</v>
@@ -4184,7 +4184,7 @@
         <v>11</v>
       </c>
       <c r="AW19" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX19" t="n">
         <v>15.5</v>
@@ -4199,26 +4199,26 @@
         <v>7.6</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC19" t="n">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BD19" t="n">
         <v>7.6</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="G20" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="H20" t="n">
         <v>4.8</v>
       </c>
       <c r="I20" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="J20" t="n">
         <v>3.3</v>
       </c>
       <c r="K20" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L20" t="n">
         <v>1.46</v>
@@ -4300,7 +4300,7 @@
         <v>1.21</v>
       </c>
       <c r="W20" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X20" t="n">
         <v>14</v>
@@ -4309,7 +4309,7 @@
         <v>18.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AA20" t="n">
         <v>180</v>
@@ -4363,7 +4363,7 @@
         <v>12.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>32</v>
+        <v>3.95</v>
       </c>
       <c r="AS20" t="n">
         <v>4.2</v>
@@ -4378,7 +4378,7 @@
         <v>17.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AX20" t="n">
         <v>9</v>
@@ -4390,7 +4390,7 @@
         <v>19</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BB20" t="n">
         <v>18</v>
@@ -4399,7 +4399,7 @@
         <v>19</v>
       </c>
       <c r="BD20" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="BE20" t="n">
         <v>4.2</v>
@@ -4408,11 +4408,11 @@
         <v>12</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="G21" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="H21" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="I21" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J21" t="n">
         <v>3.95</v>
       </c>
       <c r="K21" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L21" t="n">
         <v>1.42</v>
@@ -4473,31 +4473,31 @@
         <v>1.33</v>
       </c>
       <c r="P21" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q21" t="n">
         <v>1.99</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S21" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T21" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U21" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V21" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W21" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="X21" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y21" t="n">
         <v>19.5</v>
@@ -4506,13 +4506,13 @@
         <v>50</v>
       </c>
       <c r="AA21" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AB21" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD21" t="n">
         <v>24</v>
@@ -4527,13 +4527,13 @@
         <v>10.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI21" t="n">
         <v>110</v>
       </c>
       <c r="AJ21" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK21" t="n">
         <v>18.5</v>
@@ -4545,16 +4545,16 @@
         <v>160</v>
       </c>
       <c r="AN21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO21" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP21" t="n">
         <v>13</v>
       </c>
       <c r="AQ21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR21" t="n">
         <v>7.4</v>
@@ -4563,28 +4563,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV21" t="n">
         <v>20</v>
       </c>
       <c r="AW21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX21" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY21" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB21" t="n">
         <v>14.5</v>
@@ -4596,17 +4596,17 @@
         <v>7.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BG21" t="n">
         <v>8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="G22" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="H22" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="I22" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="J22" t="n">
         <v>3.8</v>
       </c>
       <c r="K22" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L22" t="n">
         <v>1.38</v>
@@ -4661,22 +4661,22 @@
         <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O22" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P22" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T22" t="n">
         <v>1.72</v>
@@ -4685,122 +4685,122 @@
         <v>2.26</v>
       </c>
       <c r="V22" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W22" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="X22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y22" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AE22" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG22" t="n">
         <v>10.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ22" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AK22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL22" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM22" t="n">
         <v>85</v>
       </c>
       <c r="AN22" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AO22" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AP22" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AS22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU22" t="n">
         <v>7.8</v>
       </c>
       <c r="AV22" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AX22" t="n">
         <v>12</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ22" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="BB22" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC22" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF22" t="n">
         <v>13</v>
       </c>
-      <c r="BF22" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BG22" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4840,7 @@
         <v>3.2</v>
       </c>
       <c r="I23" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J23" t="n">
         <v>3.6</v>
@@ -4879,10 +4879,10 @@
         <v>2.26</v>
       </c>
       <c r="V23" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W23" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X23" t="n">
         <v>18.5</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
         <v>1.39</v>
       </c>
       <c r="G24" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="H24" t="n">
         <v>10</v>
@@ -5037,7 +5037,7 @@
         <v>11.5</v>
       </c>
       <c r="J24" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K24" t="n">
         <v>5.3</v>
@@ -5049,25 +5049,25 @@
         <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O24" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P24" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S24" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T24" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U24" t="n">
         <v>1.74</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -5222,16 +5222,16 @@
         <v>1.44</v>
       </c>
       <c r="G25" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H25" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="J25" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K25" t="n">
         <v>5.1</v>
@@ -5270,7 +5270,7 @@
         <v>1.11</v>
       </c>
       <c r="W25" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="X25" t="n">
         <v>16.5</v>
@@ -5294,10 +5294,10 @@
         <v>34</v>
       </c>
       <c r="AE25" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AG25" t="n">
         <v>10</v>
@@ -5333,10 +5333,10 @@
         <v>25</v>
       </c>
       <c r="AR25" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AS25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AT25" t="n">
         <v>7.4</v>
@@ -5348,7 +5348,7 @@
         <v>30</v>
       </c>
       <c r="AW25" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AX25" t="n">
         <v>7.4</v>
@@ -5366,10 +5366,10 @@
         <v>10.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD25" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE25" t="n">
         <v>46</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5419,7 @@
         <v>2.58</v>
       </c>
       <c r="H26" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="I26" t="n">
         <v>2.98</v>
@@ -5431,7 +5431,7 @@
         <v>3.75</v>
       </c>
       <c r="L26" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M26" t="n">
         <v>1.06</v>
@@ -5446,7 +5446,7 @@
         <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R26" t="n">
         <v>1.44</v>
@@ -5461,7 +5461,7 @@
         <v>2.32</v>
       </c>
       <c r="V26" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W26" t="n">
         <v>1.63</v>
@@ -5488,7 +5488,7 @@
         <v>12.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF26" t="n">
         <v>17</v>
@@ -5503,7 +5503,7 @@
         <v>40</v>
       </c>
       <c r="AJ26" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK26" t="n">
         <v>26</v>
@@ -5530,7 +5530,7 @@
         <v>18</v>
       </c>
       <c r="AS26" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AT26" t="n">
         <v>11</v>
@@ -5542,7 +5542,7 @@
         <v>12</v>
       </c>
       <c r="AW26" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AX26" t="n">
         <v>15.5</v>
@@ -5557,13 +5557,13 @@
         <v>34</v>
       </c>
       <c r="BB26" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BC26" t="n">
         <v>24</v>
       </c>
       <c r="BD26" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="BE26" t="n">
         <v>34</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -5607,16 +5607,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="G27" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="H27" t="n">
         <v>5</v>
       </c>
       <c r="I27" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J27" t="n">
         <v>3.65</v>
@@ -5628,7 +5628,7 @@
         <v>1.49</v>
       </c>
       <c r="M27" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N27" t="n">
         <v>3.25</v>
@@ -5655,22 +5655,22 @@
         <v>1.85</v>
       </c>
       <c r="V27" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W27" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X27" t="n">
         <v>11</v>
       </c>
       <c r="Y27" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z27" t="n">
         <v>36</v>
       </c>
       <c r="AA27" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
         <v>7.4</v>
@@ -5697,13 +5697,13 @@
         <v>90</v>
       </c>
       <c r="AJ27" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK27" t="n">
         <v>22</v>
       </c>
       <c r="AL27" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM27" t="n">
         <v>160</v>
@@ -5712,10 +5712,10 @@
         <v>16.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP27" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ27" t="n">
         <v>14</v>
@@ -5727,13 +5727,13 @@
         <v>42</v>
       </c>
       <c r="AT27" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU27" t="n">
         <v>7.2</v>
       </c>
       <c r="AV27" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW27" t="n">
         <v>34</v>
@@ -5745,10 +5745,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ27" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA27" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB27" t="n">
         <v>18.5</v>
@@ -5757,7 +5757,7 @@
         <v>20</v>
       </c>
       <c r="BD27" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE27" t="n">
         <v>46</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -5804,13 +5804,13 @@
         <v>1.71</v>
       </c>
       <c r="G28" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H28" t="n">
         <v>5.5</v>
       </c>
       <c r="I28" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J28" t="n">
         <v>4.1</v>
@@ -5834,7 +5834,7 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R28" t="n">
         <v>1.38</v>
@@ -5858,22 +5858,22 @@
         <v>14.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z28" t="n">
         <v>42</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB28" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC28" t="n">
         <v>9</v>
       </c>
       <c r="AD28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE28" t="n">
         <v>80</v>
@@ -5891,10 +5891,10 @@
         <v>80</v>
       </c>
       <c r="AJ28" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK28" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL28" t="n">
         <v>36</v>
@@ -5915,16 +5915,16 @@
         <v>16.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AS28" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AT28" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU28" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV28" t="n">
         <v>19</v>
@@ -5939,10 +5939,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ28" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BB28" t="n">
         <v>15.5</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -6189,16 +6189,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="G30" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="H30" t="n">
         <v>5</v>
       </c>
       <c r="I30" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J30" t="n">
         <v>3.4</v>
@@ -6213,34 +6213,34 @@
         <v>1.12</v>
       </c>
       <c r="N30" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O30" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="P30" t="n">
         <v>1.56</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R30" t="n">
         <v>1.19</v>
       </c>
       <c r="S30" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U30" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="V30" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W30" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="X30" t="n">
         <v>11.5</v>
@@ -6249,13 +6249,13 @@
         <v>15.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA30" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB30" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC30" t="n">
         <v>9.800000000000001</v>
@@ -6297,62 +6297,62 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ30" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS30" t="n">
         <v>5.2</v>
       </c>
-      <c r="AS30" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AT30" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU30" t="n">
         <v>7.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>19.5</v>
+        <v>4.4</v>
       </c>
       <c r="AW30" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="AX30" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY30" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ30" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BB30" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BC30" t="n">
         <v>22</v>
       </c>
       <c r="BD30" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BE30" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BF30" t="n">
         <v>16</v>
       </c>
       <c r="BG30" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
         <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H31" t="n">
         <v>4.1</v>
@@ -6422,7 +6422,7 @@
         <v>1.29</v>
       </c>
       <c r="S31" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="T31" t="n">
         <v>1.89</v>
@@ -6431,10 +6431,10 @@
         <v>1.96</v>
       </c>
       <c r="V31" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W31" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="X31" t="n">
         <v>14</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -6577,16 +6577,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G32" t="n">
         <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I32" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J32" t="n">
         <v>3.6</v>
@@ -6601,31 +6601,31 @@
         <v>1.07</v>
       </c>
       <c r="N32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S32" t="n">
         <v>3.55</v>
       </c>
-      <c r="O32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.4</v>
-      </c>
       <c r="T32" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="U32" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V32" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W32" t="n">
         <v>2</v>
@@ -6643,10 +6643,10 @@
         <v>130</v>
       </c>
       <c r="AB32" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC32" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD32" t="n">
         <v>22</v>
@@ -6655,7 +6655,7 @@
         <v>65</v>
       </c>
       <c r="AF32" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AG32" t="n">
         <v>11</v>
@@ -6673,7 +6673,7 @@
         <v>26</v>
       </c>
       <c r="AL32" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM32" t="n">
         <v>140</v>
@@ -6691,22 +6691,22 @@
         <v>13</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AS32" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT32" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU32" t="n">
         <v>7.4</v>
       </c>
       <c r="AV32" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="AW32" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="AX32" t="n">
         <v>10</v>
@@ -6715,32 +6715,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ32" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>48</v>
+        <v>6.4</v>
       </c>
       <c r="BB32" t="n">
         <v>18.5</v>
       </c>
       <c r="BC32" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF32" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BG32" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
         <v>1.19</v>
       </c>
       <c r="G33" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="H33" t="n">
         <v>19</v>
@@ -6783,7 +6783,7 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="K33" t="n">
         <v>9.4</v>
@@ -6792,7 +6792,7 @@
         <v>1.28</v>
       </c>
       <c r="M33" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N33" t="n">
         <v>5.5</v>
@@ -6801,28 +6801,28 @@
         <v>1.18</v>
       </c>
       <c r="P33" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="R33" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="S33" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="T33" t="n">
         <v>2.44</v>
       </c>
       <c r="U33" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="V33" t="n">
         <v>1.04</v>
       </c>
       <c r="W33" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="X33" t="n">
         <v>34</v>
@@ -6849,7 +6849,7 @@
         <v>530</v>
       </c>
       <c r="AF33" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AG33" t="n">
         <v>13.5</v>
@@ -6861,7 +6861,7 @@
         <v>360</v>
       </c>
       <c r="AJ33" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AK33" t="n">
         <v>16</v>
@@ -6873,7 +6873,7 @@
         <v>360</v>
       </c>
       <c r="AN33" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AO33" t="n">
         <v>1000</v>
@@ -6882,13 +6882,13 @@
         <v>22</v>
       </c>
       <c r="AQ33" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AR33" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AS33" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT33" t="n">
         <v>8.199999999999999</v>
@@ -6897,10 +6897,10 @@
         <v>15.5</v>
       </c>
       <c r="AV33" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AW33" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AX33" t="n">
         <v>6.4</v>
@@ -6912,7 +6912,7 @@
         <v>38</v>
       </c>
       <c r="BA33" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BB33" t="n">
         <v>7.4</v>
@@ -6921,20 +6921,20 @@
         <v>12.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BE33" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BF33" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BG33" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
         <v>3.55</v>
       </c>
       <c r="K35" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L35" t="n">
         <v>1.42</v>
@@ -7189,13 +7189,13 @@
         <v>1.43</v>
       </c>
       <c r="P35" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R35" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S35" t="n">
         <v>4.4</v>
@@ -7216,10 +7216,10 @@
         <v>13</v>
       </c>
       <c r="Y35" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="Z35" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA35" t="n">
         <v>240</v>
@@ -7228,13 +7228,13 @@
         <v>7.8</v>
       </c>
       <c r="AC35" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AD35" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE35" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF35" t="n">
         <v>11</v>
@@ -7243,13 +7243,13 @@
         <v>970</v>
       </c>
       <c r="AH35" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI35" t="n">
         <v>140</v>
       </c>
       <c r="AJ35" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AK35" t="n">
         <v>22</v>
@@ -7267,16 +7267,16 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AQ35" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AR35" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AS35" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT35" t="n">
         <v>6</v>
@@ -7285,44 +7285,44 @@
         <v>7.2</v>
       </c>
       <c r="AV35" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AW35" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX35" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AY35" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AZ35" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BA35" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB35" t="n">
-        <v>5.3</v>
+        <v>14.5</v>
       </c>
       <c r="BC35" t="n">
-        <v>18.5</v>
+        <v>5.9</v>
       </c>
       <c r="BD35" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BE35" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BF35" t="n">
         <v>11</v>
       </c>
       <c r="BG35" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -7362,7 +7362,7 @@
         <v>2.14</v>
       </c>
       <c r="I36" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="J36" t="n">
         <v>3.2</v>
@@ -7392,7 +7392,7 @@
         <v>1.26</v>
       </c>
       <c r="S36" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="T36" t="n">
         <v>1.92</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -7550,22 +7550,22 @@
         <v>3.65</v>
       </c>
       <c r="G37" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="H37" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="I37" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="J37" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K37" t="n">
         <v>3.4</v>
       </c>
       <c r="L37" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="M37" t="n">
         <v>1.1</v>
@@ -7574,16 +7574,16 @@
         <v>3</v>
       </c>
       <c r="O37" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P37" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q37" t="n">
         <v>2.28</v>
       </c>
       <c r="R37" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S37" t="n">
         <v>4.3</v>
@@ -7592,13 +7592,13 @@
         <v>1.96</v>
       </c>
       <c r="U37" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V37" t="n">
         <v>1.74</v>
       </c>
       <c r="W37" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X37" t="n">
         <v>11</v>
@@ -7607,10 +7607,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Z37" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA37" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AB37" t="n">
         <v>11.5</v>
@@ -7622,40 +7622,40 @@
         <v>11.5</v>
       </c>
       <c r="AE37" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF37" t="n">
         <v>26</v>
       </c>
       <c r="AG37" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AH37" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI37" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ37" t="n">
         <v>85</v>
       </c>
       <c r="AK37" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL37" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM37" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN37" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO37" t="n">
         <v>25</v>
       </c>
       <c r="AP37" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="AQ37" t="n">
         <v>7.6</v>
@@ -7664,7 +7664,7 @@
         <v>11.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="AT37" t="n">
         <v>9.800000000000001</v>
@@ -7688,29 +7688,29 @@
         <v>18</v>
       </c>
       <c r="BA37" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BB37" t="n">
         <v>13</v>
       </c>
       <c r="BC37" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="BD37" t="n">
         <v>55</v>
       </c>
       <c r="BE37" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BF37" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="BG37" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>
@@ -7741,22 +7741,22 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G38" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H38" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I38" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J38" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K38" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L38" t="n">
         <v>1.35</v>
@@ -7765,31 +7765,31 @@
         <v>1.07</v>
       </c>
       <c r="N38" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O38" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P38" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="R38" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S38" t="n">
         <v>3.45</v>
       </c>
       <c r="T38" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="U38" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="V38" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W38" t="n">
         <v>1.8</v>
@@ -7807,104 +7807,104 @@
         <v>110</v>
       </c>
       <c r="AB38" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AC38" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AD38" t="n">
         <v>970</v>
       </c>
       <c r="AE38" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF38" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AG38" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH38" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AI38" t="n">
         <v>70</v>
       </c>
       <c r="AJ38" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AK38" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AL38" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM38" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN38" t="n">
         <v>970</v>
       </c>
       <c r="AO38" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AP38" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="AQ38" t="n">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="AR38" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="AS38" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.5</v>
+        <v>8.4</v>
       </c>
       <c r="AU38" t="n">
         <v>6.8</v>
       </c>
       <c r="AV38" t="n">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="AW38" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="AX38" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="AY38" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="AZ38" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="BA38" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BB38" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BC38" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BE38" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BF38" t="n">
         <v>12</v>
       </c>
       <c r="BG38" t="n">
-        <v>40</v>
+        <v>6.8</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-18 09:42:52</t>
+          <t>2026-03-18 11:52:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="G2" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="H2" t="n">
         <v>1.33</v>
       </c>
       <c r="I2" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="K2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L2" t="n">
         <v>1.34</v>
@@ -781,31 +781,31 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>2.98</v>
+        <v>3.35</v>
       </c>
       <c r="O2" t="n">
         <v>1.35</v>
       </c>
       <c r="P2" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="R2" t="n">
         <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="U2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="V2" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="W2" t="n">
         <v>1.05</v>
@@ -838,7 +838,7 @@
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AH2" t="n">
         <v>50</v>
@@ -865,16 +865,16 @@
         <v>9.4</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.6</v>
+        <v>12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.82</v>
+        <v>5.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.35</v>
+        <v>9</v>
       </c>
       <c r="AT2" t="n">
         <v>4.1</v>
@@ -883,10 +883,10 @@
         <v>3.45</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.75</v>
+        <v>15.5</v>
       </c>
       <c r="AX2" t="n">
         <v>4.4</v>
@@ -895,32 +895,32 @@
         <v>4.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB2" t="n">
         <v>4.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF2" t="n">
         <v>4.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.05</v>
+        <v>5.9</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="G3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H3" t="n">
         <v>1.24</v>
       </c>
       <c r="I3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="J3" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="K3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -984,137 +984,137 @@
         <v>1.93</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="R3" t="n">
         <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="V3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP3" t="n">
         <v>4.1</v>
       </c>
-      <c r="W3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AQ3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AR3" t="n">
         <v>3.25</v>
       </c>
-      <c r="AR3" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AS3" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="AT3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB3" t="n">
         <v>5.2</v>
       </c>
-      <c r="AU3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AZ3" t="n">
+      <c r="BC3" t="n">
         <v>5.2</v>
       </c>
-      <c r="BA3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BD3" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.96</v>
+        <v>5.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I4" t="n">
         <v>3.9</v>
@@ -1178,13 +1178,13 @@
         <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
         <v>1.76</v>
@@ -1193,10 +1193,10 @@
         <v>2.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X4" t="n">
         <v>14.5</v>
@@ -1217,7 +1217,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
         <v>44</v>
@@ -1229,7 +1229,7 @@
         <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI4" t="n">
         <v>55</v>
@@ -1238,10 +1238,10 @@
         <v>27</v>
       </c>
       <c r="AK4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM4" t="n">
         <v>95</v>
@@ -1250,7 +1250,7 @@
         <v>16</v>
       </c>
       <c r="AO4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP4" t="n">
         <v>13.5</v>
@@ -1262,10 +1262,10 @@
         <v>24</v>
       </c>
       <c r="AS4" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AT4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU4" t="n">
         <v>7.4</v>
@@ -1274,7 +1274,7 @@
         <v>13.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX4" t="n">
         <v>12</v>
@@ -1286,10 +1286,10 @@
         <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>13.5</v>
+        <v>44</v>
       </c>
       <c r="BB4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC4" t="n">
         <v>20</v>
@@ -1298,7 +1298,7 @@
         <v>32</v>
       </c>
       <c r="BE4" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BF4" t="n">
         <v>14</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="G5" t="n">
         <v>1.46</v>
       </c>
       <c r="H5" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K5" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L5" t="n">
         <v>1.3</v>
@@ -1363,16 +1363,16 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="O5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="R5" t="n">
         <v>1.43</v>
@@ -1381,10 +1381,10 @@
         <v>2.6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U5" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V5" t="n">
         <v>1.06</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AR5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS5" t="n">
         <v>4.3</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4.4</v>
       </c>
       <c r="AT5" t="n">
         <v>3</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.72</v>
+        <v>4.5</v>
       </c>
       <c r="BG5" t="n">
         <v>4.3</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
         <v>17</v>
       </c>
       <c r="H6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="I6" t="n">
         <v>1.29</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
         <v>1.09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="U7" t="n">
         <v>1.11</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -1921,170 +1921,170 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="H8" t="n">
         <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J8" t="n">
         <v>1.1</v>
       </c>
       <c r="K8" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M8" t="n">
         <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="O8" t="n">
         <v>1.18</v>
       </c>
       <c r="P8" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="R8" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="S8" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="T8" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="U8" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V8" t="n">
         <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>5.9</v>
+        <v>1.99</v>
       </c>
       <c r="X8" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>130</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC8" t="n">
         <v>34</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH8" t="n">
         <v>110</v>
       </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>29</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH8" t="n">
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL8" t="n">
         <v>120</v>
       </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>110</v>
-      </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT8" t="n">
         <v>4.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AV8" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="AY8" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.32</v>
+        <v>6.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -2118,10 +2118,10 @@
         <v>1.38</v>
       </c>
       <c r="G9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="H9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I9" t="n">
         <v>10.5</v>
@@ -2130,7 +2130,7 @@
         <v>5.6</v>
       </c>
       <c r="K9" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L9" t="n">
         <v>1.29</v>
@@ -2139,7 +2139,7 @@
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O9" t="n">
         <v>1.2</v>
@@ -2148,19 +2148,19 @@
         <v>2.42</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R9" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S9" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="T9" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U9" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="V9" t="n">
         <v>1.1</v>
@@ -2172,22 +2172,22 @@
         <v>24</v>
       </c>
       <c r="Y9" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Z9" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AA9" t="n">
         <v>350</v>
       </c>
       <c r="AB9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AE9" t="n">
         <v>150</v>
@@ -2199,7 +2199,7 @@
         <v>10.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI9" t="n">
         <v>120</v>
@@ -2217,49 +2217,49 @@
         <v>140</v>
       </c>
       <c r="AN9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AP9" t="n">
         <v>20</v>
       </c>
       <c r="AQ9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AR9" t="n">
         <v>11.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU9" t="n">
         <v>11</v>
       </c>
       <c r="AV9" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AW9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AX9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY9" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA9" t="n">
         <v>12</v>
       </c>
       <c r="BB9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC9" t="n">
         <v>12.5</v>
@@ -2268,17 +2268,17 @@
         <v>28</v>
       </c>
       <c r="BE9" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF9" t="n">
         <v>4.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="G10" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="H10" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I10" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J10" t="n">
         <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L10" t="n">
         <v>1.44</v>
@@ -2339,7 +2339,7 @@
         <v>1.37</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q10" t="n">
         <v>2.1</v>
@@ -2351,16 +2351,16 @@
         <v>3.7</v>
       </c>
       <c r="T10" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U10" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="V10" t="n">
         <v>1.21</v>
       </c>
       <c r="W10" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="X10" t="n">
         <v>12.5</v>
@@ -2396,7 +2396,7 @@
         <v>22</v>
       </c>
       <c r="AI10" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ10" t="n">
         <v>21</v>
@@ -2408,7 +2408,7 @@
         <v>44</v>
       </c>
       <c r="AM10" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="AN10" t="n">
         <v>15</v>
@@ -2423,7 +2423,7 @@
         <v>14</v>
       </c>
       <c r="AR10" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AS10" t="n">
         <v>10.5</v>
@@ -2435,10 +2435,10 @@
         <v>7.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AW10" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AX10" t="n">
         <v>9.199999999999999</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="G11" t="n">
         <v>1.42</v>
@@ -2536,7 +2536,7 @@
         <v>2.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R11" t="n">
         <v>1.4</v>
@@ -2560,7 +2560,7 @@
         <v>20</v>
       </c>
       <c r="Y11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
         <v>130</v>
@@ -2617,7 +2617,7 @@
         <v>4.8</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AS11" t="n">
         <v>5.7</v>
@@ -2629,10 +2629,10 @@
         <v>10</v>
       </c>
       <c r="AV11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX11" t="n">
         <v>6.8</v>
@@ -2641,7 +2641,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA11" t="n">
         <v>5.6</v>
@@ -2656,7 +2656,7 @@
         <v>5.1</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF11" t="n">
         <v>6</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -2697,13 +2697,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="G12" t="n">
         <v>6.4</v>
       </c>
       <c r="H12" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="I12" t="n">
         <v>1.66</v>
@@ -2715,7 +2715,7 @@
         <v>4.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
@@ -2727,16 +2727,16 @@
         <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q12" t="n">
         <v>2.04</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T12" t="n">
         <v>2.04</v>
@@ -2751,22 +2751,22 @@
         <v>1.18</v>
       </c>
       <c r="X12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC12" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD12" t="n">
         <v>10.5</v>
@@ -2778,22 +2778,22 @@
         <v>55</v>
       </c>
       <c r="AG12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI12" t="n">
         <v>42</v>
       </c>
       <c r="AJ12" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AK12" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AL12" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AM12" t="n">
         <v>170</v>
@@ -2817,10 +2817,10 @@
         <v>14</v>
       </c>
       <c r="AT12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV12" t="n">
         <v>9.6</v>
@@ -2829,38 +2829,38 @@
         <v>15.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="AY12" t="n">
         <v>21</v>
       </c>
       <c r="AZ12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BB12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BC12" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BD12" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BF12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="G13" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H13" t="n">
         <v>2.74</v>
@@ -2903,58 +2903,58 @@
         <v>2.86</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L13" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O13" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P13" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S13" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V13" t="n">
         <v>1.54</v>
       </c>
       <c r="W13" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X13" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Y13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AA13" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AB13" t="n">
         <v>12.5</v>
@@ -2963,19 +2963,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE13" t="n">
         <v>34</v>
       </c>
       <c r="AF13" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AG13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH13" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI13" t="n">
         <v>44</v>
@@ -2993,10 +2993,10 @@
         <v>110</v>
       </c>
       <c r="AN13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO13" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AP13" t="n">
         <v>13</v>
@@ -3008,22 +3008,22 @@
         <v>15.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="AT13" t="n">
         <v>10</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV13" t="n">
         <v>11</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="AX13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY13" t="n">
         <v>10.5</v>
@@ -3032,29 +3032,29 @@
         <v>15</v>
       </c>
       <c r="BA13" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="BC13" t="n">
         <v>24</v>
       </c>
       <c r="BD13" t="n">
-        <v>8.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BE13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BF13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BG13" t="n">
         <v>18.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -3100,10 +3100,10 @@
         <v>6.4</v>
       </c>
       <c r="K14" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="L14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M14" t="n">
         <v>1.03</v>
@@ -3112,13 +3112,13 @@
         <v>5.5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P14" t="n">
         <v>2.68</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R14" t="n">
         <v>1.62</v>
@@ -3193,7 +3193,7 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AQ14" t="n">
         <v>7.6</v>
@@ -3235,7 +3235,7 @@
         <v>12</v>
       </c>
       <c r="BD14" t="n">
-        <v>32</v>
+        <v>7.6</v>
       </c>
       <c r="BE14" t="n">
         <v>8.800000000000001</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -3279,25 +3279,25 @@
         </is>
       </c>
       <c r="F15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="G15" t="n">
         <v>3.4</v>
       </c>
-      <c r="G15" t="n">
-        <v>3.45</v>
-      </c>
       <c r="H15" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="I15" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="J15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K15" t="n">
         <v>3.75</v>
       </c>
-      <c r="K15" t="n">
-        <v>3.8</v>
-      </c>
       <c r="L15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
@@ -3321,13 +3321,13 @@
         <v>3.25</v>
       </c>
       <c r="T15" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U15" t="n">
         <v>2.28</v>
       </c>
       <c r="V15" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="W15" t="n">
         <v>1.41</v>
@@ -3339,13 +3339,13 @@
         <v>11</v>
       </c>
       <c r="Z15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB15" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC15" t="n">
         <v>8.199999999999999</v>
@@ -3357,7 +3357,7 @@
         <v>23</v>
       </c>
       <c r="AF15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG15" t="n">
         <v>14</v>
@@ -3372,19 +3372,19 @@
         <v>60</v>
       </c>
       <c r="AK15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL15" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM15" t="n">
         <v>80</v>
       </c>
       <c r="AN15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO15" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AP15" t="n">
         <v>15</v>
@@ -3399,7 +3399,7 @@
         <v>26</v>
       </c>
       <c r="AT15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU15" t="n">
         <v>7.8</v>
@@ -3408,7 +3408,7 @@
         <v>10</v>
       </c>
       <c r="AW15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX15" t="n">
         <v>22</v>
@@ -3420,10 +3420,10 @@
         <v>15.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB15" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BC15" t="n">
         <v>34</v>
@@ -3435,14 +3435,14 @@
         <v>65</v>
       </c>
       <c r="BF15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BG15" t="n">
         <v>14.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -3473,13 +3473,13 @@
         </is>
       </c>
       <c r="F16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G16" t="n">
         <v>2.14</v>
       </c>
-      <c r="G16" t="n">
-        <v>2.16</v>
-      </c>
       <c r="H16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
         <v>4.1</v>
@@ -3488,7 +3488,7 @@
         <v>3.5</v>
       </c>
       <c r="K16" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L16" t="n">
         <v>1.46</v>
@@ -3506,7 +3506,7 @@
         <v>1.84</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R16" t="n">
         <v>1.31</v>
@@ -3515,16 +3515,16 @@
         <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U16" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V16" t="n">
         <v>1.32</v>
       </c>
       <c r="W16" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="X16" t="n">
         <v>13</v>
@@ -3533,10 +3533,10 @@
         <v>13.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA16" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB16" t="n">
         <v>8.800000000000001</v>
@@ -3545,10 +3545,10 @@
         <v>7.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF16" t="n">
         <v>12.5</v>
@@ -3563,10 +3563,10 @@
         <v>65</v>
       </c>
       <c r="AJ16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL16" t="n">
         <v>42</v>
@@ -3575,13 +3575,13 @@
         <v>120</v>
       </c>
       <c r="AN16" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO16" t="n">
         <v>60</v>
       </c>
       <c r="AP16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>12.5</v>
@@ -3602,7 +3602,7 @@
         <v>15</v>
       </c>
       <c r="AW16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AX16" t="n">
         <v>11.5</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
         <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J17" t="n">
         <v>4.4</v>
@@ -3721,10 +3721,10 @@
         <v>2.56</v>
       </c>
       <c r="X17" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="Y17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z17" t="n">
         <v>50</v>
@@ -3742,10 +3742,10 @@
         <v>23</v>
       </c>
       <c r="AE17" t="n">
-        <v>80</v>
+        <v>990</v>
       </c>
       <c r="AF17" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG17" t="n">
         <v>10</v>
@@ -3772,7 +3772,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AO17" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AP17" t="n">
         <v>16</v>
@@ -3781,10 +3781,10 @@
         <v>20</v>
       </c>
       <c r="AR17" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AS17" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AT17" t="n">
         <v>8.6</v>
@@ -3799,7 +3799,7 @@
         <v>50</v>
       </c>
       <c r="AX17" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY17" t="n">
         <v>9.4</v>
@@ -3811,7 +3811,7 @@
         <v>34</v>
       </c>
       <c r="BB17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BC17" t="n">
         <v>15</v>
@@ -3826,11 +3826,11 @@
         <v>7.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="G18" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="I18" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="J18" t="n">
         <v>3.35</v>
@@ -3879,7 +3879,7 @@
         <v>3.9</v>
       </c>
       <c r="L18" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="M18" t="n">
         <v>1.1</v>
@@ -3891,7 +3891,7 @@
         <v>1.46</v>
       </c>
       <c r="P18" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q18" t="n">
         <v>2.36</v>
@@ -3900,7 +3900,7 @@
         <v>1.21</v>
       </c>
       <c r="S18" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="T18" t="n">
         <v>2.16</v>
@@ -3975,10 +3975,10 @@
         <v>5.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AS18" t="n">
-        <v>13.5</v>
+        <v>3.7</v>
       </c>
       <c r="AT18" t="n">
         <v>11.5</v>
@@ -3987,10 +3987,10 @@
         <v>7.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>7.8</v>
+        <v>3.3</v>
       </c>
       <c r="AW18" t="n">
-        <v>16.5</v>
+        <v>3.8</v>
       </c>
       <c r="AX18" t="n">
         <v>4.1</v>
@@ -3999,7 +3999,7 @@
         <v>19</v>
       </c>
       <c r="AZ18" t="n">
-        <v>19.5</v>
+        <v>3.9</v>
       </c>
       <c r="BA18" t="n">
         <v>4.1</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
         <v>2.66</v>
       </c>
       <c r="I19" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J19" t="n">
         <v>3.05</v>
@@ -4097,7 +4097,7 @@
         <v>4.8</v>
       </c>
       <c r="T19" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U19" t="n">
         <v>1.81</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>1.8</v>
       </c>
       <c r="G20" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="H20" t="n">
         <v>4.8</v>
@@ -4288,7 +4288,7 @@
         <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="T20" t="n">
         <v>1.99</v>
@@ -4300,7 +4300,7 @@
         <v>1.21</v>
       </c>
       <c r="W20" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="X20" t="n">
         <v>14</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -4443,37 +4443,37 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G21" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="H21" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I21" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K21" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M21" t="n">
         <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O21" t="n">
         <v>1.33</v>
       </c>
       <c r="P21" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="Q21" t="n">
         <v>1.99</v>
@@ -4482,7 +4482,7 @@
         <v>1.37</v>
       </c>
       <c r="S21" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T21" t="n">
         <v>1.97</v>
@@ -4491,10 +4491,10 @@
         <v>1.95</v>
       </c>
       <c r="V21" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W21" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="X21" t="n">
         <v>17.5</v>
@@ -4509,10 +4509,10 @@
         <v>210</v>
       </c>
       <c r="AB21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC21" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>9</v>
       </c>
       <c r="AD21" t="n">
         <v>24</v>
@@ -4533,7 +4533,7 @@
         <v>110</v>
       </c>
       <c r="AJ21" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK21" t="n">
         <v>18.5</v>
@@ -4557,34 +4557,34 @@
         <v>16</v>
       </c>
       <c r="AR21" t="n">
-        <v>7.4</v>
+        <v>40</v>
       </c>
       <c r="AS21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU21" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AT21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>8</v>
-      </c>
       <c r="AV21" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX21" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB21" t="n">
         <v>14.5</v>
@@ -4593,20 +4593,20 @@
         <v>16</v>
       </c>
       <c r="BD21" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF21" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG21" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G22" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H22" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I22" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J22" t="n">
         <v>3.8</v>
       </c>
       <c r="K22" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L22" t="n">
         <v>1.38</v>
@@ -4661,7 +4661,7 @@
         <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O22" t="n">
         <v>1.28</v>
@@ -4670,7 +4670,7 @@
         <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="R22" t="n">
         <v>1.42</v>
@@ -4679,31 +4679,31 @@
         <v>3.15</v>
       </c>
       <c r="T22" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U22" t="n">
         <v>2.26</v>
       </c>
       <c r="V22" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W22" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X22" t="n">
         <v>16</v>
       </c>
       <c r="Y22" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA22" t="n">
         <v>70</v>
       </c>
       <c r="AB22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC22" t="n">
         <v>8.6</v>
@@ -4712,7 +4712,7 @@
         <v>15</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF22" t="n">
         <v>14.5</v>
@@ -4721,13 +4721,13 @@
         <v>10.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AI22" t="n">
         <v>48</v>
       </c>
       <c r="AJ22" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AK22" t="n">
         <v>22</v>
@@ -4742,19 +4742,19 @@
         <v>14.5</v>
       </c>
       <c r="AO22" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP22" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ22" t="n">
         <v>13.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT22" t="n">
         <v>10</v>
@@ -4766,16 +4766,16 @@
         <v>13.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX22" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY22" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ22" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA22" t="n">
         <v>34</v>
@@ -4784,13 +4784,13 @@
         <v>23</v>
       </c>
       <c r="BC22" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD22" t="n">
         <v>29</v>
       </c>
       <c r="BE22" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BF22" t="n">
         <v>13</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G23" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H23" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I23" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J23" t="n">
         <v>3.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L23" t="n">
         <v>1.41</v>
@@ -4864,13 +4864,13 @@
         <v>2.04</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="R23" t="n">
         <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T23" t="n">
         <v>1.69</v>
@@ -4879,10 +4879,10 @@
         <v>2.26</v>
       </c>
       <c r="V23" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W23" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X23" t="n">
         <v>18.5</v>
@@ -4903,7 +4903,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD23" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE23" t="n">
         <v>44</v>
@@ -4960,7 +4960,7 @@
         <v>12</v>
       </c>
       <c r="AW23" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX23" t="n">
         <v>13.5</v>
@@ -4978,13 +4978,13 @@
         <v>4.9</v>
       </c>
       <c r="BC23" t="n">
-        <v>4.7</v>
+        <v>19</v>
       </c>
       <c r="BD23" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF23" t="n">
         <v>15.5</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -5031,10 +5031,10 @@
         <v>1.42</v>
       </c>
       <c r="H24" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J24" t="n">
         <v>5.1</v>
@@ -5049,16 +5049,16 @@
         <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O24" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P24" t="n">
         <v>2.06</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R24" t="n">
         <v>1.41</v>
@@ -5082,10 +5082,10 @@
         <v>20</v>
       </c>
       <c r="Y24" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA24" t="n">
         <v>550</v>
@@ -5094,55 +5094,55 @@
         <v>8</v>
       </c>
       <c r="AC24" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AE24" t="n">
         <v>240</v>
       </c>
       <c r="AF24" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AG24" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH24" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AI24" t="n">
         <v>190</v>
       </c>
       <c r="AJ24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK24" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM24" t="n">
         <v>240</v>
       </c>
       <c r="AN24" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ24" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AR24" t="n">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="AS24" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AT24" t="n">
         <v>7</v>
@@ -5151,10 +5151,10 @@
         <v>10</v>
       </c>
       <c r="AV24" t="n">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="AW24" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="AX24" t="n">
         <v>7</v>
@@ -5166,29 +5166,29 @@
         <v>25</v>
       </c>
       <c r="BA24" t="n">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="BB24" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC24" t="n">
         <v>13.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BG24" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="G25" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H25" t="n">
         <v>9.199999999999999</v>
@@ -5252,13 +5252,13 @@
         <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R25" t="n">
         <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T25" t="n">
         <v>2.14</v>
@@ -5270,19 +5270,19 @@
         <v>1.11</v>
       </c>
       <c r="W25" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X25" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z25" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AA25" t="n">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="AB25" t="n">
         <v>8.199999999999999</v>
@@ -5318,7 +5318,7 @@
         <v>40</v>
       </c>
       <c r="AM25" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
         <v>7</v>
@@ -5330,13 +5330,13 @@
         <v>15.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR25" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AS25" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AT25" t="n">
         <v>7.4</v>
@@ -5348,7 +5348,7 @@
         <v>30</v>
       </c>
       <c r="AW25" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX25" t="n">
         <v>7.4</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G26" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H26" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="I26" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J26" t="n">
         <v>3.65</v>
@@ -5431,7 +5431,7 @@
         <v>3.75</v>
       </c>
       <c r="L26" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M26" t="n">
         <v>1.06</v>
@@ -5443,7 +5443,7 @@
         <v>1.29</v>
       </c>
       <c r="P26" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
         <v>1.89</v>
@@ -5464,7 +5464,7 @@
         <v>1.51</v>
       </c>
       <c r="W26" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X26" t="n">
         <v>16</v>
@@ -5503,7 +5503,7 @@
         <v>40</v>
       </c>
       <c r="AJ26" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AK26" t="n">
         <v>26</v>
@@ -5515,10 +5515,10 @@
         <v>80</v>
       </c>
       <c r="AN26" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AO26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP26" t="n">
         <v>15</v>
@@ -5530,7 +5530,7 @@
         <v>18</v>
       </c>
       <c r="AS26" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AT26" t="n">
         <v>11</v>
@@ -5557,13 +5557,13 @@
         <v>34</v>
       </c>
       <c r="BB26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC26" t="n">
         <v>24</v>
       </c>
       <c r="BD26" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BE26" t="n">
         <v>34</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
         <v>2.32</v>
       </c>
       <c r="R27" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S27" t="n">
         <v>4.3</v>
@@ -5652,7 +5652,7 @@
         <v>2.1</v>
       </c>
       <c r="U27" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V27" t="n">
         <v>1.23</v>
@@ -5697,13 +5697,13 @@
         <v>90</v>
       </c>
       <c r="AJ27" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AK27" t="n">
         <v>22</v>
       </c>
       <c r="AL27" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM27" t="n">
         <v>160</v>
@@ -5748,7 +5748,7 @@
         <v>20</v>
       </c>
       <c r="BA27" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB27" t="n">
         <v>18.5</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -5804,10 +5804,10 @@
         <v>1.71</v>
       </c>
       <c r="G28" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I28" t="n">
         <v>5.6</v>
@@ -5828,7 +5828,7 @@
         <v>4</v>
       </c>
       <c r="O28" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P28" t="n">
         <v>2</v>
@@ -5843,7 +5843,7 @@
         <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U28" t="n">
         <v>2</v>
@@ -5873,7 +5873,7 @@
         <v>9</v>
       </c>
       <c r="AD28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE28" t="n">
         <v>80</v>
@@ -5891,7 +5891,7 @@
         <v>80</v>
       </c>
       <c r="AJ28" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AK28" t="n">
         <v>17.5</v>
@@ -5906,7 +5906,7 @@
         <v>10.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AP28" t="n">
         <v>14</v>
@@ -5921,7 +5921,7 @@
         <v>42</v>
       </c>
       <c r="AT28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU28" t="n">
         <v>8.6</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G30" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I30" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J30" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K30" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L30" t="n">
         <v>1.46</v>
@@ -6225,7 +6225,7 @@
         <v>2.6</v>
       </c>
       <c r="R30" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S30" t="n">
         <v>5.3</v>
@@ -6237,7 +6237,7 @@
         <v>1.69</v>
       </c>
       <c r="V30" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W30" t="n">
         <v>2.04</v>
@@ -6246,7 +6246,7 @@
         <v>11.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z30" t="n">
         <v>46</v>
@@ -6255,10 +6255,10 @@
         <v>180</v>
       </c>
       <c r="AB30" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD30" t="n">
         <v>27</v>
@@ -6267,28 +6267,28 @@
         <v>130</v>
       </c>
       <c r="AF30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG30" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH30" t="n">
         <v>34</v>
       </c>
       <c r="AI30" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ30" t="n">
         <v>27</v>
       </c>
       <c r="AK30" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL30" t="n">
         <v>1000</v>
       </c>
       <c r="AM30" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AN30" t="n">
         <v>27</v>
@@ -6300,59 +6300,59 @@
         <v>8.4</v>
       </c>
       <c r="AQ30" t="n">
-        <v>9.800000000000001</v>
+        <v>3.45</v>
       </c>
       <c r="AR30" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="AS30" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT30" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU30" t="n">
         <v>7.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="AW30" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX30" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AY30" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ30" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="BA30" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB30" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="BC30" t="n">
-        <v>22</v>
+        <v>3.9</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="BE30" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF30" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -6383,22 +6383,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="G31" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H31" t="n">
         <v>4.1</v>
       </c>
       <c r="I31" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J31" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K31" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L31" t="n">
         <v>1.39</v>
@@ -6434,7 +6434,7 @@
         <v>1.28</v>
       </c>
       <c r="W31" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="X31" t="n">
         <v>14</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="G32" t="n">
         <v>2</v>
@@ -6586,16 +6586,16 @@
         <v>4.3</v>
       </c>
       <c r="I32" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J32" t="n">
         <v>3.6</v>
       </c>
       <c r="K32" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L32" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M32" t="n">
         <v>1.07</v>
@@ -6610,7 +6610,7 @@
         <v>1.96</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R32" t="n">
         <v>1.35</v>
@@ -6625,7 +6625,7 @@
         <v>2.04</v>
       </c>
       <c r="V32" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W32" t="n">
         <v>2</v>
@@ -6637,7 +6637,7 @@
         <v>16.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA32" t="n">
         <v>130</v>
@@ -6649,7 +6649,7 @@
         <v>8.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AE32" t="n">
         <v>65</v>
@@ -6661,7 +6661,7 @@
         <v>11</v>
       </c>
       <c r="AH32" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI32" t="n">
         <v>70</v>
@@ -6670,7 +6670,7 @@
         <v>24</v>
       </c>
       <c r="AK32" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AL32" t="n">
         <v>40</v>
@@ -6679,7 +6679,7 @@
         <v>140</v>
       </c>
       <c r="AN32" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AO32" t="n">
         <v>1000</v>
@@ -6691,10 +6691,10 @@
         <v>13</v>
       </c>
       <c r="AR32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS32" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AT32" t="n">
         <v>7.8</v>
@@ -6703,10 +6703,10 @@
         <v>7.4</v>
       </c>
       <c r="AV32" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AW32" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX32" t="n">
         <v>10</v>
@@ -6715,32 +6715,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ32" t="n">
-        <v>5.5</v>
+        <v>17</v>
       </c>
       <c r="BA32" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB32" t="n">
         <v>18.5</v>
       </c>
       <c r="BC32" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BE32" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BF32" t="n">
         <v>12</v>
       </c>
       <c r="BG32" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
         <v>1.19</v>
       </c>
       <c r="G33" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="H33" t="n">
         <v>19</v>
@@ -6786,7 +6786,7 @@
         <v>7.6</v>
       </c>
       <c r="K33" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="L33" t="n">
         <v>1.28</v>
@@ -6804,10 +6804,10 @@
         <v>2.56</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="R33" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S33" t="n">
         <v>2.44</v>
@@ -6816,22 +6816,22 @@
         <v>2.44</v>
       </c>
       <c r="U33" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="V33" t="n">
         <v>1.04</v>
       </c>
       <c r="W33" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="X33" t="n">
         <v>34</v>
       </c>
       <c r="Y33" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="Z33" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AA33" t="n">
         <v>1000</v>
@@ -6843,34 +6843,34 @@
         <v>22</v>
       </c>
       <c r="AD33" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AE33" t="n">
-        <v>530</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
         <v>8.4</v>
       </c>
       <c r="AG33" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AH33" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI33" t="n">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AK33" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AL33" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM33" t="n">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AN33" t="n">
         <v>3.9</v>
@@ -6882,13 +6882,13 @@
         <v>22</v>
       </c>
       <c r="AQ33" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="AS33" t="n">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="AT33" t="n">
         <v>8.199999999999999</v>
@@ -6897,10 +6897,10 @@
         <v>15.5</v>
       </c>
       <c r="AV33" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="AW33" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="AX33" t="n">
         <v>6.4</v>
@@ -6909,32 +6909,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ33" t="n">
-        <v>38</v>
+        <v>5.4</v>
       </c>
       <c r="BA33" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="BB33" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC33" t="n">
         <v>12.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE33" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="BF33" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="BG33" t="n">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -7162,13 +7162,13 @@
         <v>1.7</v>
       </c>
       <c r="G35" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H35" t="n">
         <v>6</v>
       </c>
       <c r="I35" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J35" t="n">
         <v>3.55</v>
@@ -7183,28 +7183,28 @@
         <v>1.09</v>
       </c>
       <c r="N35" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O35" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="P35" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R35" t="n">
         <v>1.26</v>
       </c>
       <c r="S35" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T35" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U35" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="V35" t="n">
         <v>1.17</v>
@@ -7222,28 +7222,28 @@
         <v>55</v>
       </c>
       <c r="AA35" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AB35" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AC35" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AE35" t="n">
         <v>130</v>
       </c>
       <c r="AF35" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AG35" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AI35" t="n">
         <v>140</v>
@@ -7252,13 +7252,13 @@
         <v>970</v>
       </c>
       <c r="AK35" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL35" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AM35" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN35" t="n">
         <v>1000</v>
@@ -7267,62 +7267,62 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>4.9</v>
+        <v>9.4</v>
       </c>
       <c r="AQ35" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AR35" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AS35" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT35" t="n">
         <v>6</v>
       </c>
       <c r="AU35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD35" t="n">
         <v>7.2</v>
       </c>
-      <c r="AV35" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>7</v>
-      </c>
       <c r="BE35" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF35" t="n">
         <v>11</v>
       </c>
       <c r="BG35" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -7553,10 +7553,10 @@
         <v>3.85</v>
       </c>
       <c r="H37" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="I37" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J37" t="n">
         <v>3.25</v>
@@ -7601,25 +7601,25 @@
         <v>1.35</v>
       </c>
       <c r="X37" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Y37" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Z37" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AA37" t="n">
         <v>32</v>
       </c>
       <c r="AB37" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC37" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="AD37" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AE37" t="n">
         <v>28</v>
@@ -7637,7 +7637,7 @@
         <v>48</v>
       </c>
       <c r="AJ37" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AK37" t="n">
         <v>55</v>
@@ -7655,62 +7655,62 @@
         <v>25</v>
       </c>
       <c r="AP37" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ37" t="n">
         <v>7.6</v>
       </c>
       <c r="AR37" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="AS37" t="n">
-        <v>22</v>
+        <v>10.5</v>
       </c>
       <c r="AT37" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU37" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV37" t="n">
         <v>10</v>
       </c>
       <c r="AW37" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="AX37" t="n">
-        <v>21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY37" t="n">
         <v>13.5</v>
       </c>
       <c r="AZ37" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BB37" t="n">
-        <v>13</v>
+        <v>3.65</v>
       </c>
       <c r="BC37" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="BD37" t="n">
-        <v>55</v>
+        <v>7.2</v>
       </c>
       <c r="BE37" t="n">
-        <v>14</v>
+        <v>3.75</v>
       </c>
       <c r="BF37" t="n">
-        <v>50</v>
+        <v>3.65</v>
       </c>
       <c r="BG37" t="n">
-        <v>21</v>
+        <v>9.6</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
         <v>1.31</v>
       </c>
       <c r="P38" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q38" t="n">
         <v>1.87</v>
@@ -7828,16 +7828,16 @@
         <v>970</v>
       </c>
       <c r="AI38" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ38" t="n">
         <v>28</v>
       </c>
       <c r="AK38" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL38" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM38" t="n">
         <v>120</v>
@@ -7849,16 +7849,16 @@
         <v>60</v>
       </c>
       <c r="AP38" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AQ38" t="n">
-        <v>5.1</v>
+        <v>12</v>
       </c>
       <c r="AR38" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AS38" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="AT38" t="n">
         <v>8.4</v>
@@ -7867,44 +7867,44 @@
         <v>6.8</v>
       </c>
       <c r="AV38" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AW38" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY38" t="n">
         <v>5</v>
       </c>
-      <c r="AY38" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AZ38" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BA38" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BB38" t="n">
-        <v>6</v>
+        <v>18.5</v>
       </c>
       <c r="BC38" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BD38" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE38" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BF38" t="n">
         <v>12</v>
       </c>
       <c r="BG38" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-18 11:52:45</t>
+          <t>2026-03-18 14:02:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
@@ -802,7 +802,7 @@
         <v>2.48</v>
       </c>
       <c r="U2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="V2" t="n">
         <v>3.5</v>
@@ -871,16 +871,16 @@
         <v>5.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="AS2" t="n">
         <v>9</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AV2" t="n">
         <v>9.6</v>
@@ -889,19 +889,19 @@
         <v>15.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BA2" t="n">
         <v>4.3</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BC2" t="n">
         <v>4.5</v>
@@ -913,14 +913,14 @@
         <v>4.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG2" t="n">
         <v>5.9</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="G3" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="I3" t="n">
         <v>1.3</v>
       </c>
       <c r="J3" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="K3" t="n">
         <v>7.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -981,19 +981,19 @@
         <v>1.31</v>
       </c>
       <c r="P3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
         <v>3.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="U3" t="n">
         <v>1.52</v>
@@ -1002,7 +1002,7 @@
         <v>4.3</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1011,10 +1011,10 @@
         <v>7.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
         <v>1000</v>
@@ -1056,65 +1056,65 @@
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AP3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV3" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AW3" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G4" t="n">
         <v>2.2</v>
@@ -1154,13 +1154,13 @@
         <v>3.7</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K4" t="n">
         <v>3.6</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.4</v>
@@ -1184,13 +1184,13 @@
         <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V4" t="n">
         <v>1.35</v>
@@ -1214,7 +1214,7 @@
         <v>10</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD4" t="n">
         <v>15</v>
@@ -1238,7 +1238,7 @@
         <v>27</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL4" t="n">
         <v>38</v>
@@ -1262,19 +1262,19 @@
         <v>24</v>
       </c>
       <c r="AS4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV4" t="n">
         <v>13.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AX4" t="n">
         <v>12</v>
@@ -1286,7 +1286,7 @@
         <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="BB4" t="n">
         <v>24</v>
@@ -1298,17 +1298,17 @@
         <v>32</v>
       </c>
       <c r="BE4" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG4" t="n">
         <v>34</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>1.32</v>
       </c>
       <c r="G5" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="H5" t="n">
         <v>9.199999999999999</v>
@@ -1459,10 +1459,10 @@
         <v>4.3</v>
       </c>
       <c r="AT5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AV5" t="n">
         <v>4</v>
@@ -1471,22 +1471,22 @@
         <v>4.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>2.98</v>
+        <v>5.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BA5" t="n">
         <v>4.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BD5" t="n">
         <v>4</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>1.99</v>
       </c>
       <c r="H7" t="n">
-        <v>1.06</v>
+        <v>4.1</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J7" t="n">
-        <v>1.03</v>
+        <v>2.6</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1772,13 +1772,13 @@
         <v>1.69</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -1921,25 +1921,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="G8" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="H8" t="n">
         <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1</v>
+        <v>6.6</v>
       </c>
       <c r="K8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="L8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M8" t="n">
         <v>1.02</v>
@@ -1951,16 +1951,16 @@
         <v>1.18</v>
       </c>
       <c r="P8" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="R8" t="n">
         <v>1.67</v>
       </c>
       <c r="S8" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="T8" t="n">
         <v>3.05</v>
@@ -1972,7 +1972,7 @@
         <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.99</v>
+        <v>5.9</v>
       </c>
       <c r="X8" t="n">
         <v>40</v>
@@ -2041,7 +2041,7 @@
         <v>6.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AU8" t="n">
         <v>5.3</v>
@@ -2053,7 +2053,7 @@
         <v>6.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AY8" t="n">
         <v>4.8</v>
@@ -2065,7 +2065,7 @@
         <v>6.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BC8" t="n">
         <v>4.7</v>
@@ -2077,14 +2077,14 @@
         <v>6.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="BG8" t="n">
         <v>6.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         <v>10.5</v>
       </c>
       <c r="J9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="K9" t="n">
         <v>5.7</v>
@@ -2139,25 +2139,25 @@
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P9" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S9" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="T9" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="U9" t="n">
         <v>1.97</v>
@@ -2166,7 +2166,7 @@
         <v>1.1</v>
       </c>
       <c r="W9" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="X9" t="n">
         <v>24</v>
@@ -2175,10 +2175,10 @@
         <v>44</v>
       </c>
       <c r="Z9" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AA9" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AB9" t="n">
         <v>10.5</v>
@@ -2205,7 +2205,7 @@
         <v>120</v>
       </c>
       <c r="AJ9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AK9" t="n">
         <v>14.5</v>
@@ -2229,22 +2229,22 @@
         <v>30</v>
       </c>
       <c r="AR9" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU9" t="n">
         <v>11</v>
       </c>
       <c r="AV9" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AW9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX9" t="n">
         <v>8</v>
@@ -2256,7 +2256,7 @@
         <v>21</v>
       </c>
       <c r="BA9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BB9" t="n">
         <v>10.5</v>
@@ -2268,17 +2268,17 @@
         <v>28</v>
       </c>
       <c r="BE9" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF9" t="n">
         <v>4.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>1.83</v>
       </c>
       <c r="G10" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H10" t="n">
         <v>5.1</v>
@@ -2339,7 +2339,7 @@
         <v>1.37</v>
       </c>
       <c r="P10" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
         <v>2.1</v>
@@ -2351,19 +2351,19 @@
         <v>3.7</v>
       </c>
       <c r="T10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U10" t="n">
         <v>1.93</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.89</v>
       </c>
       <c r="V10" t="n">
         <v>1.21</v>
       </c>
       <c r="W10" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y10" t="n">
         <v>17</v>
@@ -2420,22 +2420,22 @@
         <v>11</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR10" t="n">
         <v>32</v>
       </c>
       <c r="AS10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT10" t="n">
         <v>7</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW10" t="n">
         <v>60</v>
@@ -2447,32 +2447,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB10" t="n">
         <v>17.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="BE10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF10" t="n">
         <v>12.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -2509,10 +2509,10 @@
         <v>1.42</v>
       </c>
       <c r="H11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="J11" t="n">
         <v>4.9</v>
@@ -2521,13 +2521,13 @@
         <v>5.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M11" t="n">
         <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O11" t="n">
         <v>1.29</v>
@@ -2536,19 +2536,19 @@
         <v>2.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R11" t="n">
         <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T11" t="n">
         <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="V11" t="n">
         <v>1.09</v>
@@ -2566,19 +2566,19 @@
         <v>130</v>
       </c>
       <c r="AA11" t="n">
-        <v>570</v>
+        <v>550</v>
       </c>
       <c r="AB11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AC11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD11" t="n">
         <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AF11" t="n">
         <v>9</v>
@@ -2590,13 +2590,13 @@
         <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AJ11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL11" t="n">
         <v>1000</v>
@@ -2614,13 +2614,13 @@
         <v>14.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT11" t="n">
         <v>6.8</v>
@@ -2629,10 +2629,10 @@
         <v>10</v>
       </c>
       <c r="AV11" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AX11" t="n">
         <v>6.8</v>
@@ -2641,10 +2641,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BB11" t="n">
         <v>9.6</v>
@@ -2653,20 +2653,20 @@
         <v>14</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.1</v>
+        <v>38</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BF11" t="n">
         <v>6</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -2712,34 +2712,34 @@
         <v>4.2</v>
       </c>
       <c r="K12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="O12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P12" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
         <v>2.04</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S12" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="T12" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U12" t="n">
         <v>1.88</v>
@@ -2751,64 +2751,64 @@
         <v>1.18</v>
       </c>
       <c r="X12" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AA12" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AB12" t="n">
         <v>19</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE12" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AG12" t="n">
         <v>24</v>
       </c>
       <c r="AH12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ12" t="n">
         <v>220</v>
       </c>
       <c r="AK12" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AL12" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AM12" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN12" t="n">
         <v>150</v>
       </c>
       <c r="AO12" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AP12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AR12" t="n">
         <v>8.199999999999999</v>
@@ -2820,13 +2820,13 @@
         <v>17</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW12" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX12" t="n">
         <v>40</v>
@@ -2835,32 +2835,32 @@
         <v>21</v>
       </c>
       <c r="AZ12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB12" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD12" t="n">
         <v>14.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
         <v>2.78</v>
       </c>
       <c r="H13" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I13" t="n">
         <v>2.86</v>
@@ -2906,37 +2906,37 @@
         <v>3.55</v>
       </c>
       <c r="K13" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O13" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R13" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T13" t="n">
         <v>1.74</v>
       </c>
       <c r="U13" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V13" t="n">
         <v>1.54</v>
@@ -2951,10 +2951,10 @@
         <v>12.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AB13" t="n">
         <v>12.5</v>
@@ -2963,40 +2963,40 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF13" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AG13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH13" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL13" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AN13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO13" t="n">
         <v>25</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>30</v>
       </c>
       <c r="AP13" t="n">
         <v>13</v>
@@ -3008,7 +3008,7 @@
         <v>15.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="AT13" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
         <v>11</v>
       </c>
       <c r="AW13" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AX13" t="n">
         <v>15.5</v>
@@ -3032,29 +3032,29 @@
         <v>15</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BD13" t="n">
         <v>32</v>
       </c>
       <c r="BE13" t="n">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="BF13" t="n">
         <v>20</v>
       </c>
       <c r="BG13" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="G14" t="n">
         <v>1.32</v>
@@ -3094,7 +3094,7 @@
         <v>11</v>
       </c>
       <c r="I14" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="J14" t="n">
         <v>6.4</v>
@@ -3103,19 +3103,19 @@
         <v>7</v>
       </c>
       <c r="L14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M14" t="n">
         <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O14" t="n">
         <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="Q14" t="n">
         <v>1.58</v>
@@ -3124,13 +3124,13 @@
         <v>1.62</v>
       </c>
       <c r="S14" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="T14" t="n">
         <v>2.12</v>
       </c>
       <c r="U14" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="V14" t="n">
         <v>1.08</v>
@@ -3145,7 +3145,7 @@
         <v>44</v>
       </c>
       <c r="Z14" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
@@ -3169,10 +3169,10 @@
         <v>12.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI14" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ14" t="n">
         <v>10.5</v>
@@ -3181,13 +3181,13 @@
         <v>15</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM14" t="n">
         <v>200</v>
       </c>
       <c r="AN14" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
@@ -3196,13 +3196,13 @@
         <v>20</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT14" t="n">
         <v>9</v>
@@ -3211,10 +3211,10 @@
         <v>13</v>
       </c>
       <c r="AV14" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AW14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX14" t="n">
         <v>7.4</v>
@@ -3223,10 +3223,10 @@
         <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>7.4</v>
+        <v>27</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BB14" t="n">
         <v>8.6</v>
@@ -3235,20 +3235,20 @@
         <v>12</v>
       </c>
       <c r="BD14" t="n">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BG14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G15" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H15" t="n">
         <v>2.3</v>
@@ -3291,19 +3291,19 @@
         <v>2.32</v>
       </c>
       <c r="J15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K15" t="n">
         <v>3.7</v>
       </c>
-      <c r="K15" t="n">
-        <v>3.75</v>
-      </c>
       <c r="L15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
         <v>1.29</v>
@@ -3312,7 +3312,7 @@
         <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R15" t="n">
         <v>1.42</v>
@@ -3324,7 +3324,7 @@
         <v>1.73</v>
       </c>
       <c r="U15" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V15" t="n">
         <v>1.76</v>
@@ -3342,13 +3342,13 @@
         <v>15</v>
       </c>
       <c r="AA15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AB15" t="n">
         <v>14</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD15" t="n">
         <v>11</v>
@@ -3393,13 +3393,13 @@
         <v>10</v>
       </c>
       <c r="AR15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS15" t="n">
         <v>26</v>
       </c>
       <c r="AT15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU15" t="n">
         <v>7.8</v>
@@ -3417,7 +3417,7 @@
         <v>13.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA15" t="n">
         <v>32</v>
@@ -3426,13 +3426,13 @@
         <v>48</v>
       </c>
       <c r="BC15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BD15" t="n">
         <v>40</v>
       </c>
       <c r="BE15" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="BF15" t="n">
         <v>29</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="F16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G16" t="n">
         <v>2.12</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2.14</v>
       </c>
       <c r="H16" t="n">
         <v>4</v>
@@ -3485,7 +3485,7 @@
         <v>4.1</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K16" t="n">
         <v>3.6</v>
@@ -3518,16 +3518,16 @@
         <v>1.91</v>
       </c>
       <c r="U16" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V16" t="n">
         <v>1.32</v>
       </c>
       <c r="W16" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="X16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y16" t="n">
         <v>13.5</v>
@@ -3539,7 +3539,7 @@
         <v>85</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC16" t="n">
         <v>7.8</v>
@@ -3566,7 +3566,7 @@
         <v>25</v>
       </c>
       <c r="AK16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL16" t="n">
         <v>42</v>
@@ -3575,7 +3575,7 @@
         <v>120</v>
       </c>
       <c r="AN16" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AO16" t="n">
         <v>60</v>
@@ -3602,7 +3602,7 @@
         <v>15</v>
       </c>
       <c r="AW16" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="AX16" t="n">
         <v>11.5</v>
@@ -3614,7 +3614,7 @@
         <v>17.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="BB16" t="n">
         <v>23</v>
@@ -3626,17 +3626,17 @@
         <v>36</v>
       </c>
       <c r="BE16" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BF16" t="n">
         <v>16.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G17" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H17" t="n">
         <v>6</v>
@@ -3679,10 +3679,10 @@
         <v>6.4</v>
       </c>
       <c r="J17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K17" t="n">
         <v>4.4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.36</v>
@@ -3718,13 +3718,13 @@
         <v>1.18</v>
       </c>
       <c r="W17" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="X17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z17" t="n">
         <v>50</v>
@@ -3742,13 +3742,13 @@
         <v>23</v>
       </c>
       <c r="AE17" t="n">
-        <v>990</v>
+        <v>85</v>
       </c>
       <c r="AF17" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AG17" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH17" t="n">
         <v>21</v>
@@ -3778,10 +3778,10 @@
         <v>16</v>
       </c>
       <c r="AQ17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR17" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AS17" t="n">
         <v>48</v>
@@ -3796,22 +3796,22 @@
         <v>21</v>
       </c>
       <c r="AW17" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AX17" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ17" t="n">
         <v>19</v>
       </c>
       <c r="BA17" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BB17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC17" t="n">
         <v>15</v>
@@ -3820,17 +3820,17 @@
         <v>30</v>
       </c>
       <c r="BE17" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BF17" t="n">
         <v>7.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -3861,37 +3861,37 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="G18" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="I18" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="J18" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K18" t="n">
         <v>3.9</v>
       </c>
       <c r="L18" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="M18" t="n">
         <v>1.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O18" t="n">
         <v>1.46</v>
       </c>
       <c r="P18" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q18" t="n">
         <v>2.36</v>
@@ -3903,10 +3903,10 @@
         <v>4.7</v>
       </c>
       <c r="T18" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V18" t="n">
         <v>1.01</v>
@@ -3918,7 +3918,7 @@
         <v>12</v>
       </c>
       <c r="Y18" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z18" t="n">
         <v>11</v>
@@ -3945,7 +3945,7 @@
         <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
@@ -3969,7 +3969,7 @@
         <v>21</v>
       </c>
       <c r="AP18" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ18" t="n">
         <v>5.5</v>
@@ -3978,7 +3978,7 @@
         <v>7.8</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AT18" t="n">
         <v>11.5</v>
@@ -3987,44 +3987,44 @@
         <v>7.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="AW18" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AX18" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AY18" t="n">
         <v>19</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG18" t="n">
         <v>12.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G19" t="n">
         <v>3.15</v>
       </c>
       <c r="H19" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I19" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J19" t="n">
         <v>3.05</v>
@@ -4073,16 +4073,16 @@
         <v>3.4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M19" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N19" t="n">
         <v>2.68</v>
       </c>
       <c r="O19" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P19" t="n">
         <v>1.57</v>
@@ -4091,19 +4091,19 @@
         <v>2.42</v>
       </c>
       <c r="R19" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T19" t="n">
         <v>1.99</v>
       </c>
       <c r="U19" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W19" t="n">
         <v>1.46</v>
@@ -4112,7 +4112,7 @@
         <v>11</v>
       </c>
       <c r="Y19" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="Z19" t="n">
         <v>1000</v>
@@ -4121,7 +4121,7 @@
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC19" t="n">
         <v>7.6</v>
@@ -4169,13 +4169,13 @@
         <v>7.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AS19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT19" t="n">
         <v>7.6</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>7.8</v>
       </c>
       <c r="AU19" t="n">
         <v>6.2</v>
@@ -4184,7 +4184,7 @@
         <v>11</v>
       </c>
       <c r="AW19" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX19" t="n">
         <v>15.5</v>
@@ -4193,32 +4193,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.6</v>
+        <v>42</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BC19" t="n">
         <v>34</v>
       </c>
       <c r="BD19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE19" t="n">
         <v>7.6</v>
       </c>
-      <c r="BE19" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BF19" t="n">
-        <v>34</v>
+        <v>6.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>32</v>
+        <v>6.8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -4249,25 +4249,25 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="G20" t="n">
         <v>1.97</v>
       </c>
       <c r="H20" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I20" t="n">
         <v>5.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K20" t="n">
         <v>3.75</v>
       </c>
       <c r="L20" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M20" t="n">
         <v>1.09</v>
@@ -4279,7 +4279,7 @@
         <v>1.4</v>
       </c>
       <c r="P20" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q20" t="n">
         <v>2.18</v>
@@ -4291,10 +4291,10 @@
         <v>4.1</v>
       </c>
       <c r="T20" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V20" t="n">
         <v>1.21</v>
@@ -4303,7 +4303,7 @@
         <v>2.02</v>
       </c>
       <c r="X20" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y20" t="n">
         <v>18.5</v>
@@ -4363,7 +4363,7 @@
         <v>12.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AS20" t="n">
         <v>4.2</v>
@@ -4378,7 +4378,7 @@
         <v>17.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX20" t="n">
         <v>9</v>
@@ -4390,7 +4390,7 @@
         <v>19</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB20" t="n">
         <v>18</v>
@@ -4399,7 +4399,7 @@
         <v>19</v>
       </c>
       <c r="BD20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE20" t="n">
         <v>4.2</v>
@@ -4408,11 +4408,11 @@
         <v>12</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -4446,31 +4446,31 @@
         <v>1.67</v>
       </c>
       <c r="G21" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="H21" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I21" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K21" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M21" t="n">
         <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O21" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P21" t="n">
         <v>1.98</v>
@@ -4479,22 +4479,22 @@
         <v>1.99</v>
       </c>
       <c r="R21" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T21" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V21" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W21" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="X21" t="n">
         <v>17.5</v>
@@ -4503,16 +4503,16 @@
         <v>19.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA21" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD21" t="n">
         <v>24</v>
@@ -4527,16 +4527,16 @@
         <v>10.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI21" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ21" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK21" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AL21" t="n">
         <v>40</v>
@@ -4557,34 +4557,34 @@
         <v>16</v>
       </c>
       <c r="AR21" t="n">
-        <v>40</v>
+        <v>7.2</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AT21" t="n">
         <v>7.2</v>
       </c>
       <c r="AU21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV21" t="n">
         <v>19.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AX21" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY21" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BB21" t="n">
         <v>14.5</v>
@@ -4593,20 +4593,20 @@
         <v>16</v>
       </c>
       <c r="BD21" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BE21" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF21" t="n">
         <v>9.4</v>
       </c>
       <c r="BG21" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
         <v>3.8</v>
       </c>
       <c r="K22" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L22" t="n">
         <v>1.38</v>
@@ -4667,7 +4667,7 @@
         <v>1.28</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q22" t="n">
         <v>1.85</v>
@@ -4688,7 +4688,7 @@
         <v>1.36</v>
       </c>
       <c r="W22" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="X22" t="n">
         <v>16</v>
@@ -4700,7 +4700,7 @@
         <v>27</v>
       </c>
       <c r="AA22" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
         <v>11</v>
@@ -4712,7 +4712,7 @@
         <v>15</v>
       </c>
       <c r="AE22" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF22" t="n">
         <v>14.5</v>
@@ -4754,7 +4754,7 @@
         <v>24</v>
       </c>
       <c r="AS22" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AT22" t="n">
         <v>10</v>
@@ -4775,22 +4775,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ22" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB22" t="n">
         <v>23</v>
       </c>
       <c r="BC22" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD22" t="n">
         <v>29</v>
       </c>
       <c r="BE22" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BF22" t="n">
         <v>13</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -4831,13 +4831,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G23" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H23" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I23" t="n">
         <v>3.3</v>
@@ -4864,7 +4864,7 @@
         <v>2.04</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R23" t="n">
         <v>1.4</v>
@@ -4882,10 +4882,10 @@
         <v>1.43</v>
       </c>
       <c r="W23" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X23" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y23" t="n">
         <v>17</v>
@@ -4912,7 +4912,7 @@
         <v>18</v>
       </c>
       <c r="AG23" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH23" t="n">
         <v>20</v>
@@ -4945,10 +4945,10 @@
         <v>12</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AT23" t="n">
         <v>10</v>
@@ -4960,41 +4960,41 @@
         <v>12</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AX23" t="n">
         <v>13.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="BA23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE23" t="n">
         <v>5.1</v>
       </c>
-      <c r="BB23" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BF23" t="n">
-        <v>15.5</v>
+        <v>4.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="G24" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="H24" t="n">
         <v>9.800000000000001</v>
@@ -5049,7 +5049,7 @@
         <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O24" t="n">
         <v>1.29</v>
@@ -5058,7 +5058,7 @@
         <v>2.06</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R24" t="n">
         <v>1.41</v>
@@ -5097,7 +5097,7 @@
         <v>13.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AE24" t="n">
         <v>240</v>
@@ -5115,13 +5115,13 @@
         <v>190</v>
       </c>
       <c r="AJ24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK24" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL24" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM24" t="n">
         <v>240</v>
@@ -5139,10 +5139,10 @@
         <v>24</v>
       </c>
       <c r="AR24" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AS24" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT24" t="n">
         <v>7</v>
@@ -5151,10 +5151,10 @@
         <v>10</v>
       </c>
       <c r="AV24" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX24" t="n">
         <v>7</v>
@@ -5163,10 +5163,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ24" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BA24" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB24" t="n">
         <v>9.800000000000001</v>
@@ -5175,20 +5175,20 @@
         <v>13.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF24" t="n">
         <v>5.9</v>
       </c>
       <c r="BG24" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -5222,16 +5222,16 @@
         <v>1.43</v>
       </c>
       <c r="G25" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="I25" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K25" t="n">
         <v>5.1</v>
@@ -5243,10 +5243,10 @@
         <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P25" t="n">
         <v>2.1</v>
@@ -5261,31 +5261,31 @@
         <v>3.25</v>
       </c>
       <c r="T25" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U25" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V25" t="n">
         <v>1.11</v>
       </c>
       <c r="W25" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="X25" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y25" t="n">
         <v>28</v>
       </c>
       <c r="Z25" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AA25" t="n">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="AB25" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC25" t="n">
         <v>11</v>
@@ -5294,19 +5294,19 @@
         <v>34</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF25" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AG25" t="n">
         <v>10</v>
       </c>
       <c r="AH25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI25" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
         <v>11.5</v>
@@ -5318,10 +5318,10 @@
         <v>40</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN25" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO25" t="n">
         <v>230</v>
@@ -5333,10 +5333,10 @@
         <v>24</v>
       </c>
       <c r="AR25" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="AS25" t="n">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="AT25" t="n">
         <v>7.4</v>
@@ -5351,7 +5351,7 @@
         <v>44</v>
       </c>
       <c r="AX25" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY25" t="n">
         <v>9.6</v>
@@ -5360,7 +5360,7 @@
         <v>25</v>
       </c>
       <c r="BA25" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB25" t="n">
         <v>10.5</v>
@@ -5369,20 +5369,20 @@
         <v>14</v>
       </c>
       <c r="BD25" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE25" t="n">
         <v>46</v>
       </c>
       <c r="BF25" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG25" t="n">
         <v>48</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         </is>
       </c>
       <c r="F26" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G26" t="n">
         <v>2.56</v>
       </c>
-      <c r="G26" t="n">
-        <v>2.6</v>
-      </c>
       <c r="H26" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="I26" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J26" t="n">
         <v>3.65</v>
@@ -5431,40 +5431,40 @@
         <v>3.75</v>
       </c>
       <c r="L26" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M26" t="n">
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="R26" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T26" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U26" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="V26" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X26" t="n">
         <v>16</v>
@@ -5479,16 +5479,16 @@
         <v>46</v>
       </c>
       <c r="AB26" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC26" t="n">
         <v>8</v>
       </c>
       <c r="AD26" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE26" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF26" t="n">
         <v>17</v>
@@ -5497,31 +5497,31 @@
         <v>12</v>
       </c>
       <c r="AH26" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI26" t="n">
         <v>40</v>
       </c>
       <c r="AJ26" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AK26" t="n">
         <v>26</v>
       </c>
       <c r="AL26" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM26" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO26" t="n">
         <v>26</v>
       </c>
-      <c r="AO26" t="n">
-        <v>24</v>
-      </c>
       <c r="AP26" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>12</v>
@@ -5533,7 +5533,7 @@
         <v>26</v>
       </c>
       <c r="AT26" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU26" t="n">
         <v>7.6</v>
@@ -5542,7 +5542,7 @@
         <v>12</v>
       </c>
       <c r="AW26" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AX26" t="n">
         <v>15.5</v>
@@ -5551,32 +5551,32 @@
         <v>11</v>
       </c>
       <c r="AZ26" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BB26" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BC26" t="n">
         <v>24</v>
       </c>
       <c r="BD26" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="BE26" t="n">
         <v>34</v>
       </c>
       <c r="BF26" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG26" t="n">
         <v>22</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
         <v>1.27</v>
       </c>
       <c r="S27" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T27" t="n">
         <v>2.1</v>
@@ -5730,7 +5730,7 @@
         <v>6.8</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV27" t="n">
         <v>19</v>
@@ -5739,7 +5739,7 @@
         <v>34</v>
       </c>
       <c r="AX27" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY27" t="n">
         <v>9.800000000000001</v>
@@ -5760,7 +5760,7 @@
         <v>40</v>
       </c>
       <c r="BE27" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BF27" t="n">
         <v>15</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -5801,10 +5801,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G28" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="H28" t="n">
         <v>5.4</v>
@@ -5813,7 +5813,7 @@
         <v>5.6</v>
       </c>
       <c r="J28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K28" t="n">
         <v>4.3</v>
@@ -5849,7 +5849,7 @@
         <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W28" t="n">
         <v>2.36</v>
@@ -5867,7 +5867,7 @@
         <v>150</v>
       </c>
       <c r="AB28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC28" t="n">
         <v>9</v>
@@ -5954,17 +5954,17 @@
         <v>32</v>
       </c>
       <c r="BE28" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="BF28" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG28" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -6201,10 +6201,10 @@
         <v>5.4</v>
       </c>
       <c r="J30" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K30" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L30" t="n">
         <v>1.46</v>
@@ -6234,7 +6234,7 @@
         <v>2.28</v>
       </c>
       <c r="U30" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V30" t="n">
         <v>1.22</v>
@@ -6249,7 +6249,7 @@
         <v>16</v>
       </c>
       <c r="Z30" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
         <v>180</v>
@@ -6297,7 +6297,7 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>8.4</v>
+        <v>3.15</v>
       </c>
       <c r="AQ30" t="n">
         <v>3.45</v>
@@ -6324,7 +6324,7 @@
         <v>8.6</v>
       </c>
       <c r="AY30" t="n">
-        <v>9.6</v>
+        <v>3.3</v>
       </c>
       <c r="AZ30" t="n">
         <v>3.9</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -6392,13 +6392,13 @@
         <v>4.1</v>
       </c>
       <c r="I31" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J31" t="n">
         <v>3.35</v>
       </c>
       <c r="K31" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L31" t="n">
         <v>1.39</v>
@@ -6422,7 +6422,7 @@
         <v>1.29</v>
       </c>
       <c r="S31" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="T31" t="n">
         <v>1.89</v>
@@ -6431,7 +6431,7 @@
         <v>1.96</v>
       </c>
       <c r="V31" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W31" t="n">
         <v>1.9</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -6577,16 +6577,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H32" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I32" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J32" t="n">
         <v>3.6</v>
@@ -6607,10 +6607,10 @@
         <v>1.34</v>
       </c>
       <c r="P32" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="Q32" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R32" t="n">
         <v>1.35</v>
@@ -6625,7 +6625,7 @@
         <v>2.04</v>
       </c>
       <c r="V32" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W32" t="n">
         <v>2</v>
@@ -6715,7 +6715,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ32" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA32" t="n">
         <v>7.6</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -6804,19 +6804,19 @@
         <v>2.56</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R33" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S33" t="n">
         <v>2.44</v>
       </c>
       <c r="T33" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="U33" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="V33" t="n">
         <v>1.04</v>
@@ -6825,70 +6825,70 @@
         <v>5.5</v>
       </c>
       <c r="X33" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="Y33" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AA33" t="n">
         <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AD33" t="n">
         <v>90</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>530</v>
       </c>
       <c r="AF33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>360</v>
+      </c>
+      <c r="AJ33" t="n">
         <v>8.4</v>
       </c>
-      <c r="AG33" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH33" t="n">
+      <c r="AK33" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL33" t="n">
         <v>55</v>
       </c>
-      <c r="AI33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>65</v>
-      </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AN33" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AO33" t="n">
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AQ33" t="n">
-        <v>5.5</v>
+        <v>38</v>
       </c>
       <c r="AR33" t="n">
-        <v>5.9</v>
+        <v>11</v>
       </c>
       <c r="AS33" t="n">
-        <v>5.9</v>
+        <v>12</v>
       </c>
       <c r="AT33" t="n">
         <v>8.199999999999999</v>
@@ -6897,10 +6897,10 @@
         <v>15.5</v>
       </c>
       <c r="AV33" t="n">
-        <v>5.6</v>
+        <v>10.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>5.9</v>
+        <v>11.5</v>
       </c>
       <c r="AX33" t="n">
         <v>6.4</v>
@@ -6909,10 +6909,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ33" t="n">
-        <v>5.4</v>
+        <v>38</v>
       </c>
       <c r="BA33" t="n">
-        <v>5.9</v>
+        <v>11.5</v>
       </c>
       <c r="BB33" t="n">
         <v>7.6</v>
@@ -6921,20 +6921,20 @@
         <v>12.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>5.5</v>
+        <v>36</v>
       </c>
       <c r="BE33" t="n">
-        <v>5.9</v>
+        <v>11.5</v>
       </c>
       <c r="BF33" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BG33" t="n">
-        <v>5.9</v>
+        <v>12</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G35" t="n">
         <v>1.79</v>
@@ -7177,7 +7177,7 @@
         <v>3.85</v>
       </c>
       <c r="L35" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M35" t="n">
         <v>1.09</v>
@@ -7222,7 +7222,7 @@
         <v>55</v>
       </c>
       <c r="AA35" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AB35" t="n">
         <v>7</v>
@@ -7267,7 +7267,7 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>9.4</v>
+        <v>5.1</v>
       </c>
       <c r="AQ35" t="n">
         <v>5.7</v>
@@ -7294,7 +7294,7 @@
         <v>8.4</v>
       </c>
       <c r="AY35" t="n">
-        <v>9</v>
+        <v>4.7</v>
       </c>
       <c r="AZ35" t="n">
         <v>6.4</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -7362,7 +7362,7 @@
         <v>2.14</v>
       </c>
       <c r="I36" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="J36" t="n">
         <v>3.2</v>
@@ -7371,7 +7371,7 @@
         <v>3.6</v>
       </c>
       <c r="L36" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="M36" t="n">
         <v>1.09</v>
@@ -7392,7 +7392,7 @@
         <v>1.26</v>
       </c>
       <c r="S36" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="T36" t="n">
         <v>1.92</v>
@@ -7401,7 +7401,7 @@
         <v>1.92</v>
       </c>
       <c r="V36" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W36" t="n">
         <v>1.32</v>
@@ -7464,7 +7464,7 @@
         <v>3.25</v>
       </c>
       <c r="AQ36" t="n">
-        <v>6.8</v>
+        <v>3</v>
       </c>
       <c r="AR36" t="n">
         <v>3.4</v>
@@ -7476,7 +7476,7 @@
         <v>3.35</v>
       </c>
       <c r="AU36" t="n">
-        <v>6.6</v>
+        <v>2.94</v>
       </c>
       <c r="AV36" t="n">
         <v>3.25</v>
@@ -7506,7 +7506,7 @@
         <v>4.1</v>
       </c>
       <c r="BE36" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF36" t="n">
         <v>4.1</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G37" t="n">
         <v>3.85</v>
@@ -7556,10 +7556,10 @@
         <v>2.28</v>
       </c>
       <c r="I37" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="J37" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K37" t="n">
         <v>3.4</v>
@@ -7586,7 +7586,7 @@
         <v>1.26</v>
       </c>
       <c r="S37" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T37" t="n">
         <v>1.96</v>
@@ -7601,13 +7601,13 @@
         <v>1.35</v>
       </c>
       <c r="X37" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Y37" t="n">
         <v>8.4</v>
       </c>
       <c r="Z37" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AA37" t="n">
         <v>32</v>
@@ -7616,10 +7616,10 @@
         <v>12</v>
       </c>
       <c r="AC37" t="n">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AD37" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AE37" t="n">
         <v>28</v>
@@ -7628,22 +7628,22 @@
         <v>26</v>
       </c>
       <c r="AG37" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AH37" t="n">
         <v>21</v>
       </c>
       <c r="AI37" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ37" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AK37" t="n">
         <v>55</v>
       </c>
       <c r="AL37" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM37" t="n">
         <v>140</v>
@@ -7652,34 +7652,34 @@
         <v>65</v>
       </c>
       <c r="AO37" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP37" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ37" t="n">
         <v>7.6</v>
       </c>
       <c r="AR37" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AT37" t="n">
         <v>10.5</v>
       </c>
       <c r="AU37" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV37" t="n">
         <v>10</v>
       </c>
       <c r="AW37" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AX37" t="n">
-        <v>9.800000000000001</v>
+        <v>22</v>
       </c>
       <c r="AY37" t="n">
         <v>13.5</v>
@@ -7688,29 +7688,29 @@
         <v>17.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB37" t="n">
-        <v>3.65</v>
+        <v>13</v>
       </c>
       <c r="BC37" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BD37" t="n">
-        <v>7.2</v>
+        <v>42</v>
       </c>
       <c r="BE37" t="n">
-        <v>3.75</v>
+        <v>13.5</v>
       </c>
       <c r="BF37" t="n">
-        <v>3.65</v>
+        <v>12.5</v>
       </c>
       <c r="BG37" t="n">
         <v>9.6</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>
@@ -7744,55 +7744,55 @@
         <v>2.06</v>
       </c>
       <c r="G38" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="H38" t="n">
         <v>3.7</v>
       </c>
       <c r="I38" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J38" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K38" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L38" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M38" t="n">
         <v>1.07</v>
       </c>
       <c r="N38" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O38" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P38" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="R38" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S38" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="T38" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U38" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V38" t="n">
         <v>1.32</v>
       </c>
       <c r="W38" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="X38" t="n">
         <v>970</v>
@@ -7807,7 +7807,7 @@
         <v>110</v>
       </c>
       <c r="AB38" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AC38" t="n">
         <v>970</v>
@@ -7858,19 +7858,19 @@
         <v>7.2</v>
       </c>
       <c r="AS38" t="n">
-        <v>5.6</v>
+        <v>1.81</v>
       </c>
       <c r="AT38" t="n">
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="AU38" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="AV38" t="n">
         <v>5.9</v>
       </c>
       <c r="AW38" t="n">
-        <v>7.8</v>
+        <v>4.1</v>
       </c>
       <c r="AX38" t="n">
         <v>5.5</v>
@@ -7882,29 +7882,29 @@
         <v>6</v>
       </c>
       <c r="BA38" t="n">
-        <v>7.8</v>
+        <v>2.2</v>
       </c>
       <c r="BB38" t="n">
-        <v>18.5</v>
+        <v>6.8</v>
       </c>
       <c r="BC38" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD38" t="n">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="BE38" t="n">
         <v>8.4</v>
       </c>
       <c r="BF38" t="n">
-        <v>12</v>
+        <v>5.9</v>
       </c>
       <c r="BG38" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-18 14:02:38</t>
+          <t>2026-03-18 16:46:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH38"/>
+  <dimension ref="A1:BH39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="G3" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="J3" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="K3" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -981,25 +981,25 @@
         <v>1.31</v>
       </c>
       <c r="P3" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
         <v>3.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="U3" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="V3" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="W3" t="n">
         <v>1.05</v>
@@ -1059,62 +1059,62 @@
         <v>6.8</v>
       </c>
       <c r="AP3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV3" t="n">
         <v>4.5</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AW3" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
         <v>3.55</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
         <v>1.4</v>
@@ -1172,31 +1172,31 @@
         <v>3.85</v>
       </c>
       <c r="O4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P4" t="n">
         <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R4" t="n">
         <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T4" t="n">
         <v>1.75</v>
       </c>
       <c r="U4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X4" t="n">
         <v>14.5</v>
@@ -1214,13 +1214,13 @@
         <v>10</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF4" t="n">
         <v>13.5</v>
@@ -1253,7 +1253,7 @@
         <v>44</v>
       </c>
       <c r="AP4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ4" t="n">
         <v>13.5</v>
@@ -1262,31 +1262,31 @@
         <v>24</v>
       </c>
       <c r="AS4" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="AT4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW4" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AX4" t="n">
         <v>12</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
         <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BB4" t="n">
         <v>24</v>
@@ -1298,17 +1298,17 @@
         <v>32</v>
       </c>
       <c r="BE4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BF4" t="n">
         <v>14.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>1.32</v>
       </c>
       <c r="G5" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="H5" t="n">
         <v>9.199999999999999</v>
@@ -1360,22 +1360,22 @@
         <v>1.3</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O5" t="n">
         <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
         <v>1.63</v>
       </c>
       <c r="R5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
         <v>2.6</v>
@@ -1384,13 +1384,13 @@
         <v>2.14</v>
       </c>
       <c r="U5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V5" t="n">
         <v>1.06</v>
       </c>
       <c r="W5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X5" t="n">
         <v>950</v>
@@ -1441,16 +1441,16 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AR5" t="n">
         <v>4.2</v>
@@ -1462,7 +1462,7 @@
         <v>6</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.45</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV5" t="n">
         <v>4</v>
@@ -1474,7 +1474,7 @@
         <v>5.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.4</v>
+        <v>7.8</v>
       </c>
       <c r="AZ5" t="n">
         <v>3.95</v>
@@ -1486,7 +1486,7 @@
         <v>3.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BD5" t="n">
         <v>4</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
         <v>17</v>
       </c>
       <c r="H6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="I6" t="n">
         <v>1.29</v>
@@ -1566,7 +1566,7 @@
         <v>2.52</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.06</v>
+        <v>1.49</v>
       </c>
       <c r="G7" t="n">
-        <v>1.99</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="I7" t="n">
-        <v>870</v>
+        <v>19</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="K7" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1754,7 +1754,7 @@
         <v>1.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P7" t="n">
         <v>1.24</v>
@@ -1766,19 +1766,19 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="T7" t="n">
         <v>1.69</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="V7" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1838,66 +1838,66 @@
         <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ukrainian Premier League</t>
+          <t>Estonian Esiliiga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,73 +1912,73 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Metalist 1925</t>
+          <t>Flora Tallinn II</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Nomme Kalju II</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="G8" t="n">
-        <v>1.13</v>
+        <v>990</v>
       </c>
       <c r="H8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I8" t="n">
+        <v>990</v>
+      </c>
+      <c r="J8" t="n">
         <v>1.04</v>
       </c>
-      <c r="I8" t="n">
-        <v>55</v>
-      </c>
-      <c r="J8" t="n">
-        <v>6.6</v>
-      </c>
       <c r="K8" t="n">
-        <v>14</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V8" t="n">
         <v>1.02</v>
       </c>
-      <c r="N8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W8" t="n">
-        <v>5.9</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -1987,10 +1987,10 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
@@ -1999,99 +1999,99 @@
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.78</v>
+        <v>1.02</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.2</v>
+        <v>1.02</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,184 +2101,184 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Metalist 1925</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kasimpasa</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="G9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H9" t="n">
+        <v>34</v>
+      </c>
+      <c r="I9" t="n">
+        <v>50</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
         <v>1.4</v>
       </c>
-      <c r="H9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="I9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.97</v>
-      </c>
       <c r="V9" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>3.45</v>
+        <v>8.6</v>
       </c>
       <c r="X9" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="Y9" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="Z9" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>12.5</v>
+        <v>34</v>
       </c>
       <c r="AD9" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>10.5</v>
+        <v>21</v>
       </c>
       <c r="AH9" t="n">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL9" t="n">
         <v>120</v>
       </c>
-      <c r="AJ9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>34</v>
-      </c>
       <c r="AM9" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>5.5</v>
+        <v>3.55</v>
       </c>
       <c r="AO9" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>20</v>
+        <v>4.7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>30</v>
+        <v>4.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="AS9" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AT9" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AV9" t="n">
-        <v>30</v>
+        <v>4.9</v>
       </c>
       <c r="AW9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY9" t="n">
         <v>13</v>
       </c>
-      <c r="AX9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ9" t="n">
-        <v>21</v>
+        <v>4.8</v>
       </c>
       <c r="BA9" t="n">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="BB9" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="BC9" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>28</v>
+        <v>4.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.8</v>
+        <v>2.76</v>
       </c>
       <c r="BG9" t="n">
-        <v>11.5</v>
+        <v>5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Genclerbirligi</t>
+          <t>Kasimpasa</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.83</v>
+        <v>1.37</v>
       </c>
       <c r="G10" t="n">
-        <v>1.9</v>
+        <v>1.39</v>
       </c>
       <c r="H10" t="n">
-        <v>5.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="J10" t="n">
-        <v>3.55</v>
+        <v>5.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="M10" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="O10" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>2.28</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>1.69</v>
       </c>
       <c r="R10" t="n">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="S10" t="n">
-        <v>3.7</v>
+        <v>2.74</v>
       </c>
       <c r="T10" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="U10" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="V10" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="X10" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>95</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>370</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC10" t="n">
         <v>12</v>
       </c>
-      <c r="Y10" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC10" t="n">
+      <c r="AD10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF10" t="n">
         <v>8.4</v>
       </c>
-      <c r="AD10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>11</v>
-      </c>
       <c r="AG10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AI10" t="n">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="AJ10" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AL10" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AM10" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN10" t="n">
-        <v>15</v>
+        <v>6.4</v>
       </c>
       <c r="AO10" t="n">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="AP10" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.5</v>
+        <v>27</v>
       </c>
       <c r="AR10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD10" t="n">
         <v>32</v>
       </c>
-      <c r="AS10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>10</v>
-      </c>
       <c r="BE10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG10" t="n">
         <v>12.5</v>
       </c>
-      <c r="BG10" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,184 +2489,184 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Genclerbirligi</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.4</v>
+        <v>1.84</v>
       </c>
       <c r="G11" t="n">
-        <v>1.42</v>
+        <v>1.89</v>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>5.2</v>
       </c>
       <c r="I11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="X11" t="n">
         <v>12</v>
       </c>
-      <c r="J11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="X11" t="n">
-        <v>20</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z11" t="n">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="AA11" t="n">
-        <v>550</v>
+        <v>140</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE11" t="n">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="AF11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG11" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AJ11" t="n">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="AK11" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM11" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="AN11" t="n">
-        <v>7.8</v>
+        <v>15</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>14.5</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AR11" t="n">
-        <v>5.8</v>
+        <v>25</v>
       </c>
       <c r="AS11" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AV11" t="n">
-        <v>5.3</v>
+        <v>19</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="AY11" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.2</v>
+        <v>18</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.9</v>
+        <v>11.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.6</v>
+        <v>18</v>
       </c>
       <c r="BC11" t="n">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.9</v>
+        <v>11.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BG11" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.9</v>
+        <v>1.38</v>
       </c>
       <c r="G12" t="n">
-        <v>6.4</v>
+        <v>1.4</v>
       </c>
       <c r="H12" t="n">
-        <v>1.63</v>
+        <v>10</v>
       </c>
       <c r="I12" t="n">
-        <v>1.66</v>
+        <v>11.5</v>
       </c>
       <c r="J12" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="K12" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M12" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="P12" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="U12" t="n">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="V12" t="n">
-        <v>2.5</v>
+        <v>1.09</v>
       </c>
       <c r="W12" t="n">
-        <v>1.18</v>
+        <v>3.5</v>
       </c>
       <c r="X12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>680</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>220</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>260</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>330</v>
+      </c>
+      <c r="AP12" t="n">
         <v>15</v>
       </c>
-      <c r="Y12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA12" t="n">
+      <c r="AQ12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AW12" t="n">
         <v>16</v>
       </c>
-      <c r="AB12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC12" t="n">
+      <c r="AX12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY12" t="n">
         <v>9.6</v>
       </c>
-      <c r="AD12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>50</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>220</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>95</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>150</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>17</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>40</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>21</v>
-      </c>
       <c r="AZ12" t="n">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>34</v>
+        <v>15.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>15.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC12" t="n">
         <v>14.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>14.5</v>
+        <v>34</v>
       </c>
       <c r="BE12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BF12" t="n">
-        <v>15.5</v>
+        <v>6.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>9.6</v>
+        <v>16</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
@@ -2882,179 +2882,179 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Rakow Czestochowa</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.68</v>
+        <v>5.9</v>
       </c>
       <c r="G13" t="n">
-        <v>2.78</v>
+        <v>6.4</v>
       </c>
       <c r="H13" t="n">
-        <v>2.76</v>
+        <v>1.62</v>
       </c>
       <c r="I13" t="n">
-        <v>2.86</v>
+        <v>1.66</v>
       </c>
       <c r="J13" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="L13" t="n">
         <v>1.39</v>
       </c>
       <c r="M13" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="O13" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="R13" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="T13" t="n">
-        <v>1.74</v>
+        <v>2.04</v>
       </c>
       <c r="U13" t="n">
-        <v>2.24</v>
+        <v>1.89</v>
       </c>
       <c r="V13" t="n">
-        <v>1.54</v>
+        <v>2.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.56</v>
+        <v>1.18</v>
       </c>
       <c r="X13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AB13" t="n">
         <v>19</v>
       </c>
-      <c r="Y13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AC13" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>190</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>95</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>130</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP13" t="n">
         <v>13.5</v>
       </c>
-      <c r="AE13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>13</v>
-      </c>
       <c r="AQ13" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>15.5</v>
+        <v>8</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV13" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>15.5</v>
+        <v>40</v>
       </c>
       <c r="AY13" t="n">
-        <v>10.5</v>
+        <v>22</v>
       </c>
       <c r="AZ13" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC13" t="n">
         <v>15</v>
       </c>
-      <c r="BA13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>21</v>
-      </c>
       <c r="BD13" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.4</v>
+        <v>16</v>
       </c>
       <c r="BF13" t="n">
         <v>20</v>
       </c>
       <c r="BG13" t="n">
-        <v>20</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Rakow Czestochowa</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>NK Celje</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.28</v>
+        <v>2.68</v>
       </c>
       <c r="G14" t="n">
-        <v>1.32</v>
+        <v>2.78</v>
       </c>
       <c r="H14" t="n">
-        <v>11</v>
+        <v>2.78</v>
       </c>
       <c r="I14" t="n">
-        <v>14.5</v>
+        <v>2.86</v>
       </c>
       <c r="J14" t="n">
-        <v>6.4</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>3.65</v>
       </c>
       <c r="L14" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="M14" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>5.4</v>
+        <v>3.85</v>
       </c>
       <c r="O14" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="P14" t="n">
-        <v>2.52</v>
+        <v>1.97</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.58</v>
+        <v>1.94</v>
       </c>
       <c r="R14" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>2.42</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.78</v>
+        <v>2.22</v>
       </c>
       <c r="V14" t="n">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="W14" t="n">
-        <v>4.1</v>
+        <v>1.56</v>
       </c>
       <c r="X14" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE14" t="n">
         <v>32</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AF14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI14" t="n">
         <v>44</v>
       </c>
-      <c r="Z14" t="n">
-        <v>130</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>48</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>230</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH14" t="n">
+      <c r="AJ14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA14" t="n">
         <v>34</v>
       </c>
-      <c r="AI14" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>27</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>8</v>
-      </c>
       <c r="BB14" t="n">
-        <v>8.6</v>
+        <v>34</v>
       </c>
       <c r="BC14" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="BD14" t="n">
         <v>32</v>
       </c>
       <c r="BE14" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.95</v>
+        <v>20</v>
       </c>
       <c r="BG14" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,179 +3270,179 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>NK Celje</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.4</v>
+        <v>1.29</v>
       </c>
       <c r="G15" t="n">
-        <v>3.45</v>
+        <v>1.31</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3</v>
+        <v>11</v>
       </c>
       <c r="I15" t="n">
-        <v>2.32</v>
+        <v>14</v>
       </c>
       <c r="J15" t="n">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="K15" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="P15" t="n">
-        <v>2.08</v>
+        <v>2.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.88</v>
+        <v>1.58</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>2.44</v>
       </c>
       <c r="T15" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="U15" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="V15" t="n">
-        <v>1.76</v>
+        <v>1.08</v>
       </c>
       <c r="W15" t="n">
-        <v>1.41</v>
+        <v>4.1</v>
       </c>
       <c r="X15" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>140</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>230</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK15" t="n">
         <v>15.5</v>
       </c>
-      <c r="Y15" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>29</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC15" t="n">
+      <c r="AL15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS15" t="n">
         <v>8</v>
       </c>
-      <c r="AD15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN15" t="n">
+      <c r="AT15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>27</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD15" t="n">
         <v>32</v>
       </c>
-      <c r="AO15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU15" t="n">
+      <c r="BE15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG15" t="n">
         <v>7.8</v>
       </c>
-      <c r="AV15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>48</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>29</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
@@ -3464,179 +3464,179 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.1</v>
+        <v>3.35</v>
       </c>
       <c r="G16" t="n">
-        <v>2.12</v>
+        <v>3.4</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>2.36</v>
       </c>
       <c r="I16" t="n">
-        <v>4.1</v>
+        <v>2.38</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L16" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="M16" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="P16" t="n">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="R16" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="T16" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="U16" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="V16" t="n">
-        <v>1.32</v>
+        <v>1.73</v>
       </c>
       <c r="W16" t="n">
-        <v>1.89</v>
+        <v>1.42</v>
       </c>
       <c r="X16" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="Y16" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>27</v>
+        <v>15.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.6</v>
+        <v>14</v>
       </c>
       <c r="AC16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU16" t="n">
         <v>7.8</v>
       </c>
-      <c r="AD16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AV16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>15</v>
       </c>
-      <c r="AW16" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BA16" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BB16" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="BC16" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="BD16" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BE16" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BF16" t="n">
-        <v>16.5</v>
+        <v>29</v>
       </c>
       <c r="BG16" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Genk</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="G17" t="n">
-        <v>1.65</v>
+        <v>2.12</v>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="J17" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="L17" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="P17" t="n">
-        <v>2.16</v>
+        <v>1.84</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="R17" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="S17" t="n">
-        <v>3.05</v>
+        <v>3.95</v>
       </c>
       <c r="T17" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U17" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V17" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="W17" t="n">
-        <v>2.52</v>
+        <v>1.89</v>
       </c>
       <c r="X17" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="Z17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG17" t="n">
         <v>50</v>
       </c>
-      <c r="AA17" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>46</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>48</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>70</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>44</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>60</v>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Genk</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5.9</v>
+        <v>1.64</v>
       </c>
       <c r="G18" t="n">
-        <v>8.199999999999999</v>
+        <v>1.66</v>
       </c>
       <c r="H18" t="n">
-        <v>1.69</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>1.83</v>
+        <v>6.2</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>2.76</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.46</v>
       </c>
-      <c r="P18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.21</v>
-      </c>
       <c r="S18" t="n">
-        <v>4.7</v>
+        <v>3.05</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="U18" t="n">
-        <v>1.69</v>
+        <v>2.08</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="X18" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="Y18" t="n">
-        <v>7.4</v>
+        <v>22</v>
       </c>
       <c r="Z18" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="AA18" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD18" t="n">
         <v>23</v>
       </c>
-      <c r="AB18" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AC18" t="n">
+      <c r="AE18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG18" t="n">
         <v>10</v>
       </c>
-      <c r="AD18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1000</v>
-      </c>
       <c r="AH18" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AO18" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV18" t="n">
         <v>21</v>
       </c>
-      <c r="AP18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AR18" t="n">
+      <c r="AW18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF18" t="n">
         <v>7.8</v>
       </c>
-      <c r="AS18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BG18" t="n">
-        <v>12.5</v>
+        <v>70</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,105 +4041,105 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Dinamo Bucharest</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Universitatea Craiova</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.82</v>
+        <v>5.9</v>
       </c>
       <c r="G19" t="n">
-        <v>3.15</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>2.68</v>
+        <v>1.69</v>
       </c>
       <c r="I19" t="n">
-        <v>2.96</v>
+        <v>1.83</v>
       </c>
       <c r="J19" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="K19" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="M19" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="O19" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="P19" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="R19" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S19" t="n">
         <v>4.7</v>
       </c>
       <c r="T19" t="n">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="V19" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z19" t="n">
         <v>11</v>
       </c>
-      <c r="Y19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1000</v>
-      </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AB19" t="n">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AD19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF19" t="n">
         <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
@@ -4160,72 +4160,72 @@
         <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>15</v>
+        <v>7.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="AT19" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>11</v>
+        <v>3.65</v>
       </c>
       <c r="AW19" t="n">
-        <v>6.8</v>
+        <v>3.95</v>
       </c>
       <c r="AX19" t="n">
-        <v>15.5</v>
+        <v>4.2</v>
       </c>
       <c r="AY19" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AZ19" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="BA19" t="n">
-        <v>42</v>
+        <v>4.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>34</v>
+        <v>4.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Dinamo Bucharest</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tecnico Universitario</t>
+          <t>Universitatea Craiova</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.84</v>
+        <v>2.88</v>
       </c>
       <c r="G20" t="n">
-        <v>1.97</v>
+        <v>3.1</v>
       </c>
       <c r="H20" t="n">
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="I20" t="n">
-        <v>5.8</v>
+        <v>2.96</v>
       </c>
       <c r="J20" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="K20" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="L20" t="n">
         <v>1.47</v>
       </c>
       <c r="M20" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="O20" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="P20" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.18</v>
+        <v>2.46</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S20" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U20" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V20" t="n">
-        <v>1.21</v>
+        <v>1.51</v>
       </c>
       <c r="W20" t="n">
-        <v>2.02</v>
+        <v>1.47</v>
       </c>
       <c r="X20" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>18.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z20" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="AA20" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD20" t="n">
-        <v>26</v>
+        <v>15.5</v>
       </c>
       <c r="AE20" t="n">
         <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AG20" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="AH20" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI20" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>12.5</v>
+        <v>7.2</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.1</v>
+        <v>15</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AT20" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV20" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AX20" t="n">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ20" t="n">
-        <v>19</v>
+        <v>4.8</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BB20" t="n">
-        <v>18</v>
+        <v>4.9</v>
       </c>
       <c r="BC20" t="n">
-        <v>19</v>
+        <v>4.9</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF20" t="n">
-        <v>12</v>
+        <v>4.9</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,184 +4429,184 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Tecnico Universitario</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="G21" t="n">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="H21" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="I21" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S21" t="n">
         <v>4.1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.55</v>
       </c>
       <c r="T21" t="n">
         <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W21" t="n">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="X21" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Z21" t="n">
         <v>48</v>
       </c>
       <c r="AA21" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AB21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX21" t="n">
         <v>9</v>
       </c>
-      <c r="AC21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AY21" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ21" t="n">
         <v>19</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="BC21" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BD21" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>7.8</v>
+        <v>4.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="BG21" t="n">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
@@ -4628,179 +4628,179 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Shakhtar</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lech Poznan</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.12</v>
+        <v>1.69</v>
       </c>
       <c r="G22" t="n">
-        <v>2.18</v>
+        <v>1.72</v>
       </c>
       <c r="H22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S22" t="n">
         <v>3.6</v>
       </c>
-      <c r="I22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.15</v>
-      </c>
       <c r="T22" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>2.26</v>
+        <v>1.92</v>
       </c>
       <c r="V22" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="W22" t="n">
-        <v>1.85</v>
+        <v>2.34</v>
       </c>
       <c r="X22" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="Z22" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF22" t="n">
         <v>11</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>14.5</v>
       </c>
       <c r="AG22" t="n">
         <v>10.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AI22" t="n">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="AJ22" t="n">
-        <v>32</v>
+        <v>17.5</v>
       </c>
       <c r="AK22" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AL22" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AM22" t="n">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="AN22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB22" t="n">
         <v>14.5</v>
       </c>
-      <c r="AO22" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU22" t="n">
+      <c r="BC22" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD22" t="n">
         <v>7.8</v>
       </c>
-      <c r="AV22" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>29</v>
-      </c>
       <c r="BE22" t="n">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF22" t="n">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="BG22" t="n">
-        <v>30</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
@@ -4822,179 +4822,179 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sparta Prague</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Az Alkmaar</t>
+          <t>Lech Poznan</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="G23" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="H23" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="I23" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="J23" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K23" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="L23" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M23" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P23" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S23" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T23" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="U23" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V23" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="W23" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="X23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y23" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH23" t="n">
         <v>17</v>
       </c>
-      <c r="Z23" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>20</v>
-      </c>
       <c r="AI23" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO23" t="n">
         <v>36</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>42</v>
       </c>
       <c r="AP23" t="n">
         <v>15</v>
       </c>
       <c r="AQ23" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>5.3</v>
+        <v>24</v>
       </c>
       <c r="AS23" t="n">
-        <v>5</v>
+        <v>14.5</v>
       </c>
       <c r="AT23" t="n">
         <v>10</v>
       </c>
       <c r="AU23" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AV23" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.8</v>
+        <v>34</v>
       </c>
       <c r="AX23" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ23" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.9</v>
+        <v>13</v>
       </c>
       <c r="BB23" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BC23" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.8</v>
+        <v>29</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.1</v>
+        <v>13</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>22</v>
+        <v>10.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Sparta Prague</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Az Alkmaar</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.4</v>
+        <v>2.38</v>
       </c>
       <c r="G24" t="n">
-        <v>1.43</v>
+        <v>2.42</v>
       </c>
       <c r="H24" t="n">
-        <v>9.800000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="I24" t="n">
-        <v>11</v>
+        <v>3.3</v>
       </c>
       <c r="J24" t="n">
-        <v>5.1</v>
+        <v>3.55</v>
       </c>
       <c r="K24" t="n">
-        <v>5.3</v>
+        <v>3.75</v>
       </c>
       <c r="L24" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M24" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N24" t="n">
         <v>4.2</v>
       </c>
       <c r="O24" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P24" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="R24" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T24" t="n">
-        <v>2.22</v>
+        <v>1.69</v>
       </c>
       <c r="U24" t="n">
-        <v>1.74</v>
+        <v>2.32</v>
       </c>
       <c r="V24" t="n">
-        <v>1.1</v>
+        <v>1.43</v>
       </c>
       <c r="W24" t="n">
-        <v>3.35</v>
+        <v>1.7</v>
       </c>
       <c r="X24" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y24" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="Z24" t="n">
-        <v>120</v>
+        <v>26</v>
       </c>
       <c r="AA24" t="n">
-        <v>550</v>
+        <v>70</v>
       </c>
       <c r="AB24" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AC24" t="n">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="AE24" t="n">
-        <v>240</v>
+        <v>42</v>
       </c>
       <c r="AF24" t="n">
-        <v>8</v>
+        <v>18.5</v>
       </c>
       <c r="AG24" t="n">
         <v>13</v>
       </c>
       <c r="AH24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>36</v>
       </c>
-      <c r="AI24" t="n">
-        <v>190</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AK24" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="AL24" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AM24" t="n">
-        <v>240</v>
+        <v>95</v>
       </c>
       <c r="AN24" t="n">
-        <v>6.8</v>
+        <v>19.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>14</v>
       </c>
-      <c r="AQ24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>23</v>
-      </c>
       <c r="BA24" t="n">
-        <v>7.4</v>
+        <v>36</v>
       </c>
       <c r="BB24" t="n">
-        <v>9.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="BD24" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="BG24" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,31 +5210,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G25" t="n">
         <v>1.43</v>
       </c>
-      <c r="G25" t="n">
-        <v>1.44</v>
-      </c>
       <c r="H25" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="I25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J25" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K25" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L25" t="n">
         <v>1.38</v>
@@ -5243,13 +5243,13 @@
         <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O25" t="n">
         <v>1.28</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q25" t="n">
         <v>1.86</v>
@@ -5258,85 +5258,85 @@
         <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T25" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="U25" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="V25" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W25" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="X25" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="Y25" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Z25" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AA25" t="n">
-        <v>320</v>
+        <v>450</v>
       </c>
       <c r="AB25" t="n">
         <v>8</v>
       </c>
       <c r="AC25" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AE25" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AF25" t="n">
         <v>7.8</v>
       </c>
       <c r="AG25" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ25" t="n">
         <v>11.5</v>
       </c>
       <c r="AK25" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AL25" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM25" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="AN25" t="n">
         <v>6.8</v>
       </c>
       <c r="AO25" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AP25" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ25" t="n">
         <v>24</v>
       </c>
       <c r="AR25" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AS25" t="n">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="AT25" t="n">
         <v>7.4</v>
@@ -5345,10 +5345,10 @@
         <v>10</v>
       </c>
       <c r="AV25" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AW25" t="n">
-        <v>44</v>
+        <v>13.5</v>
       </c>
       <c r="AX25" t="n">
         <v>7.2</v>
@@ -5357,32 +5357,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA25" t="n">
-        <v>44</v>
+        <v>13.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG25" t="n">
         <v>14</v>
       </c>
-      <c r="BD25" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>46</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>48</v>
-      </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
@@ -5404,179 +5404,179 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.54</v>
+        <v>1.43</v>
       </c>
       <c r="G26" t="n">
-        <v>2.56</v>
+        <v>1.44</v>
       </c>
       <c r="H26" t="n">
-        <v>2.94</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>2.98</v>
+        <v>10.5</v>
       </c>
       <c r="J26" t="n">
-        <v>3.65</v>
+        <v>4.9</v>
       </c>
       <c r="K26" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="L26" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M26" t="n">
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O26" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P26" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W26" t="n">
         <v>3.25</v>
       </c>
-      <c r="T26" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.64</v>
-      </c>
       <c r="X26" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="Z26" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="AA26" t="n">
+        <v>370</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>230</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>90</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE26" t="n">
         <v>46</v>
       </c>
-      <c r="AB26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>25</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>34</v>
-      </c>
       <c r="BF26" t="n">
-        <v>18.5</v>
+        <v>6.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
@@ -5598,179 +5598,179 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.87</v>
+        <v>2.6</v>
       </c>
       <c r="G27" t="n">
-        <v>1.89</v>
+        <v>2.62</v>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="I27" t="n">
-        <v>5.2</v>
+        <v>2.92</v>
       </c>
       <c r="J27" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K27" t="n">
         <v>3.7</v>
       </c>
       <c r="L27" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="M27" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="P27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T27" t="n">
         <v>1.74</v>
       </c>
-      <c r="Q27" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S27" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.1</v>
-      </c>
       <c r="U27" t="n">
-        <v>1.86</v>
+        <v>2.26</v>
       </c>
       <c r="V27" t="n">
-        <v>1.23</v>
+        <v>1.52</v>
       </c>
       <c r="W27" t="n">
-        <v>2.12</v>
+        <v>1.61</v>
       </c>
       <c r="X27" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Y27" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB27" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="AC27" t="n">
         <v>8</v>
       </c>
       <c r="AD27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN27" t="n">
         <v>21</v>
       </c>
-      <c r="AE27" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG27" t="n">
+      <c r="AO27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT27" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH27" t="n">
+      <c r="AU27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB27" t="n">
         <v>23</v>
       </c>
-      <c r="AI27" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK27" t="n">
+      <c r="BC27" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>70</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BG27" t="n">
         <v>22</v>
       </c>
-      <c r="AL27" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>44</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>40</v>
-      </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
@@ -5792,85 +5792,85 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="G28" t="n">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="H28" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="I28" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="J28" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="K28" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="L28" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="M28" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="O28" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="T28" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="U28" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="V28" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W28" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="X28" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="Y28" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="Z28" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA28" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB28" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
         <v>21</v>
@@ -5879,99 +5879,99 @@
         <v>80</v>
       </c>
       <c r="AF28" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>990</v>
+      </c>
+      <c r="AP28" t="n">
         <v>10</v>
       </c>
-      <c r="AH28" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>14</v>
-      </c>
       <c r="AQ28" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AS28" t="n">
         <v>42</v>
       </c>
       <c r="AT28" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AU28" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV28" t="n">
         <v>19</v>
       </c>
       <c r="AW28" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AX28" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ28" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA28" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BB28" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BC28" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BD28" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BE28" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="BF28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BG28" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Platense FC</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CD Motagua</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="G29" t="n">
-        <v>1000</v>
+        <v>1.73</v>
       </c>
       <c r="H29" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="I29" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="J29" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="K29" t="n">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>1.25</v>
+        <v>4</v>
       </c>
       <c r="O29" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P29" t="n">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.31</v>
+        <v>1.94</v>
       </c>
       <c r="R29" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="S29" t="n">
-        <v>1.31</v>
+        <v>3.45</v>
       </c>
       <c r="T29" t="n">
-        <v>1.11</v>
+        <v>1.95</v>
       </c>
       <c r="U29" t="n">
-        <v>1.11</v>
+        <v>1.99</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>100</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>80</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,191 +6175,191 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar</t>
+          <t>Platense FC</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>CD Motagua</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.86</v>
+        <v>1.04</v>
       </c>
       <c r="G30" t="n">
-        <v>1.96</v>
+        <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="I30" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="K30" t="n">
-        <v>3.7</v>
+        <v>950</v>
       </c>
       <c r="L30" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>2.7</v>
+        <v>1.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="P30" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.6</v>
+        <v>1.31</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>5.3</v>
+        <v>1.31</v>
       </c>
       <c r="T30" t="n">
-        <v>2.28</v>
+        <v>1.11</v>
       </c>
       <c r="U30" t="n">
-        <v>1.7</v>
+        <v>1.11</v>
       </c>
       <c r="V30" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
         <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD30" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AE30" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH30" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
         <v>1000</v>
       </c>
       <c r="AM30" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO30" t="n">
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30" t="n">
-        <v>3.45</v>
+        <v>1.02</v>
       </c>
       <c r="AR30" t="n">
-        <v>4</v>
+        <v>1.02</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.3</v>
+        <v>1.02</v>
       </c>
       <c r="AT30" t="n">
-        <v>5.7</v>
+        <v>1.02</v>
       </c>
       <c r="AU30" t="n">
-        <v>7.4</v>
+        <v>1.02</v>
       </c>
       <c r="AV30" t="n">
-        <v>3.75</v>
+        <v>1.02</v>
       </c>
       <c r="AW30" t="n">
-        <v>4.2</v>
+        <v>1.02</v>
       </c>
       <c r="AX30" t="n">
-        <v>8.6</v>
+        <v>1.02</v>
       </c>
       <c r="AY30" t="n">
-        <v>3.3</v>
+        <v>1.02</v>
       </c>
       <c r="AZ30" t="n">
-        <v>3.9</v>
+        <v>1.02</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.2</v>
+        <v>1.02</v>
       </c>
       <c r="BB30" t="n">
-        <v>3.75</v>
+        <v>1.02</v>
       </c>
       <c r="BC30" t="n">
-        <v>3.9</v>
+        <v>1.02</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.1</v>
+        <v>1.02</v>
       </c>
       <c r="BE30" t="n">
-        <v>4.3</v>
+        <v>1.02</v>
       </c>
       <c r="BF30" t="n">
-        <v>15.5</v>
+        <v>1.02</v>
       </c>
       <c r="BG30" t="n">
-        <v>4.3</v>
+        <v>1.02</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,191 +6369,191 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Alianza FC Valledupar</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="G31" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="H31" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="I31" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="J31" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K31" t="n">
         <v>3.7</v>
       </c>
       <c r="L31" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M31" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="N31" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="O31" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="P31" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="R31" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="S31" t="n">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="T31" t="n">
-        <v>1.89</v>
+        <v>2.28</v>
       </c>
       <c r="U31" t="n">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="V31" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="W31" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="X31" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z31" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AA31" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD31" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG31" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH31" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ31" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK31" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AL31" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="AN31" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>10.5</v>
+        <v>3.7</v>
       </c>
       <c r="AQ31" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AR31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV31" t="n">
         <v>4.5</v>
       </c>
-      <c r="AS31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>15</v>
-      </c>
       <c r="AW31" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AX31" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AY31" t="n">
-        <v>9.4</v>
+        <v>3.85</v>
       </c>
       <c r="AZ31" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BB31" t="n">
-        <v>21</v>
+        <v>4.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>20</v>
+        <v>4.6</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BE31" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BF31" t="n">
-        <v>13.5</v>
+        <v>4.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,184 +6563,184 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Gremio</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>EC Vitoria Salvador</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="G32" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="H32" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I32" t="n">
         <v>4.8</v>
       </c>
       <c r="J32" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="K32" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="L32" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="M32" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N32" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="O32" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="P32" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T32" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q32" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1.86</v>
-      </c>
       <c r="U32" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="V32" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W32" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="X32" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ32" t="n">
         <v>17</v>
       </c>
-      <c r="Y32" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH32" t="n">
+      <c r="BA32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB32" t="n">
         <v>21</v>
       </c>
-      <c r="AI32" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BC32" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="BD32" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="BE32" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="BF32" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
@@ -6757,191 +6757,191 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Gremio</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>EC Vitoria Salvador</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.19</v>
+        <v>1.88</v>
       </c>
       <c r="G33" t="n">
-        <v>1.22</v>
+        <v>1.96</v>
       </c>
       <c r="H33" t="n">
-        <v>19</v>
+        <v>4.5</v>
       </c>
       <c r="I33" t="n">
-        <v>25</v>
+        <v>4.8</v>
       </c>
       <c r="J33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X33" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU33" t="n">
         <v>7.6</v>
       </c>
-      <c r="K33" t="n">
+      <c r="AV33" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE33" t="n">
         <v>8.6</v>
       </c>
-      <c r="L33" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N33" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W33" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="X33" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>270</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>19</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>90</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>530</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>50</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>360</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>360</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>38</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS33" t="n">
+      <c r="BF33" t="n">
         <v>12</v>
       </c>
-      <c r="AT33" t="n">
+      <c r="BG33" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AU33" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>38</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>12</v>
-      </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6956,186 +6956,186 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M34" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="N34" t="n">
-        <v>1.02</v>
+        <v>5.5</v>
       </c>
       <c r="O34" t="n">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="P34" t="n">
-        <v>1.24</v>
+        <v>2.56</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="R34" t="n">
-        <v>1.18</v>
+        <v>1.62</v>
       </c>
       <c r="S34" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="T34" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="U34" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AA34" t="n">
         <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>520</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM34" t="n">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="AO34" t="n">
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7145,120 +7145,120 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortaleza FC</t>
+          <t>Club Sportivo Ameliano</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M35" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N35" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="O35" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="P35" t="n">
-        <v>1.71</v>
+        <v>1.24</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="R35" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S35" t="n">
-        <v>4.3</v>
+        <v>1.05</v>
       </c>
       <c r="T35" t="n">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="U35" t="n">
-        <v>1.8</v>
+        <v>1.11</v>
       </c>
       <c r="V35" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y35" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z35" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA35" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AC35" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD35" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AE35" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AG35" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH35" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI35" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK35" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL35" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM35" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN35" t="n">
         <v>1000</v>
@@ -7267,69 +7267,69 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AQ35" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AR35" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS35" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AT35" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AU35" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV35" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW35" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AX35" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY35" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AZ35" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA35" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BB35" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC35" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD35" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE35" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF35" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG35" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7339,191 +7339,191 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>Fortaleza FC</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3.7</v>
+        <v>1.73</v>
       </c>
       <c r="G36" t="n">
-        <v>4.2</v>
+        <v>1.78</v>
       </c>
       <c r="H36" t="n">
-        <v>2.14</v>
+        <v>6</v>
       </c>
       <c r="I36" t="n">
-        <v>2.3</v>
+        <v>6.8</v>
       </c>
       <c r="J36" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="K36" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="L36" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="M36" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N36" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O36" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="P36" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="R36" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S36" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="T36" t="n">
-        <v>1.92</v>
+        <v>2.22</v>
       </c>
       <c r="U36" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="V36" t="n">
-        <v>1.78</v>
+        <v>1.17</v>
       </c>
       <c r="W36" t="n">
-        <v>1.32</v>
+        <v>2.28</v>
       </c>
       <c r="X36" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="Z36" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="AA36" t="n">
-        <v>36</v>
+        <v>230</v>
       </c>
       <c r="AB36" t="n">
-        <v>15</v>
+        <v>6.6</v>
       </c>
       <c r="AC36" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF36" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AD36" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>34</v>
-      </c>
       <c r="AG36" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AI36" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="AJ36" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="AK36" t="n">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="AL36" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AM36" t="n">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="AN36" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AO36" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>3</v>
+        <v>6.2</v>
       </c>
       <c r="AR36" t="n">
-        <v>3.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS36" t="n">
-        <v>3.85</v>
+        <v>9.6</v>
       </c>
       <c r="AT36" t="n">
-        <v>3.35</v>
+        <v>6</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.94</v>
+        <v>7.8</v>
       </c>
       <c r="AV36" t="n">
-        <v>3.25</v>
+        <v>7.2</v>
       </c>
       <c r="AW36" t="n">
-        <v>3.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX36" t="n">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="AY36" t="n">
-        <v>3.55</v>
+        <v>5.1</v>
       </c>
       <c r="AZ36" t="n">
-        <v>3.65</v>
+        <v>7.2</v>
       </c>
       <c r="BA36" t="n">
-        <v>4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB36" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="BC36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BD36" t="n">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="BE36" t="n">
-        <v>4.2</v>
+        <v>9.4</v>
       </c>
       <c r="BF36" t="n">
-        <v>4.1</v>
+        <v>11</v>
       </c>
       <c r="BG36" t="n">
-        <v>16.5</v>
+        <v>9.4</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7533,378 +7533,572 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Independiente (Ecu)</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>3.7</v>
       </c>
       <c r="G37" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="H37" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="I37" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="J37" t="n">
         <v>3.2</v>
       </c>
       <c r="K37" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="L37" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="M37" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N37" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O37" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="P37" t="n">
         <v>1.7</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="R37" t="n">
         <v>1.26</v>
       </c>
       <c r="S37" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="T37" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="U37" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V37" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="W37" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="X37" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="Z37" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA37" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AB37" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AC37" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD37" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE37" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO37" t="n">
         <v>28</v>
       </c>
-      <c r="AF37" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>95</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>26</v>
-      </c>
       <c r="AP37" t="n">
-        <v>9.800000000000001</v>
+        <v>3.25</v>
       </c>
       <c r="AQ37" t="n">
-        <v>7.6</v>
+        <v>3</v>
       </c>
       <c r="AR37" t="n">
-        <v>11.5</v>
+        <v>3.4</v>
       </c>
       <c r="AS37" t="n">
-        <v>20</v>
+        <v>3.85</v>
       </c>
       <c r="AT37" t="n">
-        <v>10.5</v>
+        <v>3.35</v>
       </c>
       <c r="AU37" t="n">
-        <v>6.6</v>
+        <v>2.94</v>
       </c>
       <c r="AV37" t="n">
-        <v>10</v>
+        <v>3.25</v>
       </c>
       <c r="AW37" t="n">
-        <v>10</v>
+        <v>3.8</v>
       </c>
       <c r="AX37" t="n">
-        <v>22</v>
+        <v>3.8</v>
       </c>
       <c r="AY37" t="n">
-        <v>13.5</v>
+        <v>3.55</v>
       </c>
       <c r="AZ37" t="n">
-        <v>17.5</v>
+        <v>3.65</v>
       </c>
       <c r="BA37" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="BB37" t="n">
-        <v>13</v>
+        <v>4.1</v>
       </c>
       <c r="BC37" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="BD37" t="n">
-        <v>42</v>
+        <v>4.1</v>
       </c>
       <c r="BE37" t="n">
-        <v>13.5</v>
+        <v>4.2</v>
       </c>
       <c r="BF37" t="n">
-        <v>12.5</v>
+        <v>4.1</v>
       </c>
       <c r="BG37" t="n">
-        <v>9.6</v>
+        <v>16.5</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-18 16:46:25</t>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X38" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>22</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-03-18 19:00:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>22:30:00</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Ind Medellin</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Junior FC Barranquilla</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="F39" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I39" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N39" t="n">
+        <v>4</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U39" t="n">
         <v>2.2</v>
       </c>
-      <c r="H38" t="n">
+      <c r="V39" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC39" t="n">
         <v>3.7</v>
       </c>
-      <c r="I38" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K38" t="n">
+      <c r="BD39" t="n">
         <v>3.9</v>
       </c>
-      <c r="L38" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N38" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U38" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="X38" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AW38" t="n">
+      <c r="BE39" t="n">
         <v>4.1</v>
       </c>
-      <c r="AX38" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BG38" t="n">
-        <v>8</v>
-      </c>
-      <c r="BH38" t="inlineStr">
-        <is>
-          <t>2026-03-18 16:46:25</t>
+      <c r="BF39" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-03-18 19:00:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
@@ -760,7 +760,7 @@
         <v>12.5</v>
       </c>
       <c r="G2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H2" t="n">
         <v>1.33</v>
@@ -775,64 +775,64 @@
         <v>5.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O2" t="n">
         <v>1.35</v>
       </c>
       <c r="P2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q2" t="n">
         <v>2.02</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
         <v>3.75</v>
       </c>
       <c r="T2" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="U2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V2" t="n">
         <v>3.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA2" t="n">
         <v>12.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AC2" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AF2" t="n">
         <v>1000</v>
@@ -841,7 +841,7 @@
         <v>65</v>
       </c>
       <c r="AH2" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AI2" t="n">
         <v>75</v>
@@ -862,25 +862,25 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP2" t="n">
         <v>12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.96</v>
+        <v>5.9</v>
       </c>
       <c r="AS2" t="n">
         <v>9</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AV2" t="n">
         <v>9.6</v>
@@ -889,38 +889,38 @@
         <v>15.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.3</v>
+        <v>38</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BG2" t="n">
         <v>5.9</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -960,46 +960,46 @@
         <v>1.29</v>
       </c>
       <c r="I3" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="J3" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O3" t="n">
         <v>1.31</v>
       </c>
       <c r="P3" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="U3" t="n">
         <v>1.59</v>
       </c>
       <c r="V3" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="W3" t="n">
         <v>1.05</v>
@@ -1011,7 +1011,7 @@
         <v>7.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1056,25 +1056,25 @@
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.65</v>
+        <v>5.9</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AS3" t="n">
         <v>4.1</v>
       </c>
       <c r="AT3" t="n">
-        <v>6</v>
+        <v>3.15</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AV3" t="n">
         <v>4.5</v>
@@ -1083,38 +1083,38 @@
         <v>5.1</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.6</v>
+        <v>3.3</v>
       </c>
       <c r="AY3" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.2</v>
+        <v>3.15</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.2</v>
+        <v>3.25</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.8</v>
+        <v>3.35</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.8</v>
+        <v>3.35</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.8</v>
+        <v>3.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.8</v>
+        <v>3.35</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.8</v>
+        <v>3.35</v>
       </c>
       <c r="BG3" t="n">
         <v>3.55</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G4" t="n">
         <v>2.18</v>
@@ -1154,19 +1154,19 @@
         <v>3.8</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J4" t="n">
         <v>3.55</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.4</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
         <v>3.85</v>
@@ -1187,19 +1187,19 @@
         <v>3.35</v>
       </c>
       <c r="T4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
         <v>1.84</v>
       </c>
       <c r="X4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y4" t="n">
         <v>15</v>
@@ -1211,7 +1211,7 @@
         <v>75</v>
       </c>
       <c r="AB4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4" t="n">
         <v>8.199999999999999</v>
@@ -1250,7 +1250,7 @@
         <v>16</v>
       </c>
       <c r="AO4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AP4" t="n">
         <v>13</v>
@@ -1262,10 +1262,10 @@
         <v>24</v>
       </c>
       <c r="AS4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AT4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU4" t="n">
         <v>7.4</v>
@@ -1274,7 +1274,7 @@
         <v>14</v>
       </c>
       <c r="AW4" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AX4" t="n">
         <v>12</v>
@@ -1283,7 +1283,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA4" t="n">
         <v>46</v>
@@ -1298,17 +1298,17 @@
         <v>32</v>
       </c>
       <c r="BE4" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="BF4" t="n">
         <v>14.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -1339,25 +1339,25 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="G5" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="H5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="I5" t="n">
         <v>16</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="K5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M5" t="n">
         <v>1.04</v>
@@ -1369,7 +1369,7 @@
         <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q5" t="n">
         <v>1.63</v>
@@ -1381,16 +1381,16 @@
         <v>2.6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U5" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V5" t="n">
         <v>1.06</v>
       </c>
       <c r="W5" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="X5" t="n">
         <v>950</v>
@@ -1405,10 +1405,10 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AC5" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AD5" t="n">
         <v>950</v>
@@ -1417,7 +1417,7 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AG5" t="n">
         <v>970</v>
@@ -1429,13 +1429,13 @@
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>970</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
         <v>970</v>
       </c>
       <c r="AL5" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
@@ -1447,16 +1447,16 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AR5" t="n">
         <v>4.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AT5" t="n">
         <v>6</v>
@@ -1465,7 +1465,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AW5" t="n">
         <v>4.2</v>
@@ -1477,32 +1477,32 @@
         <v>7.8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BA5" t="n">
         <v>4.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.65</v>
+        <v>10.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="BF5" t="n">
         <v>4.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="H6" t="n">
         <v>1.25</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>1.49</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
         <v>5.4</v>
@@ -1739,10 +1739,10 @@
         <v>19</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1</v>
+        <v>2.74</v>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1754,7 +1754,7 @@
         <v>1.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P7" t="n">
         <v>1.24</v>
@@ -1766,19 +1766,19 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="U7" t="n">
         <v>1.52</v>
       </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="W7" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1817,7 +1817,7 @@
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
         <v>1000</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.02</v>
+        <v>1.54</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.05</v>
+        <v>1.52</v>
       </c>
       <c r="G8" t="n">
-        <v>990</v>
+        <v>44</v>
       </c>
       <c r="H8" t="n">
-        <v>1.05</v>
+        <v>2.36</v>
       </c>
       <c r="I8" t="n">
-        <v>990</v>
+        <v>44</v>
       </c>
       <c r="J8" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1945,7 +1945,7 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
         <v>1.08</v>
@@ -1969,7 +1969,7 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="W8" t="n">
         <v>1.02</v>
@@ -2029,62 +2029,62 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -2118,19 +2118,19 @@
         <v>1.1</v>
       </c>
       <c r="G9" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="H9" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I9" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="J9" t="n">
         <v>10.5</v>
       </c>
       <c r="K9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="L9" t="n">
         <v>1.21</v>
@@ -2148,31 +2148,31 @@
         <v>2.68</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R9" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="S9" t="n">
         <v>2.18</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
         <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="X9" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="Y9" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
@@ -2184,7 +2184,7 @@
         <v>12.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2193,92 +2193,92 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AG9" t="n">
         <v>21</v>
       </c>
       <c r="AH9" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AK9" t="n">
         <v>19</v>
       </c>
       <c r="AL9" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX9" t="n">
         <v>5.6</v>
       </c>
       <c r="AY9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC9" t="n">
         <v>13</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BD9" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -2324,155 +2324,155 @@
         <v>5.5</v>
       </c>
       <c r="K10" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M10" t="n">
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P10" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="R10" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="S10" t="n">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="T10" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="U10" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="V10" t="n">
         <v>1.1</v>
       </c>
       <c r="W10" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="X10" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Y10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z10" t="n">
-        <v>95</v>
+        <v>540</v>
       </c>
       <c r="AA10" t="n">
         <v>370</v>
       </c>
       <c r="AB10" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD10" t="n">
         <v>38</v>
       </c>
       <c r="AE10" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AF10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
         <v>29</v>
       </c>
       <c r="AI10" t="n">
-        <v>140</v>
+        <v>470</v>
       </c>
       <c r="AJ10" t="n">
         <v>11.5</v>
       </c>
       <c r="AK10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>390</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AR10" t="n">
         <v>15</v>
       </c>
-      <c r="AL10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>210</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AS10" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AT10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX10" t="n">
         <v>7.6</v>
       </c>
-      <c r="AU10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AW10" t="n">
+      <c r="AY10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC10" t="n">
         <v>12</v>
       </c>
-      <c r="AX10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>14</v>
-      </c>
       <c r="BD10" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BE10" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>1.84</v>
       </c>
       <c r="G11" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="H11" t="n">
         <v>5.2</v>
@@ -2527,40 +2527,40 @@
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O11" t="n">
         <v>1.37</v>
       </c>
       <c r="P11" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q11" t="n">
         <v>2.12</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T11" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="U11" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="V11" t="n">
         <v>1.21</v>
       </c>
       <c r="W11" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="n">
-        <v>17</v>
+        <v>360</v>
       </c>
       <c r="Z11" t="n">
         <v>40</v>
@@ -2569,16 +2569,16 @@
         <v>140</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD11" t="n">
         <v>22</v>
       </c>
       <c r="AE11" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AF11" t="n">
         <v>11</v>
@@ -2590,7 +2590,7 @@
         <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AJ11" t="n">
         <v>21</v>
@@ -2599,7 +2599,7 @@
         <v>22</v>
       </c>
       <c r="AL11" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="AM11" t="n">
         <v>150</v>
@@ -2620,7 +2620,7 @@
         <v>25</v>
       </c>
       <c r="AS11" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT11" t="n">
         <v>7</v>
@@ -2632,7 +2632,7 @@
         <v>19</v>
       </c>
       <c r="AW11" t="n">
-        <v>10.5</v>
+        <v>44</v>
       </c>
       <c r="AX11" t="n">
         <v>9.4</v>
@@ -2644,7 +2644,7 @@
         <v>18</v>
       </c>
       <c r="BA11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB11" t="n">
         <v>18</v>
@@ -2656,17 +2656,17 @@
         <v>30</v>
       </c>
       <c r="BE11" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF11" t="n">
         <v>13</v>
       </c>
       <c r="BG11" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -2697,49 +2697,49 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="G12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="H12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J12" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="K12" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P12" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T12" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U12" t="n">
         <v>1.72</v>
@@ -2754,16 +2754,16 @@
         <v>17.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Z12" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AA12" t="n">
         <v>680</v>
       </c>
       <c r="AB12" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC12" t="n">
         <v>12</v>
@@ -2772,16 +2772,16 @@
         <v>42</v>
       </c>
       <c r="AE12" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="AF12" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AG12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH12" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AI12" t="n">
         <v>260</v>
@@ -2793,7 +2793,7 @@
         <v>16</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM12" t="n">
         <v>260</v>
@@ -2802,65 +2802,65 @@
         <v>6.8</v>
       </c>
       <c r="AO12" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU12" t="n">
         <v>10.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY12" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>11.5</v>
+        <v>25</v>
       </c>
       <c r="BA12" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC12" t="n">
         <v>14.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE12" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -2891,31 +2891,31 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="G13" t="n">
         <v>6.4</v>
       </c>
       <c r="H13" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="I13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="J13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K13" t="n">
         <v>4.3</v>
       </c>
-      <c r="K13" t="n">
-        <v>4.5</v>
-      </c>
       <c r="L13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O13" t="n">
         <v>1.33</v>
@@ -2927,16 +2927,16 @@
         <v>2.02</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U13" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="V13" t="n">
         <v>2.5</v>
@@ -2945,7 +2945,7 @@
         <v>1.18</v>
       </c>
       <c r="X13" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y13" t="n">
         <v>8.199999999999999</v>
@@ -2954,16 +2954,16 @@
         <v>9</v>
       </c>
       <c r="AA13" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AB13" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AC13" t="n">
         <v>9.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AE13" t="n">
         <v>17.5</v>
@@ -2978,19 +2978,19 @@
         <v>25</v>
       </c>
       <c r="AI13" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ13" t="n">
-        <v>190</v>
+        <v>700</v>
       </c>
       <c r="AK13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL13" t="n">
         <v>95</v>
       </c>
-      <c r="AL13" t="n">
-        <v>90</v>
-      </c>
       <c r="AM13" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AN13" t="n">
         <v>130</v>
@@ -3005,16 +3005,16 @@
         <v>7.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AT13" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV13" t="n">
         <v>9.4</v>
@@ -3023,38 +3023,38 @@
         <v>16.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AY13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ13" t="n">
         <v>22</v>
       </c>
       <c r="BA13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB13" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="BC13" t="n">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="BD13" t="n">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="BE13" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="BF13" t="n">
         <v>20</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G14" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H14" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I14" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="J14" t="n">
         <v>3.55</v>
@@ -3109,13 +3109,13 @@
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
         <v>1.94</v>
@@ -3124,22 +3124,22 @@
         <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T14" t="n">
         <v>1.75</v>
       </c>
       <c r="U14" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V14" t="n">
         <v>1.53</v>
       </c>
       <c r="W14" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y14" t="n">
         <v>12.5</v>
@@ -3154,19 +3154,19 @@
         <v>12.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF14" t="n">
         <v>19</v>
       </c>
       <c r="AG14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH14" t="n">
         <v>17.5</v>
@@ -3175,80 +3175,80 @@
         <v>44</v>
       </c>
       <c r="AJ14" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM14" t="n">
-        <v>85</v>
+        <v>320</v>
       </c>
       <c r="AN14" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AO14" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AP14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR14" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AS14" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="AT14" t="n">
         <v>10</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AX14" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE14" t="n">
         <v>10.5</v>
       </c>
-      <c r="AZ14" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>55</v>
-      </c>
       <c r="BF14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BG14" t="n">
-        <v>20</v>
+        <v>8.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="G15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="H15" t="n">
         <v>11</v>
@@ -3291,7 +3291,7 @@
         <v>14</v>
       </c>
       <c r="J15" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="K15" t="n">
         <v>7</v>
@@ -3303,7 +3303,7 @@
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O15" t="n">
         <v>1.19</v>
@@ -3315,16 +3315,16 @@
         <v>1.58</v>
       </c>
       <c r="R15" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="S15" t="n">
         <v>2.44</v>
       </c>
       <c r="T15" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V15" t="n">
         <v>1.08</v>
@@ -3336,10 +3336,10 @@
         <v>28</v>
       </c>
       <c r="Y15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Z15" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
@@ -3348,16 +3348,16 @@
         <v>11</v>
       </c>
       <c r="AC15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AD15" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AE15" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AF15" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AG15" t="n">
         <v>12</v>
@@ -3366,7 +3366,7 @@
         <v>34</v>
       </c>
       <c r="AI15" t="n">
-        <v>170</v>
+        <v>470</v>
       </c>
       <c r="AJ15" t="n">
         <v>10.5</v>
@@ -3381,7 +3381,7 @@
         <v>200</v>
       </c>
       <c r="AN15" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
@@ -3390,28 +3390,28 @@
         <v>22</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.6</v>
+        <v>29</v>
       </c>
       <c r="AS15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AT15" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU15" t="n">
         <v>12.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY15" t="n">
         <v>9.800000000000001</v>
@@ -3420,7 +3420,7 @@
         <v>27</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="BB15" t="n">
         <v>8.6</v>
@@ -3432,17 +3432,17 @@
         <v>32</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.6</v>
+        <v>28</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.8</v>
+        <v>15</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="G16" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H16" t="n">
         <v>2.36</v>
@@ -3497,13 +3497,13 @@
         <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O16" t="n">
         <v>1.29</v>
       </c>
       <c r="P16" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q16" t="n">
         <v>1.9</v>
@@ -3515,19 +3515,19 @@
         <v>3.25</v>
       </c>
       <c r="T16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V16" t="n">
         <v>1.72</v>
       </c>
-      <c r="U16" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.73</v>
-      </c>
       <c r="W16" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X16" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y16" t="n">
         <v>11.5</v>
@@ -3536,10 +3536,10 @@
         <v>15.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AB16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC16" t="n">
         <v>8</v>
@@ -3548,28 +3548,28 @@
         <v>11</v>
       </c>
       <c r="AE16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF16" t="n">
         <v>23</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>24</v>
       </c>
       <c r="AG16" t="n">
         <v>14</v>
       </c>
       <c r="AH16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI16" t="n">
         <v>36</v>
       </c>
       <c r="AJ16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK16" t="n">
         <v>36</v>
       </c>
       <c r="AL16" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM16" t="n">
         <v>80</v>
@@ -3578,7 +3578,7 @@
         <v>32</v>
       </c>
       <c r="AO16" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AP16" t="n">
         <v>14.5</v>
@@ -3596,47 +3596,47 @@
         <v>13</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV16" t="n">
         <v>10.5</v>
       </c>
       <c r="AW16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX16" t="n">
         <v>21</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>22</v>
       </c>
       <c r="AY16" t="n">
         <v>13</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BC16" t="n">
         <v>32</v>
       </c>
       <c r="BD16" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE16" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="BF16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BG16" t="n">
         <v>16</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="G17" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="H17" t="n">
         <v>4</v>
@@ -3679,10 +3679,10 @@
         <v>4.1</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L17" t="n">
         <v>1.46</v>
@@ -3691,7 +3691,7 @@
         <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O17" t="n">
         <v>1.38</v>
@@ -3700,25 +3700,25 @@
         <v>1.84</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R17" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S17" t="n">
         <v>3.95</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U17" t="n">
         <v>2.04</v>
       </c>
       <c r="V17" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W17" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="X17" t="n">
         <v>12.5</v>
@@ -3730,46 +3730,46 @@
         <v>27</v>
       </c>
       <c r="AA17" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC17" t="n">
         <v>7.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF17" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG17" t="n">
         <v>11</v>
       </c>
       <c r="AH17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL17" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM17" t="n">
         <v>120</v>
       </c>
       <c r="AN17" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AO17" t="n">
         <v>60</v>
@@ -3778,13 +3778,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS17" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AT17" t="n">
         <v>8.199999999999999</v>
@@ -3793,13 +3793,13 @@
         <v>7.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="AX17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY17" t="n">
         <v>10</v>
@@ -3808,29 +3808,29 @@
         <v>17.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BB17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BC17" t="n">
         <v>21</v>
       </c>
       <c r="BD17" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE17" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="BF17" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BG17" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G18" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="H18" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I18" t="n">
         <v>6.2</v>
       </c>
       <c r="J18" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
         <v>1.36</v>
@@ -3903,34 +3903,34 @@
         <v>3.05</v>
       </c>
       <c r="T18" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U18" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V18" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W18" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="X18" t="n">
         <v>18</v>
       </c>
       <c r="Y18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z18" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA18" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD18" t="n">
         <v>23</v>
@@ -3939,22 +3939,22 @@
         <v>80</v>
       </c>
       <c r="AF18" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG18" t="n">
         <v>10</v>
       </c>
       <c r="AH18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI18" t="n">
         <v>75</v>
       </c>
       <c r="AJ18" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AK18" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AL18" t="n">
         <v>32</v>
@@ -3966,46 +3966,46 @@
         <v>8.4</v>
       </c>
       <c r="AO18" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AP18" t="n">
         <v>16</v>
       </c>
       <c r="AQ18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR18" t="n">
         <v>42</v>
       </c>
       <c r="AS18" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AT18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU18" t="n">
         <v>9</v>
       </c>
       <c r="AV18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW18" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AX18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA18" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BB18" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC18" t="n">
         <v>15</v>
@@ -4014,7 +4014,7 @@
         <v>30</v>
       </c>
       <c r="BE18" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="BF18" t="n">
         <v>7.8</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -4055,46 +4055,46 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5.9</v>
+        <v>3.65</v>
       </c>
       <c r="G19" t="n">
-        <v>8.199999999999999</v>
+        <v>600</v>
       </c>
       <c r="H19" t="n">
-        <v>1.69</v>
+        <v>1.36</v>
       </c>
       <c r="I19" t="n">
-        <v>1.83</v>
+        <v>2.72</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="K19" t="n">
-        <v>3.9</v>
+        <v>950</v>
       </c>
       <c r="L19" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N19" t="n">
         <v>1.1</v>
       </c>
-      <c r="N19" t="n">
-        <v>2.76</v>
-      </c>
       <c r="O19" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P19" t="n">
         <v>1.61</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="R19" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>4.7</v>
+        <v>1.02</v>
       </c>
       <c r="T19" t="n">
         <v>2.2</v>
@@ -4112,7 +4112,7 @@
         <v>12</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="Z19" t="n">
         <v>11</v>
@@ -4133,7 +4133,7 @@
         <v>28</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG19" t="n">
         <v>1000</v>
@@ -4172,7 +4172,7 @@
         <v>7.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="AT19" t="n">
         <v>11.5</v>
@@ -4181,44 +4181,44 @@
         <v>7.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AY19" t="n">
         <v>19</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BG19" t="n">
         <v>12.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="G20" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="H20" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="I20" t="n">
         <v>2.96</v>
       </c>
       <c r="J20" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K20" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L20" t="n">
         <v>1.47</v>
@@ -4273,25 +4273,25 @@
         <v>1.11</v>
       </c>
       <c r="N20" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="O20" t="n">
         <v>1.5</v>
       </c>
       <c r="P20" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Q20" t="n">
         <v>2.46</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S20" t="n">
         <v>4.7</v>
       </c>
       <c r="T20" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U20" t="n">
         <v>1.84</v>
@@ -4300,64 +4300,64 @@
         <v>1.51</v>
       </c>
       <c r="W20" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X20" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z20" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB20" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>380</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP20" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>8</v>
       </c>
       <c r="AQ20" t="n">
         <v>7.2</v>
@@ -4366,19 +4366,19 @@
         <v>15</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT20" t="n">
         <v>7.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV20" t="n">
         <v>11.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.8</v>
+        <v>18</v>
       </c>
       <c r="AX20" t="n">
         <v>16.5</v>
@@ -4387,32 +4387,32 @@
         <v>12</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4.8</v>
+        <v>11.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="BD20" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.8</v>
+        <v>32</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -4443,19 +4443,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="G21" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H21" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="I21" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J21" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K21" t="n">
         <v>3.75</v>
@@ -4470,13 +4470,13 @@
         <v>3</v>
       </c>
       <c r="O21" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P21" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R21" t="n">
         <v>1.25</v>
@@ -4488,10 +4488,10 @@
         <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V21" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W21" t="n">
         <v>2.02</v>
@@ -4503,16 +4503,16 @@
         <v>18</v>
       </c>
       <c r="Z21" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="AA21" t="n">
-        <v>180</v>
+        <v>900</v>
       </c>
       <c r="AB21" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD21" t="n">
         <v>25</v>
@@ -4530,7 +4530,7 @@
         <v>27</v>
       </c>
       <c r="AI21" t="n">
-        <v>110</v>
+        <v>380</v>
       </c>
       <c r="AJ21" t="n">
         <v>25</v>
@@ -4542,7 +4542,7 @@
         <v>60</v>
       </c>
       <c r="AM21" t="n">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN21" t="n">
         <v>20</v>
@@ -4557,10 +4557,10 @@
         <v>12.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT21" t="n">
         <v>6.2</v>
@@ -4572,7 +4572,7 @@
         <v>17.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AX21" t="n">
         <v>9</v>
@@ -4584,29 +4584,29 @@
         <v>19</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BB21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC21" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BF21" t="n">
         <v>12</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G22" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H22" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I22" t="n">
         <v>6.2</v>
       </c>
       <c r="J22" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K22" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L22" t="n">
         <v>1.43</v>
@@ -4661,7 +4661,7 @@
         <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O22" t="n">
         <v>1.34</v>
@@ -4679,19 +4679,19 @@
         <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U22" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="V22" t="n">
         <v>1.19</v>
       </c>
       <c r="W22" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="X22" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="Y22" t="n">
         <v>18</v>
@@ -4700,107 +4700,107 @@
         <v>46</v>
       </c>
       <c r="AA22" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB22" t="n">
         <v>9</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH22" t="n">
         <v>22</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AI22" t="n">
         <v>90</v>
       </c>
-      <c r="AF22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>85</v>
-      </c>
       <c r="AJ22" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK22" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM22" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AN22" t="n">
         <v>11</v>
       </c>
       <c r="AO22" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AP22" t="n">
         <v>13</v>
       </c>
       <c r="AQ22" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AR22" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AS22" t="n">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU22" t="n">
         <v>8.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW22" t="n">
-        <v>8.4</v>
+        <v>15.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY22" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ22" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BA22" t="n">
-        <v>8.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC22" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>29</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG22" t="n">
         <v>16</v>
       </c>
-      <c r="BD22" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -4831,25 +4831,25 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G23" t="n">
         <v>2.18</v>
       </c>
       <c r="H23" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I23" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J23" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K23" t="n">
         <v>3.9</v>
       </c>
       <c r="L23" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M23" t="n">
         <v>1.06</v>
@@ -4861,7 +4861,7 @@
         <v>1.28</v>
       </c>
       <c r="P23" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
         <v>1.84</v>
@@ -4873,19 +4873,19 @@
         <v>3.1</v>
       </c>
       <c r="T23" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U23" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V23" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W23" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X23" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y23" t="n">
         <v>15</v>
@@ -4894,7 +4894,7 @@
         <v>27</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB23" t="n">
         <v>11</v>
@@ -4906,19 +4906,19 @@
         <v>15</v>
       </c>
       <c r="AE23" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH23" t="n">
         <v>17</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ23" t="n">
         <v>27</v>
@@ -4930,10 +4930,10 @@
         <v>34</v>
       </c>
       <c r="AM23" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO23" t="n">
         <v>36</v>
@@ -4948,31 +4948,31 @@
         <v>24</v>
       </c>
       <c r="AS23" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AT23" t="n">
         <v>10</v>
       </c>
       <c r="AU23" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA23" t="n">
         <v>34</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>13</v>
       </c>
       <c r="BB23" t="n">
         <v>23</v>
@@ -4984,17 +4984,17 @@
         <v>29</v>
       </c>
       <c r="BE23" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF23" t="n">
         <v>13</v>
       </c>
-      <c r="BF23" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BG23" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -5037,34 +5037,34 @@
         <v>3.3</v>
       </c>
       <c r="J24" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K24" t="n">
         <v>3.75</v>
       </c>
       <c r="L24" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="M24" t="n">
         <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O24" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="T24" t="n">
         <v>1.69</v>
@@ -5079,16 +5079,16 @@
         <v>1.7</v>
       </c>
       <c r="X24" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Y24" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AA24" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB24" t="n">
         <v>13</v>
@@ -5106,58 +5106,58 @@
         <v>18.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH24" t="n">
         <v>19</v>
       </c>
       <c r="AI24" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ24" t="n">
         <v>36</v>
       </c>
       <c r="AK24" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AL24" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM24" t="n">
         <v>95</v>
       </c>
       <c r="AN24" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP24" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR24" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.9</v>
+        <v>30</v>
       </c>
       <c r="AT24" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU24" t="n">
         <v>7.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AW24" t="n">
         <v>30</v>
       </c>
       <c r="AX24" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AY24" t="n">
         <v>10</v>
@@ -5166,29 +5166,29 @@
         <v>14</v>
       </c>
       <c r="BA24" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB24" t="n">
-        <v>5.5</v>
+        <v>25</v>
       </c>
       <c r="BC24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.4</v>
+        <v>16</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.9</v>
+        <v>28</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>5.3</v>
+        <v>24</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="G25" t="n">
         <v>1.43</v>
@@ -5246,10 +5246,10 @@
         <v>4.2</v>
       </c>
       <c r="O25" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P25" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
         <v>1.86</v>
@@ -5261,10 +5261,10 @@
         <v>3.15</v>
       </c>
       <c r="T25" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V25" t="n">
         <v>1.1</v>
@@ -5273,7 +5273,7 @@
         <v>3.3</v>
       </c>
       <c r="X25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y25" t="n">
         <v>30</v>
@@ -5282,7 +5282,7 @@
         <v>100</v>
       </c>
       <c r="AA25" t="n">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="AB25" t="n">
         <v>8</v>
@@ -5312,10 +5312,10 @@
         <v>11.5</v>
       </c>
       <c r="AK25" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AL25" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM25" t="n">
         <v>210</v>
@@ -5324,19 +5324,19 @@
         <v>6.8</v>
       </c>
       <c r="AO25" t="n">
-        <v>250</v>
+        <v>320</v>
       </c>
       <c r="AP25" t="n">
         <v>15</v>
       </c>
       <c r="AQ25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR25" t="n">
         <v>75</v>
       </c>
       <c r="AS25" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AT25" t="n">
         <v>7.4</v>
@@ -5345,10 +5345,10 @@
         <v>10</v>
       </c>
       <c r="AV25" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AW25" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AX25" t="n">
         <v>7.2</v>
@@ -5360,10 +5360,10 @@
         <v>26</v>
       </c>
       <c r="BA25" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC25" t="n">
         <v>14.5</v>
@@ -5372,17 +5372,17 @@
         <v>38</v>
       </c>
       <c r="BE25" t="n">
-        <v>13.5</v>
+        <v>55</v>
       </c>
       <c r="BF25" t="n">
         <v>6</v>
       </c>
       <c r="BG25" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -5419,49 +5419,49 @@
         <v>1.44</v>
       </c>
       <c r="H26" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="J26" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L26" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M26" t="n">
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O26" t="n">
         <v>1.29</v>
       </c>
       <c r="P26" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R26" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T26" t="n">
         <v>2.16</v>
       </c>
       <c r="U26" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V26" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W26" t="n">
         <v>3.25</v>
@@ -5470,7 +5470,7 @@
         <v>16.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z26" t="n">
         <v>85</v>
@@ -5479,7 +5479,7 @@
         <v>370</v>
       </c>
       <c r="AB26" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC26" t="n">
         <v>11</v>
@@ -5500,7 +5500,7 @@
         <v>28</v>
       </c>
       <c r="AI26" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AJ26" t="n">
         <v>11.5</v>
@@ -5512,16 +5512,16 @@
         <v>40</v>
       </c>
       <c r="AM26" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AO26" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>24</v>
@@ -5530,19 +5530,19 @@
         <v>34</v>
       </c>
       <c r="AS26" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AT26" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU26" t="n">
         <v>10</v>
       </c>
       <c r="AV26" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AW26" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AX26" t="n">
         <v>7.4</v>
@@ -5554,7 +5554,7 @@
         <v>25</v>
       </c>
       <c r="BA26" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB26" t="n">
         <v>10.5</v>
@@ -5566,17 +5566,17 @@
         <v>34</v>
       </c>
       <c r="BE26" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="BF26" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG26" t="n">
         <v>48</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -5607,19 +5607,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G27" t="n">
         <v>2.62</v>
       </c>
       <c r="H27" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="I27" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="J27" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K27" t="n">
         <v>3.7</v>
@@ -5631,10 +5631,10 @@
         <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O27" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P27" t="n">
         <v>2.02</v>
@@ -5643,7 +5643,7 @@
         <v>1.96</v>
       </c>
       <c r="R27" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
         <v>3.3</v>
@@ -5652,22 +5652,22 @@
         <v>1.74</v>
       </c>
       <c r="U27" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V27" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W27" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X27" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y27" t="n">
         <v>12.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA27" t="n">
         <v>46</v>
@@ -5685,7 +5685,7 @@
         <v>32</v>
       </c>
       <c r="AF27" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG27" t="n">
         <v>12</v>
@@ -5694,7 +5694,7 @@
         <v>16.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ27" t="n">
         <v>38</v>
@@ -5724,7 +5724,7 @@
         <v>18</v>
       </c>
       <c r="AS27" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AT27" t="n">
         <v>10.5</v>
@@ -5748,29 +5748,29 @@
         <v>15.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BB27" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="BC27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD27" t="n">
         <v>32</v>
       </c>
       <c r="BE27" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="BF27" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BG27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="G28" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="H28" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="I28" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="J28" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K28" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L28" t="n">
         <v>1.49</v>
@@ -5825,13 +5825,13 @@
         <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O28" t="n">
         <v>1.42</v>
       </c>
       <c r="P28" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q28" t="n">
         <v>2.3</v>
@@ -5840,58 +5840,58 @@
         <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U28" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V28" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W28" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="X28" t="n">
         <v>11</v>
       </c>
       <c r="Y28" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AA28" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AB28" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC28" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE28" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AG28" t="n">
         <v>10.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI28" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AJ28" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AK28" t="n">
         <v>22</v>
@@ -5900,71 +5900,71 @@
         <v>46</v>
       </c>
       <c r="AM28" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN28" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AO28" t="n">
-        <v>990</v>
+        <v>140</v>
       </c>
       <c r="AP28" t="n">
         <v>10</v>
       </c>
       <c r="AQ28" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR28" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AS28" t="n">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="AT28" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU28" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW28" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AX28" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AY28" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA28" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB28" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BC28" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD28" t="n">
         <v>40</v>
       </c>
       <c r="BE28" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="BF28" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -6001,13 +6001,13 @@
         <v>1.73</v>
       </c>
       <c r="H29" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I29" t="n">
         <v>5.5</v>
       </c>
       <c r="J29" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K29" t="n">
         <v>4.3</v>
@@ -6016,7 +6016,7 @@
         <v>1.4</v>
       </c>
       <c r="M29" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N29" t="n">
         <v>4</v>
@@ -6025,13 +6025,13 @@
         <v>1.31</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q29" t="n">
         <v>1.94</v>
       </c>
       <c r="R29" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
         <v>3.45</v>
@@ -6040,16 +6040,16 @@
         <v>1.95</v>
       </c>
       <c r="U29" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="V29" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W29" t="n">
         <v>2.36</v>
       </c>
       <c r="X29" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y29" t="n">
         <v>18</v>
@@ -6061,7 +6061,7 @@
         <v>140</v>
       </c>
       <c r="AB29" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC29" t="n">
         <v>9</v>
@@ -6070,10 +6070,10 @@
         <v>21</v>
       </c>
       <c r="AE29" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF29" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AG29" t="n">
         <v>10</v>
@@ -6085,10 +6085,10 @@
         <v>75</v>
       </c>
       <c r="AJ29" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AK29" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL29" t="n">
         <v>36</v>
@@ -6103,7 +6103,7 @@
         <v>90</v>
       </c>
       <c r="AP29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ29" t="n">
         <v>16.5</v>
@@ -6115,7 +6115,7 @@
         <v>42</v>
       </c>
       <c r="AT29" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU29" t="n">
         <v>8.6</v>
@@ -6127,7 +6127,7 @@
         <v>65</v>
       </c>
       <c r="AX29" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY29" t="n">
         <v>9.6</v>
@@ -6136,10 +6136,10 @@
         <v>20</v>
       </c>
       <c r="BA29" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB29" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC29" t="n">
         <v>17.5</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="G30" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H30" t="n">
-        <v>1.04</v>
+        <v>1.62</v>
       </c>
       <c r="I30" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="J30" t="n">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="K30" t="n">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -6216,19 +6216,19 @@
         <v>1.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P30" t="n">
         <v>1.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="R30" t="n">
         <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T30" t="n">
         <v>1.11</v>
@@ -6237,49 +6237,49 @@
         <v>1.11</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB30" t="n">
         <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF30" t="n">
         <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI30" t="n">
         <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK30" t="n">
         <v>1000</v>
@@ -6288,7 +6288,7 @@
         <v>1000</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN30" t="n">
         <v>1000</v>
@@ -6297,62 +6297,62 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.02</v>
+        <v>5.6</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.02</v>
+        <v>1.92</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.02</v>
+        <v>2.02</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.02</v>
+        <v>1.9</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.02</v>
+        <v>5.1</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.02</v>
+        <v>1.86</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.02</v>
+        <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.02</v>
+        <v>2.02</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.02</v>
+        <v>1.92</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.02</v>
+        <v>1.99</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.02</v>
+        <v>2.06</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.02</v>
+        <v>2.06</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.02</v>
+        <v>2.06</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.02</v>
+        <v>4.6</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -6383,16 +6383,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G31" t="n">
         <v>1.96</v>
       </c>
       <c r="H31" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="I31" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J31" t="n">
         <v>3.4</v>
@@ -6407,10 +6407,10 @@
         <v>1.12</v>
       </c>
       <c r="N31" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O31" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P31" t="n">
         <v>1.57</v>
@@ -6446,19 +6446,19 @@
         <v>46</v>
       </c>
       <c r="AA31" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AB31" t="n">
         <v>7.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD31" t="n">
         <v>27</v>
       </c>
       <c r="AE31" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AF31" t="n">
         <v>12</v>
@@ -6470,7 +6470,7 @@
         <v>34</v>
       </c>
       <c r="AI31" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AJ31" t="n">
         <v>27</v>
@@ -6479,10 +6479,10 @@
         <v>34</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AM31" t="n">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="AN31" t="n">
         <v>27</v>
@@ -6491,16 +6491,16 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="AQ31" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AT31" t="n">
         <v>5.7</v>
@@ -6509,44 +6509,44 @@
         <v>7.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>4.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AX31" t="n">
         <v>8.6</v>
       </c>
       <c r="AY31" t="n">
-        <v>3.85</v>
+        <v>6.4</v>
       </c>
       <c r="AZ31" t="n">
         <v>24</v>
       </c>
       <c r="BA31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD31" t="n">
         <v>5.3</v>
       </c>
-      <c r="BB31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BE31" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BF31" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -6577,16 +6577,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G32" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H32" t="n">
         <v>4.1</v>
       </c>
       <c r="I32" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J32" t="n">
         <v>3.35</v>
@@ -6625,7 +6625,7 @@
         <v>1.96</v>
       </c>
       <c r="V32" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W32" t="n">
         <v>1.89</v>
@@ -6640,7 +6640,7 @@
         <v>38</v>
       </c>
       <c r="AA32" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB32" t="n">
         <v>9.4</v>
@@ -6652,7 +6652,7 @@
         <v>21</v>
       </c>
       <c r="AE32" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF32" t="n">
         <v>14</v>
@@ -6664,7 +6664,7 @@
         <v>23</v>
       </c>
       <c r="AI32" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AJ32" t="n">
         <v>28</v>
@@ -6676,13 +6676,13 @@
         <v>50</v>
       </c>
       <c r="AM32" t="n">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN32" t="n">
         <v>21</v>
       </c>
       <c r="AO32" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AP32" t="n">
         <v>10.5</v>
@@ -6691,10 +6691,10 @@
         <v>12</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AS32" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT32" t="n">
         <v>7.2</v>
@@ -6706,7 +6706,7 @@
         <v>15</v>
       </c>
       <c r="AW32" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX32" t="n">
         <v>10.5</v>
@@ -6718,7 +6718,7 @@
         <v>17</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB32" t="n">
         <v>21</v>
@@ -6727,20 +6727,20 @@
         <v>20</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF32" t="n">
         <v>13.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G33" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H33" t="n">
         <v>4.5</v>
@@ -6789,13 +6789,13 @@
         <v>3.85</v>
       </c>
       <c r="L33" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M33" t="n">
         <v>1.07</v>
       </c>
       <c r="N33" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O33" t="n">
         <v>1.34</v>
@@ -6810,13 +6810,13 @@
         <v>1.35</v>
       </c>
       <c r="S33" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T33" t="n">
         <v>1.87</v>
       </c>
       <c r="U33" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V33" t="n">
         <v>1.26</v>
@@ -6825,16 +6825,16 @@
         <v>2.04</v>
       </c>
       <c r="X33" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Y33" t="n">
         <v>16.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AA33" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AB33" t="n">
         <v>8.800000000000001</v>
@@ -6846,7 +6846,7 @@
         <v>19.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AF33" t="n">
         <v>12</v>
@@ -6858,7 +6858,7 @@
         <v>21</v>
       </c>
       <c r="AI33" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AJ33" t="n">
         <v>23</v>
@@ -6867,10 +6867,10 @@
         <v>22</v>
       </c>
       <c r="AL33" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="AM33" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN33" t="n">
         <v>15</v>
@@ -6888,7 +6888,7 @@
         <v>28</v>
       </c>
       <c r="AS33" t="n">
-        <v>8.6</v>
+        <v>29</v>
       </c>
       <c r="AT33" t="n">
         <v>7.8</v>
@@ -6897,7 +6897,7 @@
         <v>7.6</v>
       </c>
       <c r="AV33" t="n">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="AW33" t="n">
         <v>50</v>
@@ -6909,32 +6909,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ33" t="n">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>8.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BB33" t="n">
         <v>18.5</v>
       </c>
       <c r="BC33" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>7.4</v>
+        <v>18</v>
       </c>
       <c r="BE33" t="n">
-        <v>8.6</v>
+        <v>29</v>
       </c>
       <c r="BF33" t="n">
         <v>12</v>
       </c>
       <c r="BG33" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -6977,7 +6977,7 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="K34" t="n">
         <v>8.6</v>
@@ -6989,40 +6989,40 @@
         <v>1.03</v>
       </c>
       <c r="N34" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O34" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P34" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="R34" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="S34" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="T34" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="U34" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V34" t="n">
         <v>1.04</v>
       </c>
       <c r="W34" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="X34" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="Y34" t="n">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="Z34" t="n">
         <v>260</v>
@@ -7037,13 +7037,13 @@
         <v>19</v>
       </c>
       <c r="AD34" t="n">
-        <v>80</v>
+        <v>390</v>
       </c>
       <c r="AE34" t="n">
         <v>520</v>
       </c>
       <c r="AF34" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AG34" t="n">
         <v>13</v>
@@ -7058,7 +7058,7 @@
         <v>8.4</v>
       </c>
       <c r="AK34" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL34" t="n">
         <v>55</v>
@@ -7067,7 +7067,7 @@
         <v>360</v>
       </c>
       <c r="AN34" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AO34" t="n">
         <v>1000</v>
@@ -7079,10 +7079,10 @@
         <v>38</v>
       </c>
       <c r="AR34" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS34" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AT34" t="n">
         <v>8.199999999999999</v>
@@ -7091,13 +7091,13 @@
         <v>15.5</v>
       </c>
       <c r="AV34" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW34" t="n">
         <v>12</v>
       </c>
       <c r="AX34" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AY34" t="n">
         <v>10.5</v>
@@ -7115,20 +7115,20 @@
         <v>12.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="BE34" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="BF34" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="BG34" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -7159,22 +7159,22 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -7183,22 +7183,22 @@
         <v>1.11</v>
       </c>
       <c r="N35" t="n">
-        <v>1.1</v>
+        <v>2.18</v>
       </c>
       <c r="O35" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="P35" t="n">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="R35" t="n">
         <v>1.18</v>
       </c>
       <c r="S35" t="n">
-        <v>1.05</v>
+        <v>4.1</v>
       </c>
       <c r="T35" t="n">
         <v>1.11</v>
@@ -7207,10 +7207,10 @@
         <v>1.11</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="W35" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -7353,31 +7353,31 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G36" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="I36" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J36" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K36" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L36" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M36" t="n">
         <v>1.1</v>
       </c>
       <c r="N36" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O36" t="n">
         <v>1.44</v>
@@ -7398,125 +7398,125 @@
         <v>2.22</v>
       </c>
       <c r="U36" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V36" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W36" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="X36" t="n">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>970</v>
+        <v>120</v>
       </c>
       <c r="Z36" t="n">
-        <v>48</v>
+        <v>220</v>
       </c>
       <c r="AA36" t="n">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="AB36" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC36" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>700</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP36" t="n">
         <v>9.6</v>
       </c>
-      <c r="AD36" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AQ36" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AR36" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AS36" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="AT36" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AU36" t="n">
         <v>7.8</v>
       </c>
       <c r="AV36" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="AW36" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AX36" t="n">
         <v>8</v>
       </c>
       <c r="AY36" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AZ36" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="BA36" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB36" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BC36" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BE36" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="BF36" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG36" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G37" t="n">
         <v>4.2</v>
@@ -7556,7 +7556,7 @@
         <v>2.14</v>
       </c>
       <c r="I37" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="J37" t="n">
         <v>3.2</v>
@@ -7565,7 +7565,7 @@
         <v>3.6</v>
       </c>
       <c r="L37" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="M37" t="n">
         <v>1.09</v>
@@ -7574,13 +7574,13 @@
         <v>3.05</v>
       </c>
       <c r="O37" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P37" t="n">
         <v>1.7</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R37" t="n">
         <v>1.26</v>
@@ -7589,13 +7589,13 @@
         <v>4.2</v>
       </c>
       <c r="T37" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U37" t="n">
         <v>1.92</v>
       </c>
       <c r="V37" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="W37" t="n">
         <v>1.32</v>
@@ -7655,62 +7655,62 @@
         <v>28</v>
       </c>
       <c r="AP37" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AQ37" t="n">
-        <v>3</v>
+        <v>7.2</v>
       </c>
       <c r="AR37" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AS37" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.94</v>
+        <v>6.6</v>
       </c>
       <c r="AV37" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="AW37" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AX37" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AY37" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="AZ37" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BA37" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG37" t="n">
         <v>4</v>
       </c>
-      <c r="BB37" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG37" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -7744,13 +7744,13 @@
         <v>3.65</v>
       </c>
       <c r="G38" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H38" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J38" t="n">
         <v>3.25</v>
@@ -7759,7 +7759,7 @@
         <v>3.35</v>
       </c>
       <c r="L38" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M38" t="n">
         <v>1.1</v>
@@ -7771,10 +7771,10 @@
         <v>1.44</v>
       </c>
       <c r="P38" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="R38" t="n">
         <v>1.25</v>
@@ -7789,16 +7789,16 @@
         <v>1.94</v>
       </c>
       <c r="V38" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W38" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X38" t="n">
         <v>11</v>
       </c>
       <c r="Y38" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z38" t="n">
         <v>13.5</v>
@@ -7825,10 +7825,10 @@
         <v>15.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AI38" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ38" t="n">
         <v>90</v>
@@ -7846,10 +7846,10 @@
         <v>65</v>
       </c>
       <c r="AO38" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP38" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ38" t="n">
         <v>7.6</v>
@@ -7864,7 +7864,7 @@
         <v>10.5</v>
       </c>
       <c r="AU38" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV38" t="n">
         <v>10</v>
@@ -7879,32 +7879,32 @@
         <v>13.5</v>
       </c>
       <c r="AZ38" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA38" t="n">
-        <v>11.5</v>
+        <v>42</v>
       </c>
       <c r="BB38" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BC38" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD38" t="n">
-        <v>12.5</v>
+        <v>42</v>
       </c>
       <c r="BE38" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="BF38" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="BG38" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>
@@ -7941,7 +7941,7 @@
         <v>2.18</v>
       </c>
       <c r="H39" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I39" t="n">
         <v>4.1</v>
@@ -7950,10 +7950,10 @@
         <v>3.45</v>
       </c>
       <c r="K39" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L39" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M39" t="n">
         <v>1.06</v>
@@ -7965,7 +7965,7 @@
         <v>1.28</v>
       </c>
       <c r="P39" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q39" t="n">
         <v>1.82</v>
@@ -7974,10 +7974,10 @@
         <v>1.39</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T39" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U39" t="n">
         <v>2.2</v>
@@ -7992,7 +7992,7 @@
         <v>1000</v>
       </c>
       <c r="Y39" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z39" t="n">
         <v>1000</v>
@@ -8001,22 +8001,22 @@
         <v>1000</v>
       </c>
       <c r="AB39" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC39" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD39" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE39" t="n">
         <v>1000</v>
       </c>
       <c r="AF39" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG39" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH39" t="n">
         <v>1000</v>
@@ -8025,7 +8025,7 @@
         <v>1000</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK39" t="n">
         <v>1000</v>
@@ -8037,68 +8037,68 @@
         <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO39" t="n">
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="AQ39" t="n">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="AR39" t="n">
-        <v>3.85</v>
+        <v>5.3</v>
       </c>
       <c r="AS39" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="AT39" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU39" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="AV39" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="AW39" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AX39" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="AY39" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="AZ39" t="n">
-        <v>3.55</v>
+        <v>6</v>
       </c>
       <c r="BA39" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="BB39" t="n">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="BC39" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="BD39" t="n">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="BE39" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="BF39" t="n">
-        <v>10.5</v>
+        <v>4.7</v>
       </c>
       <c r="BG39" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-18 19:00:25</t>
+          <t>2026-03-18 21:13:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="G2" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="H2" t="n">
         <v>1.33</v>
@@ -781,13 +781,13 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q2" t="n">
         <v>2.02</v>
@@ -796,10 +796,10 @@
         <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T2" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="U2" t="n">
         <v>1.57</v>
@@ -808,19 +808,19 @@
         <v>3.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="Z2" t="n">
         <v>7</v>
       </c>
       <c r="AA2" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AB2" t="n">
         <v>34</v>
@@ -844,7 +844,7 @@
         <v>42</v>
       </c>
       <c r="AI2" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
@@ -868,7 +868,7 @@
         <v>12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AR2" t="n">
         <v>5.9</v>
@@ -877,10 +877,10 @@
         <v>9</v>
       </c>
       <c r="AT2" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AV2" t="n">
         <v>9.6</v>
@@ -889,38 +889,38 @@
         <v>15.5</v>
       </c>
       <c r="AX2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY2" t="n">
         <v>6.4</v>
       </c>
-      <c r="AY2" t="n">
-        <v>38</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG2" t="n">
         <v>5.9</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -957,16 +957,16 @@
         <v>18.5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="I3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="J3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K3" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="L3" t="n">
         <v>1.37</v>
@@ -975,31 +975,31 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="P3" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
         <v>1.83</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="T3" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="U3" t="n">
         <v>1.59</v>
       </c>
       <c r="V3" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="W3" t="n">
         <v>1.05</v>
@@ -1008,10 +1008,10 @@
         <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1020,7 +1020,7 @@
         <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.15</v>
+        <v>2.44</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.2</v>
+        <v>2.46</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.25</v>
+        <v>2.46</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.35</v>
+        <v>2.54</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.35</v>
+        <v>2.54</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.35</v>
+        <v>2.54</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.35</v>
+        <v>2.54</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
         <v>3.55</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.4</v>
@@ -1178,7 +1178,7 @@
         <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R4" t="n">
         <v>1.37</v>
@@ -1187,10 +1187,10 @@
         <v>3.35</v>
       </c>
       <c r="T4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V4" t="n">
         <v>1.33</v>
@@ -1199,7 +1199,7 @@
         <v>1.84</v>
       </c>
       <c r="X4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y4" t="n">
         <v>15</v>
@@ -1238,13 +1238,13 @@
         <v>27</v>
       </c>
       <c r="AK4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM4" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN4" t="n">
         <v>16</v>
@@ -1253,16 +1253,16 @@
         <v>46</v>
       </c>
       <c r="AP4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>13.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS4" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AT4" t="n">
         <v>9</v>
@@ -1304,11 +1304,11 @@
         <v>14.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         <v>1.39</v>
       </c>
       <c r="H5" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="I5" t="n">
         <v>16</v>
@@ -1354,7 +1354,7 @@
         <v>4.7</v>
       </c>
       <c r="K5" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="L5" t="n">
         <v>1.29</v>
@@ -1369,10 +1369,10 @@
         <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R5" t="n">
         <v>1.44</v>
@@ -1381,16 +1381,16 @@
         <v>2.6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V5" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="X5" t="n">
         <v>950</v>
@@ -1408,7 +1408,7 @@
         <v>16</v>
       </c>
       <c r="AC5" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AD5" t="n">
         <v>950</v>
@@ -1417,7 +1417,7 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AG5" t="n">
         <v>970</v>
@@ -1441,16 +1441,16 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.2</v>
+        <v>29</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AR5" t="n">
         <v>4.2</v>
@@ -1459,25 +1459,25 @@
         <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="AU5" t="n">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW5" t="n">
         <v>4.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>7.8</v>
+        <v>5.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="BA5" t="n">
         <v>4.2</v>
@@ -1486,23 +1486,23 @@
         <v>5.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BF5" t="n">
         <v>3.75</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.5</v>
       </c>
       <c r="BG5" t="n">
         <v>4.9</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>1.78</v>
       </c>
       <c r="H7" t="n">
         <v>5.4</v>
       </c>
       <c r="I7" t="n">
-        <v>19</v>
+        <v>5.9</v>
       </c>
       <c r="J7" t="n">
-        <v>2.74</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1751,64 +1751,64 @@
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1</v>
+        <v>3.45</v>
       </c>
       <c r="O7" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>2.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.09</v>
+        <v>1.41</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.79</v>
       </c>
       <c r="S7" t="n">
-        <v>1.09</v>
+        <v>1.9</v>
       </c>
       <c r="T7" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="U7" t="n">
-        <v>1.52</v>
+        <v>2.72</v>
       </c>
       <c r="V7" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH7" t="n">
         <v>1000</v>
@@ -1817,80 +1817,80 @@
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>900</v>
+        <v>22</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.36</v>
+        <v>16</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.39</v>
+        <v>4.9</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.39</v>
+        <v>5.1</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.39</v>
+        <v>4.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.32</v>
+        <v>4.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.39</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.39</v>
+        <v>17</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.39</v>
+        <v>5.1</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.31</v>
+        <v>4.3</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.28</v>
+        <v>7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.39</v>
+        <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.39</v>
+        <v>5.1</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.34</v>
+        <v>4.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.32</v>
+        <v>4.3</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.35</v>
+        <v>4.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.39</v>
+        <v>5.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.54</v>
+        <v>4.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.55</v>
+        <v>4.9</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.52</v>
+        <v>1.83</v>
       </c>
       <c r="G8" t="n">
-        <v>44</v>
+        <v>2.16</v>
       </c>
       <c r="H8" t="n">
-        <v>2.36</v>
+        <v>2.96</v>
       </c>
       <c r="I8" t="n">
-        <v>44</v>
+        <v>4.4</v>
       </c>
       <c r="J8" t="n">
         <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>32</v>
+        <v>6.8</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1945,22 +1945,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>2.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.86</v>
       </c>
       <c r="S8" t="n">
-        <v>1.08</v>
+        <v>1.75</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -1969,10 +1969,10 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.86</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2002,7 +2002,7 @@
         <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH8" t="n">
         <v>1000</v>
@@ -2029,62 +2029,62 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.14</v>
+        <v>2.12</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.14</v>
+        <v>2.16</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.14</v>
+        <v>2.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.14</v>
+        <v>2.04</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.13</v>
+        <v>2.28</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.06</v>
+        <v>6.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.14</v>
+        <v>2.56</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.14</v>
+        <v>2.18</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.13</v>
+        <v>2.18</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.13</v>
+        <v>3.8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.09</v>
+        <v>4</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.14</v>
+        <v>2.18</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.13</v>
+        <v>2.32</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.13</v>
+        <v>2.9</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.13</v>
+        <v>2.22</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.14</v>
+        <v>4.7</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.13</v>
+        <v>3.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.55</v>
+        <v>2.88</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="G9" t="n">
         <v>1.14</v>
@@ -2148,7 +2148,7 @@
         <v>2.68</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R9" t="n">
         <v>1.66</v>
@@ -2157,16 +2157,16 @@
         <v>2.18</v>
       </c>
       <c r="T9" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V9" t="n">
         <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X9" t="n">
         <v>36</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G10" t="n">
         <v>1.39</v>
@@ -2318,10 +2318,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K10" t="n">
         <v>5.7</v>
@@ -2339,7 +2339,7 @@
         <v>1.21</v>
       </c>
       <c r="P10" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
         <v>1.65</v>
@@ -2372,7 +2372,7 @@
         <v>540</v>
       </c>
       <c r="AA10" t="n">
-        <v>370</v>
+        <v>450</v>
       </c>
       <c r="AB10" t="n">
         <v>9.800000000000001</v>
@@ -2396,7 +2396,7 @@
         <v>29</v>
       </c>
       <c r="AI10" t="n">
-        <v>470</v>
+        <v>130</v>
       </c>
       <c r="AJ10" t="n">
         <v>11.5</v>
@@ -2423,7 +2423,7 @@
         <v>30</v>
       </c>
       <c r="AR10" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="AS10" t="n">
         <v>14</v>
@@ -2432,7 +2432,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV10" t="n">
         <v>32</v>
@@ -2456,10 +2456,10 @@
         <v>10.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE10" t="n">
         <v>29</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -2506,19 +2506,19 @@
         <v>1.84</v>
       </c>
       <c r="G11" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="H11" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="I11" t="n">
         <v>5.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K11" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
         <v>1.44</v>
@@ -2539,28 +2539,28 @@
         <v>2.12</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
         <v>3.85</v>
       </c>
       <c r="T11" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V11" t="n">
         <v>1.21</v>
       </c>
       <c r="W11" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="X11" t="n">
         <v>13</v>
       </c>
       <c r="Y11" t="n">
-        <v>360</v>
+        <v>950</v>
       </c>
       <c r="Z11" t="n">
         <v>40</v>
@@ -2569,7 +2569,7 @@
         <v>140</v>
       </c>
       <c r="AB11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC11" t="n">
         <v>8</v>
@@ -2608,10 +2608,10 @@
         <v>15</v>
       </c>
       <c r="AO11" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AP11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ11" t="n">
         <v>14.5</v>
@@ -2623,13 +2623,13 @@
         <v>12.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AW11" t="n">
         <v>44</v>
@@ -2653,7 +2653,7 @@
         <v>18.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="BE11" t="n">
         <v>12.5</v>
@@ -2662,11 +2662,11 @@
         <v>13</v>
       </c>
       <c r="BG11" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="H12" t="n">
         <v>10.5</v>
@@ -2712,7 +2712,7 @@
         <v>5.3</v>
       </c>
       <c r="K12" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L12" t="n">
         <v>1.37</v>
@@ -2721,28 +2721,28 @@
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="O12" t="n">
         <v>1.3</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R12" t="n">
         <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V12" t="n">
         <v>1.09</v>
@@ -2751,16 +2751,16 @@
         <v>3.5</v>
       </c>
       <c r="X12" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y12" t="n">
         <v>32</v>
       </c>
       <c r="Z12" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AA12" t="n">
-        <v>680</v>
+        <v>490</v>
       </c>
       <c r="AB12" t="n">
         <v>7.2</v>
@@ -2769,10 +2769,10 @@
         <v>12</v>
       </c>
       <c r="AD12" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AE12" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="AF12" t="n">
         <v>7.4</v>
@@ -2784,40 +2784,40 @@
         <v>34</v>
       </c>
       <c r="AI12" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AJ12" t="n">
         <v>11</v>
       </c>
       <c r="AK12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AM12" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AN12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AP12" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AQ12" t="n">
         <v>22</v>
       </c>
       <c r="AR12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS12" t="n">
         <v>55</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU12" t="n">
         <v>10.5</v>
@@ -2826,7 +2826,7 @@
         <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AX12" t="n">
         <v>6.6</v>
@@ -2835,10 +2835,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BA12" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BB12" t="n">
         <v>10</v>
@@ -2850,17 +2850,17 @@
         <v>32</v>
       </c>
       <c r="BE12" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BF12" t="n">
         <v>6.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>6.2</v>
       </c>
       <c r="G13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H13" t="n">
         <v>1.65</v>
@@ -2915,7 +2915,7 @@
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O13" t="n">
         <v>1.33</v>
@@ -2924,7 +2924,7 @@
         <v>1.96</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
         <v>1.36</v>
@@ -2936,7 +2936,7 @@
         <v>2.02</v>
       </c>
       <c r="U13" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V13" t="n">
         <v>2.5</v>
@@ -2948,13 +2948,13 @@
         <v>14.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z13" t="n">
         <v>9</v>
       </c>
       <c r="AA13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AB13" t="n">
         <v>19.5</v>
@@ -2969,7 +2969,7 @@
         <v>17.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AG13" t="n">
         <v>24</v>
@@ -2984,10 +2984,10 @@
         <v>700</v>
       </c>
       <c r="AK13" t="n">
-        <v>100</v>
+        <v>210</v>
       </c>
       <c r="AL13" t="n">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="AM13" t="n">
         <v>140</v>
@@ -3002,7 +3002,7 @@
         <v>13.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR13" t="n">
         <v>8.199999999999999</v>
@@ -3014,7 +3014,7 @@
         <v>16.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV13" t="n">
         <v>9.4</v>
@@ -3023,10 +3023,10 @@
         <v>16.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AY13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ13" t="n">
         <v>22</v>
@@ -3035,26 +3035,26 @@
         <v>34</v>
       </c>
       <c r="BB13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC13" t="n">
         <v>85</v>
       </c>
       <c r="BD13" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="BE13" t="n">
         <v>29</v>
       </c>
       <c r="BF13" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>2.66</v>
       </c>
       <c r="G14" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H14" t="n">
         <v>2.8</v>
@@ -3115,7 +3115,7 @@
         <v>1.3</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q14" t="n">
         <v>1.94</v>
@@ -3124,13 +3124,13 @@
         <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U14" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V14" t="n">
         <v>1.53</v>
@@ -3139,28 +3139,28 @@
         <v>1.57</v>
       </c>
       <c r="X14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z14" t="n">
         <v>19</v>
       </c>
       <c r="AA14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AB14" t="n">
         <v>12.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF14" t="n">
         <v>19</v>
@@ -3169,16 +3169,16 @@
         <v>12.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ14" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL14" t="n">
         <v>40</v>
@@ -3187,10 +3187,10 @@
         <v>320</v>
       </c>
       <c r="AN14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO14" t="n">
         <v>28</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>32</v>
       </c>
       <c r="AP14" t="n">
         <v>13.5</v>
@@ -3199,56 +3199,56 @@
         <v>10</v>
       </c>
       <c r="AR14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS14" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="AT14" t="n">
         <v>10</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV14" t="n">
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AX14" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ14" t="n">
         <v>14.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="BB14" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="BC14" t="n">
         <v>21</v>
       </c>
       <c r="BD14" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="BE14" t="n">
-        <v>10.5</v>
+        <v>38</v>
       </c>
       <c r="BF14" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.4</v>
+        <v>22</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -3300,10 +3300,10 @@
         <v>1.28</v>
       </c>
       <c r="M15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="O15" t="n">
         <v>1.19</v>
@@ -3324,7 +3324,7 @@
         <v>2.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="V15" t="n">
         <v>1.08</v>
@@ -3333,7 +3333,7 @@
         <v>4.1</v>
       </c>
       <c r="X15" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Y15" t="n">
         <v>42</v>
@@ -3348,7 +3348,7 @@
         <v>11</v>
       </c>
       <c r="AC15" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AD15" t="n">
         <v>46</v>
@@ -3357,7 +3357,7 @@
         <v>220</v>
       </c>
       <c r="AF15" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AG15" t="n">
         <v>12</v>
@@ -3387,31 +3387,31 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AQ15" t="n">
         <v>16</v>
       </c>
       <c r="AR15" t="n">
-        <v>29</v>
+        <v>10.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT15" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU15" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AV15" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="AW15" t="n">
         <v>9.4</v>
       </c>
       <c r="AX15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY15" t="n">
         <v>9.800000000000001</v>
@@ -3420,7 +3420,7 @@
         <v>27</v>
       </c>
       <c r="BA15" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB15" t="n">
         <v>8.6</v>
@@ -3432,17 +3432,17 @@
         <v>32</v>
       </c>
       <c r="BE15" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="BF15" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BG15" t="n">
         <v>15</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -3485,34 +3485,34 @@
         <v>2.38</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K16" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L16" t="n">
         <v>1.4</v>
       </c>
       <c r="M16" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O16" t="n">
         <v>1.29</v>
       </c>
       <c r="P16" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T16" t="n">
         <v>1.73</v>
@@ -3527,7 +3527,7 @@
         <v>1.43</v>
       </c>
       <c r="X16" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y16" t="n">
         <v>11.5</v>
@@ -3536,10 +3536,10 @@
         <v>15.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB16" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC16" t="n">
         <v>8</v>
@@ -3548,7 +3548,7 @@
         <v>11</v>
       </c>
       <c r="AE16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF16" t="n">
         <v>23</v>
@@ -3560,28 +3560,28 @@
         <v>15.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ16" t="n">
         <v>55</v>
       </c>
       <c r="AK16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL16" t="n">
         <v>42</v>
       </c>
       <c r="AM16" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO16" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ16" t="n">
         <v>10.5</v>
@@ -3629,14 +3629,14 @@
         <v>70</v>
       </c>
       <c r="BF16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BG16" t="n">
         <v>16</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G17" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I17" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J17" t="n">
         <v>3.45</v>
@@ -3691,7 +3691,7 @@
         <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O17" t="n">
         <v>1.38</v>
@@ -3718,7 +3718,7 @@
         <v>1.33</v>
       </c>
       <c r="W17" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X17" t="n">
         <v>12.5</v>
@@ -3736,7 +3736,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD17" t="n">
         <v>15.5</v>
@@ -3757,10 +3757,10 @@
         <v>60</v>
       </c>
       <c r="AJ17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL17" t="n">
         <v>40</v>
@@ -3769,7 +3769,7 @@
         <v>120</v>
       </c>
       <c r="AN17" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AO17" t="n">
         <v>60</v>
@@ -3790,13 +3790,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV17" t="n">
         <v>14.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AX17" t="n">
         <v>12</v>
@@ -3805,7 +3805,7 @@
         <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA17" t="n">
         <v>48</v>
@@ -3814,10 +3814,10 @@
         <v>25</v>
       </c>
       <c r="BC17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD17" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE17" t="n">
         <v>60</v>
@@ -3826,11 +3826,11 @@
         <v>18</v>
       </c>
       <c r="BG17" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -3861,19 +3861,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G18" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H18" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
         <v>6.2</v>
       </c>
       <c r="J18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K18" t="n">
         <v>4.4</v>
@@ -3900,7 +3900,7 @@
         <v>1.46</v>
       </c>
       <c r="S18" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
         <v>1.87</v>
@@ -3909,19 +3909,19 @@
         <v>2.1</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W18" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X18" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y18" t="n">
         <v>21</v>
       </c>
       <c r="Z18" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AA18" t="n">
         <v>160</v>
@@ -3933,10 +3933,10 @@
         <v>9.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE18" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF18" t="n">
         <v>9.800000000000001</v>
@@ -3984,7 +3984,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU18" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV18" t="n">
         <v>20</v>
@@ -3996,10 +3996,10 @@
         <v>9.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA18" t="n">
         <v>60</v>
@@ -4008,7 +4008,7 @@
         <v>15</v>
       </c>
       <c r="BC18" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD18" t="n">
         <v>30</v>
@@ -4017,14 +4017,14 @@
         <v>60</v>
       </c>
       <c r="BF18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG18" t="n">
         <v>70</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -4061,16 +4061,16 @@
         <v>600</v>
       </c>
       <c r="H19" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="I19" t="n">
-        <v>2.72</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
         <v>2.8</v>
       </c>
       <c r="K19" t="n">
-        <v>950</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4082,25 +4082,25 @@
         <v>1.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P19" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="R19" t="n">
         <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>1.02</v>
+        <v>4.4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U19" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
@@ -4109,10 +4109,10 @@
         <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="Z19" t="n">
         <v>11</v>
@@ -4121,16 +4121,16 @@
         <v>23</v>
       </c>
       <c r="AB19" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
         <v>10</v>
       </c>
       <c r="AD19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE19" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="AF19" t="n">
         <v>500</v>
@@ -4139,10 +4139,10 @@
         <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ19" t="n">
         <v>1000</v>
@@ -4163,10 +4163,10 @@
         <v>21</v>
       </c>
       <c r="AP19" t="n">
-        <v>8.6</v>
+        <v>4.9</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AR19" t="n">
         <v>7.8</v>
@@ -4184,41 +4184,41 @@
         <v>6.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AY19" t="n">
         <v>19</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BE19" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BF19" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BG19" t="n">
         <v>12.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -4252,16 +4252,16 @@
         <v>2.92</v>
       </c>
       <c r="G20" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H20" t="n">
         <v>2.74</v>
       </c>
       <c r="I20" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J20" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K20" t="n">
         <v>3.2</v>
@@ -4273,19 +4273,19 @@
         <v>1.11</v>
       </c>
       <c r="N20" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="O20" t="n">
         <v>1.5</v>
       </c>
       <c r="P20" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="Q20" t="n">
         <v>2.46</v>
       </c>
       <c r="R20" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
         <v>4.7</v>
@@ -4300,49 +4300,49 @@
         <v>1.51</v>
       </c>
       <c r="W20" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y20" t="n">
         <v>9</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AB20" t="n">
         <v>9.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD20" t="n">
         <v>14</v>
       </c>
       <c r="AE20" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AK20" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AL20" t="n">
         <v>380</v>
@@ -4351,7 +4351,7 @@
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO20" t="n">
         <v>500</v>
@@ -4360,59 +4360,59 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AR20" t="n">
         <v>15</v>
       </c>
       <c r="AS20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT20" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AT20" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AU20" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV20" t="n">
         <v>11.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="AX20" t="n">
         <v>16.5</v>
       </c>
       <c r="AY20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE20" t="n">
         <v>12</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BF20" t="n">
         <v>11.5</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="BG20" t="n">
         <v>32</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="G21" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="H21" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I21" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="J21" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K21" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L21" t="n">
         <v>1.47</v>
@@ -4467,13 +4467,13 @@
         <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O21" t="n">
         <v>1.41</v>
       </c>
       <c r="P21" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q21" t="n">
         <v>2.2</v>
@@ -4488,19 +4488,19 @@
         <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V21" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W21" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="X21" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="Z21" t="n">
         <v>120</v>
@@ -4509,104 +4509,104 @@
         <v>900</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK21" t="n">
         <v>25</v>
       </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>380</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>28</v>
-      </c>
       <c r="AL21" t="n">
-        <v>60</v>
+        <v>290</v>
       </c>
       <c r="AM21" t="n">
         <v>580</v>
       </c>
       <c r="AN21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB21" t="n">
         <v>20</v>
       </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX21" t="n">
+      <c r="BC21" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD21" t="n">
         <v>9</v>
       </c>
-      <c r="AY21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BE21" t="n">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="BF21" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -4640,16 +4640,16 @@
         <v>1.7</v>
       </c>
       <c r="G22" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="H22" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I22" t="n">
         <v>6.2</v>
       </c>
       <c r="J22" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K22" t="n">
         <v>4.1</v>
@@ -4688,19 +4688,19 @@
         <v>1.19</v>
       </c>
       <c r="W22" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="X22" t="n">
         <v>14</v>
       </c>
       <c r="Y22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z22" t="n">
         <v>46</v>
       </c>
       <c r="AA22" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB22" t="n">
         <v>9</v>
@@ -4754,7 +4754,7 @@
         <v>26</v>
       </c>
       <c r="AS22" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AT22" t="n">
         <v>7.6</v>
@@ -4766,7 +4766,7 @@
         <v>20</v>
       </c>
       <c r="AW22" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AX22" t="n">
         <v>8.800000000000001</v>
@@ -4778,7 +4778,7 @@
         <v>20</v>
       </c>
       <c r="BA22" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BB22" t="n">
         <v>15</v>
@@ -4796,11 +4796,11 @@
         <v>10</v>
       </c>
       <c r="BG22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -4831,16 +4831,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G23" t="n">
         <v>2.18</v>
       </c>
       <c r="H23" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I23" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="J23" t="n">
         <v>3.8</v>
@@ -4864,13 +4864,13 @@
         <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R23" t="n">
         <v>1.43</v>
       </c>
       <c r="S23" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T23" t="n">
         <v>1.74</v>
@@ -4879,10 +4879,10 @@
         <v>2.28</v>
       </c>
       <c r="V23" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W23" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X23" t="n">
         <v>19.5</v>
@@ -4891,22 +4891,22 @@
         <v>15</v>
       </c>
       <c r="Z23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA23" t="n">
         <v>150</v>
       </c>
       <c r="AB23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC23" t="n">
         <v>8.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF23" t="n">
         <v>14</v>
@@ -4921,7 +4921,7 @@
         <v>48</v>
       </c>
       <c r="AJ23" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AK23" t="n">
         <v>22</v>
@@ -4930,13 +4930,13 @@
         <v>34</v>
       </c>
       <c r="AM23" t="n">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="AN23" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AO23" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AP23" t="n">
         <v>15</v>
@@ -4945,16 +4945,16 @@
         <v>13.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AS23" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AT23" t="n">
         <v>10</v>
       </c>
       <c r="AU23" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV23" t="n">
         <v>14</v>
@@ -4963,7 +4963,7 @@
         <v>36</v>
       </c>
       <c r="AX23" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY23" t="n">
         <v>10</v>
@@ -4972,29 +4972,29 @@
         <v>15.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BB23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC23" t="n">
         <v>19.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE23" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="BF23" t="n">
         <v>13</v>
       </c>
       <c r="BG23" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -5043,34 +5043,34 @@
         <v>3.75</v>
       </c>
       <c r="L24" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M24" t="n">
         <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P24" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R24" t="n">
         <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="U24" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V24" t="n">
         <v>1.43</v>
@@ -5079,61 +5079,61 @@
         <v>1.7</v>
       </c>
       <c r="X24" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="Y24" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF24" t="n">
         <v>16.5</v>
       </c>
-      <c r="Z24" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AG24" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL24" t="n">
         <v>36</v>
       </c>
-      <c r="AK24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>38</v>
-      </c>
       <c r="AM24" t="n">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="AN24" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ24" t="n">
         <v>13</v>
@@ -5142,53 +5142,53 @@
         <v>20</v>
       </c>
       <c r="AS24" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AT24" t="n">
         <v>10.5</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AW24" t="n">
         <v>30</v>
       </c>
       <c r="AX24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY24" t="n">
         <v>10</v>
       </c>
       <c r="AZ24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BB24" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BC24" t="n">
         <v>20</v>
       </c>
       <c r="BD24" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="BE24" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="BF24" t="n">
         <v>14.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
         <v>1.43</v>
       </c>
       <c r="H25" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I25" t="n">
         <v>11</v>
@@ -5237,34 +5237,34 @@
         <v>5.3</v>
       </c>
       <c r="L25" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M25" t="n">
         <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S25" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U25" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="V25" t="n">
         <v>1.1</v>
@@ -5294,13 +5294,13 @@
         <v>38</v>
       </c>
       <c r="AE25" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AF25" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG25" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH25" t="n">
         <v>30</v>
@@ -5315,10 +5315,10 @@
         <v>16.5</v>
       </c>
       <c r="AL25" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM25" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN25" t="n">
         <v>6.8</v>
@@ -5327,7 +5327,7 @@
         <v>320</v>
       </c>
       <c r="AP25" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ25" t="n">
         <v>23</v>
@@ -5348,7 +5348,7 @@
         <v>30</v>
       </c>
       <c r="AW25" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX25" t="n">
         <v>7.2</v>
@@ -5360,16 +5360,16 @@
         <v>26</v>
       </c>
       <c r="BA25" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC25" t="n">
         <v>14.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE25" t="n">
         <v>55</v>
@@ -5378,11 +5378,11 @@
         <v>6</v>
       </c>
       <c r="BG25" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="G26" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="H26" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="I26" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K26" t="n">
         <v>5</v>
-      </c>
-      <c r="K26" t="n">
-        <v>5.1</v>
       </c>
       <c r="L26" t="n">
         <v>1.39</v>
@@ -5437,49 +5437,49 @@
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O26" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T26" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U26" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="V26" t="n">
         <v>1.11</v>
       </c>
       <c r="W26" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="X26" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z26" t="n">
         <v>85</v>
       </c>
       <c r="AA26" t="n">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="AB26" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC26" t="n">
         <v>11</v>
@@ -5494,10 +5494,10 @@
         <v>7.8</v>
       </c>
       <c r="AG26" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI26" t="n">
         <v>150</v>
@@ -5506,10 +5506,10 @@
         <v>11.5</v>
       </c>
       <c r="AK26" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AL26" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM26" t="n">
         <v>190</v>
@@ -5518,22 +5518,22 @@
         <v>7.2</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AP26" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ26" t="n">
         <v>24</v>
       </c>
       <c r="AR26" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AS26" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AT26" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU26" t="n">
         <v>10</v>
@@ -5542,41 +5542,41 @@
         <v>30</v>
       </c>
       <c r="AW26" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AX26" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY26" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ26" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BA26" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BB26" t="n">
         <v>10.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BE26" t="n">
         <v>70</v>
       </c>
       <c r="BF26" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG26" t="n">
         <v>48</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -5640,10 +5640,10 @@
         <v>2.02</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S27" t="n">
         <v>3.3</v>
@@ -5736,7 +5736,7 @@
         <v>12</v>
       </c>
       <c r="AW27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX27" t="n">
         <v>15.5</v>
@@ -5748,7 +5748,7 @@
         <v>15.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB27" t="n">
         <v>34</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
         <v>1.81</v>
       </c>
       <c r="G28" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H28" t="n">
         <v>5.4</v>
@@ -5831,7 +5831,7 @@
         <v>1.42</v>
       </c>
       <c r="P28" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q28" t="n">
         <v>2.3</v>
@@ -5864,7 +5864,7 @@
         <v>40</v>
       </c>
       <c r="AA28" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AB28" t="n">
         <v>7.2</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
         <v>5.4</v>
       </c>
       <c r="I29" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J29" t="n">
         <v>4.2</v>
@@ -6022,16 +6022,16 @@
         <v>4</v>
       </c>
       <c r="O29" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P29" t="n">
         <v>2.02</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R29" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
         <v>3.45</v>
@@ -6040,7 +6040,7 @@
         <v>1.95</v>
       </c>
       <c r="U29" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V29" t="n">
         <v>1.22</v>
@@ -6061,7 +6061,7 @@
         <v>140</v>
       </c>
       <c r="AB29" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC29" t="n">
         <v>9</v>
@@ -6073,7 +6073,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG29" t="n">
         <v>10</v>
@@ -6082,7 +6082,7 @@
         <v>21</v>
       </c>
       <c r="AI29" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ29" t="n">
         <v>17</v>
@@ -6115,7 +6115,7 @@
         <v>42</v>
       </c>
       <c r="AT29" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU29" t="n">
         <v>8.6</v>
@@ -6130,13 +6130,13 @@
         <v>9.4</v>
       </c>
       <c r="AY29" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ29" t="n">
         <v>20</v>
       </c>
       <c r="BA29" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BB29" t="n">
         <v>16</v>
@@ -6151,14 +6151,14 @@
         <v>100</v>
       </c>
       <c r="BF29" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG29" t="n">
         <v>80</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -6192,19 +6192,19 @@
         <v>2.24</v>
       </c>
       <c r="G30" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H30" t="n">
         <v>1.62</v>
       </c>
       <c r="I30" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="J30" t="n">
         <v>3.05</v>
       </c>
       <c r="K30" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -6237,7 +6237,7 @@
         <v>1.11</v>
       </c>
       <c r="V30" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="W30" t="n">
         <v>1.17</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -6491,16 +6491,16 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AQ31" t="n">
-        <v>11</v>
+        <v>5.8</v>
       </c>
       <c r="AR31" t="n">
         <v>5</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AT31" t="n">
         <v>5.7</v>
@@ -6512,7 +6512,7 @@
         <v>16.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AX31" t="n">
         <v>8.6</v>
@@ -6542,11 +6542,11 @@
         <v>5</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -6577,22 +6577,22 @@
         </is>
       </c>
       <c r="F32" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G32" t="n">
         <v>2</v>
       </c>
-      <c r="G32" t="n">
-        <v>2.12</v>
-      </c>
       <c r="H32" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I32" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="J32" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K32" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L32" t="n">
         <v>1.39</v>
@@ -6601,19 +6601,19 @@
         <v>1.08</v>
       </c>
       <c r="N32" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O32" t="n">
         <v>1.37</v>
       </c>
       <c r="P32" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R32" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S32" t="n">
         <v>3.9</v>
@@ -6625,10 +6625,10 @@
         <v>1.96</v>
       </c>
       <c r="V32" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="W32" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="X32" t="n">
         <v>14</v>
@@ -6670,7 +6670,7 @@
         <v>28</v>
       </c>
       <c r="AK32" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AL32" t="n">
         <v>50</v>
@@ -6679,7 +6679,7 @@
         <v>580</v>
       </c>
       <c r="AN32" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO32" t="n">
         <v>260</v>
@@ -6691,10 +6691,10 @@
         <v>12</v>
       </c>
       <c r="AR32" t="n">
-        <v>5.3</v>
+        <v>14.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AT32" t="n">
         <v>7.2</v>
@@ -6706,10 +6706,10 @@
         <v>15</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX32" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY32" t="n">
         <v>9.4</v>
@@ -6718,29 +6718,29 @@
         <v>17</v>
       </c>
       <c r="BA32" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BB32" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="BC32" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF32" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG32" t="n">
         <v>5.4</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
         <v>1.89</v>
       </c>
       <c r="G33" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H33" t="n">
         <v>4.5</v>
@@ -6783,40 +6783,40 @@
         <v>4.8</v>
       </c>
       <c r="J33" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K33" t="n">
         <v>3.85</v>
       </c>
       <c r="L33" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M33" t="n">
         <v>1.07</v>
       </c>
       <c r="N33" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="O33" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P33" t="n">
         <v>1.95</v>
       </c>
       <c r="Q33" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R33" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T33" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="U33" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V33" t="n">
         <v>1.26</v>
@@ -6825,13 +6825,13 @@
         <v>2.04</v>
       </c>
       <c r="X33" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z33" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA33" t="n">
         <v>500</v>
@@ -6846,10 +6846,10 @@
         <v>19.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AF33" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG33" t="n">
         <v>11</v>
@@ -6861,13 +6861,13 @@
         <v>500</v>
       </c>
       <c r="AJ33" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AK33" t="n">
         <v>22</v>
       </c>
       <c r="AL33" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AM33" t="n">
         <v>580</v>
@@ -6876,10 +6876,10 @@
         <v>15</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AP33" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ33" t="n">
         <v>13</v>
@@ -6888,10 +6888,10 @@
         <v>28</v>
       </c>
       <c r="AS33" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AT33" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU33" t="n">
         <v>7.6</v>
@@ -6909,32 +6909,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ33" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="BA33" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BB33" t="n">
         <v>18.5</v>
       </c>
       <c r="BC33" t="n">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="BE33" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BF33" t="n">
         <v>12</v>
       </c>
       <c r="BG33" t="n">
-        <v>9.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -6968,19 +6968,19 @@
         <v>1.19</v>
       </c>
       <c r="G34" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="H34" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I34" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J34" t="n">
         <v>8</v>
       </c>
       <c r="K34" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="L34" t="n">
         <v>1.28</v>
@@ -6989,28 +6989,28 @@
         <v>1.03</v>
       </c>
       <c r="N34" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O34" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P34" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="Q34" t="n">
         <v>1.55</v>
       </c>
       <c r="R34" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="S34" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="T34" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="U34" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V34" t="n">
         <v>1.04</v>
@@ -7022,7 +7022,7 @@
         <v>50</v>
       </c>
       <c r="Y34" t="n">
-        <v>220</v>
+        <v>950</v>
       </c>
       <c r="Z34" t="n">
         <v>260</v>
@@ -7037,10 +7037,10 @@
         <v>19</v>
       </c>
       <c r="AD34" t="n">
-        <v>390</v>
+        <v>950</v>
       </c>
       <c r="AE34" t="n">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="AF34" t="n">
         <v>7.8</v>
@@ -7049,10 +7049,10 @@
         <v>13</v>
       </c>
       <c r="AH34" t="n">
-        <v>50</v>
+        <v>950</v>
       </c>
       <c r="AI34" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AJ34" t="n">
         <v>8.4</v>
@@ -7064,25 +7064,25 @@
         <v>55</v>
       </c>
       <c r="AM34" t="n">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="AN34" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AO34" t="n">
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AQ34" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AR34" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AT34" t="n">
         <v>8.199999999999999</v>
@@ -7091,10 +7091,10 @@
         <v>15.5</v>
       </c>
       <c r="AV34" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="AW34" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AX34" t="n">
         <v>6.8</v>
@@ -7106,7 +7106,7 @@
         <v>38</v>
       </c>
       <c r="BA34" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="BB34" t="n">
         <v>7.6</v>
@@ -7115,20 +7115,20 @@
         <v>12.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="BE34" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BF34" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BG34" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -7159,22 +7159,22 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="G35" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="H35" t="n">
         <v>2.74</v>
       </c>
       <c r="I35" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J35" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="K35" t="n">
-        <v>3.6</v>
+        <v>950</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -7183,22 +7183,22 @@
         <v>1.11</v>
       </c>
       <c r="N35" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="O35" t="n">
         <v>1.11</v>
       </c>
       <c r="P35" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="R35" t="n">
         <v>1.18</v>
       </c>
       <c r="S35" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T35" t="n">
         <v>1.11</v>
@@ -7207,10 +7207,10 @@
         <v>1.11</v>
       </c>
       <c r="V35" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W35" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -7353,22 +7353,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G36" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H36" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I36" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J36" t="n">
         <v>3.65</v>
       </c>
       <c r="K36" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L36" t="n">
         <v>1.49</v>
@@ -7431,7 +7431,7 @@
         <v>700</v>
       </c>
       <c r="AF36" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AG36" t="n">
         <v>11</v>
@@ -7455,13 +7455,13 @@
         <v>700</v>
       </c>
       <c r="AN36" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO36" t="n">
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ36" t="n">
         <v>8.4</v>
@@ -7473,13 +7473,13 @@
         <v>12</v>
       </c>
       <c r="AT36" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU36" t="n">
         <v>7.8</v>
       </c>
       <c r="AV36" t="n">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW36" t="n">
         <v>11.5</v>
@@ -7488,13 +7488,13 @@
         <v>8</v>
       </c>
       <c r="AY36" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AZ36" t="n">
         <v>13</v>
       </c>
       <c r="BA36" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="BB36" t="n">
         <v>8.4</v>
@@ -7503,20 +7503,20 @@
         <v>10.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BE36" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="BF36" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BG36" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -7562,10 +7562,10 @@
         <v>3.2</v>
       </c>
       <c r="K37" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L37" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="M37" t="n">
         <v>1.09</v>
@@ -7604,7 +7604,7 @@
         <v>13.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Z37" t="n">
         <v>16</v>
@@ -7616,10 +7616,10 @@
         <v>15</v>
       </c>
       <c r="AC37" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD37" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE37" t="n">
         <v>34</v>
@@ -7658,16 +7658,16 @@
         <v>3.6</v>
       </c>
       <c r="AQ37" t="n">
-        <v>7.2</v>
+        <v>3.35</v>
       </c>
       <c r="AR37" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AS37" t="n">
         <v>4.2</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AU37" t="n">
         <v>6.6</v>
@@ -7676,10 +7676,10 @@
         <v>3.55</v>
       </c>
       <c r="AW37" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX37" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AY37" t="n">
         <v>3.9</v>
@@ -7691,26 +7691,26 @@
         <v>4.4</v>
       </c>
       <c r="BB37" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC37" t="n">
         <v>4.5</v>
       </c>
-      <c r="BC37" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD37" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE37" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF37" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG37" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="G38" t="n">
         <v>3.8</v>
@@ -7750,16 +7750,16 @@
         <v>2.32</v>
       </c>
       <c r="I38" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J38" t="n">
         <v>3.25</v>
       </c>
       <c r="K38" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L38" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M38" t="n">
         <v>1.1</v>
@@ -7777,10 +7777,10 @@
         <v>2.36</v>
       </c>
       <c r="R38" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S38" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T38" t="n">
         <v>1.96</v>
@@ -7789,10 +7789,10 @@
         <v>1.94</v>
       </c>
       <c r="V38" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="W38" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X38" t="n">
         <v>11</v>
@@ -7825,10 +7825,10 @@
         <v>15.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AI38" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ38" t="n">
         <v>90</v>
@@ -7837,7 +7837,7 @@
         <v>55</v>
       </c>
       <c r="AL38" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM38" t="n">
         <v>140</v>
@@ -7858,19 +7858,19 @@
         <v>12</v>
       </c>
       <c r="AS38" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT38" t="n">
         <v>10.5</v>
       </c>
       <c r="AU38" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV38" t="n">
         <v>10</v>
       </c>
       <c r="AW38" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AX38" t="n">
         <v>21</v>
@@ -7879,19 +7879,19 @@
         <v>13.5</v>
       </c>
       <c r="AZ38" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="BA38" t="n">
         <v>42</v>
       </c>
       <c r="BB38" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="BC38" t="n">
-        <v>14.5</v>
+        <v>44</v>
       </c>
       <c r="BD38" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BE38" t="n">
         <v>17</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>
@@ -7935,13 +7935,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G39" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="H39" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I39" t="n">
         <v>4.1</v>
@@ -7953,7 +7953,7 @@
         <v>3.7</v>
       </c>
       <c r="L39" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M39" t="n">
         <v>1.06</v>
@@ -7965,28 +7965,28 @@
         <v>1.28</v>
       </c>
       <c r="P39" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="R39" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S39" t="n">
         <v>3.1</v>
       </c>
       <c r="T39" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U39" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V39" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W39" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -8001,19 +8001,19 @@
         <v>1000</v>
       </c>
       <c r="AB39" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC39" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD39" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE39" t="n">
         <v>1000</v>
       </c>
       <c r="AF39" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG39" t="n">
         <v>11.5</v>
@@ -8025,7 +8025,7 @@
         <v>1000</v>
       </c>
       <c r="AJ39" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK39" t="n">
         <v>1000</v>
@@ -8037,68 +8037,68 @@
         <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AO39" t="n">
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AQ39" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AR39" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AS39" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="AT39" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU39" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="AV39" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AW39" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX39" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AY39" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AZ39" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC39" t="n">
         <v>6</v>
       </c>
-      <c r="BA39" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BD39" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BE39" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BF39" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG39" t="n">
         <v>4.7</v>
       </c>
-      <c r="BG39" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-18 21:13:42</t>
+          <t>2026-03-18 23:25:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
@@ -757,58 +757,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="G2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="I2" t="n">
         <v>1.4</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K2" t="n">
         <v>5.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="O2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P2" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="R2" t="n">
         <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="T2" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="U2" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="V2" t="n">
         <v>3.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X2" t="n">
         <v>16.5</v>
@@ -823,7 +823,7 @@
         <v>11</v>
       </c>
       <c r="AB2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AC2" t="n">
         <v>13.5</v>
@@ -832,16 +832,16 @@
         <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AF2" t="n">
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
         <v>65</v>
@@ -868,7 +868,7 @@
         <v>12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AR2" t="n">
         <v>5.9</v>
@@ -877,10 +877,10 @@
         <v>9</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="AV2" t="n">
         <v>9.6</v>
@@ -889,38 +889,38 @@
         <v>15.5</v>
       </c>
       <c r="AX2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA2" t="n">
         <v>7</v>
       </c>
-      <c r="AY2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BB2" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BG2" t="n">
         <v>5.9</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="G3" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="H3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="I3" t="n">
         <v>1.28</v>
       </c>
-      <c r="I3" t="n">
-        <v>1.33</v>
-      </c>
       <c r="J3" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -978,28 +978,28 @@
         <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S3" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="T3" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="U3" t="n">
         <v>1.59</v>
       </c>
       <c r="V3" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="W3" t="n">
         <v>1.05</v>
@@ -1008,10 +1008,10 @@
         <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1056,10 +1056,10 @@
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.7</v>
+        <v>14.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>6.2</v>
@@ -1068,53 +1068,53 @@
         <v>5.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.44</v>
+        <v>4.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AV3" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.7</v>
+        <v>3.75</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="AY3" t="n">
-        <v>2.46</v>
+        <v>4.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.42</v>
+        <v>4.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.54</v>
+        <v>4.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.52</v>
+        <v>2.76</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.54</v>
+        <v>2.76</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -1145,82 +1145,82 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P4" t="n">
         <v>2.12</v>
       </c>
-      <c r="G4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.98</v>
-      </c>
       <c r="Q4" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="R4" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="T4" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="X4" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AA4" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF4" t="n">
         <v>13.5</v>
@@ -1229,86 +1229,86 @@
         <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI4" t="n">
         <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
         <v>36</v>
       </c>
       <c r="AM4" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN4" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP4" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AR4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS4" t="n">
         <v>28</v>
       </c>
       <c r="AT4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW4" t="n">
         <v>30</v>
       </c>
       <c r="AX4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
         <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BB4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BC4" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BE4" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="BF4" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BG4" t="n">
-        <v>14.5</v>
+        <v>36</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -1339,58 +1339,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="G5" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="H5" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="J5" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
         <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="P5" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="S5" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="T5" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="V5" t="n">
         <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="X5" t="n">
         <v>950</v>
@@ -1405,13 +1405,13 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AD5" t="n">
-        <v>950</v>
+        <v>120</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
@@ -1435,19 +1435,19 @@
         <v>970</v>
       </c>
       <c r="AL5" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ5" t="n">
         <v>4.2</v>
@@ -1465,7 +1465,7 @@
         <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="AW5" t="n">
         <v>4.2</v>
@@ -1474,10 +1474,10 @@
         <v>4.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="BA5" t="n">
         <v>4.2</v>
@@ -1486,23 +1486,23 @@
         <v>5.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.199999999999999</v>
+        <v>2.68</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.75</v>
+        <v>2.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -1539,16 +1539,16 @@
         <v>16.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="I6" t="n">
         <v>1.29</v>
       </c>
       <c r="J6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -1727,73 +1727,73 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="G7" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="H7" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="K7" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M7" t="n">
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>3.45</v>
+        <v>6.8</v>
       </c>
       <c r="O7" t="n">
         <v>1.12</v>
       </c>
       <c r="P7" t="n">
-        <v>2.72</v>
+        <v>3.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="S7" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="T7" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="U7" t="n">
-        <v>2.72</v>
+        <v>2.4</v>
       </c>
       <c r="V7" t="n">
         <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>2.28</v>
+        <v>2.54</v>
       </c>
       <c r="X7" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="Y7" t="n">
         <v>40</v>
       </c>
       <c r="Z7" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB7" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AC7" t="n">
         <v>13</v>
@@ -1802,95 +1802,95 @@
         <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AG7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX7" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4.3</v>
       </c>
       <c r="AY7" t="n">
         <v>7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>12.5</v>
+        <v>5.7</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.3</v>
+        <v>13</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.8</v>
+        <v>19</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.2</v>
+        <v>50</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -1921,58 +1921,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.16</v>
+        <v>2.84</v>
       </c>
       <c r="H8" t="n">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="I8" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="O8" t="n">
         <v>1.1</v>
       </c>
       <c r="P8" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="R8" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="S8" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>3.2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="W8" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -1990,7 +1990,7 @@
         <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
@@ -2002,10 +2002,10 @@
         <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
@@ -2023,68 +2023,68 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.12</v>
+        <v>3.35</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.16</v>
+        <v>4.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.04</v>
+        <v>3.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.28</v>
+        <v>3.25</v>
       </c>
       <c r="AU8" t="n">
         <v>6.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.56</v>
+        <v>4.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.18</v>
+        <v>4.6</v>
       </c>
       <c r="AX8" t="n">
-        <v>2.18</v>
+        <v>4.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.18</v>
+        <v>4.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>2.32</v>
+        <v>3.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.22</v>
+        <v>3.3</v>
       </c>
       <c r="BE8" t="n">
         <v>4.7</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="G9" t="n">
         <v>1.14</v>
       </c>
       <c r="H9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J9" t="n">
         <v>10.5</v>
@@ -2133,7 +2133,7 @@
         <v>13</v>
       </c>
       <c r="L9" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
@@ -2142,31 +2142,31 @@
         <v>6.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P9" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="R9" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="S9" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="T9" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V9" t="n">
         <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="X9" t="n">
         <v>36</v>
@@ -2181,10 +2181,10 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2196,7 +2196,7 @@
         <v>6.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AH9" t="n">
         <v>1000</v>
@@ -2217,46 +2217,46 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU9" t="n">
         <v>22</v>
       </c>
       <c r="AV9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>7.6</v>
       </c>
-      <c r="AW9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BA9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB9" t="n">
         <v>5.8</v>
@@ -2265,20 +2265,20 @@
         <v>13</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -2312,13 +2312,13 @@
         <v>1.38</v>
       </c>
       <c r="G10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="H10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="I10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="J10" t="n">
         <v>5.6</v>
@@ -2327,40 +2327,40 @@
         <v>5.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="M10" t="n">
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="Q10" t="n">
         <v>1.65</v>
       </c>
       <c r="R10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S10" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="T10" t="n">
         <v>1.95</v>
       </c>
       <c r="U10" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V10" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="X10" t="n">
         <v>25</v>
@@ -2369,13 +2369,13 @@
         <v>36</v>
       </c>
       <c r="Z10" t="n">
-        <v>540</v>
+        <v>90</v>
       </c>
       <c r="AA10" t="n">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC10" t="n">
         <v>12.5</v>
@@ -2384,7 +2384,7 @@
         <v>38</v>
       </c>
       <c r="AE10" t="n">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="AF10" t="n">
         <v>8.6</v>
@@ -2393,10 +2393,10 @@
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI10" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ10" t="n">
         <v>11.5</v>
@@ -2411,13 +2411,13 @@
         <v>390</v>
       </c>
       <c r="AN10" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AO10" t="n">
         <v>180</v>
       </c>
       <c r="AP10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ10" t="n">
         <v>30</v>
@@ -2426,16 +2426,16 @@
         <v>28</v>
       </c>
       <c r="AS10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AW10" t="n">
         <v>15</v>
@@ -2447,32 +2447,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA10" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BB10" t="n">
         <v>10.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD10" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BE10" t="n">
         <v>29</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BG10" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -2506,61 +2506,61 @@
         <v>1.84</v>
       </c>
       <c r="G11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H11" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I11" t="n">
         <v>5.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L11" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M11" t="n">
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="O11" t="n">
         <v>1.37</v>
       </c>
       <c r="P11" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T11" t="n">
         <v>1.95</v>
       </c>
       <c r="U11" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="V11" t="n">
         <v>1.21</v>
       </c>
       <c r="W11" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X11" t="n">
         <v>13</v>
       </c>
       <c r="Y11" t="n">
-        <v>950</v>
+        <v>20</v>
       </c>
       <c r="Z11" t="n">
         <v>40</v>
@@ -2578,7 +2578,7 @@
         <v>22</v>
       </c>
       <c r="AE11" t="n">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="AF11" t="n">
         <v>11</v>
@@ -2593,7 +2593,7 @@
         <v>200</v>
       </c>
       <c r="AJ11" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AK11" t="n">
         <v>22</v>
@@ -2602,71 +2602,71 @@
         <v>95</v>
       </c>
       <c r="AM11" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="AP11" t="n">
         <v>11</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS11" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT11" t="n">
         <v>7.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AX11" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY11" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="BB11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC11" t="n">
         <v>18.5</v>
       </c>
       <c r="BD11" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF11" t="n">
         <v>12</v>
       </c>
-      <c r="BE11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>13</v>
-      </c>
       <c r="BG11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>10.5</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J12" t="n">
         <v>5.3</v>
@@ -2715,19 +2715,19 @@
         <v>5.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O12" t="n">
         <v>1.3</v>
       </c>
       <c r="P12" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q12" t="n">
         <v>1.91</v>
@@ -2736,7 +2736,7 @@
         <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T12" t="n">
         <v>2.3</v>
@@ -2745,7 +2745,7 @@
         <v>1.7</v>
       </c>
       <c r="V12" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W12" t="n">
         <v>3.5</v>
@@ -2769,7 +2769,7 @@
         <v>12</v>
       </c>
       <c r="AD12" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="AE12" t="n">
         <v>220</v>
@@ -2784,19 +2784,19 @@
         <v>34</v>
       </c>
       <c r="AI12" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="AJ12" t="n">
         <v>11</v>
       </c>
       <c r="AK12" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AL12" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AM12" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AN12" t="n">
         <v>7</v>
@@ -2805,13 +2805,13 @@
         <v>340</v>
       </c>
       <c r="AP12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ12" t="n">
         <v>22</v>
       </c>
       <c r="AR12" t="n">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="AS12" t="n">
         <v>55</v>
@@ -2823,10 +2823,10 @@
         <v>10.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AW12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX12" t="n">
         <v>6.6</v>
@@ -2838,7 +2838,7 @@
         <v>30</v>
       </c>
       <c r="BA12" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BB12" t="n">
         <v>10</v>
@@ -2847,10 +2847,10 @@
         <v>14.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BE12" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BF12" t="n">
         <v>6.2</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>6.2</v>
       </c>
       <c r="G13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H13" t="n">
         <v>1.65</v>
@@ -2909,34 +2909,34 @@
         <v>4.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S13" t="n">
         <v>3.8</v>
       </c>
-      <c r="O13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.5</v>
-      </c>
       <c r="T13" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="V13" t="n">
         <v>2.5</v>
@@ -2945,31 +2945,31 @@
         <v>1.18</v>
       </c>
       <c r="X13" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA13" t="n">
         <v>15.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE13" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AG13" t="n">
         <v>24</v>
@@ -2978,40 +2978,40 @@
         <v>25</v>
       </c>
       <c r="AI13" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AJ13" t="n">
         <v>700</v>
       </c>
       <c r="AK13" t="n">
-        <v>210</v>
+        <v>110</v>
       </c>
       <c r="AL13" t="n">
-        <v>320</v>
+        <v>100</v>
       </c>
       <c r="AM13" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN13" t="n">
         <v>130</v>
       </c>
       <c r="AO13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP13" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS13" t="n">
         <v>14</v>
       </c>
       <c r="AT13" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AU13" t="n">
         <v>8.800000000000001</v>
@@ -3020,41 +3020,41 @@
         <v>9.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX13" t="n">
         <v>44</v>
       </c>
       <c r="AY13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA13" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB13" t="n">
         <v>22</v>
       </c>
       <c r="BC13" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="BD13" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BE13" t="n">
         <v>29</v>
       </c>
       <c r="BF13" t="n">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -3085,13 +3085,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G14" t="n">
         <v>2.74</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I14" t="n">
         <v>2.88</v>
@@ -3100,37 +3100,37 @@
         <v>3.55</v>
       </c>
       <c r="K14" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O14" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P14" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="T14" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U14" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="V14" t="n">
         <v>1.53</v>
@@ -3139,116 +3139,116 @@
         <v>1.57</v>
       </c>
       <c r="X14" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y14" t="n">
         <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA14" t="n">
         <v>48</v>
       </c>
       <c r="AB14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD14" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>13.5</v>
       </c>
       <c r="AE14" t="n">
         <v>32</v>
       </c>
       <c r="AF14" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH14" t="n">
         <v>16.5</v>
       </c>
       <c r="AI14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL14" t="n">
         <v>42</v>
       </c>
-      <c r="AJ14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>40</v>
-      </c>
       <c r="AM14" t="n">
-        <v>320</v>
+        <v>90</v>
       </c>
       <c r="AN14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP14" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX14" t="n">
         <v>16</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="AY14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA14" t="n">
         <v>36</v>
       </c>
-      <c r="AT14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>34</v>
-      </c>
       <c r="BB14" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC14" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BD14" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BE14" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="BF14" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BG14" t="n">
         <v>22</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -3279,19 +3279,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="G15" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="H15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="I15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="J15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K15" t="n">
         <v>7</v>
@@ -3300,40 +3300,40 @@
         <v>1.28</v>
       </c>
       <c r="M15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P15" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="R15" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="S15" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U15" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V15" t="n">
         <v>1.08</v>
       </c>
       <c r="W15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X15" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y15" t="n">
         <v>42</v>
@@ -3348,37 +3348,37 @@
         <v>11</v>
       </c>
       <c r="AC15" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AD15" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AE15" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AF15" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG15" t="n">
         <v>12</v>
       </c>
       <c r="AH15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI15" t="n">
         <v>470</v>
       </c>
       <c r="AJ15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AK15" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM15" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="AN15" t="n">
         <v>4.4</v>
@@ -3387,16 +3387,16 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="AR15" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT15" t="n">
         <v>9.199999999999999</v>
@@ -3408,41 +3408,41 @@
         <v>32</v>
       </c>
       <c r="AW15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA15" t="n">
         <v>9.4</v>
       </c>
-      <c r="AX15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>27</v>
-      </c>
-      <c r="BA15" t="n">
+      <c r="BB15" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>8.6</v>
       </c>
       <c r="BC15" t="n">
         <v>12</v>
       </c>
       <c r="BD15" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BE15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BG15" t="n">
-        <v>15</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
         <v>2.38</v>
       </c>
       <c r="J16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K16" t="n">
         <v>3.7</v>
@@ -3503,13 +3503,13 @@
         <v>1.29</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q16" t="n">
         <v>1.89</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
         <v>3.2</v>
@@ -3536,7 +3536,7 @@
         <v>15.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AB16" t="n">
         <v>14</v>
@@ -3551,13 +3551,13 @@
         <v>23</v>
       </c>
       <c r="AF16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG16" t="n">
         <v>14</v>
       </c>
       <c r="AH16" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI16" t="n">
         <v>34</v>
@@ -3572,13 +3572,13 @@
         <v>42</v>
       </c>
       <c r="AM16" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN16" t="n">
         <v>30</v>
       </c>
       <c r="AO16" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AP16" t="n">
         <v>15</v>
@@ -3611,19 +3611,19 @@
         <v>13</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
         <v>30</v>
       </c>
       <c r="BB16" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BC16" t="n">
         <v>32</v>
       </c>
       <c r="BD16" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE16" t="n">
         <v>70</v>
@@ -3632,11 +3632,11 @@
         <v>27</v>
       </c>
       <c r="BG16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="H17" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="I17" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="J17" t="n">
         <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L17" t="n">
         <v>1.46</v>
@@ -3706,46 +3706,46 @@
         <v>1.32</v>
       </c>
       <c r="S17" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
         <v>1.89</v>
       </c>
       <c r="U17" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V17" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W17" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="X17" t="n">
         <v>12.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AA17" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE17" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG17" t="n">
         <v>11</v>
@@ -3757,49 +3757,49 @@
         <v>60</v>
       </c>
       <c r="AJ17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL17" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM17" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN17" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AO17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP17" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS17" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU17" t="n">
         <v>7.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW17" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AX17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY17" t="n">
         <v>10</v>
@@ -3808,29 +3808,29 @@
         <v>17</v>
       </c>
       <c r="BA17" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD17" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE17" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="BF17" t="n">
         <v>18</v>
       </c>
       <c r="BG17" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -3879,34 +3879,34 @@
         <v>4.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
         <v>1.27</v>
       </c>
       <c r="P18" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R18" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T18" t="n">
         <v>1.87</v>
       </c>
       <c r="U18" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V18" t="n">
         <v>1.19</v>
@@ -3927,13 +3927,13 @@
         <v>160</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
         <v>75</v>
@@ -3942,10 +3942,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG18" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH18" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI18" t="n">
         <v>75</v>
@@ -3966,13 +3966,13 @@
         <v>8.4</v>
       </c>
       <c r="AO18" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AP18" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AR18" t="n">
         <v>42</v>
@@ -3990,41 +3990,41 @@
         <v>20</v>
       </c>
       <c r="AW18" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AX18" t="n">
         <v>9.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ18" t="n">
         <v>18.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BB18" t="n">
         <v>15</v>
       </c>
       <c r="BC18" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD18" t="n">
         <v>30</v>
       </c>
       <c r="BE18" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="BF18" t="n">
         <v>8</v>
       </c>
       <c r="BG18" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -4055,52 +4055,52 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.65</v>
+        <v>5.5</v>
       </c>
       <c r="G19" t="n">
-        <v>600</v>
+        <v>6.8</v>
       </c>
       <c r="H19" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="J19" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="K19" t="n">
-        <v>9.199999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="M19" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="N19" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="O19" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.4</v>
+        <v>2.78</v>
       </c>
       <c r="R19" t="n">
         <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="T19" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="U19" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
@@ -4109,37 +4109,37 @@
         <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="Z19" t="n">
         <v>11</v>
       </c>
       <c r="AA19" t="n">
-        <v>23</v>
+        <v>900</v>
       </c>
       <c r="AB19" t="n">
         <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AE19" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
         <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
         <v>500</v>
@@ -4160,65 +4160,65 @@
         <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AR19" t="n">
         <v>7.8</v>
       </c>
       <c r="AS19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT19" t="n">
         <v>8.4</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>11.5</v>
       </c>
       <c r="AU19" t="n">
         <v>7.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="AY19" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ19" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="BA19" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC19" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF19" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG19" t="n">
         <v>12.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
         <v>3.15</v>
@@ -4258,61 +4258,61 @@
         <v>2.74</v>
       </c>
       <c r="I20" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="J20" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K20" t="n">
         <v>3.2</v>
       </c>
       <c r="L20" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="M20" t="n">
         <v>1.11</v>
       </c>
       <c r="N20" t="n">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="O20" t="n">
         <v>1.5</v>
       </c>
       <c r="P20" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="R20" t="n">
         <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T20" t="n">
         <v>1.99</v>
       </c>
       <c r="U20" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V20" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="W20" t="n">
         <v>1.47</v>
       </c>
       <c r="X20" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z20" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AB20" t="n">
         <v>9.6</v>
@@ -4321,22 +4321,22 @@
         <v>7.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AF20" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG20" t="n">
         <v>14.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ20" t="n">
         <v>60</v>
@@ -4345,22 +4345,22 @@
         <v>100</v>
       </c>
       <c r="AL20" t="n">
-        <v>380</v>
+        <v>70</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AP20" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ20" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>7.8</v>
       </c>
       <c r="AR20" t="n">
         <v>15</v>
@@ -4369,16 +4369,16 @@
         <v>18</v>
       </c>
       <c r="AT20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV20" t="n">
         <v>11.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>32</v>
+        <v>11.5</v>
       </c>
       <c r="AX20" t="n">
         <v>16.5</v>
@@ -4387,32 +4387,32 @@
         <v>12.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>10.5</v>
+        <v>42</v>
       </c>
       <c r="BB20" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="BD20" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BE20" t="n">
         <v>12</v>
       </c>
       <c r="BF20" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>32</v>
+        <v>12.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -4443,49 +4443,49 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="G21" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H21" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I21" t="n">
         <v>5.3</v>
       </c>
       <c r="J21" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K21" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="L21" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="M21" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N21" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="P21" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="R21" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U21" t="n">
         <v>1.85</v>
@@ -4494,13 +4494,13 @@
         <v>1.23</v>
       </c>
       <c r="W21" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="X21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y21" t="n">
-        <v>14.5</v>
+        <v>30</v>
       </c>
       <c r="Z21" t="n">
         <v>120</v>
@@ -4509,10 +4509,10 @@
         <v>900</v>
       </c>
       <c r="AB21" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD21" t="n">
         <v>42</v>
@@ -4521,22 +4521,22 @@
         <v>700</v>
       </c>
       <c r="AF21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG21" t="n">
         <v>11</v>
       </c>
       <c r="AH21" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="AI21" t="n">
         <v>700</v>
       </c>
       <c r="AJ21" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="AK21" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="AL21" t="n">
         <v>290</v>
@@ -4557,10 +4557,10 @@
         <v>12</v>
       </c>
       <c r="AR21" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AS21" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AT21" t="n">
         <v>6.4</v>
@@ -4572,7 +4572,7 @@
         <v>16.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="AX21" t="n">
         <v>9.800000000000001</v>
@@ -4584,7 +4584,7 @@
         <v>18.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BB21" t="n">
         <v>20</v>
@@ -4593,20 +4593,20 @@
         <v>20</v>
       </c>
       <c r="BD21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BE21" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BF21" t="n">
         <v>16.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -4640,61 +4640,61 @@
         <v>1.7</v>
       </c>
       <c r="G22" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="H22" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="I22" t="n">
         <v>6.2</v>
       </c>
       <c r="J22" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K22" t="n">
         <v>4.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M22" t="n">
         <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O22" t="n">
         <v>1.34</v>
       </c>
       <c r="P22" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T22" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V22" t="n">
         <v>1.19</v>
       </c>
       <c r="W22" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="X22" t="n">
         <v>14</v>
       </c>
       <c r="Y22" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z22" t="n">
         <v>46</v>
@@ -4703,10 +4703,10 @@
         <v>170</v>
       </c>
       <c r="AB22" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD22" t="n">
         <v>23</v>
@@ -4715,13 +4715,13 @@
         <v>85</v>
       </c>
       <c r="AF22" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AG22" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI22" t="n">
         <v>90</v>
@@ -4733,43 +4733,43 @@
         <v>18.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM22" t="n">
         <v>140</v>
       </c>
       <c r="AN22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO22" t="n">
         <v>110</v>
       </c>
       <c r="AP22" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AS22" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU22" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AV22" t="n">
         <v>20</v>
       </c>
       <c r="AW22" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="AX22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY22" t="n">
         <v>9.199999999999999</v>
@@ -4778,16 +4778,16 @@
         <v>20</v>
       </c>
       <c r="BA22" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="BB22" t="n">
         <v>15</v>
       </c>
       <c r="BC22" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE22" t="n">
         <v>29</v>
@@ -4796,11 +4796,11 @@
         <v>10</v>
       </c>
       <c r="BG22" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -4831,16 +4831,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="G23" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="H23" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="I23" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="J23" t="n">
         <v>3.8</v>
@@ -4849,13 +4849,13 @@
         <v>3.9</v>
       </c>
       <c r="L23" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M23" t="n">
         <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O23" t="n">
         <v>1.28</v>
@@ -4870,58 +4870,58 @@
         <v>1.43</v>
       </c>
       <c r="S23" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T23" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U23" t="n">
         <v>2.28</v>
       </c>
       <c r="V23" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W23" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="X23" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y23" t="n">
         <v>15</v>
       </c>
       <c r="Z23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA23" t="n">
         <v>150</v>
       </c>
       <c r="AB23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC23" t="n">
         <v>8.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE23" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF23" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH23" t="n">
         <v>17</v>
       </c>
       <c r="AI23" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ23" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AK23" t="n">
         <v>22</v>
@@ -4930,40 +4930,40 @@
         <v>34</v>
       </c>
       <c r="AM23" t="n">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AN23" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO23" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AP23" t="n">
         <v>15</v>
       </c>
       <c r="AQ23" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR23" t="n">
         <v>22</v>
       </c>
       <c r="AS23" t="n">
-        <v>14.5</v>
+        <v>55</v>
       </c>
       <c r="AT23" t="n">
         <v>10</v>
       </c>
       <c r="AU23" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AX23" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY23" t="n">
         <v>10</v>
@@ -4975,10 +4975,10 @@
         <v>40</v>
       </c>
       <c r="BB23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC23" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD23" t="n">
         <v>30</v>
@@ -4987,14 +4987,14 @@
         <v>65</v>
       </c>
       <c r="BF23" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG23" t="n">
         <v>30</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G24" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H24" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I24" t="n">
         <v>3.3</v>
@@ -5040,85 +5040,85 @@
         <v>3.6</v>
       </c>
       <c r="K24" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L24" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="M24" t="n">
         <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O24" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P24" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U24" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V24" t="n">
         <v>1.43</v>
       </c>
       <c r="W24" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X24" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="Y24" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Z24" t="n">
         <v>29</v>
       </c>
       <c r="AA24" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="AE24" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="AF24" t="n">
         <v>16.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>11.5</v>
+        <v>50</v>
       </c>
       <c r="AH24" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ24" t="n">
         <v>130</v>
       </c>
       <c r="AK24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL24" t="n">
         <v>36</v>
@@ -5127,25 +5127,25 @@
         <v>320</v>
       </c>
       <c r="AN24" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="AS24" t="n">
         <v>23</v>
       </c>
       <c r="AT24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU24" t="n">
         <v>7.6</v>
@@ -5154,7 +5154,7 @@
         <v>12</v>
       </c>
       <c r="AW24" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="AX24" t="n">
         <v>14.5</v>
@@ -5163,32 +5163,32 @@
         <v>10</v>
       </c>
       <c r="AZ24" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BB24" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD24" t="n">
         <v>27</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>29</v>
       </c>
       <c r="BE24" t="n">
         <v>50</v>
       </c>
       <c r="BF24" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -5219,16 +5219,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="G25" t="n">
         <v>1.43</v>
       </c>
       <c r="H25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="I25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J25" t="n">
         <v>5.1</v>
@@ -5240,7 +5240,7 @@
         <v>1.37</v>
       </c>
       <c r="M25" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N25" t="n">
         <v>4.3</v>
@@ -5249,19 +5249,19 @@
         <v>1.28</v>
       </c>
       <c r="P25" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R25" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T25" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="U25" t="n">
         <v>1.8</v>
@@ -5276,55 +5276,55 @@
         <v>18</v>
       </c>
       <c r="Y25" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Z25" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AA25" t="n">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="AB25" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC25" t="n">
         <v>11.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE25" t="n">
         <v>180</v>
       </c>
       <c r="AF25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH25" t="n">
         <v>30</v>
       </c>
       <c r="AI25" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ25" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AK25" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL25" t="n">
         <v>44</v>
       </c>
       <c r="AM25" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN25" t="n">
         <v>6.8</v>
       </c>
       <c r="AO25" t="n">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="AP25" t="n">
         <v>15.5</v>
@@ -5333,10 +5333,10 @@
         <v>23</v>
       </c>
       <c r="AR25" t="n">
-        <v>75</v>
+        <v>15.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="AT25" t="n">
         <v>7.4</v>
@@ -5345,28 +5345,28 @@
         <v>10</v>
       </c>
       <c r="AV25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AW25" t="n">
-        <v>16.5</v>
+        <v>36</v>
       </c>
       <c r="AX25" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY25" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA25" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BB25" t="n">
         <v>10</v>
       </c>
       <c r="BC25" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD25" t="n">
         <v>36</v>
@@ -5378,11 +5378,11 @@
         <v>6</v>
       </c>
       <c r="BG25" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5419,7 @@
         <v>1.45</v>
       </c>
       <c r="H26" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="I26" t="n">
         <v>9.800000000000001</v>
@@ -5428,7 +5428,7 @@
         <v>4.9</v>
       </c>
       <c r="K26" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L26" t="n">
         <v>1.39</v>
@@ -5437,16 +5437,16 @@
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O26" t="n">
         <v>1.3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R26" t="n">
         <v>1.4</v>
@@ -5491,7 +5491,7 @@
         <v>170</v>
       </c>
       <c r="AF26" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AG26" t="n">
         <v>10.5</v>
@@ -5509,28 +5509,28 @@
         <v>16</v>
       </c>
       <c r="AL26" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM26" t="n">
         <v>190</v>
       </c>
       <c r="AN26" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AO26" t="n">
         <v>270</v>
       </c>
       <c r="AP26" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>24</v>
       </c>
       <c r="AR26" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AS26" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AT26" t="n">
         <v>7</v>
@@ -5560,23 +5560,23 @@
         <v>10.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD26" t="n">
         <v>38</v>
       </c>
       <c r="BE26" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="BF26" t="n">
         <v>6.8</v>
       </c>
       <c r="BG26" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -5613,58 +5613,58 @@
         <v>2.62</v>
       </c>
       <c r="H27" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="I27" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K27" t="n">
         <v>3.65</v>
       </c>
-      <c r="K27" t="n">
-        <v>3.7</v>
-      </c>
       <c r="L27" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="O27" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P27" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="S27" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="T27" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="U27" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="V27" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W27" t="n">
         <v>1.62</v>
       </c>
       <c r="X27" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z27" t="n">
         <v>19.5</v>
@@ -5673,16 +5673,16 @@
         <v>46</v>
       </c>
       <c r="AB27" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC27" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD27" t="n">
         <v>13</v>
       </c>
       <c r="AE27" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF27" t="n">
         <v>16.5</v>
@@ -5691,7 +5691,7 @@
         <v>12</v>
       </c>
       <c r="AH27" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI27" t="n">
         <v>42</v>
@@ -5703,34 +5703,34 @@
         <v>27</v>
       </c>
       <c r="AL27" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM27" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO27" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AP27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ27" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR27" t="n">
         <v>18</v>
       </c>
       <c r="AS27" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT27" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV27" t="n">
         <v>12</v>
@@ -5745,32 +5745,32 @@
         <v>11</v>
       </c>
       <c r="AZ27" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB27" t="n">
         <v>34</v>
       </c>
       <c r="BC27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD27" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BE27" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="BF27" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BG27" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -5801,70 +5801,70 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="G28" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="H28" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="I28" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="J28" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K28" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L28" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M28" t="n">
         <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O28" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P28" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="R28" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T28" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U28" t="n">
         <v>1.84</v>
       </c>
       <c r="V28" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W28" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="X28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y28" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA28" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB28" t="n">
         <v>7.2</v>
@@ -5873,13 +5873,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE28" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AF28" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG28" t="n">
         <v>10.5</v>
@@ -5891,40 +5891,40 @@
         <v>100</v>
       </c>
       <c r="AJ28" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AK28" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL28" t="n">
         <v>46</v>
       </c>
       <c r="AM28" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO28" t="n">
         <v>140</v>
       </c>
       <c r="AP28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR28" t="n">
         <v>36</v>
       </c>
       <c r="AS28" t="n">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="AT28" t="n">
         <v>6.8</v>
       </c>
       <c r="AU28" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV28" t="n">
         <v>20</v>
@@ -5945,10 +5945,10 @@
         <v>38</v>
       </c>
       <c r="BB28" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD28" t="n">
         <v>40</v>
@@ -5957,14 +5957,14 @@
         <v>85</v>
       </c>
       <c r="BF28" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG28" t="n">
         <v>100</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -5998,16 +5998,16 @@
         <v>1.72</v>
       </c>
       <c r="G29" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="H29" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I29" t="n">
         <v>5.6</v>
       </c>
       <c r="J29" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K29" t="n">
         <v>4.3</v>
@@ -6019,55 +6019,55 @@
         <v>1.06</v>
       </c>
       <c r="N29" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O29" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P29" t="n">
         <v>2.02</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R29" t="n">
         <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T29" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V29" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W29" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="X29" t="n">
         <v>15.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA29" t="n">
         <v>140</v>
       </c>
       <c r="AB29" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC29" t="n">
         <v>9</v>
       </c>
       <c r="AD29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE29" t="n">
         <v>75</v>
@@ -6082,7 +6082,7 @@
         <v>21</v>
       </c>
       <c r="AI29" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ29" t="n">
         <v>17</v>
@@ -6115,7 +6115,7 @@
         <v>42</v>
       </c>
       <c r="AT29" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU29" t="n">
         <v>8.6</v>
@@ -6136,7 +6136,7 @@
         <v>20</v>
       </c>
       <c r="BA29" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BB29" t="n">
         <v>16</v>
@@ -6151,14 +6151,14 @@
         <v>100</v>
       </c>
       <c r="BF29" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG29" t="n">
         <v>80</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -6189,13 +6189,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.24</v>
+        <v>2.74</v>
       </c>
       <c r="G30" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="H30" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="I30" t="n">
         <v>2.7</v>
@@ -6204,7 +6204,7 @@
         <v>3.05</v>
       </c>
       <c r="K30" t="n">
-        <v>85</v>
+        <v>3.8</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="G31" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H31" t="n">
         <v>4.7</v>
@@ -6395,43 +6395,43 @@
         <v>5.3</v>
       </c>
       <c r="J31" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K31" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L31" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="M31" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N31" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="O31" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="P31" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="R31" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S31" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U31" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V31" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W31" t="n">
         <v>2.04</v>
@@ -6440,7 +6440,7 @@
         <v>11.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z31" t="n">
         <v>46</v>
@@ -6464,7 +6464,7 @@
         <v>12</v>
       </c>
       <c r="AG31" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH31" t="n">
         <v>34</v>
@@ -6494,13 +6494,13 @@
         <v>6.2</v>
       </c>
       <c r="AQ31" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="AR31" t="n">
-        <v>5</v>
+        <v>14.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AT31" t="n">
         <v>5.7</v>
@@ -6512,41 +6512,41 @@
         <v>16.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AX31" t="n">
         <v>8.6</v>
       </c>
       <c r="AY31" t="n">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ31" t="n">
         <v>24</v>
       </c>
       <c r="BA31" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BB31" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="BC31" t="n">
         <v>13</v>
       </c>
       <c r="BD31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE31" t="n">
         <v>5.3</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>5.8</v>
       </c>
       <c r="BF31" t="n">
         <v>5</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -6577,58 +6577,58 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="H32" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I32" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="J32" t="n">
         <v>3.4</v>
       </c>
       <c r="K32" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L32" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="M32" t="n">
         <v>1.08</v>
       </c>
       <c r="N32" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O32" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P32" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="R32" t="n">
         <v>1.3</v>
       </c>
       <c r="S32" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T32" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U32" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V32" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="W32" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="X32" t="n">
         <v>14</v>
@@ -6637,7 +6637,7 @@
         <v>16</v>
       </c>
       <c r="Z32" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AA32" t="n">
         <v>900</v>
@@ -6652,19 +6652,19 @@
         <v>21</v>
       </c>
       <c r="AE32" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG32" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH32" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AI32" t="n">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="AJ32" t="n">
         <v>28</v>
@@ -6682,7 +6682,7 @@
         <v>20</v>
       </c>
       <c r="AO32" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AP32" t="n">
         <v>10.5</v>
@@ -6691,10 +6691,10 @@
         <v>12</v>
       </c>
       <c r="AR32" t="n">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="AS32" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT32" t="n">
         <v>7.2</v>
@@ -6706,7 +6706,7 @@
         <v>15</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AX32" t="n">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>17</v>
       </c>
       <c r="BA32" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BB32" t="n">
         <v>11.5</v>
@@ -6727,20 +6727,20 @@
         <v>11.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF32" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG32" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -6771,49 +6771,49 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G33" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="H33" t="n">
         <v>4.5</v>
       </c>
       <c r="I33" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J33" t="n">
         <v>3.65</v>
       </c>
       <c r="K33" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L33" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="M33" t="n">
         <v>1.07</v>
       </c>
       <c r="N33" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O33" t="n">
         <v>1.35</v>
       </c>
       <c r="P33" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R33" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S33" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T33" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U33" t="n">
         <v>2.04</v>
@@ -6822,85 +6822,85 @@
         <v>1.26</v>
       </c>
       <c r="W33" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X33" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y33" t="n">
         <v>16</v>
       </c>
       <c r="Z33" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AA33" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD33" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>320</v>
+        <v>65</v>
       </c>
       <c r="AF33" t="n">
         <v>11.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH33" t="n">
         <v>21</v>
       </c>
       <c r="AI33" t="n">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AJ33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL33" t="n">
         <v>38</v>
       </c>
-      <c r="AK33" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>85</v>
-      </c>
       <c r="AM33" t="n">
-        <v>580</v>
+        <v>120</v>
       </c>
       <c r="AN33" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO33" t="n">
-        <v>270</v>
+        <v>80</v>
       </c>
       <c r="AP33" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR33" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AS33" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AT33" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU33" t="n">
         <v>7.6</v>
       </c>
       <c r="AV33" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AX33" t="n">
         <v>10</v>
@@ -6909,13 +6909,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ33" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB33" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BC33" t="n">
         <v>18.5</v>
@@ -6924,17 +6924,17 @@
         <v>28</v>
       </c>
       <c r="BE33" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BF33" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG33" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
         <v>1.21</v>
       </c>
       <c r="H34" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I34" t="n">
         <v>24</v>
@@ -6980,7 +6980,7 @@
         <v>8</v>
       </c>
       <c r="K34" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="L34" t="n">
         <v>1.28</v>
@@ -6989,7 +6989,7 @@
         <v>1.03</v>
       </c>
       <c r="N34" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O34" t="n">
         <v>1.18</v>
@@ -6998,19 +6998,19 @@
         <v>2.68</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="R34" t="n">
         <v>1.68</v>
       </c>
       <c r="S34" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="T34" t="n">
         <v>2.42</v>
       </c>
       <c r="U34" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="V34" t="n">
         <v>1.04</v>
@@ -7019,7 +7019,7 @@
         <v>5.7</v>
       </c>
       <c r="X34" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="Y34" t="n">
         <v>950</v>
@@ -7034,7 +7034,7 @@
         <v>9.6</v>
       </c>
       <c r="AC34" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AD34" t="n">
         <v>950</v>
@@ -7067,7 +7067,7 @@
         <v>340</v>
       </c>
       <c r="AN34" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AO34" t="n">
         <v>1000</v>
@@ -7076,22 +7076,22 @@
         <v>23</v>
       </c>
       <c r="AQ34" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AR34" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS34" t="n">
         <v>14</v>
       </c>
       <c r="AT34" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU34" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AV34" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="AW34" t="n">
         <v>17</v>
@@ -7121,14 +7121,14 @@
         <v>38</v>
       </c>
       <c r="BF34" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BG34" t="n">
         <v>15</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -7159,58 +7159,58 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.44</v>
+        <v>2.86</v>
       </c>
       <c r="G35" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="H35" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="I35" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J35" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="K35" t="n">
-        <v>950</v>
+        <v>3.2</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="M35" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N35" t="n">
-        <v>2.28</v>
+        <v>2.84</v>
       </c>
       <c r="O35" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="P35" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="R35" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S35" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="T35" t="n">
-        <v>1.11</v>
+        <v>1.84</v>
       </c>
       <c r="U35" t="n">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="V35" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="W35" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="G36" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H36" t="n">
         <v>5.7</v>
@@ -7377,34 +7377,34 @@
         <v>1.1</v>
       </c>
       <c r="N36" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O36" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P36" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R36" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S36" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T36" t="n">
         <v>2.22</v>
       </c>
       <c r="U36" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="V36" t="n">
         <v>1.18</v>
       </c>
       <c r="W36" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X36" t="n">
         <v>19.5</v>
@@ -7422,7 +7422,7 @@
         <v>6.8</v>
       </c>
       <c r="AC36" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD36" t="n">
         <v>950</v>
@@ -7431,7 +7431,7 @@
         <v>700</v>
       </c>
       <c r="AF36" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AG36" t="n">
         <v>11</v>
@@ -7449,7 +7449,7 @@
         <v>60</v>
       </c>
       <c r="AL36" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AM36" t="n">
         <v>700</v>
@@ -7467,10 +7467,10 @@
         <v>8.4</v>
       </c>
       <c r="AR36" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AS36" t="n">
-        <v>12</v>
+        <v>5.8</v>
       </c>
       <c r="AT36" t="n">
         <v>6</v>
@@ -7479,22 +7479,22 @@
         <v>7.8</v>
       </c>
       <c r="AV36" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AW36" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX36" t="n">
         <v>8</v>
       </c>
       <c r="AY36" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AZ36" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="BA36" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB36" t="n">
         <v>8.4</v>
@@ -7503,20 +7503,20 @@
         <v>10.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BE36" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="BF36" t="n">
         <v>13</v>
       </c>
       <c r="BG36" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -7550,43 +7550,43 @@
         <v>3.75</v>
       </c>
       <c r="G37" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="H37" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="I37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q37" t="n">
         <v>2.32</v>
-      </c>
-      <c r="J37" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K37" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N37" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2.22</v>
       </c>
       <c r="R37" t="n">
         <v>1.26</v>
       </c>
       <c r="S37" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T37" t="n">
         <v>1.94</v>
@@ -7595,37 +7595,37 @@
         <v>1.92</v>
       </c>
       <c r="V37" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W37" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X37" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y37" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z37" t="n">
         <v>16</v>
       </c>
       <c r="AA37" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB37" t="n">
         <v>15</v>
       </c>
       <c r="AC37" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD37" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AE37" t="n">
         <v>34</v>
       </c>
       <c r="AF37" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AG37" t="n">
         <v>20</v>
@@ -7637,7 +7637,7 @@
         <v>60</v>
       </c>
       <c r="AJ37" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="n">
         <v>70</v>
@@ -7655,62 +7655,62 @@
         <v>28</v>
       </c>
       <c r="AP37" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="AQ37" t="n">
-        <v>3.35</v>
+        <v>7.2</v>
       </c>
       <c r="AR37" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AS37" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="AU37" t="n">
         <v>6.6</v>
       </c>
       <c r="AV37" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="AW37" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AX37" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AY37" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AZ37" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BA37" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BB37" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BC37" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE37" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BF37" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BG37" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -7741,22 +7741,22 @@
         </is>
       </c>
       <c r="F38" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G38" t="n">
         <v>3.75</v>
       </c>
-      <c r="G38" t="n">
-        <v>3.8</v>
-      </c>
       <c r="H38" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I38" t="n">
         <v>2.32</v>
       </c>
-      <c r="I38" t="n">
-        <v>2.36</v>
-      </c>
       <c r="J38" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K38" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L38" t="n">
         <v>1.5</v>
@@ -7765,13 +7765,13 @@
         <v>1.1</v>
       </c>
       <c r="N38" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O38" t="n">
         <v>1.44</v>
       </c>
       <c r="P38" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q38" t="n">
         <v>2.36</v>
@@ -7780,7 +7780,7 @@
         <v>1.26</v>
       </c>
       <c r="S38" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T38" t="n">
         <v>1.96</v>
@@ -7789,10 +7789,10 @@
         <v>1.94</v>
       </c>
       <c r="V38" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W38" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X38" t="n">
         <v>11</v>
@@ -7816,7 +7816,7 @@
         <v>11.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF38" t="n">
         <v>24</v>
@@ -7828,7 +7828,7 @@
         <v>21</v>
       </c>
       <c r="AI38" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ38" t="n">
         <v>90</v>
@@ -7837,7 +7837,7 @@
         <v>55</v>
       </c>
       <c r="AL38" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM38" t="n">
         <v>140</v>
@@ -7846,10 +7846,10 @@
         <v>65</v>
       </c>
       <c r="AO38" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP38" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ38" t="n">
         <v>7.6</v>
@@ -7858,7 +7858,7 @@
         <v>12</v>
       </c>
       <c r="AS38" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AT38" t="n">
         <v>10.5</v>
@@ -7870,41 +7870,41 @@
         <v>10</v>
       </c>
       <c r="AW38" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AX38" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY38" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ38" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA38" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="BB38" t="n">
         <v>60</v>
       </c>
       <c r="BC38" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="BD38" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BE38" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BF38" t="n">
         <v>50</v>
       </c>
       <c r="BG38" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
         <v>2.1</v>
       </c>
       <c r="G39" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="H39" t="n">
         <v>3.75</v>
@@ -7947,13 +7947,13 @@
         <v>4.1</v>
       </c>
       <c r="J39" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K39" t="n">
         <v>3.7</v>
       </c>
       <c r="L39" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M39" t="n">
         <v>1.06</v>
@@ -7962,19 +7962,19 @@
         <v>4</v>
       </c>
       <c r="O39" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="P39" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="R39" t="n">
         <v>1.4</v>
       </c>
       <c r="S39" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T39" t="n">
         <v>1.68</v>
@@ -7983,13 +7983,13 @@
         <v>2.22</v>
       </c>
       <c r="V39" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W39" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="X39" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y39" t="n">
         <v>18</v>
@@ -8043,34 +8043,34 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AQ39" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AR39" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="AS39" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="AT39" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU39" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AV39" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX39" t="n">
         <v>5.7</v>
       </c>
-      <c r="AW39" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX39" t="n">
+      <c r="AY39" t="n">
         <v>5.2</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>4.9</v>
       </c>
       <c r="AZ39" t="n">
         <v>14</v>
@@ -8079,26 +8079,26 @@
         <v>4.8</v>
       </c>
       <c r="BB39" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BC39" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE39" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF39" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BG39" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-18 23:25:51</t>
+          <t>2026-03-19 01:43:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="G2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="H2" t="n">
         <v>1.36</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.43</v>
@@ -796,16 +796,16 @@
         <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="U2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="V2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="W2" t="n">
         <v>1.07</v>
@@ -814,7 +814,7 @@
         <v>16.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="Z2" t="n">
         <v>7</v>
@@ -826,10 +826,10 @@
         <v>32</v>
       </c>
       <c r="AC2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE2" t="n">
         <v>18</v>
@@ -838,13 +838,13 @@
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AI2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
@@ -862,13 +862,13 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AP2" t="n">
-        <v>12</v>
+        <v>5.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AR2" t="n">
         <v>5.9</v>
@@ -877,50 +877,50 @@
         <v>9</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AU2" t="n">
         <v>10.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.6</v>
+        <v>5.1</v>
       </c>
       <c r="AW2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY2" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BG2" t="n">
         <v>5.9</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="G3" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H3" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="I3" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K3" t="n">
         <v>7</v>
@@ -978,31 +978,31 @@
         <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="R3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="T3" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="U3" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="V3" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1011,7 +1011,7 @@
         <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1020,7 +1020,7 @@
         <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>6.2</v>
       </c>
       <c r="AP3" t="n">
-        <v>14.5</v>
+        <v>6.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.2</v>
+        <v>3.95</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.4</v>
+        <v>2.62</v>
       </c>
       <c r="AU3" t="n">
         <v>6</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.75</v>
+        <v>14</v>
       </c>
       <c r="AX3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BB3" t="n">
         <v>2.74</v>
       </c>
-      <c r="AY3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>2.78</v>
-      </c>
       <c r="BC3" t="n">
-        <v>4.8</v>
+        <v>2.76</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G4" t="n">
         <v>2.04</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.06</v>
       </c>
       <c r="H4" t="n">
         <v>4</v>
@@ -1169,34 +1169,34 @@
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
         <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U4" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V4" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W4" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X4" t="n">
         <v>16.5</v>
@@ -1220,34 +1220,34 @@
         <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ4" t="n">
         <v>24</v>
       </c>
       <c r="AK4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AL4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM4" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="AN4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO4" t="n">
         <v>42</v>
@@ -1259,16 +1259,16 @@
         <v>15</v>
       </c>
       <c r="AR4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AS4" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AT4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV4" t="n">
         <v>14.5</v>
@@ -1280,19 +1280,19 @@
         <v>11.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA4" t="n">
         <v>42</v>
       </c>
       <c r="BB4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD4" t="n">
         <v>29</v>
@@ -1301,14 +1301,14 @@
         <v>48</v>
       </c>
       <c r="BF4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG4" t="n">
         <v>36</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="G5" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="H5" t="n">
         <v>10</v>
@@ -1351,52 +1351,52 @@
         <v>14.5</v>
       </c>
       <c r="J5" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K5" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M5" t="n">
         <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="T5" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="V5" t="n">
         <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="X5" t="n">
         <v>950</v>
       </c>
       <c r="Y5" t="n">
-        <v>950</v>
+        <v>95</v>
       </c>
       <c r="Z5" t="n">
         <v>1000</v>
@@ -1405,7 +1405,7 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC5" t="n">
         <v>970</v>
@@ -1441,7 +1441,7 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
@@ -1450,7 +1450,7 @@
         <v>7.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.2</v>
+        <v>22</v>
       </c>
       <c r="AR5" t="n">
         <v>4.2</v>
@@ -1471,13 +1471,13 @@
         <v>4.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AY5" t="n">
         <v>7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.64</v>
+        <v>2.9</v>
       </c>
       <c r="BA5" t="n">
         <v>4.2</v>
@@ -1486,23 +1486,23 @@
         <v>5.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.68</v>
+        <v>5.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.4</v>
+        <v>3.65</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -1536,19 +1536,19 @@
         <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="I6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="J6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="K6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="G7" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I7" t="n">
         <v>6</v>
@@ -1745,34 +1745,34 @@
         <v>5.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="M7" t="n">
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P7" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="R7" t="n">
         <v>1.89</v>
       </c>
       <c r="S7" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="T7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U7" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="V7" t="n">
         <v>1.2</v>
@@ -1784,7 +1784,7 @@
         <v>85</v>
       </c>
       <c r="Y7" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="Z7" t="n">
         <v>1000</v>
@@ -1793,10 +1793,10 @@
         <v>140</v>
       </c>
       <c r="AB7" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="AC7" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -1817,7 +1817,7 @@
         <v>50</v>
       </c>
       <c r="AJ7" t="n">
-        <v>38</v>
+        <v>18.5</v>
       </c>
       <c r="AK7" t="n">
         <v>1000</v>
@@ -1835,19 +1835,19 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AS7" t="n">
-        <v>55</v>
+        <v>7.2</v>
       </c>
       <c r="AT7" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AU7" t="n">
         <v>11</v>
@@ -1856,7 +1856,7 @@
         <v>18.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AX7" t="n">
         <v>12.5</v>
@@ -1865,32 +1865,32 @@
         <v>7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BC7" t="n">
         <v>13</v>
       </c>
       <c r="BD7" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="BE7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="G8" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="H8" t="n">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J8" t="n">
         <v>3.6</v>
@@ -1939,40 +1939,40 @@
         <v>4.7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="O8" t="n">
         <v>1.1</v>
       </c>
       <c r="P8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q8" t="n">
         <v>1.31</v>
       </c>
       <c r="R8" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="S8" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="T8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="U8" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W8" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -1990,7 +1990,7 @@
         <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
@@ -2005,7 +2005,7 @@
         <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
@@ -2026,22 +2026,22 @@
         <v>55</v>
       </c>
       <c r="AO8" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AR8" t="n">
         <v>4.7</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AU8" t="n">
         <v>6.4</v>
@@ -2050,41 +2050,41 @@
         <v>4.4</v>
       </c>
       <c r="AW8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE8" t="n">
         <v>4.6</v>
       </c>
-      <c r="AX8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BF8" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -2118,19 +2118,19 @@
         <v>1.12</v>
       </c>
       <c r="G9" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="H9" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="K9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="L9" t="n">
         <v>1.27</v>
@@ -2142,34 +2142,34 @@
         <v>6.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P9" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="R9" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="S9" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.84</v>
+        <v>1.54</v>
       </c>
       <c r="U9" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="V9" t="n">
         <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="X9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y9" t="n">
         <v>1000</v>
@@ -2181,7 +2181,7 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC9" t="n">
         <v>28</v>
@@ -2193,7 +2193,7 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AG9" t="n">
         <v>19.5</v>
@@ -2217,68 +2217,68 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.3</v>
+        <v>29</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>7.2</v>
+        <v>2.58</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.6</v>
+        <v>5.1</v>
       </c>
       <c r="AU9" t="n">
-        <v>22</v>
+        <v>2.52</v>
       </c>
       <c r="AV9" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.8</v>
+        <v>3.85</v>
       </c>
       <c r="AY9" t="n">
-        <v>13.5</v>
+        <v>7.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7.6</v>
+        <v>2.66</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.8</v>
+        <v>3.85</v>
       </c>
       <c r="BC9" t="n">
-        <v>13</v>
+        <v>7.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.8</v>
+        <v>2.68</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.4</v>
+        <v>2.76</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.86</v>
+        <v>2.32</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="H10" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="I10" t="n">
         <v>10</v>
@@ -2324,7 +2324,7 @@
         <v>5.6</v>
       </c>
       <c r="K10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L10" t="n">
         <v>1.31</v>
@@ -2348,7 +2348,7 @@
         <v>1.58</v>
       </c>
       <c r="S10" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T10" t="n">
         <v>1.95</v>
@@ -2360,7 +2360,7 @@
         <v>1.11</v>
       </c>
       <c r="W10" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="X10" t="n">
         <v>25</v>
@@ -2375,7 +2375,7 @@
         <v>430</v>
       </c>
       <c r="AB10" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC10" t="n">
         <v>12.5</v>
@@ -2411,7 +2411,7 @@
         <v>390</v>
       </c>
       <c r="AN10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AO10" t="n">
         <v>180</v>
@@ -2426,22 +2426,22 @@
         <v>28</v>
       </c>
       <c r="AS10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU10" t="n">
         <v>10.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AW10" t="n">
         <v>15</v>
       </c>
       <c r="AX10" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AY10" t="n">
         <v>9.6</v>
@@ -2450,13 +2450,13 @@
         <v>23</v>
       </c>
       <c r="BA10" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BB10" t="n">
         <v>10.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD10" t="n">
         <v>29</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="G11" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H11" t="n">
         <v>5.4</v>
@@ -2515,7 +2515,7 @@
         <v>5.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K11" t="n">
         <v>3.65</v>
@@ -2533,7 +2533,7 @@
         <v>1.37</v>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q11" t="n">
         <v>2.14</v>
@@ -2548,7 +2548,7 @@
         <v>1.95</v>
       </c>
       <c r="U11" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V11" t="n">
         <v>1.21</v>
@@ -2560,7 +2560,7 @@
         <v>13</v>
       </c>
       <c r="Y11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Z11" t="n">
         <v>40</v>
@@ -2572,7 +2572,7 @@
         <v>8</v>
       </c>
       <c r="AC11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD11" t="n">
         <v>22</v>
@@ -2581,7 +2581,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG11" t="n">
         <v>10.5</v>
@@ -2596,7 +2596,7 @@
         <v>19.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL11" t="n">
         <v>95</v>
@@ -2605,10 +2605,10 @@
         <v>140</v>
       </c>
       <c r="AN11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO11" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP11" t="n">
         <v>11</v>
@@ -2620,7 +2620,7 @@
         <v>26</v>
       </c>
       <c r="AS11" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="AT11" t="n">
         <v>7.2</v>
@@ -2629,13 +2629,13 @@
         <v>7.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>46</v>
+        <v>17.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY11" t="n">
         <v>9.4</v>
@@ -2644,7 +2644,7 @@
         <v>18.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB11" t="n">
         <v>17.5</v>
@@ -2656,17 +2656,17 @@
         <v>30</v>
       </c>
       <c r="BE11" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="BF11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -2700,13 +2700,13 @@
         <v>1.38</v>
       </c>
       <c r="G12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="H12" t="n">
         <v>10.5</v>
       </c>
       <c r="I12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J12" t="n">
         <v>5.3</v>
@@ -2715,7 +2715,7 @@
         <v>5.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
@@ -2724,31 +2724,31 @@
         <v>4.1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P12" t="n">
         <v>2.06</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
         <v>3.35</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U12" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="V12" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W12" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="X12" t="n">
         <v>16.5</v>
@@ -2760,10 +2760,10 @@
         <v>100</v>
       </c>
       <c r="AA12" t="n">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="AB12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC12" t="n">
         <v>12</v>
@@ -2775,49 +2775,49 @@
         <v>220</v>
       </c>
       <c r="AF12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH12" t="n">
         <v>34</v>
       </c>
       <c r="AI12" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AJ12" t="n">
         <v>11</v>
       </c>
       <c r="AK12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL12" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AM12" t="n">
         <v>220</v>
       </c>
       <c r="AN12" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO12" t="n">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="AP12" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AR12" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="AS12" t="n">
         <v>55</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU12" t="n">
         <v>10.5</v>
@@ -2826,41 +2826,41 @@
         <v>36</v>
       </c>
       <c r="AW12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AX12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY12" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="BA12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB12" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC12" t="n">
         <v>14.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BE12" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG12" t="n">
         <v>16.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -2894,13 +2894,13 @@
         <v>6.2</v>
       </c>
       <c r="G13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="I13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="J13" t="n">
         <v>4.2</v>
@@ -2915,37 +2915,37 @@
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q13" t="n">
         <v>2.06</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S13" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U13" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V13" t="n">
         <v>2.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X13" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y13" t="n">
         <v>7.6</v>
@@ -2957,22 +2957,22 @@
         <v>15.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC13" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AE13" t="n">
         <v>18.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AG13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH13" t="n">
         <v>25</v>
@@ -2984,7 +2984,7 @@
         <v>700</v>
       </c>
       <c r="AK13" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AL13" t="n">
         <v>100</v>
@@ -3002,10 +3002,10 @@
         <v>13</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AR13" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AS13" t="n">
         <v>14</v>
@@ -3020,7 +3020,7 @@
         <v>9.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AX13" t="n">
         <v>44</v>
@@ -3035,26 +3035,26 @@
         <v>36</v>
       </c>
       <c r="BB13" t="n">
-        <v>22</v>
+        <v>170</v>
       </c>
       <c r="BC13" t="n">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="BD13" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BE13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BF13" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BG13" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G14" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H14" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I14" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="J14" t="n">
         <v>3.55</v>
@@ -3103,19 +3103,19 @@
         <v>3.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O14" t="n">
         <v>1.32</v>
       </c>
       <c r="P14" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q14" t="n">
         <v>1.99</v>
@@ -3124,7 +3124,7 @@
         <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T14" t="n">
         <v>1.76</v>
@@ -3133,10 +3133,10 @@
         <v>2.24</v>
       </c>
       <c r="V14" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X14" t="n">
         <v>14.5</v>
@@ -3166,13 +3166,13 @@
         <v>18.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH14" t="n">
         <v>16.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="AJ14" t="n">
         <v>40</v>
@@ -3181,16 +3181,16 @@
         <v>29</v>
       </c>
       <c r="AL14" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM14" t="n">
         <v>90</v>
       </c>
       <c r="AN14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP14" t="n">
         <v>13.5</v>
@@ -3217,7 +3217,7 @@
         <v>27</v>
       </c>
       <c r="AX14" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY14" t="n">
         <v>11</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -3288,10 +3288,10 @@
         <v>11.5</v>
       </c>
       <c r="I15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="J15" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="K15" t="n">
         <v>7</v>
@@ -3315,16 +3315,16 @@
         <v>1.56</v>
       </c>
       <c r="R15" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="S15" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T15" t="n">
         <v>2.06</v>
       </c>
       <c r="U15" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V15" t="n">
         <v>1.08</v>
@@ -3333,7 +3333,7 @@
         <v>4.2</v>
       </c>
       <c r="X15" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y15" t="n">
         <v>42</v>
@@ -3342,37 +3342,37 @@
         <v>130</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>520</v>
       </c>
       <c r="AB15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AD15" t="n">
         <v>44</v>
       </c>
       <c r="AE15" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AF15" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AG15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI15" t="n">
-        <v>470</v>
+        <v>150</v>
       </c>
       <c r="AJ15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AK15" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AL15" t="n">
         <v>36</v>
@@ -3384,65 +3384,65 @@
         <v>4.4</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AP15" t="n">
         <v>23</v>
       </c>
       <c r="AQ15" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AR15" t="n">
-        <v>9.6</v>
+        <v>16</v>
       </c>
       <c r="AS15" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AW15" t="n">
-        <v>9.6</v>
+        <v>17</v>
       </c>
       <c r="AX15" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY15" t="n">
         <v>10</v>
       </c>
       <c r="AZ15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BB15" t="n">
         <v>9.4</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="BC15" t="n">
         <v>12</v>
       </c>
       <c r="BD15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE15" t="n">
-        <v>9.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BG15" t="n">
-        <v>9.800000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G16" t="n">
         <v>3.25</v>
       </c>
-      <c r="G16" t="n">
-        <v>3.3</v>
-      </c>
       <c r="H16" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="I16" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="J16" t="n">
         <v>3.6</v>
       </c>
       <c r="K16" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L16" t="n">
         <v>1.4</v>
@@ -3506,10 +3506,10 @@
         <v>2.08</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
         <v>3.2</v>
@@ -3521,19 +3521,19 @@
         <v>2.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X16" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z16" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA16" t="n">
         <v>32</v>
@@ -3587,7 +3587,7 @@
         <v>10.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS16" t="n">
         <v>28</v>
@@ -3596,7 +3596,7 @@
         <v>13</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV16" t="n">
         <v>10.5</v>
@@ -3617,10 +3617,10 @@
         <v>30</v>
       </c>
       <c r="BB16" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BC16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD16" t="n">
         <v>40</v>
@@ -3629,14 +3629,14 @@
         <v>70</v>
       </c>
       <c r="BF16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BG16" t="n">
         <v>15.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G17" t="n">
         <v>2.26</v>
@@ -3676,7 +3676,7 @@
         <v>3.7</v>
       </c>
       <c r="I17" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J17" t="n">
         <v>3.45</v>
@@ -3697,7 +3697,7 @@
         <v>1.38</v>
       </c>
       <c r="P17" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q17" t="n">
         <v>2.14</v>
@@ -3709,13 +3709,13 @@
         <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W17" t="n">
         <v>1.79</v>
@@ -3769,7 +3769,7 @@
         <v>110</v>
       </c>
       <c r="AN17" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO17" t="n">
         <v>55</v>
@@ -3820,17 +3820,17 @@
         <v>38</v>
       </c>
       <c r="BE17" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BF17" t="n">
         <v>18</v>
       </c>
       <c r="BG17" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="F18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G18" t="n">
         <v>1.65</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1.67</v>
       </c>
       <c r="H18" t="n">
         <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J18" t="n">
         <v>4.3</v>
@@ -3894,10 +3894,10 @@
         <v>2.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R18" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S18" t="n">
         <v>3.05</v>
@@ -3909,43 +3909,43 @@
         <v>2.08</v>
       </c>
       <c r="V18" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W18" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X18" t="n">
         <v>17.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z18" t="n">
         <v>48</v>
       </c>
       <c r="AA18" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB18" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD18" t="n">
         <v>23</v>
       </c>
       <c r="AE18" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG18" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH18" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI18" t="n">
         <v>75</v>
@@ -3978,7 +3978,7 @@
         <v>42</v>
       </c>
       <c r="AS18" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="AT18" t="n">
         <v>8.800000000000001</v>
@@ -4017,14 +4017,14 @@
         <v>85</v>
       </c>
       <c r="BF18" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BG18" t="n">
         <v>75</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -4055,52 +4055,52 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G19" t="n">
         <v>6.8</v>
       </c>
       <c r="H19" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="I19" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K19" t="n">
         <v>3.7</v>
       </c>
       <c r="L19" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M19" t="n">
         <v>1.12</v>
       </c>
       <c r="N19" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="O19" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P19" t="n">
         <v>1.57</v>
       </c>
-      <c r="P19" t="n">
-        <v>1.52</v>
-      </c>
       <c r="Q19" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="R19" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S19" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="T19" t="n">
         <v>2.36</v>
       </c>
       <c r="U19" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
@@ -4115,19 +4115,19 @@
         <v>5.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA19" t="n">
         <v>900</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC19" t="n">
         <v>8.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE19" t="n">
         <v>1000</v>
@@ -4136,7 +4136,7 @@
         <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH19" t="n">
         <v>1000</v>
@@ -4160,13 +4160,13 @@
         <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>26</v>
+        <v>600</v>
       </c>
       <c r="AP19" t="n">
         <v>8</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AR19" t="n">
         <v>7.8</v>
@@ -4175,50 +4175,50 @@
         <v>8.6</v>
       </c>
       <c r="AT19" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="AU19" t="n">
         <v>7.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW19" t="n">
         <v>11.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>18</v>
+        <v>8.4</v>
       </c>
       <c r="AY19" t="n">
         <v>13</v>
       </c>
       <c r="AZ19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF19" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>12.5</v>
+        <v>6.8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
         <v>2.74</v>
       </c>
       <c r="I20" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J20" t="n">
         <v>3.15</v>
@@ -4270,19 +4270,19 @@
         <v>1.54</v>
       </c>
       <c r="M20" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N20" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="O20" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P20" t="n">
         <v>1.61</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R20" t="n">
         <v>1.22</v>
@@ -4303,7 +4303,7 @@
         <v>1.47</v>
       </c>
       <c r="X20" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y20" t="n">
         <v>8.800000000000001</v>
@@ -4330,13 +4330,13 @@
         <v>18.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH20" t="n">
         <v>22</v>
       </c>
       <c r="AI20" t="n">
-        <v>65</v>
+        <v>380</v>
       </c>
       <c r="AJ20" t="n">
         <v>60</v>
@@ -4345,19 +4345,19 @@
         <v>100</v>
       </c>
       <c r="AL20" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO20" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP20" t="n">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="AQ20" t="n">
         <v>8.199999999999999</v>
@@ -4366,7 +4366,7 @@
         <v>15</v>
       </c>
       <c r="AS20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT20" t="n">
         <v>8.6</v>
@@ -4378,7 +4378,7 @@
         <v>11.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>11.5</v>
+        <v>32</v>
       </c>
       <c r="AX20" t="n">
         <v>16.5</v>
@@ -4390,29 +4390,29 @@
         <v>18.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="BD20" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="BE20" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BG20" t="n">
         <v>12.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="G21" t="n">
         <v>2.02</v>
       </c>
       <c r="H21" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I21" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J21" t="n">
         <v>3.3</v>
@@ -4461,7 +4461,7 @@
         <v>3.55</v>
       </c>
       <c r="L21" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M21" t="n">
         <v>1.1</v>
@@ -4470,25 +4470,25 @@
         <v>3.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P21" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="R21" t="n">
         <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T21" t="n">
         <v>2.04</v>
       </c>
       <c r="U21" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="V21" t="n">
         <v>1.23</v>
@@ -4533,7 +4533,7 @@
         <v>700</v>
       </c>
       <c r="AJ21" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AK21" t="n">
         <v>65</v>
@@ -4572,10 +4572,10 @@
         <v>16.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY21" t="n">
         <v>9.199999999999999</v>
@@ -4593,20 +4593,20 @@
         <v>20</v>
       </c>
       <c r="BD21" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="BE21" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BF21" t="n">
         <v>16.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
         <v>4.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M22" t="n">
         <v>1.07</v>
@@ -4667,7 +4667,7 @@
         <v>1.34</v>
       </c>
       <c r="P22" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q22" t="n">
         <v>2.04</v>
@@ -4703,7 +4703,7 @@
         <v>170</v>
       </c>
       <c r="AB22" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC22" t="n">
         <v>8.800000000000001</v>
@@ -4712,7 +4712,7 @@
         <v>23</v>
       </c>
       <c r="AE22" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF22" t="n">
         <v>9.6</v>
@@ -4724,7 +4724,7 @@
         <v>23</v>
       </c>
       <c r="AI22" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ22" t="n">
         <v>16.5</v>
@@ -4745,10 +4745,10 @@
         <v>110</v>
       </c>
       <c r="AP22" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ22" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AR22" t="n">
         <v>40</v>
@@ -4757,7 +4757,7 @@
         <v>36</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU22" t="n">
         <v>8</v>
@@ -4766,13 +4766,13 @@
         <v>20</v>
       </c>
       <c r="AW22" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AX22" t="n">
         <v>8.6</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ22" t="n">
         <v>20</v>
@@ -4796,11 +4796,11 @@
         <v>10</v>
       </c>
       <c r="BG22" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G23" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H23" t="n">
         <v>3.45</v>
       </c>
       <c r="I23" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K23" t="n">
         <v>3.8</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3.9</v>
       </c>
       <c r="L23" t="n">
         <v>1.38</v>
@@ -4873,19 +4873,19 @@
         <v>3.2</v>
       </c>
       <c r="T23" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U23" t="n">
         <v>2.28</v>
       </c>
       <c r="V23" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W23" t="n">
         <v>1.8</v>
       </c>
       <c r="X23" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Y23" t="n">
         <v>15</v>
@@ -4894,16 +4894,16 @@
         <v>25</v>
       </c>
       <c r="AA23" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AB23" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC23" t="n">
         <v>8.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE23" t="n">
         <v>38</v>
@@ -4912,7 +4912,7 @@
         <v>14.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH23" t="n">
         <v>17</v>
@@ -4930,7 +4930,7 @@
         <v>34</v>
       </c>
       <c r="AM23" t="n">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="AN23" t="n">
         <v>15</v>
@@ -4942,10 +4942,10 @@
         <v>15</v>
       </c>
       <c r="AQ23" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS23" t="n">
         <v>55</v>
@@ -4969,13 +4969,13 @@
         <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA23" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BB23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC23" t="n">
         <v>20</v>
@@ -4984,17 +4984,17 @@
         <v>30</v>
       </c>
       <c r="BE23" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BF23" t="n">
         <v>13.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
         <v>2.4</v>
       </c>
       <c r="H24" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I24" t="n">
         <v>3.3</v>
@@ -5049,7 +5049,7 @@
         <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O24" t="n">
         <v>1.26</v>
@@ -5058,19 +5058,19 @@
         <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R24" t="n">
         <v>1.47</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T24" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="U24" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V24" t="n">
         <v>1.43</v>
@@ -5079,10 +5079,10 @@
         <v>1.71</v>
       </c>
       <c r="X24" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z24" t="n">
         <v>29</v>
@@ -5091,13 +5091,13 @@
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="AE24" t="n">
         <v>95</v>
@@ -5106,43 +5106,43 @@
         <v>16.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>50</v>
+        <v>11.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI24" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="AK24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL24" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM24" t="n">
         <v>320</v>
       </c>
       <c r="AN24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
         <v>16</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>13.5</v>
       </c>
       <c r="AQ24" t="n">
         <v>13.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AS24" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AT24" t="n">
         <v>11</v>
@@ -5169,26 +5169,26 @@
         <v>34</v>
       </c>
       <c r="BB24" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="BC24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE24" t="n">
         <v>50</v>
       </c>
       <c r="BF24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG24" t="n">
         <v>23</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
         <v>1.43</v>
       </c>
       <c r="H25" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="I25" t="n">
         <v>10.5</v>
@@ -5240,7 +5240,7 @@
         <v>1.37</v>
       </c>
       <c r="M25" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N25" t="n">
         <v>4.3</v>
@@ -5252,10 +5252,10 @@
         <v>2.14</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S25" t="n">
         <v>3.2</v>
@@ -5264,7 +5264,7 @@
         <v>2.14</v>
       </c>
       <c r="U25" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V25" t="n">
         <v>1.1</v>
@@ -5285,7 +5285,7 @@
         <v>410</v>
       </c>
       <c r="AB25" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC25" t="n">
         <v>11.5</v>
@@ -5297,7 +5297,7 @@
         <v>180</v>
       </c>
       <c r="AF25" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG25" t="n">
         <v>10.5</v>
@@ -5315,28 +5315,28 @@
         <v>16</v>
       </c>
       <c r="AL25" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM25" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN25" t="n">
         <v>6.8</v>
       </c>
       <c r="AO25" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AP25" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR25" t="n">
-        <v>15.5</v>
+        <v>42</v>
       </c>
       <c r="AS25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT25" t="n">
         <v>7.4</v>
@@ -5345,7 +5345,7 @@
         <v>10</v>
       </c>
       <c r="AV25" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW25" t="n">
         <v>36</v>
@@ -5360,7 +5360,7 @@
         <v>25</v>
       </c>
       <c r="BA25" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BB25" t="n">
         <v>10</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -5422,13 +5422,13 @@
         <v>9.4</v>
       </c>
       <c r="I26" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J26" t="n">
         <v>4.9</v>
       </c>
       <c r="K26" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L26" t="n">
         <v>1.39</v>
@@ -5443,10 +5443,10 @@
         <v>1.3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R26" t="n">
         <v>1.4</v>
@@ -5470,13 +5470,13 @@
         <v>16</v>
       </c>
       <c r="Y26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z26" t="n">
         <v>85</v>
       </c>
       <c r="AA26" t="n">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="AB26" t="n">
         <v>7.4</v>
@@ -5500,7 +5500,7 @@
         <v>29</v>
       </c>
       <c r="AI26" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ26" t="n">
         <v>11.5</v>
@@ -5521,16 +5521,16 @@
         <v>270</v>
       </c>
       <c r="AP26" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR26" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="AS26" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AT26" t="n">
         <v>7</v>
@@ -5554,7 +5554,7 @@
         <v>27</v>
       </c>
       <c r="BA26" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BB26" t="n">
         <v>10.5</v>
@@ -5572,11 +5572,11 @@
         <v>6.8</v>
       </c>
       <c r="BG26" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -5631,28 +5631,28 @@
         <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O27" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P27" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R27" t="n">
         <v>1.37</v>
       </c>
       <c r="S27" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T27" t="n">
         <v>1.79</v>
       </c>
       <c r="U27" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V27" t="n">
         <v>1.5</v>
@@ -5667,10 +5667,10 @@
         <v>12</v>
       </c>
       <c r="Z27" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AA27" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AB27" t="n">
         <v>11</v>
@@ -5694,7 +5694,7 @@
         <v>17</v>
       </c>
       <c r="AI27" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ27" t="n">
         <v>38</v>
@@ -5754,7 +5754,7 @@
         <v>34</v>
       </c>
       <c r="BC27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD27" t="n">
         <v>36</v>
@@ -5763,14 +5763,14 @@
         <v>80</v>
       </c>
       <c r="BF27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BG27" t="n">
         <v>27</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -5801,16 +5801,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="G28" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="H28" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="I28" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J28" t="n">
         <v>3.8</v>
@@ -5825,22 +5825,22 @@
         <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O28" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P28" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R28" t="n">
         <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T28" t="n">
         <v>2.12</v>
@@ -5849,19 +5849,19 @@
         <v>1.84</v>
       </c>
       <c r="V28" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W28" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="X28" t="n">
         <v>12</v>
       </c>
       <c r="Y28" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA28" t="n">
         <v>160</v>
@@ -5873,10 +5873,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE28" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF28" t="n">
         <v>9.199999999999999</v>
@@ -5888,10 +5888,10 @@
         <v>24</v>
       </c>
       <c r="AI28" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ28" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="n">
         <v>20</v>
@@ -5900,25 +5900,25 @@
         <v>46</v>
       </c>
       <c r="AM28" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN28" t="n">
         <v>14</v>
       </c>
       <c r="AO28" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AP28" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ28" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR28" t="n">
         <v>36</v>
       </c>
       <c r="AS28" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AT28" t="n">
         <v>6.8</v>
@@ -5930,19 +5930,19 @@
         <v>20</v>
       </c>
       <c r="AW28" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AX28" t="n">
         <v>8.6</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ28" t="n">
         <v>21</v>
       </c>
       <c r="BA28" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="BB28" t="n">
         <v>16.5</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="F29" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G29" t="n">
         <v>1.72</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1.74</v>
       </c>
       <c r="H29" t="n">
         <v>5.5</v>
@@ -6019,16 +6019,16 @@
         <v>1.06</v>
       </c>
       <c r="N29" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O29" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P29" t="n">
         <v>2.02</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R29" t="n">
         <v>1.38</v>
@@ -6037,16 +6037,16 @@
         <v>3.5</v>
       </c>
       <c r="T29" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U29" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V29" t="n">
         <v>1.21</v>
       </c>
       <c r="W29" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="X29" t="n">
         <v>15.5</v>
@@ -6055,7 +6055,7 @@
         <v>17.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA29" t="n">
         <v>140</v>
@@ -6064,16 +6064,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE29" t="n">
         <v>75</v>
       </c>
       <c r="AF29" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG29" t="n">
         <v>10</v>
@@ -6082,7 +6082,7 @@
         <v>21</v>
       </c>
       <c r="AI29" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ29" t="n">
         <v>17</v>
@@ -6100,31 +6100,31 @@
         <v>10.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP29" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ29" t="n">
         <v>16.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AS29" t="n">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="AT29" t="n">
         <v>8</v>
       </c>
       <c r="AU29" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW29" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AX29" t="n">
         <v>9.4</v>
@@ -6136,7 +6136,7 @@
         <v>20</v>
       </c>
       <c r="BA29" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BB29" t="n">
         <v>16</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -6213,13 +6213,13 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="O30" t="n">
         <v>1.31</v>
       </c>
       <c r="P30" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="Q30" t="n">
         <v>1.3</v>
@@ -6234,7 +6234,7 @@
         <v>1.11</v>
       </c>
       <c r="U30" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="V30" t="n">
         <v>1.58</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -6383,13 +6383,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="G31" t="n">
         <v>1.95</v>
       </c>
       <c r="H31" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I31" t="n">
         <v>5.3</v>
@@ -6398,7 +6398,7 @@
         <v>3.45</v>
       </c>
       <c r="K31" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L31" t="n">
         <v>1.57</v>
@@ -6407,31 +6407,31 @@
         <v>1.11</v>
       </c>
       <c r="N31" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="O31" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P31" t="n">
         <v>1.56</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="R31" t="n">
         <v>1.19</v>
       </c>
       <c r="S31" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="T31" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="U31" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V31" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W31" t="n">
         <v>2.04</v>
@@ -6440,7 +6440,7 @@
         <v>11.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z31" t="n">
         <v>46</v>
@@ -6500,7 +6500,7 @@
         <v>14.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT31" t="n">
         <v>5.7</v>
@@ -6512,7 +6512,7 @@
         <v>16.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX31" t="n">
         <v>8.6</v>
@@ -6524,7 +6524,7 @@
         <v>24</v>
       </c>
       <c r="BA31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB31" t="n">
         <v>19</v>
@@ -6533,20 +6533,20 @@
         <v>13</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE31" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF31" t="n">
         <v>5</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="G32" t="n">
         <v>2.06</v>
@@ -6586,10 +6586,10 @@
         <v>4.3</v>
       </c>
       <c r="I32" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J32" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K32" t="n">
         <v>3.7</v>
@@ -6601,22 +6601,22 @@
         <v>1.08</v>
       </c>
       <c r="N32" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O32" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P32" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R32" t="n">
         <v>1.3</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T32" t="n">
         <v>1.92</v>
@@ -6634,22 +6634,22 @@
         <v>14</v>
       </c>
       <c r="Y32" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="AA32" t="n">
         <v>900</v>
       </c>
       <c r="AB32" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC32" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD32" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE32" t="n">
         <v>1000</v>
@@ -6664,7 +6664,7 @@
         <v>38</v>
       </c>
       <c r="AI32" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AJ32" t="n">
         <v>28</v>
@@ -6691,10 +6691,10 @@
         <v>12</v>
       </c>
       <c r="AR32" t="n">
-        <v>6.4</v>
+        <v>27</v>
       </c>
       <c r="AS32" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT32" t="n">
         <v>7.2</v>
@@ -6703,10 +6703,10 @@
         <v>7</v>
       </c>
       <c r="AV32" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX32" t="n">
         <v>10</v>
@@ -6718,29 +6718,29 @@
         <v>17</v>
       </c>
       <c r="BA32" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB32" t="n">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC32" t="n">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE32" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF32" t="n">
         <v>15</v>
       </c>
       <c r="BG32" t="n">
-        <v>6.6</v>
+        <v>55</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -6777,10 +6777,10 @@
         <v>1.94</v>
       </c>
       <c r="H33" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I33" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J33" t="n">
         <v>3.65</v>
@@ -6792,7 +6792,7 @@
         <v>1.43</v>
       </c>
       <c r="M33" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N33" t="n">
         <v>3.7</v>
@@ -6804,13 +6804,13 @@
         <v>1.91</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R33" t="n">
         <v>1.34</v>
       </c>
       <c r="S33" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T33" t="n">
         <v>1.89</v>
@@ -6825,10 +6825,10 @@
         <v>2.06</v>
       </c>
       <c r="X33" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y33" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z33" t="n">
         <v>34</v>
@@ -6849,7 +6849,7 @@
         <v>65</v>
       </c>
       <c r="AF33" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG33" t="n">
         <v>10.5</v>
@@ -6861,7 +6861,7 @@
         <v>320</v>
       </c>
       <c r="AJ33" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK33" t="n">
         <v>21</v>
@@ -6873,7 +6873,7 @@
         <v>120</v>
       </c>
       <c r="AN33" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AO33" t="n">
         <v>80</v>
@@ -6882,13 +6882,13 @@
         <v>12</v>
       </c>
       <c r="AQ33" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR33" t="n">
         <v>30</v>
       </c>
       <c r="AS33" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AT33" t="n">
         <v>8</v>
@@ -6900,7 +6900,7 @@
         <v>16.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AX33" t="n">
         <v>10</v>
@@ -6912,7 +6912,7 @@
         <v>17.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BB33" t="n">
         <v>19</v>
@@ -6921,20 +6921,20 @@
         <v>18.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE33" t="n">
         <v>40</v>
       </c>
       <c r="BF33" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG33" t="n">
         <v>60</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
         <v>21</v>
       </c>
       <c r="I34" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J34" t="n">
         <v>8</v>
@@ -7001,13 +7001,13 @@
         <v>1.57</v>
       </c>
       <c r="R34" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="S34" t="n">
         <v>2.44</v>
       </c>
       <c r="T34" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="U34" t="n">
         <v>1.62</v>
@@ -7016,7 +7016,7 @@
         <v>1.04</v>
       </c>
       <c r="W34" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="X34" t="n">
         <v>32</v>
@@ -7088,7 +7088,7 @@
         <v>8.6</v>
       </c>
       <c r="AU34" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="AV34" t="n">
         <v>60</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -7162,19 +7162,19 @@
         <v>2.86</v>
       </c>
       <c r="G35" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H35" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="I35" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J35" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K35" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L35" t="n">
         <v>1.56</v>
@@ -7186,7 +7186,7 @@
         <v>2.84</v>
       </c>
       <c r="O35" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P35" t="n">
         <v>1.58</v>
@@ -7198,67 +7198,67 @@
         <v>1.21</v>
       </c>
       <c r="S35" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T35" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U35" t="n">
         <v>1.84</v>
       </c>
-      <c r="U35" t="n">
-        <v>1.69</v>
-      </c>
       <c r="V35" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W35" t="n">
         <v>1.47</v>
       </c>
-      <c r="W35" t="n">
-        <v>1.48</v>
-      </c>
       <c r="X35" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y35" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z35" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA35" t="n">
         <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC35" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE35" t="n">
         <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG35" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI35" t="n">
         <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK35" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL35" t="n">
         <v>1000</v>
       </c>
       <c r="AM35" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN35" t="n">
         <v>1000</v>
@@ -7267,62 +7267,62 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -7353,13 +7353,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G36" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H36" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I36" t="n">
         <v>6.4</v>
@@ -7368,19 +7368,19 @@
         <v>3.65</v>
       </c>
       <c r="K36" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L36" t="n">
         <v>1.49</v>
       </c>
       <c r="M36" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N36" t="n">
         <v>3.1</v>
       </c>
       <c r="O36" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P36" t="n">
         <v>1.72</v>
@@ -7389,16 +7389,16 @@
         <v>2.3</v>
       </c>
       <c r="R36" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S36" t="n">
         <v>4.4</v>
       </c>
       <c r="T36" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="U36" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V36" t="n">
         <v>1.18</v>
@@ -7407,7 +7407,7 @@
         <v>2.28</v>
       </c>
       <c r="X36" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Y36" t="n">
         <v>120</v>
@@ -7419,7 +7419,7 @@
         <v>700</v>
       </c>
       <c r="AB36" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC36" t="n">
         <v>8.800000000000001</v>
@@ -7431,7 +7431,7 @@
         <v>700</v>
       </c>
       <c r="AF36" t="n">
-        <v>19.5</v>
+        <v>9.6</v>
       </c>
       <c r="AG36" t="n">
         <v>11</v>
@@ -7449,7 +7449,7 @@
         <v>60</v>
       </c>
       <c r="AL36" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AM36" t="n">
         <v>700</v>
@@ -7461,16 +7461,16 @@
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="AQ36" t="n">
         <v>8.4</v>
       </c>
       <c r="AR36" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AS36" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AT36" t="n">
         <v>6</v>
@@ -7482,41 +7482,41 @@
         <v>13</v>
       </c>
       <c r="AW36" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AX36" t="n">
         <v>8</v>
       </c>
       <c r="AY36" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AZ36" t="n">
         <v>22</v>
       </c>
       <c r="BA36" t="n">
-        <v>13.5</v>
+        <v>8.6</v>
       </c>
       <c r="BB36" t="n">
         <v>8.4</v>
       </c>
       <c r="BC36" t="n">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BE36" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BF36" t="n">
         <v>13</v>
       </c>
       <c r="BG36" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -7547,16 +7547,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G37" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H37" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="I37" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="J37" t="n">
         <v>3.25</v>
@@ -7565,28 +7565,28 @@
         <v>3.5</v>
       </c>
       <c r="L37" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M37" t="n">
         <v>1.1</v>
       </c>
       <c r="N37" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O37" t="n">
         <v>1.43</v>
       </c>
       <c r="P37" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R37" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S37" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T37" t="n">
         <v>1.94</v>
@@ -7595,7 +7595,7 @@
         <v>1.92</v>
       </c>
       <c r="V37" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="W37" t="n">
         <v>1.33</v>
@@ -7610,7 +7610,7 @@
         <v>16</v>
       </c>
       <c r="AA37" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB37" t="n">
         <v>15</v>
@@ -7625,13 +7625,13 @@
         <v>34</v>
       </c>
       <c r="AF37" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AG37" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AH37" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AI37" t="n">
         <v>60</v>
@@ -7640,10 +7640,10 @@
         <v>100</v>
       </c>
       <c r="AK37" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL37" t="n">
         <v>70</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>85</v>
       </c>
       <c r="AM37" t="n">
         <v>160</v>
@@ -7652,65 +7652,65 @@
         <v>85</v>
       </c>
       <c r="AO37" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP37" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="AQ37" t="n">
         <v>7.2</v>
       </c>
       <c r="AR37" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>4.8</v>
+        <v>25</v>
       </c>
       <c r="AT37" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AU37" t="n">
         <v>6.6</v>
       </c>
       <c r="AV37" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AW37" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AX37" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AY37" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AZ37" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BA37" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BG37" t="n">
         <v>5.1</v>
       </c>
-      <c r="BB37" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG37" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G38" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="H38" t="n">
         <v>2.28</v>
@@ -7753,7 +7753,7 @@
         <v>2.32</v>
       </c>
       <c r="J38" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K38" t="n">
         <v>3.35</v>
@@ -7792,7 +7792,7 @@
         <v>1.75</v>
       </c>
       <c r="W38" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X38" t="n">
         <v>11</v>
@@ -7825,7 +7825,7 @@
         <v>15.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AI38" t="n">
         <v>50</v>
@@ -7849,7 +7849,7 @@
         <v>25</v>
       </c>
       <c r="AP38" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AQ38" t="n">
         <v>7.6</v>
@@ -7858,7 +7858,7 @@
         <v>12</v>
       </c>
       <c r="AS38" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AT38" t="n">
         <v>10.5</v>
@@ -7870,7 +7870,7 @@
         <v>10</v>
       </c>
       <c r="AW38" t="n">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX38" t="n">
         <v>22</v>
@@ -7879,22 +7879,22 @@
         <v>14.5</v>
       </c>
       <c r="AZ38" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BA38" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="BB38" t="n">
         <v>60</v>
       </c>
       <c r="BC38" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="BD38" t="n">
         <v>55</v>
       </c>
       <c r="BE38" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BF38" t="n">
         <v>50</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G39" t="n">
         <v>2.18</v>
@@ -7950,7 +7950,7 @@
         <v>3.5</v>
       </c>
       <c r="K39" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L39" t="n">
         <v>1.4</v>
@@ -7962,22 +7962,22 @@
         <v>4</v>
       </c>
       <c r="O39" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P39" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R39" t="n">
         <v>1.4</v>
       </c>
       <c r="S39" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T39" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U39" t="n">
         <v>2.22</v>
@@ -7986,10 +7986,10 @@
         <v>1.32</v>
       </c>
       <c r="W39" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X39" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y39" t="n">
         <v>18</v>
@@ -8025,7 +8025,7 @@
         <v>1000</v>
       </c>
       <c r="AJ39" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK39" t="n">
         <v>1000</v>
@@ -8043,16 +8043,16 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ39" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AR39" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AS39" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="AT39" t="n">
         <v>9.199999999999999</v>
@@ -8061,44 +8061,44 @@
         <v>4.3</v>
       </c>
       <c r="AV39" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AW39" t="n">
         <v>5</v>
       </c>
       <c r="AX39" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AY39" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AZ39" t="n">
         <v>14</v>
       </c>
       <c r="BA39" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD39" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB39" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD39" t="n">
+      <c r="BE39" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG39" t="n">
         <v>4.9</v>
       </c>
-      <c r="BE39" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-19.xlsx
@@ -757,25 +757,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="G2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H2" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="I2" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="J2" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="K2" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -784,10 +784,10 @@
         <v>3.55</v>
       </c>
       <c r="O2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P2" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q2" t="n">
         <v>2.08</v>
@@ -796,55 +796,55 @@
         <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="T2" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="U2" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="V2" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="W2" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X2" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AC2" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AG2" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AH2" t="n">
         <v>42</v>
       </c>
       <c r="AI2" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
@@ -862,65 +862,65 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>30</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC2" t="n">
         <v>7.8</v>
       </c>
-      <c r="AP2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX2" t="n">
+      <c r="BD2" t="n">
         <v>7.8</v>
       </c>
-      <c r="AY2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BA2" t="n">
+      <c r="BE2" t="n">
         <v>7.8</v>
       </c>
-      <c r="BB2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD2" t="n">
+      <c r="BF2" t="n">
         <v>8</v>
       </c>
-      <c r="BE2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BG2" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-19 04:01:01</t>
+          <t>2026-03-19 06:19:43</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>18.5</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X3" t="n">
         <v>28</v>
       </c>
-      <c r="H3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="J3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K3" t="n">
-        <v>7</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N3" t="n">
-        <v>4</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V3" t="n">
-        <v>5</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ3" t="n">
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AO3" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.95</v>
+        <v>8.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.8</v>
+        <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.62</v>
+        <v>23</v>
       </c>
       <c r="AU3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.7</v>
+        <v>46</v>
       </c>
       <c r="AY3" t="n">
-        <v>2.68</v>
+        <v>30</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.64</v>
+        <v>22</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.68</v>
+        <v>25</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.74</v>
+        <v>13</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.76</v>
+        <v>13.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.72</v>
+        <v>50</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.74</v>
+        <v>13.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.74</v>
+        <v>12.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-19 04:01:01</t>
+          <t>2026-03-19 06:19:43</t>
         </is>
       </c>
     </row>
@@ -1145,76 +1145,76 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="G4" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K4" t="n">
         <v>3.75</v>
       </c>
-      <c r="K4" t="n">
-        <v>3.8</v>
-      </c>
       <c r="L4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.39</v>
       </c>
-      <c r="M4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.45</v>
-      </c>
       <c r="S4" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="U4" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="V4" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W4" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="X4" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Z4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA4" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD4" t="n">
         <v>16</v>
@@ -1223,92 +1223,92 @@
         <v>46</v>
       </c>
       <c r="AF4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>13</v>
       </c>
-      <c r="AG4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>15</v>
-      </c>
       <c r="AR4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AS4" t="n">
         <v>48</v>
       </c>
       <c r="AT4" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AU4" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AV4" t="n">
         <v>14.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AX4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="BB4" t="n">
         <v>22</v>
       </c>
       <c r="BC4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE4" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BF4" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-19 04:01:01</t>
+          <t>2026-03-19 06:19:43</t>
         </is>
       </c>
     </row>
@@ -1345,46 +1345,46 @@
         <v>1.34</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I5" t="n">
         <v>14.5</v>
       </c>
       <c r="J5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K5" t="n">
         <v>6.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R5" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="S5" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="V5" t="n">
         <v>1.08</v>
@@ -1435,7 +1435,7 @@
         <v>970</v>
       </c>
       <c r="AL5" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
@@ -1447,13 +1447,13 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AS5" t="n">
         <v>4.2</v>
@@ -1465,22 +1465,22 @@
         <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AW5" t="n">
         <v>4.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AY5" t="n">
         <v>7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.9</v>
+        <v>9.6</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BB5" t="n">
         <v>5.6</v>
@@ -1489,20 +1489,20 @@
         <v>7</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.9</v>
+        <v>10</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-19 04:01:01</t>
+          <t>2026-03-19 06:19:43</t>
         </is>
       </c>
     </row>
@@ -1536,19 +1536,19 @@
         <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="H6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="I6" t="n">
         <v>1.28</v>
       </c>
       <c r="J6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-19 04:01:01</t>
+          <t>2026-03-19 06:19:43</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="G7" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="H7" t="n">
         <v>5.4</v>
@@ -1742,73 +1742,73 @@
         <v>4.7</v>
       </c>
       <c r="K7" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="S7" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="T7" t="n">
         <v>1.54</v>
       </c>
       <c r="U7" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V7" t="n">
         <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="X7" t="n">
         <v>85</v>
       </c>
       <c r="Y7" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA7" t="n">
         <v>140</v>
       </c>
       <c r="AB7" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE7" t="n">
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
         <v>17</v>
@@ -1817,10 +1817,10 @@
         <v>50</v>
       </c>
       <c r="AJ7" t="n">
-        <v>18.5</v>
+        <v>500</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL7" t="n">
         <v>23</v>
@@ -1829,31 +1829,31 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR7" t="n">
         <v>29</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>8</v>
-      </c>
       <c r="AS7" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="AU7" t="n">
         <v>11</v>
       </c>
       <c r="AV7" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AW7" t="n">
         <v>48</v>
@@ -1868,7 +1868,7 @@
         <v>7.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB7" t="n">
         <v>9</v>
@@ -1880,17 +1880,17 @@
         <v>11</v>
       </c>
       <c r="BE7" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-19 04:01:01</t>
+          <t>2026-03-19 06:19:43</t>
         </is>
       </c>
     </row>
@@ -1921,58 +1921,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="G8" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="I8" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P8" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="Q8" t="n">
         <v>1.31</v>
       </c>
       <c r="R8" t="n">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="S8" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="T8" t="n">
         <v>1.32</v>
       </c>
       <c r="U8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -1981,10 +1981,10 @@
         <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AB8" t="n">
         <v>1000</v>
@@ -2002,7 +2002,7 @@
         <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH8" t="n">
         <v>25</v>
@@ -2020,71 +2020,71 @@
         <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
         <v>55</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.15</v>
+        <v>4.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AS8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.05</v>
+        <v>5.1</v>
       </c>
       <c r="AU8" t="n">
         <v>6.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.05</v>
+        <v>5.4</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.9</v>
+        <v>12</v>
       </c>
       <c r="AY8" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="AZ8" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.15</v>
+        <v>5.3</v>
       </c>
       <c r="BC8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD8" t="n">
         <v>5.4</v>
       </c>
-      <c r="BD8" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BE8" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-19 04:01:01</t>
+          <t>2026-03-19 06:19:43</t>
         </is>
       </c>
     </row>
@@ -2115,64 +2115,64 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="G9" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="H9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I9" t="n">
+        <v>36</v>
+      </c>
+      <c r="J9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="X9" t="n">
         <v>42</v>
       </c>
-      <c r="J9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="K9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="X9" t="n">
-        <v>38</v>
-      </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
@@ -2181,104 +2181,104 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AK9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>29</v>
+        <v>3.45</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.58</v>
+        <v>15.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.52</v>
+        <v>20</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.85</v>
+        <v>5.9</v>
       </c>
       <c r="AY9" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.66</v>
+        <v>5.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.85</v>
+        <v>6.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>7.4</v>
+        <v>13</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.68</v>
+        <v>5.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.76</v>
+        <v>5.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.32</v>
+        <v>2.98</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-19 04:01:01</t>
+          <t>2026-03-19 06:19:43</t>
         </is>
       </c>
     </row>
@@ -2327,22 +2327,22 @@
         <v>5.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P10" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="R10" t="n">
         <v>1.58</v>
@@ -2354,13 +2354,13 @@
         <v>1.95</v>
       </c>
       <c r="U10" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V10" t="n">
         <v>1.11</v>
       </c>
       <c r="W10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="X10" t="n">
         <v>25</v>
@@ -2372,7 +2372,7 @@
         <v>90</v>
       </c>
       <c r="AA10" t="n">
-        <v>430</v>
+        <v>360</v>
       </c>
       <c r="AB10" t="n">
         <v>9.800000000000001</v>
@@ -2381,22 +2381,22 @@
         <v>12.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE10" t="n">
         <v>140</v>
       </c>
       <c r="AF10" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI10" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ10" t="n">
         <v>11.5</v>
@@ -2408,49 +2408,49 @@
         <v>34</v>
       </c>
       <c r="AM10" t="n">
-        <v>390</v>
+        <v>140</v>
       </c>
       <c r="AN10" t="n">
         <v>5.3</v>
       </c>
       <c r="AO10" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AP10" t="n">
         <v>21</v>
       </c>
       <c r="AQ10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR10" t="n">
         <v>28</v>
       </c>
       <c r="AS10" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AT10" t="n">
         <v>9</v>
       </c>
       <c r="AU10" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AW10" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="AX10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
         <v>23</v>
       </c>
       <c r="BA10" t="n">
-        <v>17.5</v>
+        <v>65</v>
       </c>
       <c r="BB10" t="n">
         <v>10.5</v>
@@ -2462,17 +2462,17 @@
         <v>29</v>
       </c>
       <c r="BE10" t="n">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="BF10" t="n">
         <v>5</v>
       </c>
       <c r="BG10" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-19 04:01:01</t>
+          <t>2026-03-19 06:19:43</t>
         </is>
       </c>
     </row>
@@ -2512,16 +2512,16 @@
         <v>5.4</v>
       </c>
       <c r="I11" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J11" t="n">
         <v>3.6</v>
       </c>
       <c r="K11" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M11" t="n">
         <v>1.08</v>
@@ -2542,22 +2542,22 @@
         <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T11" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U11" t="n">
         <v>1.95</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.94</v>
       </c>
       <c r="V11" t="n">
         <v>1.21</v>
       </c>
       <c r="W11" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y11" t="n">
         <v>17</v>
@@ -2569,13 +2569,13 @@
         <v>140</v>
       </c>
       <c r="AB11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC11" t="n">
         <v>8</v>
       </c>
-      <c r="AC11" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AD11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE11" t="n">
         <v>80</v>
@@ -2584,7 +2584,7 @@
         <v>10</v>
       </c>
       <c r="AG11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH11" t="n">
         <v>22</v>
@@ -2596,10 +2596,10 @@
         <v>19.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL11" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AM11" t="n">
         <v>140</v>
@@ -2608,19 +2608,19 @@
         <v>14</v>
       </c>
       <c r="AO11" t="n">
-        <v>110</v>
+        <v>310</v>
       </c>
       <c r="AP11" t="n">
         <v>11</v>
       </c>
       <c r="AQ11" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AS11" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AT11" t="n">
         <v>7.2</v>
@@ -2632,7 +2632,7 @@
         <v>19.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>17.5</v>
+        <v>34</v>
       </c>
       <c r="AX11" t="n">
         <v>9.4</v>
@@ -2641,7 +2641,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA11" t="n">
         <v>48</v>
@@ -2653,20 +2653,20 @@
         <v>18.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BE11" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="BF11" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG11" t="n">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-19 04:01:01</t>
+          <t>2026-03-19 06:19:43</t>
         </is>
       </c>
     </row>
@@ -2700,124 +2700,124 @@
         <v>1.38</v>
       </c>
       <c r="G12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="H12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="I12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J12" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="O12" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="T12" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="U12" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="V12" t="n">
         <v>1.09</v>
       </c>
       <c r="W12" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="X12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y12" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Z12" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AA12" t="n">
-        <v>480</v>
+        <v>520</v>
       </c>
       <c r="AB12" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AC12" t="n">
         <v>12</v>
       </c>
       <c r="AD12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AE12" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AF12" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AG12" t="n">
         <v>10.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI12" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AJ12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL12" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AM12" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="AN12" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AO12" t="n">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="AP12" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR12" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="AS12" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU12" t="n">
         <v>10.5</v>
@@ -2826,41 +2826,41 @@
         <v>36</v>
       </c>
       <c r="AW12" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY12" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BA12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE12" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-19 04:01:01</t>
+          <t>2026-03-19 06:19:43</t>
         </is>
       </c>
     </row>
@@ -2891,64 +2891,64 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="G13" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="H13" t="n">
         <v>1.64</v>
       </c>
       <c r="I13" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="J13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K13" t="n">
         <v>4.2</v>
       </c>
-      <c r="K13" t="n">
-        <v>4.3</v>
-      </c>
       <c r="L13" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="O13" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="P13" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="R13" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="T13" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U13" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="V13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="W13" t="n">
         <v>1.17</v>
       </c>
       <c r="X13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y13" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z13" t="n">
         <v>8.800000000000001</v>
@@ -2966,43 +2966,43 @@
         <v>10</v>
       </c>
       <c r="AE13" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AF13" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AG13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH13" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI13" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ13" t="n">
-        <v>700</v>
+        <v>270</v>
       </c>
       <c r="AK13" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AL13" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AM13" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN13" t="n">
         <v>150</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>130</v>
       </c>
       <c r="AO13" t="n">
         <v>11</v>
       </c>
       <c r="AP13" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR13" t="n">
         <v>8</v>
@@ -3014,10 +3014,10 @@
         <v>16</v>
       </c>
       <c r="AU13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW13" t="n">
         <v>17.5</v>
@@ -3026,7 +3026,7 @@
         <v>44</v>
       </c>
       <c r="AY13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AZ13" t="n">
         <v>23</v>
@@ -3035,16 +3035,16 @@
         <v>36</v>
       </c>
       <c r="BB13" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="BC13" t="n">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="BD13" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BE13" t="n">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="BF13" t="n">
         <v>18.5</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-19 04:01:01</t>
+          <t>2026-03-19 06:19:43</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G14" t="n">
         <v>2.66</v>
       </c>
-      <c r="G14" t="n">
-        <v>2.72</v>
-      </c>
       <c r="H14" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="I14" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="J14" t="n">
         <v>3.55</v>
@@ -3103,40 +3103,40 @@
         <v>3.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="O14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P14" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
         <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T14" t="n">
         <v>1.76</v>
       </c>
       <c r="U14" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V14" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W14" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X14" t="n">
         <v>14.5</v>
@@ -3145,34 +3145,34 @@
         <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AA14" t="n">
         <v>48</v>
       </c>
       <c r="AB14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC14" t="n">
         <v>7.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE14" t="n">
         <v>32</v>
       </c>
       <c r="AF14" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG14" t="n">
         <v>12</v>
       </c>
       <c r="AH14" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI14" t="n">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="AJ14" t="n">
         <v>40</v>
@@ -3181,19 +3181,19 @@
         <v>29</v>
       </c>
       <c r="AL14" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM14" t="n">
         <v>90</v>
       </c>
       <c r="AN14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO14" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AP14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ14" t="n">
         <v>11</v>
@@ -3202,22 +3202,22 @@
         <v>17</v>
       </c>
       <c r="AS14" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AT14" t="n">
         <v>10.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV14" t="n">
         <v>11.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AX14" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY14" t="n">
         <v>11</v>
@@ -3229,26 +3229,26 @@
         <v>36</v>
       </c>
       <c r="BB14" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BC14" t="n">
         <v>25</v>
       </c>
       <c r="BD14" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BE14" t="n">
         <v>75</v>
       </c>
       <c r="BF14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BG14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-19 04:01:01</t>
+          <t>2026-03-19 06:19:43</t>
         </is>
       </c>
     </row>
@@ -3285,40 +3285,40 @@
         <v>1.31</v>
       </c>
       <c r="H15" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="I15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="J15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K15" t="n">
         <v>6.8</v>
       </c>
-      <c r="K15" t="n">
-        <v>7</v>
-      </c>
       <c r="L15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M15" t="n">
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O15" t="n">
         <v>1.18</v>
       </c>
       <c r="P15" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R15" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="S15" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="T15" t="n">
         <v>2.06</v>
@@ -3333,34 +3333,34 @@
         <v>4.2</v>
       </c>
       <c r="X15" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="Y15" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Z15" t="n">
         <v>130</v>
       </c>
       <c r="AA15" t="n">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="AB15" t="n">
         <v>10.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AE15" t="n">
         <v>200</v>
       </c>
       <c r="AF15" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH15" t="n">
         <v>30</v>
@@ -3375,7 +3375,7 @@
         <v>13.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM15" t="n">
         <v>160</v>
@@ -3384,16 +3384,16 @@
         <v>4.4</v>
       </c>
       <c r="AO15" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AP15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AQ15" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AR15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS15" t="n">
         <v>18</v>
@@ -3405,7 +3405,7 @@
         <v>13.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AW15" t="n">
         <v>17</v>
@@ -3417,13 +3417,13 @@
         <v>10</v>
       </c>
       <c r="AZ15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA15" t="n">
-        <v>16.5</v>
+        <v>29</v>
       </c>
       <c r="BB15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC15" t="n">
         <v>12</v>
@@ -3438,11 +3438,11 @@
         <v>4</v>
       </c>
       <c r="BG15" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-19 04:01:01</t>
+          <t>2026-03-19 06:19:43</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>3.2</v>
       </c>
       <c r="G16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H16" t="n">
         <v>2.4</v>
@@ -3497,7 +3497,7 @@
         <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O16" t="n">
         <v>1.29</v>
@@ -3506,10 +3506,10 @@
         <v>2.08</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
         <v>3.2</v>
@@ -3527,7 +3527,7 @@
         <v>1.44</v>
       </c>
       <c r="X16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y16" t="n">
         <v>11</v>
@@ -3539,7 +3539,7 @@
         <v>32</v>
       </c>
       <c r="AB16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC16" t="n">
         <v>8</v>
@@ -3548,13 +3548,13 @@
         <v>11</v>
       </c>
       <c r="AE16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF16" t="n">
         <v>22</v>
       </c>
       <c r="AG16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH16" t="n">
         <v>16</v>
@@ -3575,7 +3575,7 @@
         <v>80</v>
       </c>
       <c r="AN16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO16" t="n">
         <v>17</v>
@@ -3587,7 +3587,7 @@
         <v>10.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS16" t="n">
         <v>28</v>
@@ -3605,7 +3605,7 @@
         <v>22</v>
       </c>
       <c r="AX16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY16" t="n">
         <v>13</v>
@@ -3614,10 +3614,10 @@
         <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB16" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BC16" t="n">
         <v>30</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-19 04:01:01</t>
+          <t>2026-03-19 06:19:43</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
         <v>2.26</v>
       </c>
       <c r="H17" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I17" t="n">
         <v>3.8</v>
@@ -3697,22 +3697,22 @@
         <v>1.38</v>
       </c>
       <c r="P17" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R17" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V17" t="n">
         <v>1.35</v>
@@ -3742,7 +3742,7 @@
         <v>15</v>
       </c>
       <c r="AE17" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF17" t="n">
         <v>13.5</v>
@@ -3769,7 +3769,7 @@
         <v>110</v>
       </c>
       <c r="AN17" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AO17" t="n">
         <v>55</v>
@@ -3778,7 +3778,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR17" t="n">
         <v>23</v>
@@ -3820,7 +3820,7 @@
         <v>38</v>
       </c>
       <c r="BE17" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="BF17" t="n">
         <v>18</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-19 04:01:01</t>
+          <t>2026-03-19 06:19:43</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="G18" t="n">
         <v>1.65</v>
@@ -3870,19 +3870,19 @@
         <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J18" t="n">
         <v>4.3</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L18" t="n">
         <v>1.37</v>
       </c>
       <c r="M18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
         <v>4.5</v>
@@ -3894,28 +3894,28 @@
         <v>2.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R18" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S18" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U18" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V18" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W18" t="n">
         <v>2.52</v>
       </c>
       <c r="X18" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y18" t="n">
         <v>22</v>
@@ -3948,10 +3948,10 @@
         <v>20</v>
       </c>
       <c r="AI18" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ18" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK18" t="n">
         <v>16.5</v>
@@ -3966,46 +3966,46 @@
         <v>8.4</v>
       </c>
       <c r="AO18" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP18" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ18" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR18" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AS18" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AT18" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU18" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW18" t="n">
         <v>70</v>
       </c>
       <c r="AX18" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY18" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA18" t="n">
         <v>65</v>
       </c>
       <c r="BB18" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC18" t="n">
         <v>15</v>
@@ -4017,14 +4017,14 @@
         <v>85</v>
       </c>
       <c r="BF18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG18" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-19 04:01:01</t>
+          <t>2026-03-19 06:19:43</t>
         </is>
       </c>
     </row>
@@ -4055,52 +4055,52 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="G19" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="H19" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="I19" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="J19" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K19" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="M19" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N19" t="n">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="O19" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="P19" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="R19" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="U19" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
@@ -4109,40 +4109,40 @@
         <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="Z19" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>900</v>
+        <v>34</v>
       </c>
       <c r="AB19" t="n">
         <v>18</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AD19" t="n">
         <v>11.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AG19" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AI19" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AJ19" t="n">
         <v>1000</v>
@@ -4160,22 +4160,22 @@
         <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>600</v>
+        <v>16.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT19" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="AU19" t="n">
         <v>7.2</v>
@@ -4184,41 +4184,41 @@
         <v>9.4</v>
       </c>
       <c r="AW19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY19" t="n">
         <v>11.5</v>
       </c>
-      <c r="AX19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY19" t="n">
+      <c r="AZ19" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG19" t="n">
         <v>13</v>
       </c>
-      <c r="AZ19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-19 04:01:01</t>
+          <t>2026-03-19 06:19:43</t>
         </is>
       </c>
     </row>
@@ -4255,130 +4255,130 @@
         <v>3.15</v>
       </c>
       <c r="H20" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I20" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="J20" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K20" t="n">
         <v>3.2</v>
       </c>
       <c r="L20" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="M20" t="n">
         <v>1.12</v>
       </c>
       <c r="N20" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="O20" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="P20" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="R20" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="U20" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="V20" t="n">
         <v>1.54</v>
       </c>
       <c r="W20" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA20" t="n">
         <v>46</v>
       </c>
       <c r="AB20" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AC20" t="n">
         <v>7.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>95</v>
+        <v>190</v>
       </c>
       <c r="AF20" t="n">
         <v>18.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI20" t="n">
-        <v>380</v>
+        <v>70</v>
       </c>
       <c r="AJ20" t="n">
         <v>60</v>
       </c>
       <c r="AK20" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AL20" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="AM20" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AN20" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AO20" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AP20" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AR20" t="n">
         <v>15</v>
       </c>
       <c r="AS20" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="AT20" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV20" t="n">
         <v>11.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX20" t="n">
         <v>16.5</v>
@@ -4387,32 +4387,32 @@
         <v>12.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA20" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE20" t="n">
         <v>28</v>
       </c>
-      <c r="BB20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BF20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BG20" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-19 04:01:01</t>
+          <t>2026-03-19 06:19:43</t>
         </is>
       </c>
     </row>
@@ -4443,88 +4443,88 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="G21" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="H21" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="I21" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="J21" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K21" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="L21" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M21" t="n">
         <v>1.1</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O21" t="n">
         <v>1.43</v>
       </c>
       <c r="P21" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
         <v>4.4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U21" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="V21" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="W21" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="X21" t="n">
         <v>11</v>
       </c>
       <c r="Y21" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AA21" t="n">
         <v>900</v>
       </c>
       <c r="AB21" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AE21" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AG21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH21" t="n">
         <v>60</v>
@@ -4551,62 +4551,62 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR21" t="n">
         <v>12</v>
       </c>
-      <c r="AR21" t="n">
-        <v>10</v>
-      </c>
       <c r="AS21" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AW21" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AX21" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY21" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ21" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BB21" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="BC21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BD21" t="n">
         <v>23</v>
       </c>
       <c r="BE21" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-19 04:01:01</t>
+          <t>2026-03-19 06:19:43</t>
         </is>
       </c>
     </row>
@@ -4640,13 +4640,13 @@
         <v>1.7</v>
       </c>
       <c r="G22" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="H22" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I22" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J22" t="n">
         <v>3.95</v>
@@ -4658,16 +4658,16 @@
         <v>1.44</v>
       </c>
       <c r="M22" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N22" t="n">
         <v>3.75</v>
       </c>
       <c r="O22" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P22" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="Q22" t="n">
         <v>2.04</v>
@@ -4679,22 +4679,22 @@
         <v>3.75</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U22" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V22" t="n">
         <v>1.19</v>
       </c>
       <c r="W22" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="X22" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z22" t="n">
         <v>46</v>
@@ -4715,7 +4715,7 @@
         <v>90</v>
       </c>
       <c r="AF22" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG22" t="n">
         <v>9.800000000000001</v>
@@ -4751,34 +4751,34 @@
         <v>16</v>
       </c>
       <c r="AR22" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AS22" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW22" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="AX22" t="n">
         <v>8.6</v>
       </c>
       <c r="AY22" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ22" t="n">
         <v>20</v>
       </c>
       <c r="BA22" t="n">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="BB22" t="n">
         <v>15</v>
@@ -4787,20 +4787,20 @@
         <v>16.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BE22" t="n">
         <v>29</v>
       </c>
       <c r="BF22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-19 04:01:01</t>
+          <t>2026-03-19 06:19:43</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="G23" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="H23" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="I23" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="J23" t="n">
         <v>3.75</v>
       </c>
       <c r="K23" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L23" t="n">
         <v>1.38</v>
@@ -4861,40 +4861,40 @@
         <v>1.28</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q23" t="n">
         <v>1.86</v>
       </c>
       <c r="R23" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T23" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U23" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V23" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W23" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="X23" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA23" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB23" t="n">
         <v>11.5</v>
@@ -4903,67 +4903,67 @@
         <v>8.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE23" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF23" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG23" t="n">
         <v>11</v>
       </c>
       <c r="AH23" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ23" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AK23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL23" t="n">
         <v>34</v>
       </c>
       <c r="AM23" t="n">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="AN23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO23" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AP23" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AS23" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AT23" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU23" t="n">
         <v>7.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW23" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX23" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AY23" t="n">
         <v>10</v>
@@ -4972,29 +4972,29 @@
         <v>15</v>
       </c>
       <c r="BA23" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BB23" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BC23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD23" t="n">
         <v>30</v>
       </c>
       <c r="BE23" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="BF23" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG23" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-19 04:01:01</t>
+          <t>2026-03-19 06:19:43</t>
         </is>
       </c>
     </row>
@@ -5031,16 +5031,16 @@
         <v>2.4</v>
       </c>
       <c r="H24" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I24" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K24" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L24" t="n">
         <v>1.36</v>
@@ -5049,70 +5049,70 @@
         <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="R24" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="S24" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="T24" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="U24" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="V24" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W24" t="n">
         <v>1.71</v>
       </c>
       <c r="X24" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="Y24" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="AF24" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG24" t="n">
         <v>11.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ24" t="n">
         <v>32</v>
@@ -5121,43 +5121,43 @@
         <v>23</v>
       </c>
       <c r="AL24" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM24" t="n">
-        <v>320</v>
+        <v>65</v>
       </c>
       <c r="AN24" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AP24" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AQ24" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR24" t="n">
         <v>21</v>
       </c>
       <c r="AS24" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="AT24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV24" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="AX24" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY24" t="n">
         <v>10</v>
@@ -5166,10 +5166,10 @@
         <v>13.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC24" t="n">
         <v>20</v>
@@ -5178,17 +5178,17 @@
         <v>28</v>
       </c>
       <c r="BE24" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="BF24" t="n">
         <v>13</v>
       </c>
       <c r="BG24" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-19 04:01:01</t>
+          <t>2026-03-19 06:19:43</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="G25" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="H25" t="n">
         <v>9.4</v>
       </c>
       <c r="I25" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J25" t="n">
+        <v>5</v>
+      </c>
+      <c r="K25" t="n">
         <v>5.1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>5.3</v>
       </c>
       <c r="L25" t="n">
         <v>1.37</v>
@@ -5243,19 +5243,19 @@
         <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O25" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P25" t="n">
         <v>2.14</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R25" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
         <v>3.2</v>
@@ -5264,25 +5264,25 @@
         <v>2.14</v>
       </c>
       <c r="U25" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="V25" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W25" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="X25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z25" t="n">
         <v>90</v>
       </c>
       <c r="AA25" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="AB25" t="n">
         <v>8</v>
@@ -5294,7 +5294,7 @@
         <v>36</v>
       </c>
       <c r="AE25" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AF25" t="n">
         <v>8.199999999999999</v>
@@ -5303,19 +5303,19 @@
         <v>10.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AI25" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ25" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AK25" t="n">
         <v>16</v>
       </c>
       <c r="AL25" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM25" t="n">
         <v>180</v>
@@ -5324,7 +5324,7 @@
         <v>6.8</v>
       </c>
       <c r="AO25" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AP25" t="n">
         <v>15.5</v>
@@ -5333,13 +5333,13 @@
         <v>24</v>
       </c>
       <c r="AR25" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AS25" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU25" t="n">
         <v>10</v>
@@ -5348,10 +5348,10 @@
         <v>30</v>
       </c>
       <c r="AW25" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="AX25" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY25" t="n">
         <v>9.6</v>
@@ -5360,10 +5360,10 @@
         <v>25</v>
       </c>
       <c r="BA25" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC25" t="n">
         <v>14</v>
@@ -5372,17 +5372,17 @@
         <v>36</v>
       </c>
       <c r="BE25" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="BF25" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>15</v>
+        <v>140</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-19 04:01:01</t>
+          <t>2026-03-19 06:19:43</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="G26" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="H26" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="I26" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J26" t="n">
         <v>4.9</v>
       </c>
       <c r="K26" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L26" t="n">
         <v>1.39</v>
@@ -5437,67 +5437,67 @@
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O26" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P26" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S26" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="T26" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="U26" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="V26" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W26" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="X26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Y26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z26" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AA26" t="n">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AB26" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AC26" t="n">
         <v>11</v>
       </c>
       <c r="AD26" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AE26" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AF26" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AG26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH26" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI26" t="n">
         <v>140</v>
@@ -5506,77 +5506,77 @@
         <v>11.5</v>
       </c>
       <c r="AK26" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL26" t="n">
         <v>42</v>
       </c>
       <c r="AM26" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AN26" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AO26" t="n">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="AP26" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>23</v>
       </c>
       <c r="AR26" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AS26" t="n">
         <v>70</v>
       </c>
       <c r="AT26" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AU26" t="n">
         <v>10</v>
       </c>
       <c r="AV26" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AW26" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AX26" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ26" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BA26" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="BB26" t="n">
         <v>10.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE26" t="n">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="BF26" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-19 04:01:01</t>
+          <t>2026-03-19 06:19:43</t>
         </is>
       </c>
     </row>
@@ -5619,49 +5619,49 @@
         <v>3</v>
       </c>
       <c r="J27" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K27" t="n">
         <v>3.65</v>
       </c>
       <c r="L27" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O27" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P27" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="R27" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="T27" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="U27" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V27" t="n">
         <v>1.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X27" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y27" t="n">
         <v>12</v>
@@ -5676,13 +5676,13 @@
         <v>11</v>
       </c>
       <c r="AC27" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD27" t="n">
         <v>13</v>
       </c>
       <c r="AE27" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF27" t="n">
         <v>16.5</v>
@@ -5691,10 +5691,10 @@
         <v>12</v>
       </c>
       <c r="AH27" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ27" t="n">
         <v>38</v>
@@ -5709,16 +5709,16 @@
         <v>90</v>
       </c>
       <c r="AN27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO27" t="n">
         <v>29</v>
       </c>
       <c r="AP27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ27" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR27" t="n">
         <v>18</v>
@@ -5736,16 +5736,16 @@
         <v>12</v>
       </c>
       <c r="AW27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX27" t="n">
         <v>15.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA27" t="n">
         <v>38</v>
@@ -5754,23 +5754,23 @@
         <v>34</v>
       </c>
       <c r="BC27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD27" t="n">
         <v>36</v>
       </c>
       <c r="BE27" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BF27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-19 04:01:01</t>
+          <t>2026-03-19 06:19:43</t>
         </is>
       </c>
     </row>
@@ -5801,16 +5801,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G28" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I28" t="n">
         <v>5.5</v>
-      </c>
-      <c r="I28" t="n">
-        <v>5.6</v>
       </c>
       <c r="J28" t="n">
         <v>3.8</v>
@@ -5819,34 +5819,34 @@
         <v>3.85</v>
       </c>
       <c r="L28" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M28" t="n">
         <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O28" t="n">
         <v>1.4</v>
       </c>
       <c r="P28" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R28" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S28" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T28" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U28" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V28" t="n">
         <v>1.22</v>
@@ -5861,13 +5861,13 @@
         <v>15.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA28" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB28" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC28" t="n">
         <v>8.199999999999999</v>
@@ -5876,7 +5876,7 @@
         <v>22</v>
       </c>
       <c r="AE28" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF28" t="n">
         <v>9.199999999999999</v>
@@ 